--- a/daerung.xlsx
+++ b/daerung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\seat(gpt)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875F289C-1AE9-472B-8B0D-6A755C784B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579941A1-B419-4F07-B679-CB7FF7987372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{587763B1-5925-4572-BEE1-BFB765F321C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="307">
   <si>
     <t>출입문</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,11 +48,6 @@
   </si>
   <si>
     <t>창고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>임원실
-(임세원)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1273,7 +1268,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2474,31 +2469,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2507,56 +2496,473 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
@@ -2567,88 +2973,31 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2657,6 +3006,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2666,440 +3024,77 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3421,13 +3416,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F4268-D3FD-4BA2-863A-5B4D908C2C7C}">
   <dimension ref="A1:BV75"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="30" max="30" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:74" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:74" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:74" ht="16.5" customHeight="1">
       <c r="B2" s="23"/>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -3502,7 +3497,7 @@
       <c r="BU2" s="16"/>
       <c r="BV2" s="24"/>
     </row>
-    <row r="3" spans="2:74" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:74" ht="16.5" customHeight="1">
       <c r="B3" s="25"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
@@ -3577,7 +3572,7 @@
       <c r="BU3" s="19"/>
       <c r="BV3" s="26"/>
     </row>
-    <row r="4" spans="2:74" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:74" ht="16.5" customHeight="1" thickBot="1">
       <c r="B4" s="18"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -3647,14 +3642,14 @@
       <c r="BP4" s="19"/>
       <c r="BQ4" s="19"/>
       <c r="BR4" s="19"/>
-      <c r="BS4" s="72" t="s">
-        <v>296</v>
-      </c>
-      <c r="BT4" s="72"/>
-      <c r="BU4" s="72"/>
-      <c r="BV4" s="73"/>
+      <c r="BS4" s="70" t="s">
+        <v>295</v>
+      </c>
+      <c r="BT4" s="70"/>
+      <c r="BU4" s="70"/>
+      <c r="BV4" s="71"/>
     </row>
-    <row r="5" spans="2:74" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:74" ht="16.5" customHeight="1">
       <c r="B5" s="18"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -3682,15 +3677,15 @@
       <c r="Z5" s="19"/>
       <c r="AA5" s="19"/>
       <c r="AB5" s="19"/>
-      <c r="AC5" s="114" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD5" s="115"/>
-      <c r="AE5" s="115"/>
-      <c r="AF5" s="115"/>
-      <c r="AG5" s="115"/>
-      <c r="AH5" s="115"/>
-      <c r="AI5" s="129"/>
+      <c r="AC5" s="66" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="67"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="68"/>
       <c r="AJ5" s="55"/>
       <c r="AK5" s="55"/>
       <c r="AL5" s="55"/>
@@ -3726,12 +3721,12 @@
       <c r="BP5" s="19"/>
       <c r="BQ5" s="19"/>
       <c r="BR5" s="19"/>
-      <c r="BS5" s="72"/>
-      <c r="BT5" s="72"/>
-      <c r="BU5" s="72"/>
-      <c r="BV5" s="73"/>
+      <c r="BS5" s="70"/>
+      <c r="BT5" s="70"/>
+      <c r="BU5" s="70"/>
+      <c r="BV5" s="71"/>
     </row>
-    <row r="6" spans="2:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -3759,13 +3754,13 @@
       <c r="Z6" s="19"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="26"/>
-      <c r="AC6" s="117"/>
-      <c r="AD6" s="72"/>
-      <c r="AE6" s="72"/>
-      <c r="AF6" s="72"/>
-      <c r="AG6" s="72"/>
-      <c r="AH6" s="72"/>
-      <c r="AI6" s="73"/>
+      <c r="AC6" s="69"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="70"/>
+      <c r="AF6" s="70"/>
+      <c r="AG6" s="70"/>
+      <c r="AH6" s="70"/>
+      <c r="AI6" s="71"/>
       <c r="AJ6" s="55"/>
       <c r="AK6" s="55"/>
       <c r="AL6" s="55"/>
@@ -3801,64 +3796,64 @@
       <c r="BP6" s="28"/>
       <c r="BQ6" s="28"/>
       <c r="BR6" s="28"/>
-      <c r="BS6" s="74"/>
-      <c r="BT6" s="74"/>
-      <c r="BU6" s="74"/>
-      <c r="BV6" s="75"/>
+      <c r="BS6" s="73"/>
+      <c r="BT6" s="73"/>
+      <c r="BU6" s="73"/>
+      <c r="BV6" s="74"/>
     </row>
-    <row r="7" spans="2:74" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:74" ht="16.5" customHeight="1">
       <c r="B7" s="18"/>
       <c r="C7" s="42"/>
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
-      <c r="F7" s="100" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="94"/>
+      <c r="F7" s="139" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="100"/>
       <c r="H7" s="28"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
       <c r="K7" s="28"/>
       <c r="L7" s="28"/>
-      <c r="M7" s="211" t="s">
+      <c r="M7" s="183" t="s">
+        <v>117</v>
+      </c>
+      <c r="N7" s="180" t="s">
         <v>118</v>
       </c>
-      <c r="N7" s="138" t="s">
+      <c r="O7" s="28"/>
+      <c r="P7" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="O7" s="28"/>
-      <c r="P7" s="141" t="s">
+      <c r="Q7" s="104" t="s">
         <v>120</v>
-      </c>
-      <c r="Q7" s="141" t="s">
-        <v>121</v>
       </c>
       <c r="R7" s="28"/>
       <c r="S7" s="43"/>
-      <c r="T7" s="153" t="s">
+      <c r="T7" s="187" t="s">
+        <v>121</v>
+      </c>
+      <c r="U7" s="190" t="s">
         <v>122</v>
       </c>
-      <c r="U7" s="156" t="s">
+      <c r="V7" s="29"/>
+      <c r="W7" s="178" t="s">
         <v>123</v>
       </c>
-      <c r="V7" s="29"/>
-      <c r="W7" s="144" t="s">
+      <c r="X7" s="178" t="s">
         <v>124</v>
-      </c>
-      <c r="X7" s="144" t="s">
-        <v>125</v>
       </c>
       <c r="Y7" s="29"/>
       <c r="Z7" s="29"/>
       <c r="AA7" s="29"/>
       <c r="AB7" s="30"/>
-      <c r="AC7" s="117"/>
-      <c r="AD7" s="72"/>
-      <c r="AE7" s="72"/>
-      <c r="AF7" s="72"/>
-      <c r="AG7" s="72"/>
-      <c r="AH7" s="72"/>
-      <c r="AI7" s="73"/>
+      <c r="AC7" s="69"/>
+      <c r="AD7" s="70"/>
+      <c r="AE7" s="70"/>
+      <c r="AF7" s="70"/>
+      <c r="AG7" s="70"/>
+      <c r="AH7" s="70"/>
+      <c r="AI7" s="71"/>
       <c r="AJ7" s="55"/>
       <c r="AK7" s="55"/>
       <c r="AL7" s="55"/>
@@ -3882,11 +3877,11 @@
       <c r="BD7" s="28"/>
       <c r="BE7" s="28"/>
       <c r="BF7" s="28"/>
-      <c r="BG7" s="106" t="s">
-        <v>189</v>
-      </c>
-      <c r="BH7" s="132" t="s">
-        <v>196</v>
+      <c r="BG7" s="142" t="s">
+        <v>188</v>
+      </c>
+      <c r="BH7" s="145" t="s">
+        <v>195</v>
       </c>
       <c r="BI7" s="28"/>
       <c r="BJ7" s="38"/>
@@ -3903,43 +3898,43 @@
       <c r="BU7" s="48"/>
       <c r="BV7" s="24"/>
     </row>
-    <row r="8" spans="2:74" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:74" ht="17.45" customHeight="1">
       <c r="B8" s="18"/>
       <c r="C8" s="41"/>
       <c r="D8" s="28"/>
       <c r="E8" s="28"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="95"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="101"/>
       <c r="H8" s="28"/>
-      <c r="I8" s="203" t="s">
-        <v>126</v>
-      </c>
-      <c r="J8" s="203"/>
+      <c r="I8" s="197" t="s">
+        <v>125</v>
+      </c>
+      <c r="J8" s="197"/>
       <c r="K8" s="42"/>
       <c r="L8" s="28"/>
-      <c r="M8" s="212"/>
-      <c r="N8" s="139"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="181"/>
       <c r="O8" s="28"/>
-      <c r="P8" s="142"/>
-      <c r="Q8" s="142"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="105"/>
       <c r="R8" s="28"/>
       <c r="S8" s="42"/>
-      <c r="T8" s="154"/>
-      <c r="U8" s="157"/>
+      <c r="T8" s="188"/>
+      <c r="U8" s="191"/>
       <c r="V8" s="29"/>
-      <c r="W8" s="145"/>
-      <c r="X8" s="145"/>
+      <c r="W8" s="179"/>
+      <c r="X8" s="179"/>
       <c r="Y8" s="42"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="30"/>
-      <c r="AC8" s="117"/>
-      <c r="AD8" s="72"/>
-      <c r="AE8" s="72"/>
-      <c r="AF8" s="72"/>
-      <c r="AG8" s="72"/>
-      <c r="AH8" s="72"/>
-      <c r="AI8" s="73"/>
+      <c r="AC8" s="69"/>
+      <c r="AD8" s="70"/>
+      <c r="AE8" s="70"/>
+      <c r="AF8" s="70"/>
+      <c r="AG8" s="70"/>
+      <c r="AH8" s="70"/>
+      <c r="AI8" s="71"/>
       <c r="AJ8" s="55"/>
       <c r="AK8" s="55"/>
       <c r="AL8" s="55"/>
@@ -3963,8 +3958,8 @@
       <c r="BD8" s="28"/>
       <c r="BE8" s="42"/>
       <c r="BF8" s="28"/>
-      <c r="BG8" s="107"/>
-      <c r="BH8" s="133"/>
+      <c r="BG8" s="143"/>
+      <c r="BH8" s="146"/>
       <c r="BI8" s="28"/>
       <c r="BJ8" s="38"/>
       <c r="BK8" s="38"/>
@@ -3980,45 +3975,45 @@
       <c r="BU8" s="19"/>
       <c r="BV8" s="26"/>
     </row>
-    <row r="9" spans="2:74" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:74" ht="19.5" customHeight="1">
       <c r="B9" s="27"/>
-      <c r="C9" s="100" t="s">
-        <v>127</v>
+      <c r="C9" s="139" t="s">
+        <v>126</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="28"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="96"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="102"/>
       <c r="H9" s="28"/>
-      <c r="I9" s="203"/>
-      <c r="J9" s="203"/>
+      <c r="I9" s="197"/>
+      <c r="J9" s="197"/>
       <c r="K9" s="28"/>
       <c r="L9" s="28"/>
-      <c r="M9" s="213"/>
-      <c r="N9" s="140"/>
+      <c r="M9" s="185"/>
+      <c r="N9" s="182"/>
       <c r="O9" s="28"/>
-      <c r="P9" s="143"/>
-      <c r="Q9" s="143"/>
+      <c r="P9" s="106"/>
+      <c r="Q9" s="106"/>
       <c r="R9" s="28"/>
       <c r="S9" s="28"/>
-      <c r="T9" s="155"/>
-      <c r="U9" s="158"/>
+      <c r="T9" s="189"/>
+      <c r="U9" s="192"/>
       <c r="V9" s="29"/>
-      <c r="W9" s="145"/>
-      <c r="X9" s="145"/>
+      <c r="W9" s="179"/>
+      <c r="X9" s="179"/>
       <c r="Y9" s="29"/>
-      <c r="Z9" s="135" t="s">
-        <v>288</v>
-      </c>
-      <c r="AA9" s="135"/>
-      <c r="AB9" s="136"/>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="72"/>
-      <c r="AF9" s="72"/>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="73"/>
+      <c r="Z9" s="238" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA9" s="238"/>
+      <c r="AB9" s="239"/>
+      <c r="AC9" s="69"/>
+      <c r="AD9" s="70"/>
+      <c r="AE9" s="70"/>
+      <c r="AF9" s="70"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="71"/>
       <c r="AJ9" s="55"/>
       <c r="AK9" s="55"/>
       <c r="AL9" s="55"/>
@@ -4037,20 +4032,20 @@
       <c r="AY9" s="55"/>
       <c r="AZ9" s="56"/>
       <c r="BA9" s="36"/>
-      <c r="BB9" s="219" t="s">
-        <v>190</v>
-      </c>
-      <c r="BC9" s="220"/>
+      <c r="BB9" s="163" t="s">
+        <v>189</v>
+      </c>
+      <c r="BC9" s="164"/>
       <c r="BD9" s="28"/>
       <c r="BE9" s="28"/>
       <c r="BF9" s="28"/>
-      <c r="BG9" s="108"/>
-      <c r="BH9" s="134"/>
+      <c r="BG9" s="144"/>
+      <c r="BH9" s="147"/>
       <c r="BI9" s="28"/>
-      <c r="BJ9" s="219" t="s">
-        <v>191</v>
-      </c>
-      <c r="BK9" s="220"/>
+      <c r="BJ9" s="163" t="s">
+        <v>190</v>
+      </c>
+      <c r="BK9" s="164"/>
       <c r="BL9" s="28"/>
       <c r="BM9" s="28"/>
       <c r="BN9" s="28"/>
@@ -4059,73 +4054,73 @@
       <c r="BQ9" s="28"/>
       <c r="BR9" s="28"/>
       <c r="BS9" s="36"/>
-      <c r="BT9" s="217" t="s">
-        <v>221</v>
-      </c>
-      <c r="BU9" s="218"/>
+      <c r="BT9" s="161" t="s">
+        <v>220</v>
+      </c>
+      <c r="BU9" s="162"/>
       <c r="BV9" s="26"/>
     </row>
-    <row r="10" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:74" ht="15" customHeight="1">
       <c r="B10" s="27"/>
-      <c r="C10" s="101"/>
+      <c r="C10" s="140"/>
       <c r="D10" s="28"/>
       <c r="E10" s="28"/>
-      <c r="F10" s="100" t="s">
+      <c r="F10" s="139" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="142" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="106" t="s">
+      <c r="H10" s="28"/>
+      <c r="I10" s="196" t="s">
         <v>129</v>
       </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="195" t="s">
+      <c r="J10" s="196" t="s">
         <v>130</v>
-      </c>
-      <c r="J10" s="195" t="s">
-        <v>131</v>
       </c>
       <c r="K10" s="28"/>
       <c r="L10" s="28"/>
-      <c r="M10" s="138" t="s">
+      <c r="M10" s="180" t="s">
+        <v>131</v>
+      </c>
+      <c r="N10" s="180" t="s">
         <v>132</v>
       </c>
-      <c r="N10" s="138" t="s">
+      <c r="O10" s="28"/>
+      <c r="P10" s="104" t="s">
         <v>133</v>
       </c>
-      <c r="O10" s="28"/>
-      <c r="P10" s="141" t="s">
+      <c r="Q10" s="104" t="s">
         <v>134</v>
-      </c>
-      <c r="Q10" s="141" t="s">
-        <v>135</v>
       </c>
       <c r="R10" s="28"/>
       <c r="S10" s="28"/>
-      <c r="T10" s="153" t="s">
+      <c r="T10" s="187" t="s">
+        <v>135</v>
+      </c>
+      <c r="U10" s="190" t="s">
         <v>136</v>
       </c>
-      <c r="U10" s="156" t="s">
+      <c r="V10" s="29"/>
+      <c r="W10" s="178" t="s">
         <v>137</v>
       </c>
-      <c r="V10" s="29"/>
-      <c r="W10" s="144" t="s">
+      <c r="X10" s="178" t="s">
         <v>138</v>
-      </c>
-      <c r="X10" s="144" t="s">
-        <v>139</v>
       </c>
       <c r="Y10" s="29"/>
       <c r="Z10" s="29"/>
-      <c r="AA10" s="259" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB10" s="260"/>
-      <c r="AC10" s="117"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="73"/>
+      <c r="AA10" s="84" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="69"/>
+      <c r="AD10" s="70"/>
+      <c r="AE10" s="70"/>
+      <c r="AF10" s="70"/>
+      <c r="AG10" s="70"/>
+      <c r="AH10" s="70"/>
+      <c r="AI10" s="71"/>
       <c r="AJ10" s="55"/>
       <c r="AK10" s="55"/>
       <c r="AL10" s="55"/>
@@ -4144,81 +4139,81 @@
       <c r="AY10" s="55"/>
       <c r="AZ10" s="56"/>
       <c r="BA10" s="36"/>
-      <c r="BB10" s="101" t="s">
-        <v>192</v>
-      </c>
-      <c r="BC10" s="101" t="s">
-        <v>200</v>
+      <c r="BB10" s="140" t="s">
+        <v>191</v>
+      </c>
+      <c r="BC10" s="140" t="s">
+        <v>199</v>
       </c>
       <c r="BD10" s="28"/>
       <c r="BE10" s="28"/>
       <c r="BF10" s="28"/>
-      <c r="BG10" s="106" t="s">
-        <v>194</v>
-      </c>
-      <c r="BH10" s="132" t="s">
-        <v>202</v>
+      <c r="BG10" s="142" t="s">
+        <v>193</v>
+      </c>
+      <c r="BH10" s="145" t="s">
+        <v>201</v>
       </c>
       <c r="BI10" s="28"/>
-      <c r="BJ10" s="132" t="s">
-        <v>293</v>
-      </c>
-      <c r="BK10" s="104"/>
+      <c r="BJ10" s="145" t="s">
+        <v>292</v>
+      </c>
+      <c r="BK10" s="125"/>
       <c r="BL10" s="28"/>
       <c r="BM10" s="28"/>
       <c r="BN10" s="28"/>
-      <c r="BO10" s="171" t="s">
+      <c r="BO10" s="149" t="s">
+        <v>196</v>
+      </c>
+      <c r="BP10" s="149" t="s">
         <v>197</v>
-      </c>
-      <c r="BP10" s="171" t="s">
-        <v>198</v>
       </c>
       <c r="BQ10" s="28"/>
       <c r="BR10" s="28"/>
       <c r="BS10" s="36"/>
-      <c r="BT10" s="95" t="s">
-        <v>222</v>
-      </c>
-      <c r="BU10" s="95" t="s">
-        <v>305</v>
+      <c r="BT10" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="BU10" s="101" t="s">
+        <v>304</v>
       </c>
       <c r="BV10" s="26"/>
     </row>
-    <row r="11" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:74" ht="15" customHeight="1">
       <c r="B11" s="27"/>
-      <c r="C11" s="102"/>
+      <c r="C11" s="141"/>
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="107"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="143"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="195"/>
-      <c r="J11" s="195"/>
+      <c r="I11" s="196"/>
+      <c r="J11" s="196"/>
       <c r="K11" s="28"/>
       <c r="L11" s="28"/>
-      <c r="M11" s="139"/>
-      <c r="N11" s="139"/>
+      <c r="M11" s="181"/>
+      <c r="N11" s="181"/>
       <c r="O11" s="28"/>
-      <c r="P11" s="142"/>
-      <c r="Q11" s="142"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="105"/>
       <c r="R11" s="28"/>
       <c r="S11" s="28"/>
-      <c r="T11" s="154"/>
-      <c r="U11" s="157"/>
+      <c r="T11" s="188"/>
+      <c r="U11" s="191"/>
       <c r="V11" s="29"/>
-      <c r="W11" s="145"/>
-      <c r="X11" s="145"/>
+      <c r="W11" s="179"/>
+      <c r="X11" s="179"/>
       <c r="Y11" s="29"/>
       <c r="Z11" s="29"/>
-      <c r="AA11" s="261"/>
-      <c r="AB11" s="262"/>
-      <c r="AC11" s="117"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="72"/>
-      <c r="AF11" s="72"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="73"/>
+      <c r="AA11" s="86"/>
+      <c r="AB11" s="87"/>
+      <c r="AC11" s="69"/>
+      <c r="AD11" s="70"/>
+      <c r="AE11" s="70"/>
+      <c r="AF11" s="70"/>
+      <c r="AG11" s="70"/>
+      <c r="AH11" s="70"/>
+      <c r="AI11" s="71"/>
       <c r="AJ11" s="55"/>
       <c r="AK11" s="55"/>
       <c r="AL11" s="55"/>
@@ -4237,67 +4232,67 @@
       <c r="AY11" s="55"/>
       <c r="AZ11" s="56"/>
       <c r="BA11" s="36"/>
-      <c r="BB11" s="101"/>
-      <c r="BC11" s="101"/>
+      <c r="BB11" s="140"/>
+      <c r="BC11" s="140"/>
       <c r="BD11" s="28"/>
       <c r="BE11" s="39"/>
       <c r="BF11" s="39"/>
-      <c r="BG11" s="107"/>
-      <c r="BH11" s="133"/>
+      <c r="BG11" s="143"/>
+      <c r="BH11" s="146"/>
       <c r="BI11" s="28"/>
-      <c r="BJ11" s="133"/>
-      <c r="BK11" s="104"/>
+      <c r="BJ11" s="146"/>
+      <c r="BK11" s="125"/>
       <c r="BL11" s="39"/>
       <c r="BM11" s="28"/>
       <c r="BN11" s="28"/>
-      <c r="BO11" s="171"/>
-      <c r="BP11" s="171"/>
+      <c r="BO11" s="149"/>
+      <c r="BP11" s="149"/>
       <c r="BQ11" s="28"/>
       <c r="BR11" s="28"/>
       <c r="BS11" s="36"/>
-      <c r="BT11" s="95"/>
-      <c r="BU11" s="95"/>
+      <c r="BT11" s="101"/>
+      <c r="BU11" s="101"/>
       <c r="BV11" s="40"/>
     </row>
-    <row r="12" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:74" ht="15" customHeight="1">
       <c r="B12" s="27"/>
-      <c r="C12" s="100" t="s">
-        <v>141</v>
+      <c r="C12" s="139" t="s">
+        <v>140</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="108"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="144"/>
       <c r="H12" s="28"/>
-      <c r="I12" s="195"/>
-      <c r="J12" s="195"/>
+      <c r="I12" s="196"/>
+      <c r="J12" s="196"/>
       <c r="K12" s="28"/>
       <c r="L12" s="28"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="140"/>
+      <c r="M12" s="182"/>
+      <c r="N12" s="182"/>
       <c r="O12" s="28"/>
-      <c r="P12" s="143"/>
-      <c r="Q12" s="143"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
       <c r="R12" s="28"/>
       <c r="S12" s="28"/>
-      <c r="T12" s="155"/>
-      <c r="U12" s="158"/>
+      <c r="T12" s="189"/>
+      <c r="U12" s="192"/>
       <c r="V12" s="29"/>
-      <c r="W12" s="146"/>
-      <c r="X12" s="146"/>
+      <c r="W12" s="186"/>
+      <c r="X12" s="186"/>
       <c r="Y12" s="29"/>
       <c r="Z12" s="29"/>
       <c r="AA12" s="29"/>
-      <c r="AB12" s="263" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC12" s="117"/>
-      <c r="AD12" s="72"/>
-      <c r="AE12" s="72"/>
-      <c r="AF12" s="72"/>
-      <c r="AG12" s="72"/>
-      <c r="AH12" s="72"/>
-      <c r="AI12" s="73"/>
+      <c r="AB12" s="88" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC12" s="69"/>
+      <c r="AD12" s="70"/>
+      <c r="AE12" s="70"/>
+      <c r="AF12" s="70"/>
+      <c r="AG12" s="70"/>
+      <c r="AH12" s="70"/>
+      <c r="AI12" s="71"/>
       <c r="AJ12" s="55"/>
       <c r="AK12" s="55"/>
       <c r="AL12" s="55"/>
@@ -4316,83 +4311,83 @@
       <c r="AY12" s="55"/>
       <c r="AZ12" s="56"/>
       <c r="BA12" s="36"/>
-      <c r="BB12" s="102"/>
-      <c r="BC12" s="102"/>
+      <c r="BB12" s="141"/>
+      <c r="BC12" s="141"/>
       <c r="BD12" s="28"/>
       <c r="BE12" s="28"/>
       <c r="BF12" s="28"/>
-      <c r="BG12" s="108"/>
-      <c r="BH12" s="134"/>
+      <c r="BG12" s="144"/>
+      <c r="BH12" s="147"/>
       <c r="BI12" s="28"/>
-      <c r="BJ12" s="134"/>
-      <c r="BK12" s="105"/>
+      <c r="BJ12" s="147"/>
+      <c r="BK12" s="126"/>
       <c r="BL12" s="28"/>
       <c r="BM12" s="28"/>
       <c r="BN12" s="28"/>
-      <c r="BO12" s="172"/>
-      <c r="BP12" s="172"/>
+      <c r="BO12" s="150"/>
+      <c r="BP12" s="150"/>
       <c r="BQ12" s="28"/>
       <c r="BR12" s="28"/>
       <c r="BS12" s="36"/>
-      <c r="BT12" s="96"/>
-      <c r="BU12" s="96"/>
+      <c r="BT12" s="102"/>
+      <c r="BU12" s="102"/>
       <c r="BV12" s="40"/>
     </row>
-    <row r="13" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:74" ht="15" customHeight="1">
       <c r="B13" s="27"/>
-      <c r="C13" s="101"/>
+      <c r="C13" s="140"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
-      <c r="F13" s="100" t="s">
+      <c r="F13" s="139" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="106" t="s">
+      <c r="H13" s="28"/>
+      <c r="I13" s="196" t="s">
         <v>144</v>
       </c>
-      <c r="H13" s="28"/>
-      <c r="I13" s="195" t="s">
+      <c r="J13" s="196" t="s">
         <v>145</v>
-      </c>
-      <c r="J13" s="195" t="s">
-        <v>146</v>
       </c>
       <c r="K13" s="28"/>
       <c r="L13" s="28"/>
-      <c r="M13" s="138" t="s">
+      <c r="M13" s="180" t="s">
+        <v>146</v>
+      </c>
+      <c r="N13" s="180" t="s">
         <v>147</v>
       </c>
-      <c r="N13" s="138" t="s">
+      <c r="O13" s="28"/>
+      <c r="P13" s="104" t="s">
         <v>148</v>
       </c>
-      <c r="O13" s="28"/>
-      <c r="P13" s="141" t="s">
+      <c r="Q13" s="104" t="s">
         <v>149</v>
-      </c>
-      <c r="Q13" s="141" t="s">
-        <v>150</v>
       </c>
       <c r="R13" s="28"/>
       <c r="S13" s="28"/>
-      <c r="T13" s="153" t="s">
+      <c r="T13" s="187" t="s">
+        <v>150</v>
+      </c>
+      <c r="U13" s="165"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="178" t="s">
         <v>151</v>
       </c>
-      <c r="U13" s="150"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="144" t="s">
-        <v>152</v>
-      </c>
-      <c r="X13" s="94"/>
+      <c r="X13" s="100"/>
       <c r="Y13" s="29"/>
       <c r="Z13" s="29"/>
       <c r="AA13" s="29"/>
-      <c r="AB13" s="264"/>
-      <c r="AC13" s="117"/>
-      <c r="AD13" s="72"/>
-      <c r="AE13" s="72"/>
-      <c r="AF13" s="72"/>
-      <c r="AG13" s="72"/>
-      <c r="AH13" s="72"/>
-      <c r="AI13" s="73"/>
+      <c r="AB13" s="89"/>
+      <c r="AC13" s="69"/>
+      <c r="AD13" s="70"/>
+      <c r="AE13" s="70"/>
+      <c r="AF13" s="70"/>
+      <c r="AG13" s="70"/>
+      <c r="AH13" s="70"/>
+      <c r="AI13" s="71"/>
       <c r="AJ13" s="55"/>
       <c r="AK13" s="55"/>
       <c r="AL13" s="55"/>
@@ -4411,81 +4406,81 @@
       <c r="AY13" s="55"/>
       <c r="AZ13" s="56"/>
       <c r="BA13" s="36"/>
-      <c r="BB13" s="100" t="s">
-        <v>199</v>
-      </c>
-      <c r="BC13" s="100" t="s">
-        <v>193</v>
+      <c r="BB13" s="139" t="s">
+        <v>198</v>
+      </c>
+      <c r="BC13" s="139" t="s">
+        <v>192</v>
       </c>
       <c r="BD13" s="28"/>
       <c r="BE13" s="28"/>
       <c r="BF13" s="28"/>
-      <c r="BG13" s="106" t="s">
-        <v>201</v>
-      </c>
-      <c r="BH13" s="132" t="s">
-        <v>207</v>
+      <c r="BG13" s="142" t="s">
+        <v>200</v>
+      </c>
+      <c r="BH13" s="145" t="s">
+        <v>206</v>
       </c>
       <c r="BI13" s="28"/>
-      <c r="BJ13" s="132" t="s">
-        <v>294</v>
-      </c>
-      <c r="BK13" s="103"/>
+      <c r="BJ13" s="145" t="s">
+        <v>293</v>
+      </c>
+      <c r="BK13" s="124"/>
       <c r="BL13" s="28"/>
       <c r="BM13" s="28"/>
       <c r="BN13" s="28"/>
-      <c r="BO13" s="170" t="s">
+      <c r="BO13" s="148" t="s">
+        <v>202</v>
+      </c>
+      <c r="BP13" s="148" t="s">
         <v>203</v>
-      </c>
-      <c r="BP13" s="170" t="s">
-        <v>204</v>
       </c>
       <c r="BQ13" s="28"/>
       <c r="BR13" s="28"/>
       <c r="BS13" s="36"/>
-      <c r="BT13" s="94" t="s">
-        <v>224</v>
-      </c>
-      <c r="BU13" s="94" t="s">
+      <c r="BT13" s="100" t="s">
         <v>223</v>
+      </c>
+      <c r="BU13" s="100" t="s">
+        <v>222</v>
       </c>
       <c r="BV13" s="40"/>
     </row>
-    <row r="14" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:74" ht="15" customHeight="1">
       <c r="B14" s="27"/>
-      <c r="C14" s="102"/>
+      <c r="C14" s="141"/>
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="107"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="143"/>
       <c r="H14" s="28"/>
-      <c r="I14" s="195"/>
-      <c r="J14" s="195"/>
+      <c r="I14" s="196"/>
+      <c r="J14" s="196"/>
       <c r="K14" s="28"/>
       <c r="L14" s="28"/>
-      <c r="M14" s="139"/>
-      <c r="N14" s="139"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="181"/>
       <c r="O14" s="28"/>
-      <c r="P14" s="142"/>
-      <c r="Q14" s="142"/>
+      <c r="P14" s="105"/>
+      <c r="Q14" s="105"/>
       <c r="R14" s="28"/>
       <c r="S14" s="28"/>
-      <c r="T14" s="154"/>
-      <c r="U14" s="151"/>
+      <c r="T14" s="188"/>
+      <c r="U14" s="166"/>
       <c r="V14" s="29"/>
-      <c r="W14" s="145"/>
-      <c r="X14" s="95"/>
+      <c r="W14" s="179"/>
+      <c r="X14" s="101"/>
       <c r="Y14" s="29"/>
       <c r="Z14" s="29"/>
       <c r="AA14" s="29"/>
-      <c r="AB14" s="265"/>
-      <c r="AC14" s="117"/>
-      <c r="AD14" s="72"/>
-      <c r="AE14" s="72"/>
-      <c r="AF14" s="72"/>
-      <c r="AG14" s="72"/>
-      <c r="AH14" s="72"/>
-      <c r="AI14" s="73"/>
+      <c r="AB14" s="90"/>
+      <c r="AC14" s="69"/>
+      <c r="AD14" s="70"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="70"/>
+      <c r="AG14" s="70"/>
+      <c r="AH14" s="70"/>
+      <c r="AI14" s="71"/>
       <c r="AJ14" s="55"/>
       <c r="AK14" s="55"/>
       <c r="AL14" s="55"/>
@@ -4504,67 +4499,67 @@
       <c r="AY14" s="55"/>
       <c r="AZ14" s="56"/>
       <c r="BA14" s="36"/>
-      <c r="BB14" s="101"/>
-      <c r="BC14" s="101"/>
+      <c r="BB14" s="140"/>
+      <c r="BC14" s="140"/>
       <c r="BD14" s="28"/>
       <c r="BE14" s="39"/>
       <c r="BF14" s="39"/>
-      <c r="BG14" s="107"/>
-      <c r="BH14" s="133"/>
+      <c r="BG14" s="143"/>
+      <c r="BH14" s="146"/>
       <c r="BI14" s="28"/>
-      <c r="BJ14" s="133"/>
-      <c r="BK14" s="104"/>
+      <c r="BJ14" s="146"/>
+      <c r="BK14" s="125"/>
       <c r="BL14" s="39"/>
       <c r="BM14" s="28"/>
       <c r="BN14" s="28"/>
-      <c r="BO14" s="171"/>
-      <c r="BP14" s="171"/>
+      <c r="BO14" s="149"/>
+      <c r="BP14" s="149"/>
       <c r="BQ14" s="28"/>
       <c r="BR14" s="28"/>
       <c r="BS14" s="36"/>
-      <c r="BT14" s="95"/>
-      <c r="BU14" s="95"/>
+      <c r="BT14" s="101"/>
+      <c r="BU14" s="101"/>
       <c r="BV14" s="40"/>
     </row>
-    <row r="15" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:74" ht="15" customHeight="1">
       <c r="B15" s="27"/>
-      <c r="C15" s="100" t="s">
-        <v>153</v>
+      <c r="C15" s="139" t="s">
+        <v>152</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="108"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="144"/>
       <c r="H15" s="28"/>
-      <c r="I15" s="195"/>
-      <c r="J15" s="195"/>
+      <c r="I15" s="196"/>
+      <c r="J15" s="196"/>
       <c r="K15" s="28"/>
       <c r="L15" s="28"/>
-      <c r="M15" s="140"/>
-      <c r="N15" s="140"/>
+      <c r="M15" s="182"/>
+      <c r="N15" s="182"/>
       <c r="O15" s="28"/>
-      <c r="P15" s="143"/>
-      <c r="Q15" s="143"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="106"/>
       <c r="R15" s="28"/>
       <c r="S15" s="28"/>
-      <c r="T15" s="155"/>
-      <c r="U15" s="152"/>
+      <c r="T15" s="189"/>
+      <c r="U15" s="167"/>
       <c r="V15" s="29"/>
-      <c r="W15" s="146"/>
-      <c r="X15" s="96"/>
+      <c r="W15" s="186"/>
+      <c r="X15" s="102"/>
       <c r="Y15" s="29"/>
       <c r="Z15" s="29"/>
       <c r="AA15" s="29"/>
-      <c r="AB15" s="263" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC15" s="117"/>
-      <c r="AD15" s="72"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="72"/>
-      <c r="AG15" s="72"/>
-      <c r="AH15" s="72"/>
-      <c r="AI15" s="73"/>
+      <c r="AB15" s="88" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="70"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+      <c r="AI15" s="71"/>
       <c r="AJ15" s="55"/>
       <c r="AK15" s="55"/>
       <c r="AL15" s="55"/>
@@ -4583,73 +4578,73 @@
       <c r="AY15" s="55"/>
       <c r="AZ15" s="56"/>
       <c r="BA15" s="36"/>
-      <c r="BB15" s="102"/>
-      <c r="BC15" s="102"/>
+      <c r="BB15" s="141"/>
+      <c r="BC15" s="141"/>
       <c r="BD15" s="28"/>
       <c r="BE15" s="28"/>
       <c r="BF15" s="28"/>
-      <c r="BG15" s="108"/>
-      <c r="BH15" s="134"/>
+      <c r="BG15" s="144"/>
+      <c r="BH15" s="147"/>
       <c r="BI15" s="28"/>
-      <c r="BJ15" s="134"/>
-      <c r="BK15" s="105"/>
+      <c r="BJ15" s="147"/>
+      <c r="BK15" s="126"/>
       <c r="BL15" s="28"/>
       <c r="BM15" s="28"/>
       <c r="BN15" s="28"/>
-      <c r="BO15" s="172"/>
-      <c r="BP15" s="172"/>
+      <c r="BO15" s="150"/>
+      <c r="BP15" s="150"/>
       <c r="BQ15" s="28"/>
       <c r="BR15" s="28"/>
       <c r="BS15" s="36"/>
-      <c r="BT15" s="96"/>
-      <c r="BU15" s="96"/>
+      <c r="BT15" s="102"/>
+      <c r="BU15" s="102"/>
       <c r="BV15" s="40"/>
     </row>
-    <row r="16" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:74" ht="15" customHeight="1">
       <c r="B16" s="27"/>
-      <c r="C16" s="101"/>
+      <c r="C16" s="140"/>
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="F16" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G16" s="28"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="173" t="s">
-        <v>280</v>
-      </c>
-      <c r="J16" s="173"/>
+      <c r="I16" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="J16" s="65"/>
       <c r="K16" s="28"/>
       <c r="L16" s="28"/>
-      <c r="M16" s="173" t="s">
+      <c r="M16" s="65" t="s">
+        <v>283</v>
+      </c>
+      <c r="N16" s="65"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="111" t="s">
         <v>284</v>
       </c>
-      <c r="N16" s="173"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="159" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q16" s="159"/>
-      <c r="R16" s="159"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
       <c r="U16" s="29"/>
       <c r="V16" s="29"/>
-      <c r="W16" s="204" t="s">
-        <v>287</v>
-      </c>
-      <c r="X16" s="204"/>
+      <c r="W16" s="177" t="s">
+        <v>286</v>
+      </c>
+      <c r="X16" s="177"/>
       <c r="Y16" s="29"/>
       <c r="Z16" s="29"/>
       <c r="AA16" s="29"/>
-      <c r="AB16" s="264"/>
-      <c r="AC16" s="117"/>
-      <c r="AD16" s="72"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="72"/>
-      <c r="AG16" s="72"/>
-      <c r="AH16" s="72"/>
-      <c r="AI16" s="73"/>
+      <c r="AB16" s="89"/>
+      <c r="AC16" s="69"/>
+      <c r="AD16" s="70"/>
+      <c r="AE16" s="70"/>
+      <c r="AF16" s="70"/>
+      <c r="AG16" s="70"/>
+      <c r="AH16" s="70"/>
+      <c r="AI16" s="71"/>
       <c r="AJ16" s="55"/>
       <c r="AK16" s="55"/>
       <c r="AL16" s="55"/>
@@ -4668,29 +4663,29 @@
       <c r="AY16" s="55"/>
       <c r="AZ16" s="56"/>
       <c r="BA16" s="36"/>
-      <c r="BB16" s="173" t="s">
-        <v>289</v>
-      </c>
-      <c r="BC16" s="173"/>
+      <c r="BB16" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="BC16" s="65"/>
       <c r="BD16" s="28"/>
       <c r="BE16" s="28"/>
       <c r="BF16" s="28"/>
-      <c r="BG16" s="173" t="s">
-        <v>290</v>
+      <c r="BG16" s="65" t="s">
+        <v>289</v>
       </c>
       <c r="BH16" s="28"/>
       <c r="BI16" s="28"/>
-      <c r="BJ16" s="173" t="s">
-        <v>291</v>
-      </c>
-      <c r="BK16" s="173"/>
+      <c r="BJ16" s="65" t="s">
+        <v>290</v>
+      </c>
+      <c r="BK16" s="65"/>
       <c r="BL16" s="28"/>
       <c r="BM16" s="28"/>
       <c r="BN16" s="28"/>
-      <c r="BO16" s="173" t="s">
-        <v>292</v>
-      </c>
-      <c r="BP16" s="173"/>
+      <c r="BO16" s="65" t="s">
+        <v>291</v>
+      </c>
+      <c r="BP16" s="65"/>
       <c r="BQ16" s="28"/>
       <c r="BR16" s="28"/>
       <c r="BS16" s="36"/>
@@ -4698,17 +4693,17 @@
       <c r="BU16" s="28"/>
       <c r="BV16" s="40"/>
     </row>
-    <row r="17" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:74" ht="15" customHeight="1">
       <c r="B17" s="27"/>
-      <c r="C17" s="102"/>
+      <c r="C17" s="141"/>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
       <c r="F17" s="62"/>
-      <c r="G17" s="72" t="s">
-        <v>279</v>
-      </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
+      <c r="G17" s="70" t="s">
+        <v>278</v>
+      </c>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
       <c r="J17" s="28"/>
       <c r="K17" s="28"/>
       <c r="L17" s="28"/>
@@ -4727,14 +4722,14 @@
       <c r="Y17" s="29"/>
       <c r="Z17" s="29"/>
       <c r="AA17" s="29"/>
-      <c r="AB17" s="265"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="73"/>
+      <c r="AB17" s="90"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="70"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="70"/>
+      <c r="AI17" s="71"/>
       <c r="AJ17" s="55"/>
       <c r="AK17" s="55"/>
       <c r="AL17" s="55"/>
@@ -4753,16 +4748,16 @@
       <c r="AY17" s="55"/>
       <c r="AZ17" s="56"/>
       <c r="BA17" s="36"/>
-      <c r="BB17" s="121"/>
-      <c r="BC17" s="121"/>
+      <c r="BB17" s="63"/>
+      <c r="BC17" s="63"/>
       <c r="BD17" s="28"/>
       <c r="BE17" s="28"/>
       <c r="BF17" s="28"/>
-      <c r="BG17" s="121"/>
+      <c r="BG17" s="63"/>
       <c r="BH17" s="28"/>
       <c r="BI17" s="28"/>
-      <c r="BJ17" s="121"/>
-      <c r="BK17" s="121"/>
+      <c r="BJ17" s="63"/>
+      <c r="BK17" s="63"/>
       <c r="BL17" s="28"/>
       <c r="BM17" s="28"/>
       <c r="BN17" s="28"/>
@@ -4775,59 +4770,59 @@
       <c r="BU17" s="28"/>
       <c r="BV17" s="40"/>
     </row>
-    <row r="18" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:74" ht="15" customHeight="1">
       <c r="B18" s="27"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
-      <c r="F18" s="100" t="s">
+      <c r="F18" s="139" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="193" t="s">
         <v>155</v>
       </c>
-      <c r="G18" s="97" t="s">
+      <c r="H18" s="28"/>
+      <c r="I18" s="193" t="s">
         <v>156</v>
       </c>
-      <c r="H18" s="28"/>
-      <c r="I18" s="97" t="s">
-        <v>157</v>
-      </c>
-      <c r="J18" s="94"/>
+      <c r="J18" s="100"/>
       <c r="K18" s="28"/>
       <c r="L18" s="28"/>
-      <c r="M18" s="138" t="s">
-        <v>278</v>
-      </c>
-      <c r="N18" s="94"/>
+      <c r="M18" s="180" t="s">
+        <v>277</v>
+      </c>
+      <c r="N18" s="100"/>
       <c r="O18" s="28"/>
-      <c r="P18" s="150"/>
-      <c r="Q18" s="150"/>
+      <c r="P18" s="165"/>
+      <c r="Q18" s="165"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
-      <c r="T18" s="205" t="s">
-        <v>299</v>
-      </c>
-      <c r="U18" s="205" t="s">
+      <c r="T18" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="U18" s="94" t="s">
+        <v>157</v>
+      </c>
+      <c r="V18" s="29"/>
+      <c r="W18" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="V18" s="29"/>
-      <c r="W18" s="205" t="s">
+      <c r="X18" s="168" t="s">
         <v>159</v>
-      </c>
-      <c r="X18" s="208" t="s">
-        <v>160</v>
       </c>
       <c r="Y18" s="29"/>
       <c r="Z18" s="29"/>
       <c r="AA18" s="29"/>
-      <c r="AB18" s="263" t="s">
-        <v>161</v>
-      </c>
-      <c r="AC18" s="117"/>
-      <c r="AD18" s="72"/>
-      <c r="AE18" s="72"/>
-      <c r="AF18" s="72"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="73"/>
+      <c r="AB18" s="88" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="70"/>
+      <c r="AI18" s="71"/>
       <c r="AJ18" s="55"/>
       <c r="AK18" s="55"/>
       <c r="AL18" s="55"/>
@@ -4846,79 +4841,79 @@
       <c r="AY18" s="55"/>
       <c r="AZ18" s="56"/>
       <c r="BA18" s="36"/>
-      <c r="BB18" s="100" t="s">
+      <c r="BB18" s="139" t="s">
+        <v>204</v>
+      </c>
+      <c r="BC18" s="139" t="s">
         <v>205</v>
-      </c>
-      <c r="BC18" s="100" t="s">
-        <v>206</v>
       </c>
       <c r="BD18" s="28"/>
       <c r="BE18" s="28"/>
       <c r="BF18" s="28"/>
-      <c r="BG18" s="106" t="s">
-        <v>297</v>
-      </c>
-      <c r="BH18" s="132" t="s">
-        <v>195</v>
+      <c r="BG18" s="142" t="s">
+        <v>296</v>
+      </c>
+      <c r="BH18" s="145" t="s">
+        <v>194</v>
       </c>
       <c r="BI18" s="28"/>
-      <c r="BJ18" s="132" t="s">
-        <v>212</v>
-      </c>
-      <c r="BK18" s="103"/>
+      <c r="BJ18" s="145" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK18" s="124"/>
       <c r="BL18" s="28"/>
       <c r="BM18" s="28"/>
       <c r="BN18" s="28"/>
-      <c r="BO18" s="94"/>
-      <c r="BP18" s="170" t="s">
-        <v>208</v>
+      <c r="BO18" s="100"/>
+      <c r="BP18" s="148" t="s">
+        <v>207</v>
       </c>
       <c r="BQ18" s="28"/>
       <c r="BR18" s="28"/>
       <c r="BS18" s="36"/>
-      <c r="BT18" s="94" t="s">
+      <c r="BT18" s="100" t="s">
+        <v>224</v>
+      </c>
+      <c r="BU18" s="100" t="s">
         <v>225</v>
-      </c>
-      <c r="BU18" s="94" t="s">
-        <v>226</v>
       </c>
       <c r="BV18" s="40"/>
     </row>
-    <row r="19" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:74" ht="15" customHeight="1">
       <c r="B19" s="18"/>
       <c r="C19" s="20"/>
       <c r="D19" s="28"/>
       <c r="E19" s="28"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="98"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="194"/>
       <c r="H19" s="28"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="95"/>
+      <c r="I19" s="194"/>
+      <c r="J19" s="101"/>
       <c r="K19" s="28"/>
       <c r="L19" s="28"/>
-      <c r="M19" s="139"/>
-      <c r="N19" s="95"/>
+      <c r="M19" s="181"/>
+      <c r="N19" s="101"/>
       <c r="O19" s="28"/>
-      <c r="P19" s="151"/>
-      <c r="Q19" s="151"/>
+      <c r="P19" s="166"/>
+      <c r="Q19" s="166"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
-      <c r="T19" s="206"/>
-      <c r="U19" s="206"/>
+      <c r="T19" s="95"/>
+      <c r="U19" s="95"/>
       <c r="V19" s="29"/>
-      <c r="W19" s="206"/>
-      <c r="X19" s="209"/>
+      <c r="W19" s="95"/>
+      <c r="X19" s="169"/>
       <c r="Y19" s="29"/>
       <c r="Z19" s="29"/>
       <c r="AA19" s="29"/>
-      <c r="AB19" s="264"/>
-      <c r="AC19" s="117"/>
-      <c r="AD19" s="72"/>
-      <c r="AE19" s="72"/>
-      <c r="AF19" s="72"/>
-      <c r="AG19" s="72"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="73"/>
+      <c r="AB19" s="89"/>
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="70"/>
+      <c r="AE19" s="70"/>
+      <c r="AF19" s="70"/>
+      <c r="AG19" s="70"/>
+      <c r="AH19" s="70"/>
+      <c r="AI19" s="71"/>
       <c r="AJ19" s="55"/>
       <c r="AK19" s="55"/>
       <c r="AL19" s="55"/>
@@ -4937,63 +4932,63 @@
       <c r="AY19" s="55"/>
       <c r="AZ19" s="56"/>
       <c r="BA19" s="36"/>
-      <c r="BB19" s="101"/>
-      <c r="BC19" s="101"/>
+      <c r="BB19" s="140"/>
+      <c r="BC19" s="140"/>
       <c r="BD19" s="28"/>
       <c r="BE19" s="39"/>
       <c r="BF19" s="39"/>
-      <c r="BG19" s="107"/>
-      <c r="BH19" s="133"/>
+      <c r="BG19" s="143"/>
+      <c r="BH19" s="146"/>
       <c r="BI19" s="28"/>
-      <c r="BJ19" s="133"/>
-      <c r="BK19" s="104"/>
+      <c r="BJ19" s="146"/>
+      <c r="BK19" s="125"/>
       <c r="BL19" s="39"/>
       <c r="BM19" s="28"/>
       <c r="BN19" s="28"/>
-      <c r="BO19" s="95"/>
-      <c r="BP19" s="171"/>
+      <c r="BO19" s="101"/>
+      <c r="BP19" s="149"/>
       <c r="BQ19" s="28"/>
       <c r="BR19" s="28"/>
       <c r="BS19" s="36"/>
-      <c r="BT19" s="95"/>
-      <c r="BU19" s="95"/>
+      <c r="BT19" s="101"/>
+      <c r="BU19" s="101"/>
       <c r="BV19" s="40"/>
     </row>
-    <row r="20" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:74" ht="15" customHeight="1" thickBot="1">
       <c r="B20" s="18"/>
       <c r="C20" s="43"/>
       <c r="D20" s="28"/>
       <c r="E20" s="28"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="99"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="195"/>
       <c r="H20" s="28"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="96"/>
+      <c r="I20" s="195"/>
+      <c r="J20" s="102"/>
       <c r="K20" s="28"/>
       <c r="L20" s="28"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="96"/>
+      <c r="M20" s="182"/>
+      <c r="N20" s="102"/>
       <c r="O20" s="28"/>
-      <c r="P20" s="152"/>
-      <c r="Q20" s="152"/>
+      <c r="P20" s="167"/>
+      <c r="Q20" s="167"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
-      <c r="T20" s="207"/>
-      <c r="U20" s="207"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
       <c r="V20" s="29"/>
-      <c r="W20" s="207"/>
-      <c r="X20" s="210"/>
+      <c r="W20" s="96"/>
+      <c r="X20" s="170"/>
       <c r="Y20" s="29"/>
       <c r="Z20" s="29"/>
       <c r="AA20" s="29"/>
-      <c r="AB20" s="265"/>
-      <c r="AC20" s="117"/>
-      <c r="AD20" s="72"/>
-      <c r="AE20" s="72"/>
-      <c r="AF20" s="72"/>
-      <c r="AG20" s="72"/>
-      <c r="AH20" s="72"/>
-      <c r="AI20" s="73"/>
+      <c r="AB20" s="90"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="70"/>
+      <c r="AE20" s="70"/>
+      <c r="AF20" s="70"/>
+      <c r="AG20" s="70"/>
+      <c r="AH20" s="70"/>
+      <c r="AI20" s="71"/>
       <c r="AJ20" s="55"/>
       <c r="AK20" s="55"/>
       <c r="AL20" s="55"/>
@@ -5012,89 +5007,89 @@
       <c r="AY20" s="55"/>
       <c r="AZ20" s="56"/>
       <c r="BA20" s="36"/>
-      <c r="BB20" s="102"/>
-      <c r="BC20" s="102"/>
+      <c r="BB20" s="141"/>
+      <c r="BC20" s="141"/>
       <c r="BD20" s="28"/>
       <c r="BE20" s="28"/>
       <c r="BF20" s="28"/>
-      <c r="BG20" s="108"/>
-      <c r="BH20" s="134"/>
+      <c r="BG20" s="144"/>
+      <c r="BH20" s="147"/>
       <c r="BI20" s="28"/>
-      <c r="BJ20" s="134"/>
-      <c r="BK20" s="105"/>
+      <c r="BJ20" s="147"/>
+      <c r="BK20" s="126"/>
       <c r="BL20" s="28"/>
       <c r="BM20" s="28"/>
       <c r="BN20" s="28"/>
-      <c r="BO20" s="96"/>
-      <c r="BP20" s="172"/>
+      <c r="BO20" s="102"/>
+      <c r="BP20" s="150"/>
       <c r="BQ20" s="28"/>
       <c r="BR20" s="28"/>
       <c r="BS20" s="36"/>
-      <c r="BT20" s="96"/>
-      <c r="BU20" s="96"/>
+      <c r="BT20" s="102"/>
+      <c r="BU20" s="102"/>
       <c r="BV20" s="40"/>
     </row>
-    <row r="21" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="114" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="129"/>
+    <row r="21" spans="2:74" ht="15" customHeight="1" thickBot="1">
+      <c r="B21" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="68"/>
       <c r="D21" s="28"/>
       <c r="E21" s="28"/>
-      <c r="F21" s="100" t="s">
+      <c r="F21" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="193" t="s">
         <v>163</v>
       </c>
-      <c r="G21" s="97" t="s">
+      <c r="H21" s="28"/>
+      <c r="I21" s="193" t="s">
         <v>164</v>
       </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="97" t="s">
+      <c r="J21" s="171" t="s">
         <v>165</v>
-      </c>
-      <c r="J21" s="147" t="s">
-        <v>166</v>
       </c>
       <c r="K21" s="28"/>
       <c r="L21" s="28"/>
-      <c r="M21" s="147" t="s">
-        <v>281</v>
-      </c>
-      <c r="N21" s="147" t="s">
+      <c r="M21" s="171" t="s">
+        <v>280</v>
+      </c>
+      <c r="N21" s="171" t="s">
+        <v>166</v>
+      </c>
+      <c r="O21" s="28"/>
+      <c r="P21" s="174" t="s">
         <v>167</v>
       </c>
-      <c r="O21" s="28"/>
-      <c r="P21" s="214" t="s">
+      <c r="Q21" s="94" t="s">
         <v>168</v>
-      </c>
-      <c r="Q21" s="205" t="s">
-        <v>169</v>
       </c>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
-      <c r="T21" s="205"/>
-      <c r="U21" s="205" t="s">
+      <c r="T21" s="94"/>
+      <c r="U21" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="V21" s="29"/>
+      <c r="W21" s="94" t="s">
         <v>171</v>
       </c>
-      <c r="V21" s="29"/>
-      <c r="W21" s="205" t="s">
+      <c r="X21" s="168" t="s">
         <v>172</v>
-      </c>
-      <c r="X21" s="208" t="s">
-        <v>173</v>
       </c>
       <c r="Y21" s="29"/>
       <c r="Z21" s="29"/>
       <c r="AA21" s="29"/>
-      <c r="AB21" s="263" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC21" s="119"/>
-      <c r="AD21" s="74"/>
-      <c r="AE21" s="74"/>
-      <c r="AF21" s="74"/>
-      <c r="AG21" s="74"/>
-      <c r="AH21" s="74"/>
-      <c r="AI21" s="75"/>
+      <c r="AB21" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="AC21" s="72"/>
+      <c r="AD21" s="73"/>
+      <c r="AE21" s="73"/>
+      <c r="AF21" s="73"/>
+      <c r="AG21" s="73"/>
+      <c r="AH21" s="73"/>
+      <c r="AI21" s="74"/>
       <c r="AJ21" s="55"/>
       <c r="AK21" s="55"/>
       <c r="AL21" s="55"/>
@@ -5113,83 +5108,83 @@
       <c r="AY21" s="55"/>
       <c r="AZ21" s="56"/>
       <c r="BA21" s="36"/>
-      <c r="BB21" s="100" t="s">
+      <c r="BB21" s="139" t="s">
+        <v>208</v>
+      </c>
+      <c r="BC21" s="139" t="s">
         <v>209</v>
-      </c>
-      <c r="BC21" s="100" t="s">
-        <v>210</v>
       </c>
       <c r="BD21" s="28"/>
       <c r="BE21" s="28"/>
       <c r="BF21" s="28"/>
-      <c r="BG21" s="106" t="s">
-        <v>211</v>
-      </c>
-      <c r="BH21" s="132" t="s">
-        <v>213</v>
+      <c r="BG21" s="142" t="s">
+        <v>210</v>
+      </c>
+      <c r="BH21" s="145" t="s">
+        <v>212</v>
       </c>
       <c r="BI21" s="28"/>
-      <c r="BJ21" s="132" t="s">
-        <v>217</v>
-      </c>
-      <c r="BK21" s="103"/>
+      <c r="BJ21" s="145" t="s">
+        <v>216</v>
+      </c>
+      <c r="BK21" s="124"/>
       <c r="BL21" s="28"/>
       <c r="BM21" s="28"/>
       <c r="BN21" s="28"/>
-      <c r="BO21" s="94"/>
-      <c r="BP21" s="170" t="s">
-        <v>214</v>
+      <c r="BO21" s="100"/>
+      <c r="BP21" s="148" t="s">
+        <v>213</v>
       </c>
       <c r="BQ21" s="28"/>
       <c r="BR21" s="28"/>
       <c r="BS21" s="36"/>
-      <c r="BT21" s="94" t="s">
-        <v>228</v>
-      </c>
-      <c r="BU21" s="94" t="s">
+      <c r="BT21" s="100" t="s">
         <v>227</v>
+      </c>
+      <c r="BU21" s="100" t="s">
+        <v>226</v>
       </c>
       <c r="BV21" s="40"/>
     </row>
-    <row r="22" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="117"/>
-      <c r="C22" s="73"/>
+    <row r="22" spans="2:74" ht="15" customHeight="1">
+      <c r="B22" s="69"/>
+      <c r="C22" s="71"/>
       <c r="D22" s="28"/>
       <c r="E22" s="28"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="98"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="194"/>
       <c r="H22" s="28"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="148"/>
+      <c r="I22" s="194"/>
+      <c r="J22" s="172"/>
       <c r="K22" s="28"/>
       <c r="L22" s="28"/>
-      <c r="M22" s="148"/>
-      <c r="N22" s="148"/>
+      <c r="M22" s="172"/>
+      <c r="N22" s="172"/>
       <c r="O22" s="28"/>
-      <c r="P22" s="215"/>
-      <c r="Q22" s="206"/>
+      <c r="P22" s="175"/>
+      <c r="Q22" s="95"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
-      <c r="T22" s="206"/>
-      <c r="U22" s="206"/>
+      <c r="T22" s="95"/>
+      <c r="U22" s="95"/>
       <c r="V22" s="29"/>
-      <c r="W22" s="206"/>
-      <c r="X22" s="209"/>
+      <c r="W22" s="95"/>
+      <c r="X22" s="169"/>
       <c r="Y22" s="29"/>
       <c r="Z22" s="29"/>
       <c r="AA22" s="29"/>
-      <c r="AB22" s="264"/>
-      <c r="AC22" s="114" t="s">
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="66" t="s">
+        <v>258</v>
+      </c>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="68"/>
+      <c r="AG22" s="66" t="s">
         <v>259</v>
       </c>
-      <c r="AD22" s="115"/>
-      <c r="AE22" s="115"/>
-      <c r="AF22" s="129"/>
-      <c r="AG22" s="114" t="s">
-        <v>260</v>
-      </c>
-      <c r="AH22" s="115"/>
-      <c r="AI22" s="129"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="68"/>
       <c r="AJ22" s="55"/>
       <c r="AK22" s="55"/>
       <c r="AL22" s="55"/>
@@ -5208,63 +5203,63 @@
       <c r="AY22" s="55"/>
       <c r="AZ22" s="56"/>
       <c r="BA22" s="36"/>
-      <c r="BB22" s="101"/>
-      <c r="BC22" s="101"/>
+      <c r="BB22" s="140"/>
+      <c r="BC22" s="140"/>
       <c r="BD22" s="28"/>
       <c r="BE22" s="39"/>
       <c r="BF22" s="39"/>
-      <c r="BG22" s="107"/>
-      <c r="BH22" s="133"/>
+      <c r="BG22" s="143"/>
+      <c r="BH22" s="146"/>
       <c r="BI22" s="28"/>
-      <c r="BJ22" s="133"/>
-      <c r="BK22" s="104"/>
+      <c r="BJ22" s="146"/>
+      <c r="BK22" s="125"/>
       <c r="BL22" s="39"/>
       <c r="BM22" s="28"/>
       <c r="BN22" s="28"/>
-      <c r="BO22" s="95"/>
-      <c r="BP22" s="171"/>
+      <c r="BO22" s="101"/>
+      <c r="BP22" s="149"/>
       <c r="BQ22" s="28"/>
       <c r="BR22" s="28"/>
       <c r="BS22" s="36"/>
-      <c r="BT22" s="95"/>
-      <c r="BU22" s="95"/>
+      <c r="BT22" s="101"/>
+      <c r="BU22" s="101"/>
       <c r="BV22" s="40"/>
     </row>
-    <row r="23" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="117"/>
-      <c r="C23" s="73"/>
+    <row r="23" spans="2:74" ht="15" customHeight="1">
+      <c r="B23" s="69"/>
+      <c r="C23" s="71"/>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="99"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="195"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="99"/>
-      <c r="J23" s="149"/>
+      <c r="I23" s="195"/>
+      <c r="J23" s="173"/>
       <c r="K23" s="28"/>
       <c r="L23" s="28"/>
-      <c r="M23" s="149"/>
-      <c r="N23" s="149"/>
+      <c r="M23" s="173"/>
+      <c r="N23" s="173"/>
       <c r="O23" s="28"/>
-      <c r="P23" s="216"/>
-      <c r="Q23" s="207"/>
+      <c r="P23" s="176"/>
+      <c r="Q23" s="96"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
-      <c r="T23" s="207"/>
-      <c r="U23" s="207"/>
+      <c r="T23" s="96"/>
+      <c r="U23" s="96"/>
       <c r="V23" s="29"/>
-      <c r="W23" s="207"/>
-      <c r="X23" s="210"/>
+      <c r="W23" s="96"/>
+      <c r="X23" s="170"/>
       <c r="Y23" s="29"/>
       <c r="Z23" s="29"/>
       <c r="AA23" s="29"/>
-      <c r="AB23" s="265"/>
-      <c r="AC23" s="117"/>
-      <c r="AD23" s="72"/>
-      <c r="AE23" s="72"/>
-      <c r="AF23" s="73"/>
-      <c r="AG23" s="117"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="73"/>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="69"/>
+      <c r="AD23" s="70"/>
+      <c r="AE23" s="70"/>
+      <c r="AF23" s="71"/>
+      <c r="AG23" s="69"/>
+      <c r="AH23" s="70"/>
+      <c r="AI23" s="71"/>
       <c r="AJ23" s="55"/>
       <c r="AK23" s="55"/>
       <c r="AL23" s="55"/>
@@ -5283,83 +5278,83 @@
       <c r="AY23" s="55"/>
       <c r="AZ23" s="56"/>
       <c r="BA23" s="36"/>
-      <c r="BB23" s="102"/>
-      <c r="BC23" s="102"/>
+      <c r="BB23" s="141"/>
+      <c r="BC23" s="141"/>
       <c r="BD23" s="28"/>
       <c r="BE23" s="28"/>
       <c r="BF23" s="28"/>
-      <c r="BG23" s="108"/>
-      <c r="BH23" s="134"/>
+      <c r="BG23" s="144"/>
+      <c r="BH23" s="147"/>
       <c r="BI23" s="28"/>
-      <c r="BJ23" s="134"/>
-      <c r="BK23" s="105"/>
+      <c r="BJ23" s="147"/>
+      <c r="BK23" s="126"/>
       <c r="BL23" s="28"/>
       <c r="BM23" s="28"/>
       <c r="BN23" s="28"/>
-      <c r="BO23" s="96"/>
-      <c r="BP23" s="172"/>
+      <c r="BO23" s="102"/>
+      <c r="BP23" s="150"/>
       <c r="BQ23" s="28"/>
       <c r="BR23" s="28"/>
       <c r="BS23" s="36"/>
-      <c r="BT23" s="96"/>
-      <c r="BU23" s="96"/>
+      <c r="BT23" s="102"/>
+      <c r="BU23" s="102"/>
       <c r="BV23" s="40"/>
     </row>
-    <row r="24" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="117"/>
-      <c r="C24" s="73"/>
+    <row r="24" spans="2:74" ht="15" customHeight="1">
+      <c r="B24" s="69"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="97" t="s">
+      <c r="F24" s="100"/>
+      <c r="G24" s="193" t="s">
+        <v>174</v>
+      </c>
+      <c r="H24" s="28"/>
+      <c r="I24" s="193" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="28"/>
-      <c r="I24" s="97" t="s">
+      <c r="J24" s="171" t="s">
         <v>176</v>
-      </c>
-      <c r="J24" s="147" t="s">
-        <v>177</v>
       </c>
       <c r="K24" s="28"/>
       <c r="L24" s="28"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="147" t="s">
+      <c r="M24" s="100"/>
+      <c r="N24" s="171" t="s">
+        <v>177</v>
+      </c>
+      <c r="O24" s="28"/>
+      <c r="P24" s="174" t="s">
         <v>178</v>
       </c>
-      <c r="O24" s="28"/>
-      <c r="P24" s="214" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q24" s="150"/>
+      <c r="Q24" s="165"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
-      <c r="T24" s="205" t="s">
+      <c r="T24" s="94" t="s">
+        <v>179</v>
+      </c>
+      <c r="U24" s="94" t="s">
         <v>180</v>
       </c>
-      <c r="U24" s="205" t="s">
+      <c r="V24" s="29"/>
+      <c r="W24" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="V24" s="29"/>
-      <c r="W24" s="205" t="s">
+      <c r="X24" s="94" t="s">
         <v>182</v>
-      </c>
-      <c r="X24" s="205" t="s">
-        <v>183</v>
       </c>
       <c r="Y24" s="29"/>
       <c r="Z24" s="29"/>
       <c r="AA24" s="29"/>
-      <c r="AB24" s="263" t="s">
-        <v>184</v>
-      </c>
-      <c r="AC24" s="117"/>
-      <c r="AD24" s="72"/>
-      <c r="AE24" s="72"/>
-      <c r="AF24" s="73"/>
-      <c r="AG24" s="117"/>
-      <c r="AH24" s="72"/>
-      <c r="AI24" s="73"/>
+      <c r="AB24" s="88" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="70"/>
+      <c r="AE24" s="70"/>
+      <c r="AF24" s="71"/>
+      <c r="AG24" s="69"/>
+      <c r="AH24" s="70"/>
+      <c r="AI24" s="71"/>
       <c r="AJ24" s="55"/>
       <c r="AK24" s="55"/>
       <c r="AL24" s="55"/>
@@ -5378,77 +5373,77 @@
       <c r="AY24" s="55"/>
       <c r="AZ24" s="56"/>
       <c r="BA24" s="36"/>
-      <c r="BB24" s="103"/>
-      <c r="BC24" s="100" t="s">
-        <v>215</v>
+      <c r="BB24" s="124"/>
+      <c r="BC24" s="139" t="s">
+        <v>214</v>
       </c>
       <c r="BD24" s="28"/>
       <c r="BE24" s="28"/>
       <c r="BF24" s="28"/>
-      <c r="BG24" s="106" t="s">
-        <v>216</v>
-      </c>
-      <c r="BH24" s="132" t="s">
-        <v>218</v>
+      <c r="BG24" s="142" t="s">
+        <v>215</v>
+      </c>
+      <c r="BH24" s="145" t="s">
+        <v>217</v>
       </c>
       <c r="BI24" s="28"/>
-      <c r="BJ24" s="132" t="s">
-        <v>295</v>
-      </c>
-      <c r="BK24" s="103"/>
+      <c r="BJ24" s="145" t="s">
+        <v>294</v>
+      </c>
+      <c r="BK24" s="124"/>
       <c r="BL24" s="28"/>
       <c r="BM24" s="28"/>
       <c r="BN24" s="28"/>
-      <c r="BO24" s="94" t="s">
-        <v>230</v>
-      </c>
-      <c r="BP24" s="94" t="s">
-        <v>307</v>
+      <c r="BO24" s="100" t="s">
+        <v>229</v>
+      </c>
+      <c r="BP24" s="100" t="s">
+        <v>306</v>
       </c>
       <c r="BQ24" s="28"/>
       <c r="BR24" s="28"/>
       <c r="BS24" s="36"/>
-      <c r="BT24" s="94" t="s">
-        <v>229</v>
-      </c>
-      <c r="BU24" s="94"/>
+      <c r="BT24" s="100" t="s">
+        <v>228</v>
+      </c>
+      <c r="BU24" s="100"/>
       <c r="BV24" s="40"/>
     </row>
-    <row r="25" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="117"/>
-      <c r="C25" s="73"/>
+    <row r="25" spans="2:74" ht="15" customHeight="1">
+      <c r="B25" s="69"/>
+      <c r="C25" s="71"/>
       <c r="D25" s="28"/>
       <c r="E25" s="28"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="98"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="194"/>
       <c r="H25" s="28"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="148"/>
+      <c r="I25" s="194"/>
+      <c r="J25" s="172"/>
       <c r="K25" s="28"/>
       <c r="L25" s="28"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="148"/>
+      <c r="M25" s="101"/>
+      <c r="N25" s="172"/>
       <c r="O25" s="28"/>
-      <c r="P25" s="215"/>
-      <c r="Q25" s="151"/>
+      <c r="P25" s="175"/>
+      <c r="Q25" s="166"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
-      <c r="T25" s="206"/>
-      <c r="U25" s="206"/>
+      <c r="T25" s="95"/>
+      <c r="U25" s="95"/>
       <c r="V25" s="29"/>
-      <c r="W25" s="206"/>
-      <c r="X25" s="206"/>
+      <c r="W25" s="95"/>
+      <c r="X25" s="95"/>
       <c r="Y25" s="29"/>
       <c r="Z25" s="29"/>
       <c r="AA25" s="29"/>
-      <c r="AB25" s="264"/>
-      <c r="AC25" s="117"/>
-      <c r="AD25" s="72"/>
-      <c r="AE25" s="72"/>
-      <c r="AF25" s="73"/>
-      <c r="AG25" s="117"/>
-      <c r="AH25" s="72"/>
-      <c r="AI25" s="73"/>
+      <c r="AB25" s="89"/>
+      <c r="AC25" s="69"/>
+      <c r="AD25" s="70"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="71"/>
+      <c r="AG25" s="69"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="71"/>
       <c r="AJ25" s="55"/>
       <c r="AK25" s="55"/>
       <c r="AL25" s="55"/>
@@ -5467,63 +5462,63 @@
       <c r="AY25" s="55"/>
       <c r="AZ25" s="56"/>
       <c r="BA25" s="36"/>
-      <c r="BB25" s="104"/>
-      <c r="BC25" s="101"/>
+      <c r="BB25" s="125"/>
+      <c r="BC25" s="140"/>
       <c r="BD25" s="28"/>
       <c r="BE25" s="39"/>
       <c r="BF25" s="39"/>
-      <c r="BG25" s="107"/>
-      <c r="BH25" s="133"/>
+      <c r="BG25" s="143"/>
+      <c r="BH25" s="146"/>
       <c r="BI25" s="28"/>
-      <c r="BJ25" s="133"/>
-      <c r="BK25" s="104"/>
+      <c r="BJ25" s="146"/>
+      <c r="BK25" s="125"/>
       <c r="BL25" s="39"/>
       <c r="BM25" s="28"/>
       <c r="BN25" s="28"/>
-      <c r="BO25" s="95"/>
-      <c r="BP25" s="95"/>
+      <c r="BO25" s="101"/>
+      <c r="BP25" s="101"/>
       <c r="BQ25" s="28"/>
       <c r="BR25" s="28"/>
       <c r="BS25" s="36"/>
-      <c r="BT25" s="95"/>
-      <c r="BU25" s="95"/>
+      <c r="BT25" s="101"/>
+      <c r="BU25" s="101"/>
       <c r="BV25" s="40"/>
     </row>
-    <row r="26" spans="2:74" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119"/>
-      <c r="C26" s="75"/>
+    <row r="26" spans="2:74" ht="17.45" customHeight="1" thickBot="1">
+      <c r="B26" s="72"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="42"/>
       <c r="E26" s="28"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="99"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="195"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="149"/>
+      <c r="I26" s="195"/>
+      <c r="J26" s="173"/>
       <c r="K26" s="44"/>
       <c r="L26" s="28"/>
-      <c r="M26" s="96"/>
-      <c r="N26" s="149"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="173"/>
       <c r="O26" s="28"/>
-      <c r="P26" s="216"/>
-      <c r="Q26" s="152"/>
+      <c r="P26" s="176"/>
+      <c r="Q26" s="167"/>
       <c r="R26" s="28"/>
       <c r="S26" s="45"/>
-      <c r="T26" s="207"/>
-      <c r="U26" s="207"/>
+      <c r="T26" s="96"/>
+      <c r="U26" s="96"/>
       <c r="V26" s="29"/>
-      <c r="W26" s="207"/>
-      <c r="X26" s="207"/>
+      <c r="W26" s="96"/>
+      <c r="X26" s="96"/>
       <c r="Y26" s="42"/>
       <c r="Z26" s="29"/>
       <c r="AA26" s="29"/>
-      <c r="AB26" s="265"/>
-      <c r="AC26" s="119"/>
-      <c r="AD26" s="74"/>
-      <c r="AE26" s="74"/>
-      <c r="AF26" s="75"/>
-      <c r="AG26" s="119"/>
-      <c r="AH26" s="74"/>
-      <c r="AI26" s="75"/>
+      <c r="AB26" s="90"/>
+      <c r="AC26" s="72"/>
+      <c r="AD26" s="73"/>
+      <c r="AE26" s="73"/>
+      <c r="AF26" s="74"/>
+      <c r="AG26" s="72"/>
+      <c r="AH26" s="73"/>
+      <c r="AI26" s="74"/>
       <c r="AJ26" s="55"/>
       <c r="AK26" s="55"/>
       <c r="AL26" s="55"/>
@@ -5542,29 +5537,29 @@
       <c r="AY26" s="55"/>
       <c r="AZ26" s="56"/>
       <c r="BA26" s="36"/>
-      <c r="BB26" s="105"/>
-      <c r="BC26" s="102"/>
+      <c r="BB26" s="126"/>
+      <c r="BC26" s="141"/>
       <c r="BD26" s="28"/>
       <c r="BE26" s="42"/>
       <c r="BF26" s="28"/>
-      <c r="BG26" s="108"/>
-      <c r="BH26" s="134"/>
+      <c r="BG26" s="144"/>
+      <c r="BH26" s="147"/>
       <c r="BI26" s="28"/>
-      <c r="BJ26" s="134"/>
-      <c r="BK26" s="105"/>
+      <c r="BJ26" s="147"/>
+      <c r="BK26" s="126"/>
       <c r="BL26" s="28"/>
       <c r="BM26" s="42"/>
       <c r="BN26" s="28"/>
-      <c r="BO26" s="96"/>
-      <c r="BP26" s="96"/>
+      <c r="BO26" s="102"/>
+      <c r="BP26" s="102"/>
       <c r="BQ26" s="28"/>
       <c r="BR26" s="42"/>
       <c r="BS26" s="50"/>
-      <c r="BT26" s="230"/>
-      <c r="BU26" s="230"/>
+      <c r="BT26" s="151"/>
+      <c r="BU26" s="151"/>
       <c r="BV26" s="34"/>
     </row>
-    <row r="27" spans="2:74" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:74" ht="16.5" customHeight="1">
       <c r="B27" s="18"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -5576,19 +5571,19 @@
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
       <c r="L27" s="19"/>
-      <c r="M27" s="173" t="s">
-        <v>282</v>
-      </c>
-      <c r="N27" s="173"/>
+      <c r="M27" s="65" t="s">
+        <v>281</v>
+      </c>
+      <c r="N27" s="65"/>
       <c r="O27" s="19"/>
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
       <c r="S27" s="19"/>
-      <c r="T27" s="173" t="s">
-        <v>286</v>
-      </c>
-      <c r="U27" s="173"/>
+      <c r="T27" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="U27" s="65"/>
       <c r="V27" s="19"/>
       <c r="W27" s="19"/>
       <c r="X27" s="19"/>
@@ -5643,7 +5638,7 @@
       <c r="BU27" s="19"/>
       <c r="BV27" s="26"/>
     </row>
-    <row r="28" spans="2:74" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:74" ht="17.45" customHeight="1">
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -5655,10 +5650,10 @@
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
-      <c r="M28" s="72" t="s">
-        <v>283</v>
-      </c>
-      <c r="N28" s="72"/>
+      <c r="M28" s="70" t="s">
+        <v>282</v>
+      </c>
+      <c r="N28" s="70"/>
       <c r="O28" s="19"/>
       <c r="P28" s="19"/>
       <c r="Q28" s="19"/>
@@ -5720,24 +5715,24 @@
       <c r="BU28" s="19"/>
       <c r="BV28" s="26"/>
     </row>
-    <row r="29" spans="2:74" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:74" ht="17.45" customHeight="1" thickBot="1">
       <c r="B29" s="18"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
-      <c r="F29" s="141" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="103"/>
+      <c r="F29" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="124"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="269" t="s">
+      <c r="J29" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="100"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="91" t="s">
         <v>186</v>
-      </c>
-      <c r="K29" s="94"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="266" t="s">
-        <v>187</v>
       </c>
       <c r="N29" s="19"/>
       <c r="O29" s="19"/>
@@ -5801,19 +5796,19 @@
       <c r="BU29" s="19"/>
       <c r="BV29" s="26"/>
     </row>
-    <row r="30" spans="2:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="B30" s="18"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="104"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="125"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
-      <c r="J30" s="270"/>
-      <c r="K30" s="95"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="101"/>
       <c r="L30" s="19"/>
-      <c r="M30" s="267"/>
+      <c r="M30" s="92"/>
       <c r="N30" s="19"/>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
@@ -5849,12 +5844,12 @@
       <c r="AT30" s="55"/>
       <c r="AU30" s="55"/>
       <c r="AV30" s="55"/>
-      <c r="AW30" s="114" t="s">
-        <v>261</v>
-      </c>
-      <c r="AX30" s="115"/>
-      <c r="AY30" s="115"/>
-      <c r="AZ30" s="129"/>
+      <c r="AW30" s="66" t="s">
+        <v>260</v>
+      </c>
+      <c r="AX30" s="67"/>
+      <c r="AY30" s="67"/>
+      <c r="AZ30" s="68"/>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
       <c r="BC30" s="19"/>
@@ -5865,38 +5860,38 @@
       <c r="BH30" s="19"/>
       <c r="BI30" s="19"/>
       <c r="BJ30" s="19"/>
-      <c r="BK30" s="221" t="s">
-        <v>219</v>
-      </c>
-      <c r="BL30" s="223"/>
-      <c r="BM30" s="221" t="s">
-        <v>257</v>
-      </c>
-      <c r="BN30" s="222"/>
-      <c r="BO30" s="222"/>
-      <c r="BP30" s="222"/>
-      <c r="BQ30" s="223"/>
-      <c r="BR30" s="221" t="s">
+      <c r="BK30" s="152" t="s">
+        <v>218</v>
+      </c>
+      <c r="BL30" s="154"/>
+      <c r="BM30" s="152" t="s">
         <v>256</v>
       </c>
-      <c r="BS30" s="222"/>
-      <c r="BT30" s="222"/>
-      <c r="BU30" s="222"/>
-      <c r="BV30" s="223"/>
+      <c r="BN30" s="153"/>
+      <c r="BO30" s="153"/>
+      <c r="BP30" s="153"/>
+      <c r="BQ30" s="154"/>
+      <c r="BR30" s="152" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS30" s="153"/>
+      <c r="BT30" s="153"/>
+      <c r="BU30" s="153"/>
+      <c r="BV30" s="154"/>
     </row>
-    <row r="31" spans="2:74" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:74" ht="16.5" customHeight="1" thickBot="1">
       <c r="B31" s="18"/>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
-      <c r="F31" s="143"/>
-      <c r="G31" s="105"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="126"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
-      <c r="J31" s="271"/>
-      <c r="K31" s="96"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="102"/>
       <c r="L31" s="19"/>
-      <c r="M31" s="268"/>
+      <c r="M31" s="93"/>
       <c r="N31" s="19"/>
       <c r="O31" s="19"/>
       <c r="P31" s="19"/>
@@ -5904,27 +5899,27 @@
       <c r="R31" s="19"/>
       <c r="S31" s="19"/>
       <c r="T31" s="19"/>
-      <c r="U31" s="114" t="s">
-        <v>253</v>
-      </c>
-      <c r="V31" s="115"/>
-      <c r="W31" s="115"/>
-      <c r="X31" s="129"/>
-      <c r="Y31" s="115" t="s">
+      <c r="U31" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="Z31" s="129"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="68"/>
+      <c r="Y31" s="67" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z31" s="68"/>
       <c r="AA31" s="19"/>
       <c r="AB31" s="19"/>
-      <c r="AC31" s="231" t="s">
-        <v>244</v>
-      </c>
-      <c r="AD31" s="231"/>
-      <c r="AE31" s="231"/>
-      <c r="AF31" s="231"/>
-      <c r="AG31" s="231"/>
-      <c r="AH31" s="231"/>
-      <c r="AI31" s="231"/>
+      <c r="AC31" s="114" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD31" s="114"/>
+      <c r="AE31" s="114"/>
+      <c r="AF31" s="114"/>
+      <c r="AG31" s="114"/>
+      <c r="AH31" s="114"/>
+      <c r="AI31" s="114"/>
       <c r="AJ31" s="55"/>
       <c r="AK31" s="55"/>
       <c r="AL31" s="55"/>
@@ -5938,51 +5933,51 @@
       <c r="AT31" s="55"/>
       <c r="AU31" s="55"/>
       <c r="AV31" s="55"/>
-      <c r="AW31" s="117"/>
-      <c r="AX31" s="72"/>
-      <c r="AY31" s="72"/>
-      <c r="AZ31" s="73"/>
+      <c r="AW31" s="69"/>
+      <c r="AX31" s="70"/>
+      <c r="AY31" s="70"/>
+      <c r="AZ31" s="71"/>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
       <c r="BC31" s="19"/>
       <c r="BD31" s="19"/>
-      <c r="BE31" s="250" t="s">
-        <v>220</v>
-      </c>
-      <c r="BF31" s="251"/>
-      <c r="BG31" s="251"/>
-      <c r="BH31" s="252"/>
+      <c r="BE31" s="75" t="s">
+        <v>219</v>
+      </c>
+      <c r="BF31" s="76"/>
+      <c r="BG31" s="76"/>
+      <c r="BH31" s="77"/>
       <c r="BI31" s="19"/>
       <c r="BJ31" s="19"/>
-      <c r="BK31" s="224"/>
-      <c r="BL31" s="226"/>
-      <c r="BM31" s="224"/>
-      <c r="BN31" s="225"/>
-      <c r="BO31" s="225"/>
-      <c r="BP31" s="225"/>
-      <c r="BQ31" s="226"/>
-      <c r="BR31" s="224"/>
-      <c r="BS31" s="225"/>
-      <c r="BT31" s="225"/>
-      <c r="BU31" s="225"/>
-      <c r="BV31" s="226"/>
+      <c r="BK31" s="155"/>
+      <c r="BL31" s="157"/>
+      <c r="BM31" s="155"/>
+      <c r="BN31" s="156"/>
+      <c r="BO31" s="156"/>
+      <c r="BP31" s="156"/>
+      <c r="BQ31" s="157"/>
+      <c r="BR31" s="155"/>
+      <c r="BS31" s="156"/>
+      <c r="BT31" s="156"/>
+      <c r="BU31" s="156"/>
+      <c r="BV31" s="157"/>
     </row>
-    <row r="32" spans="2:74" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:74" ht="17.45" customHeight="1">
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
-      <c r="F32" s="141" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="103"/>
+      <c r="F32" s="104" t="s">
+        <v>169</v>
+      </c>
+      <c r="G32" s="124"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
-      <c r="J32" s="103"/>
-      <c r="K32" s="103"/>
+      <c r="J32" s="124"/>
+      <c r="K32" s="124"/>
       <c r="L32" s="19"/>
-      <c r="M32" s="266" t="s">
-        <v>188</v>
+      <c r="M32" s="91" t="s">
+        <v>187</v>
       </c>
       <c r="N32" s="19"/>
       <c r="O32" s="19"/>
@@ -5991,36 +5986,36 @@
       <c r="R32" s="19"/>
       <c r="S32" s="19"/>
       <c r="T32" s="19"/>
-      <c r="U32" s="117"/>
-      <c r="V32" s="72"/>
-      <c r="W32" s="72"/>
-      <c r="X32" s="73"/>
-      <c r="Y32" s="72"/>
-      <c r="Z32" s="73"/>
-      <c r="AA32" s="115" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB32" s="129"/>
-      <c r="AC32" s="239" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD32" s="239" t="s">
+      <c r="U32" s="69"/>
+      <c r="V32" s="70"/>
+      <c r="W32" s="70"/>
+      <c r="X32" s="71"/>
+      <c r="Y32" s="70"/>
+      <c r="Z32" s="71"/>
+      <c r="AA32" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB32" s="68"/>
+      <c r="AC32" s="134" t="s">
         <v>250</v>
       </c>
-      <c r="AE32" s="239" t="s">
+      <c r="AD32" s="134" t="s">
         <v>249</v>
       </c>
-      <c r="AF32" s="239" t="s">
+      <c r="AE32" s="134" t="s">
         <v>248</v>
       </c>
-      <c r="AG32" s="239" t="s">
+      <c r="AF32" s="134" t="s">
         <v>247</v>
       </c>
-      <c r="AH32" s="239" t="s">
+      <c r="AG32" s="134" t="s">
         <v>246</v>
       </c>
-      <c r="AI32" s="239" t="s">
+      <c r="AH32" s="134" t="s">
         <v>245</v>
+      </c>
+      <c r="AI32" s="134" t="s">
+        <v>244</v>
       </c>
       <c r="AJ32" s="55"/>
       <c r="AK32" s="55"/>
@@ -6035,46 +6030,46 @@
       <c r="AT32" s="55"/>
       <c r="AU32" s="55"/>
       <c r="AV32" s="55"/>
-      <c r="AW32" s="117"/>
-      <c r="AX32" s="72"/>
-      <c r="AY32" s="72"/>
-      <c r="AZ32" s="73"/>
+      <c r="AW32" s="69"/>
+      <c r="AX32" s="70"/>
+      <c r="AY32" s="70"/>
+      <c r="AZ32" s="71"/>
       <c r="BA32" s="18"/>
       <c r="BB32" s="19"/>
       <c r="BC32" s="19"/>
       <c r="BD32" s="19"/>
-      <c r="BE32" s="253"/>
-      <c r="BF32" s="254"/>
-      <c r="BG32" s="254"/>
-      <c r="BH32" s="255"/>
+      <c r="BE32" s="78"/>
+      <c r="BF32" s="79"/>
+      <c r="BG32" s="79"/>
+      <c r="BH32" s="80"/>
       <c r="BI32" s="19"/>
       <c r="BJ32" s="19"/>
-      <c r="BK32" s="224"/>
-      <c r="BL32" s="226"/>
-      <c r="BM32" s="224"/>
-      <c r="BN32" s="225"/>
-      <c r="BO32" s="225"/>
-      <c r="BP32" s="225"/>
-      <c r="BQ32" s="226"/>
-      <c r="BR32" s="224"/>
-      <c r="BS32" s="225"/>
-      <c r="BT32" s="225"/>
-      <c r="BU32" s="225"/>
-      <c r="BV32" s="226"/>
+      <c r="BK32" s="155"/>
+      <c r="BL32" s="157"/>
+      <c r="BM32" s="155"/>
+      <c r="BN32" s="156"/>
+      <c r="BO32" s="156"/>
+      <c r="BP32" s="156"/>
+      <c r="BQ32" s="157"/>
+      <c r="BR32" s="155"/>
+      <c r="BS32" s="156"/>
+      <c r="BT32" s="156"/>
+      <c r="BU32" s="156"/>
+      <c r="BV32" s="157"/>
     </row>
-    <row r="33" spans="1:74" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:74" ht="16.5" customHeight="1">
       <c r="B33" s="18"/>
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="104"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="125"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
+      <c r="J33" s="125"/>
+      <c r="K33" s="125"/>
       <c r="L33" s="19"/>
-      <c r="M33" s="267"/>
+      <c r="M33" s="92"/>
       <c r="N33" s="19"/>
       <c r="O33" s="19"/>
       <c r="P33" s="19"/>
@@ -6082,21 +6077,21 @@
       <c r="R33" s="19"/>
       <c r="S33" s="19"/>
       <c r="T33" s="19"/>
-      <c r="U33" s="117"/>
-      <c r="V33" s="72"/>
-      <c r="W33" s="72"/>
-      <c r="X33" s="73"/>
-      <c r="Y33" s="72"/>
-      <c r="Z33" s="73"/>
-      <c r="AA33" s="72"/>
-      <c r="AB33" s="73"/>
-      <c r="AC33" s="240"/>
-      <c r="AD33" s="240"/>
-      <c r="AE33" s="240"/>
-      <c r="AF33" s="240"/>
-      <c r="AG33" s="240"/>
-      <c r="AH33" s="240"/>
-      <c r="AI33" s="240"/>
+      <c r="U33" s="69"/>
+      <c r="V33" s="70"/>
+      <c r="W33" s="70"/>
+      <c r="X33" s="71"/>
+      <c r="Y33" s="70"/>
+      <c r="Z33" s="71"/>
+      <c r="AA33" s="70"/>
+      <c r="AB33" s="71"/>
+      <c r="AC33" s="135"/>
+      <c r="AD33" s="135"/>
+      <c r="AE33" s="135"/>
+      <c r="AF33" s="135"/>
+      <c r="AG33" s="135"/>
+      <c r="AH33" s="135"/>
+      <c r="AI33" s="135"/>
       <c r="AJ33" s="55"/>
       <c r="AK33" s="55"/>
       <c r="AL33" s="55"/>
@@ -6110,46 +6105,46 @@
       <c r="AT33" s="55"/>
       <c r="AU33" s="55"/>
       <c r="AV33" s="55"/>
-      <c r="AW33" s="117"/>
-      <c r="AX33" s="72"/>
-      <c r="AY33" s="72"/>
-      <c r="AZ33" s="73"/>
+      <c r="AW33" s="69"/>
+      <c r="AX33" s="70"/>
+      <c r="AY33" s="70"/>
+      <c r="AZ33" s="71"/>
       <c r="BA33" s="18"/>
       <c r="BB33" s="19"/>
       <c r="BC33" s="19"/>
       <c r="BD33" s="19"/>
-      <c r="BE33" s="253"/>
-      <c r="BF33" s="254"/>
-      <c r="BG33" s="254"/>
-      <c r="BH33" s="255"/>
+      <c r="BE33" s="78"/>
+      <c r="BF33" s="79"/>
+      <c r="BG33" s="79"/>
+      <c r="BH33" s="80"/>
       <c r="BI33" s="19"/>
       <c r="BJ33" s="19"/>
-      <c r="BK33" s="224"/>
-      <c r="BL33" s="226"/>
-      <c r="BM33" s="224"/>
-      <c r="BN33" s="225"/>
-      <c r="BO33" s="225"/>
-      <c r="BP33" s="225"/>
-      <c r="BQ33" s="226"/>
-      <c r="BR33" s="224"/>
-      <c r="BS33" s="225"/>
-      <c r="BT33" s="225"/>
-      <c r="BU33" s="225"/>
-      <c r="BV33" s="226"/>
+      <c r="BK33" s="155"/>
+      <c r="BL33" s="157"/>
+      <c r="BM33" s="155"/>
+      <c r="BN33" s="156"/>
+      <c r="BO33" s="156"/>
+      <c r="BP33" s="156"/>
+      <c r="BQ33" s="157"/>
+      <c r="BR33" s="155"/>
+      <c r="BS33" s="156"/>
+      <c r="BT33" s="156"/>
+      <c r="BU33" s="156"/>
+      <c r="BV33" s="157"/>
     </row>
-    <row r="34" spans="1:74" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:74" ht="16.5" customHeight="1" thickBot="1">
       <c r="B34" s="18"/>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
       <c r="E34" s="19"/>
-      <c r="F34" s="143"/>
-      <c r="G34" s="105"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="126"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="105"/>
+      <c r="J34" s="126"/>
+      <c r="K34" s="126"/>
       <c r="L34" s="19"/>
-      <c r="M34" s="268"/>
+      <c r="M34" s="93"/>
       <c r="N34" s="19"/>
       <c r="O34" s="19"/>
       <c r="P34" s="19"/>
@@ -6157,21 +6152,21 @@
       <c r="R34" s="19"/>
       <c r="S34" s="19"/>
       <c r="T34" s="19"/>
-      <c r="U34" s="117"/>
-      <c r="V34" s="72"/>
-      <c r="W34" s="72"/>
-      <c r="X34" s="73"/>
-      <c r="Y34" s="72"/>
-      <c r="Z34" s="73"/>
-      <c r="AA34" s="72"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="240"/>
-      <c r="AD34" s="240"/>
-      <c r="AE34" s="240"/>
-      <c r="AF34" s="240"/>
-      <c r="AG34" s="240"/>
-      <c r="AH34" s="240"/>
-      <c r="AI34" s="240"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="70"/>
+      <c r="W34" s="70"/>
+      <c r="X34" s="71"/>
+      <c r="Y34" s="70"/>
+      <c r="Z34" s="71"/>
+      <c r="AA34" s="70"/>
+      <c r="AB34" s="71"/>
+      <c r="AC34" s="135"/>
+      <c r="AD34" s="135"/>
+      <c r="AE34" s="135"/>
+      <c r="AF34" s="135"/>
+      <c r="AG34" s="135"/>
+      <c r="AH34" s="135"/>
+      <c r="AI34" s="135"/>
       <c r="AJ34" s="55"/>
       <c r="AK34" s="55"/>
       <c r="AL34" s="55"/>
@@ -6185,34 +6180,34 @@
       <c r="AT34" s="55"/>
       <c r="AU34" s="55"/>
       <c r="AV34" s="55"/>
-      <c r="AW34" s="117"/>
-      <c r="AX34" s="72"/>
-      <c r="AY34" s="72"/>
-      <c r="AZ34" s="73"/>
+      <c r="AW34" s="69"/>
+      <c r="AX34" s="70"/>
+      <c r="AY34" s="70"/>
+      <c r="AZ34" s="71"/>
       <c r="BA34" s="18"/>
       <c r="BB34" s="19"/>
       <c r="BC34" s="19"/>
       <c r="BD34" s="19"/>
-      <c r="BE34" s="253"/>
-      <c r="BF34" s="254"/>
-      <c r="BG34" s="254"/>
-      <c r="BH34" s="255"/>
+      <c r="BE34" s="78"/>
+      <c r="BF34" s="79"/>
+      <c r="BG34" s="79"/>
+      <c r="BH34" s="80"/>
       <c r="BI34" s="19"/>
       <c r="BJ34" s="19"/>
-      <c r="BK34" s="224"/>
-      <c r="BL34" s="226"/>
-      <c r="BM34" s="224"/>
-      <c r="BN34" s="225"/>
-      <c r="BO34" s="225"/>
-      <c r="BP34" s="225"/>
-      <c r="BQ34" s="226"/>
-      <c r="BR34" s="224"/>
-      <c r="BS34" s="225"/>
-      <c r="BT34" s="225"/>
-      <c r="BU34" s="225"/>
-      <c r="BV34" s="226"/>
+      <c r="BK34" s="155"/>
+      <c r="BL34" s="157"/>
+      <c r="BM34" s="155"/>
+      <c r="BN34" s="156"/>
+      <c r="BO34" s="156"/>
+      <c r="BP34" s="156"/>
+      <c r="BQ34" s="157"/>
+      <c r="BR34" s="155"/>
+      <c r="BS34" s="156"/>
+      <c r="BT34" s="156"/>
+      <c r="BU34" s="156"/>
+      <c r="BV34" s="157"/>
     </row>
-    <row r="35" spans="1:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="B35" s="32"/>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
@@ -6225,30 +6220,30 @@
       <c r="K35" s="33"/>
       <c r="L35" s="33"/>
       <c r="M35" s="33"/>
-      <c r="N35" s="198" t="s">
+      <c r="N35" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="O35" s="198"/>
+      <c r="O35" s="128"/>
       <c r="P35" s="33"/>
       <c r="Q35" s="33"/>
       <c r="R35" s="33"/>
       <c r="S35" s="33"/>
       <c r="T35" s="33"/>
-      <c r="U35" s="119"/>
-      <c r="V35" s="74"/>
-      <c r="W35" s="74"/>
-      <c r="X35" s="75"/>
-      <c r="Y35" s="74"/>
-      <c r="Z35" s="75"/>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="75"/>
-      <c r="AC35" s="241"/>
-      <c r="AD35" s="241"/>
-      <c r="AE35" s="241"/>
-      <c r="AF35" s="241"/>
-      <c r="AG35" s="241"/>
-      <c r="AH35" s="241"/>
-      <c r="AI35" s="241"/>
+      <c r="U35" s="72"/>
+      <c r="V35" s="73"/>
+      <c r="W35" s="73"/>
+      <c r="X35" s="74"/>
+      <c r="Y35" s="73"/>
+      <c r="Z35" s="74"/>
+      <c r="AA35" s="73"/>
+      <c r="AB35" s="74"/>
+      <c r="AC35" s="136"/>
+      <c r="AD35" s="136"/>
+      <c r="AE35" s="136"/>
+      <c r="AF35" s="136"/>
+      <c r="AG35" s="136"/>
+      <c r="AH35" s="136"/>
+      <c r="AI35" s="136"/>
       <c r="AJ35" s="57"/>
       <c r="AK35" s="57"/>
       <c r="AL35" s="57"/>
@@ -6257,321 +6252,321 @@
       <c r="AO35" s="57"/>
       <c r="AP35" s="57"/>
       <c r="AQ35" s="57"/>
-      <c r="AR35" s="112" t="s">
+      <c r="AR35" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="AS35" s="113"/>
-      <c r="AT35" s="113"/>
-      <c r="AU35" s="113"/>
-      <c r="AV35" s="113"/>
-      <c r="AW35" s="119"/>
-      <c r="AX35" s="74"/>
-      <c r="AY35" s="74"/>
-      <c r="AZ35" s="75"/>
+      <c r="AS35" s="138"/>
+      <c r="AT35" s="138"/>
+      <c r="AU35" s="138"/>
+      <c r="AV35" s="138"/>
+      <c r="AW35" s="72"/>
+      <c r="AX35" s="73"/>
+      <c r="AY35" s="73"/>
+      <c r="AZ35" s="74"/>
       <c r="BA35" s="32"/>
       <c r="BB35" s="33"/>
       <c r="BC35" s="33"/>
       <c r="BD35" s="33"/>
-      <c r="BE35" s="256"/>
-      <c r="BF35" s="257"/>
-      <c r="BG35" s="257"/>
-      <c r="BH35" s="258"/>
+      <c r="BE35" s="81"/>
+      <c r="BF35" s="82"/>
+      <c r="BG35" s="82"/>
+      <c r="BH35" s="83"/>
       <c r="BI35" s="33"/>
       <c r="BJ35" s="33"/>
-      <c r="BK35" s="227"/>
-      <c r="BL35" s="229"/>
-      <c r="BM35" s="227"/>
-      <c r="BN35" s="228"/>
-      <c r="BO35" s="228"/>
-      <c r="BP35" s="228"/>
-      <c r="BQ35" s="229"/>
-      <c r="BR35" s="227"/>
-      <c r="BS35" s="228"/>
-      <c r="BT35" s="228"/>
-      <c r="BU35" s="228"/>
-      <c r="BV35" s="229"/>
+      <c r="BK35" s="158"/>
+      <c r="BL35" s="160"/>
+      <c r="BM35" s="158"/>
+      <c r="BN35" s="159"/>
+      <c r="BO35" s="159"/>
+      <c r="BP35" s="159"/>
+      <c r="BQ35" s="160"/>
+      <c r="BR35" s="158"/>
+      <c r="BS35" s="159"/>
+      <c r="BT35" s="159"/>
+      <c r="BU35" s="159"/>
+      <c r="BV35" s="160"/>
     </row>
-    <row r="36" spans="1:74" x14ac:dyDescent="0.3">
-      <c r="B36" s="114" t="s">
-        <v>306</v>
-      </c>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="115"/>
-      <c r="G36" s="129"/>
-      <c r="BQ36" s="114" t="s">
-        <v>306</v>
-      </c>
-      <c r="BR36" s="115"/>
-      <c r="BS36" s="115"/>
-      <c r="BT36" s="115"/>
-      <c r="BU36" s="115"/>
-      <c r="BV36" s="129"/>
+    <row r="36" spans="1:74">
+      <c r="B36" s="66" t="s">
+        <v>305</v>
+      </c>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="68"/>
+      <c r="BQ36" s="66" t="s">
+        <v>305</v>
+      </c>
+      <c r="BR36" s="67"/>
+      <c r="BS36" s="67"/>
+      <c r="BT36" s="67"/>
+      <c r="BU36" s="67"/>
+      <c r="BV36" s="68"/>
     </row>
-    <row r="37" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="117"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="73"/>
-      <c r="BQ37" s="117"/>
-      <c r="BR37" s="72"/>
-      <c r="BS37" s="72"/>
-      <c r="BT37" s="72"/>
-      <c r="BU37" s="72"/>
-      <c r="BV37" s="73"/>
+    <row r="37" spans="1:74" ht="17.25" thickBot="1">
+      <c r="B37" s="69"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="71"/>
+      <c r="BQ37" s="69"/>
+      <c r="BR37" s="70"/>
+      <c r="BS37" s="70"/>
+      <c r="BT37" s="70"/>
+      <c r="BU37" s="70"/>
+      <c r="BV37" s="71"/>
     </row>
-    <row r="38" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="117"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="73"/>
-      <c r="M38" s="232" t="s">
-        <v>254</v>
-      </c>
-      <c r="N38" s="233"/>
-      <c r="O38" s="233"/>
-      <c r="P38" s="233"/>
-      <c r="Q38" s="233"/>
-      <c r="R38" s="233"/>
-      <c r="S38" s="233"/>
-      <c r="T38" s="233"/>
-      <c r="U38" s="234"/>
-      <c r="AP38" s="198" t="s">
-        <v>240</v>
-      </c>
-      <c r="AQ38" s="198"/>
+    <row r="38" spans="1:74" ht="17.25" thickBot="1">
+      <c r="B38" s="69"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="71"/>
+      <c r="M38" s="107" t="s">
+        <v>253</v>
+      </c>
+      <c r="N38" s="108"/>
+      <c r="O38" s="108"/>
+      <c r="P38" s="108"/>
+      <c r="Q38" s="108"/>
+      <c r="R38" s="108"/>
+      <c r="S38" s="108"/>
+      <c r="T38" s="108"/>
+      <c r="U38" s="109"/>
+      <c r="AP38" s="128" t="s">
+        <v>239</v>
+      </c>
+      <c r="AQ38" s="128"/>
       <c r="AR38" s="52"/>
       <c r="AS38" s="52"/>
       <c r="AU38" s="52"/>
       <c r="AV38" s="52"/>
-      <c r="AW38" s="114" t="s">
-        <v>240</v>
-      </c>
-      <c r="AX38" s="129"/>
-      <c r="BE38" s="114" t="s">
-        <v>243</v>
-      </c>
-      <c r="BF38" s="115"/>
-      <c r="BG38" s="115"/>
-      <c r="BH38" s="129"/>
-      <c r="BQ38" s="117"/>
-      <c r="BR38" s="72"/>
-      <c r="BS38" s="72"/>
-      <c r="BT38" s="72"/>
-      <c r="BU38" s="72"/>
-      <c r="BV38" s="73"/>
+      <c r="AW38" s="66" t="s">
+        <v>239</v>
+      </c>
+      <c r="AX38" s="68"/>
+      <c r="BE38" s="66" t="s">
+        <v>242</v>
+      </c>
+      <c r="BF38" s="67"/>
+      <c r="BG38" s="67"/>
+      <c r="BH38" s="68"/>
+      <c r="BQ38" s="69"/>
+      <c r="BR38" s="70"/>
+      <c r="BS38" s="70"/>
+      <c r="BT38" s="70"/>
+      <c r="BU38" s="70"/>
+      <c r="BV38" s="71"/>
     </row>
-    <row r="39" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="75"/>
-      <c r="M39" s="235"/>
-      <c r="N39" s="159"/>
-      <c r="O39" s="159"/>
-      <c r="P39" s="159"/>
-      <c r="Q39" s="159"/>
-      <c r="R39" s="159"/>
-      <c r="S39" s="159"/>
-      <c r="T39" s="159"/>
-      <c r="U39" s="236"/>
-      <c r="AP39" s="198"/>
-      <c r="AQ39" s="198"/>
+    <row r="39" spans="1:74" ht="17.25" thickBot="1">
+      <c r="B39" s="72"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="74"/>
+      <c r="M39" s="110"/>
+      <c r="N39" s="111"/>
+      <c r="O39" s="111"/>
+      <c r="P39" s="111"/>
+      <c r="Q39" s="111"/>
+      <c r="R39" s="111"/>
+      <c r="S39" s="111"/>
+      <c r="T39" s="111"/>
+      <c r="U39" s="112"/>
+      <c r="AP39" s="128"/>
+      <c r="AQ39" s="128"/>
       <c r="AR39" s="52"/>
       <c r="AS39" s="52"/>
       <c r="AU39" s="52"/>
       <c r="AV39" s="52"/>
-      <c r="AW39" s="117"/>
-      <c r="AX39" s="73"/>
-      <c r="BE39" s="117"/>
-      <c r="BF39" s="72"/>
-      <c r="BG39" s="72"/>
-      <c r="BH39" s="73"/>
-      <c r="BQ39" s="119"/>
-      <c r="BR39" s="74"/>
-      <c r="BS39" s="74"/>
-      <c r="BT39" s="74"/>
-      <c r="BU39" s="74"/>
-      <c r="BV39" s="75"/>
+      <c r="AW39" s="69"/>
+      <c r="AX39" s="71"/>
+      <c r="BE39" s="69"/>
+      <c r="BF39" s="70"/>
+      <c r="BG39" s="70"/>
+      <c r="BH39" s="71"/>
+      <c r="BQ39" s="72"/>
+      <c r="BR39" s="73"/>
+      <c r="BS39" s="73"/>
+      <c r="BT39" s="73"/>
+      <c r="BU39" s="73"/>
+      <c r="BV39" s="74"/>
     </row>
-    <row r="40" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M40" s="237"/>
-      <c r="N40" s="231"/>
-      <c r="O40" s="231"/>
-      <c r="P40" s="231"/>
-      <c r="Q40" s="231"/>
-      <c r="R40" s="231"/>
-      <c r="S40" s="231"/>
-      <c r="T40" s="231"/>
-      <c r="U40" s="238"/>
-      <c r="AP40" s="198"/>
-      <c r="AQ40" s="198"/>
+    <row r="40" spans="1:74" ht="17.25" thickBot="1">
+      <c r="M40" s="113"/>
+      <c r="N40" s="114"/>
+      <c r="O40" s="114"/>
+      <c r="P40" s="114"/>
+      <c r="Q40" s="114"/>
+      <c r="R40" s="114"/>
+      <c r="S40" s="114"/>
+      <c r="T40" s="114"/>
+      <c r="U40" s="115"/>
+      <c r="AP40" s="128"/>
+      <c r="AQ40" s="128"/>
       <c r="AR40" s="52"/>
       <c r="AS40" s="52"/>
       <c r="AU40" s="52"/>
       <c r="AV40" s="52"/>
-      <c r="AW40" s="117"/>
-      <c r="AX40" s="73"/>
-      <c r="BE40" s="119"/>
-      <c r="BF40" s="74"/>
-      <c r="BG40" s="74"/>
-      <c r="BH40" s="75"/>
+      <c r="AW40" s="69"/>
+      <c r="AX40" s="71"/>
+      <c r="BE40" s="72"/>
+      <c r="BF40" s="73"/>
+      <c r="BG40" s="73"/>
+      <c r="BH40" s="74"/>
     </row>
-    <row r="41" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M41" s="232" t="s">
-        <v>255</v>
-      </c>
-      <c r="N41" s="233"/>
-      <c r="O41" s="233"/>
-      <c r="P41" s="233"/>
-      <c r="Q41" s="233"/>
-      <c r="R41" s="233"/>
-      <c r="S41" s="233"/>
-      <c r="T41" s="233"/>
-      <c r="U41" s="234"/>
-      <c r="AF41" s="232" t="s">
-        <v>241</v>
-      </c>
-      <c r="AG41" s="233"/>
-      <c r="AH41" s="233"/>
-      <c r="AI41" s="233"/>
-      <c r="AJ41" s="233"/>
-      <c r="AK41" s="234"/>
-      <c r="AP41" s="198"/>
-      <c r="AQ41" s="198"/>
+    <row r="41" spans="1:74" ht="17.25" thickBot="1">
+      <c r="M41" s="107" t="s">
+        <v>254</v>
+      </c>
+      <c r="N41" s="108"/>
+      <c r="O41" s="108"/>
+      <c r="P41" s="108"/>
+      <c r="Q41" s="108"/>
+      <c r="R41" s="108"/>
+      <c r="S41" s="108"/>
+      <c r="T41" s="108"/>
+      <c r="U41" s="109"/>
+      <c r="AF41" s="107" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG41" s="108"/>
+      <c r="AH41" s="108"/>
+      <c r="AI41" s="108"/>
+      <c r="AJ41" s="108"/>
+      <c r="AK41" s="109"/>
+      <c r="AP41" s="128"/>
+      <c r="AQ41" s="128"/>
       <c r="AR41" s="52"/>
       <c r="AS41" s="52"/>
       <c r="AU41" s="52"/>
       <c r="AV41" s="52"/>
-      <c r="AW41" s="117"/>
-      <c r="AX41" s="73"/>
-      <c r="BC41" s="232" t="s">
-        <v>242</v>
-      </c>
-      <c r="BD41" s="233"/>
-      <c r="BE41" s="233"/>
-      <c r="BF41" s="233"/>
-      <c r="BG41" s="233"/>
-      <c r="BH41" s="234"/>
+      <c r="AW41" s="69"/>
+      <c r="AX41" s="71"/>
+      <c r="BC41" s="107" t="s">
+        <v>241</v>
+      </c>
+      <c r="BD41" s="108"/>
+      <c r="BE41" s="108"/>
+      <c r="BF41" s="108"/>
+      <c r="BG41" s="108"/>
+      <c r="BH41" s="109"/>
     </row>
-    <row r="42" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="114" t="s">
-        <v>306</v>
-      </c>
-      <c r="C42" s="115"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="115"/>
-      <c r="F42" s="115"/>
-      <c r="G42" s="129"/>
-      <c r="M42" s="235"/>
-      <c r="N42" s="159"/>
-      <c r="O42" s="159"/>
-      <c r="P42" s="159"/>
-      <c r="Q42" s="159"/>
-      <c r="R42" s="159"/>
-      <c r="S42" s="159"/>
-      <c r="T42" s="159"/>
-      <c r="U42" s="236"/>
-      <c r="AF42" s="235"/>
-      <c r="AG42" s="159"/>
-      <c r="AH42" s="159"/>
-      <c r="AI42" s="159"/>
-      <c r="AJ42" s="159"/>
-      <c r="AK42" s="236"/>
-      <c r="AP42" s="198"/>
-      <c r="AQ42" s="198"/>
+    <row r="42" spans="1:74" ht="17.25" thickBot="1">
+      <c r="B42" s="66" t="s">
+        <v>305</v>
+      </c>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="68"/>
+      <c r="M42" s="110"/>
+      <c r="N42" s="111"/>
+      <c r="O42" s="111"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="111"/>
+      <c r="S42" s="111"/>
+      <c r="T42" s="111"/>
+      <c r="U42" s="112"/>
+      <c r="AF42" s="110"/>
+      <c r="AG42" s="111"/>
+      <c r="AH42" s="111"/>
+      <c r="AI42" s="111"/>
+      <c r="AJ42" s="111"/>
+      <c r="AK42" s="112"/>
+      <c r="AP42" s="128"/>
+      <c r="AQ42" s="128"/>
       <c r="AR42" s="52"/>
       <c r="AS42" s="52"/>
       <c r="AU42" s="52"/>
       <c r="AV42" s="52"/>
-      <c r="AW42" s="117"/>
-      <c r="AX42" s="73"/>
-      <c r="BC42" s="235"/>
-      <c r="BD42" s="159"/>
-      <c r="BE42" s="159"/>
-      <c r="BF42" s="159"/>
-      <c r="BG42" s="159"/>
-      <c r="BH42" s="236"/>
-      <c r="BQ42" s="114" t="s">
-        <v>306</v>
-      </c>
-      <c r="BR42" s="115"/>
-      <c r="BS42" s="115"/>
-      <c r="BT42" s="115"/>
-      <c r="BU42" s="115"/>
-      <c r="BV42" s="129"/>
+      <c r="AW42" s="69"/>
+      <c r="AX42" s="71"/>
+      <c r="BC42" s="110"/>
+      <c r="BD42" s="111"/>
+      <c r="BE42" s="111"/>
+      <c r="BF42" s="111"/>
+      <c r="BG42" s="111"/>
+      <c r="BH42" s="112"/>
+      <c r="BQ42" s="66" t="s">
+        <v>305</v>
+      </c>
+      <c r="BR42" s="67"/>
+      <c r="BS42" s="67"/>
+      <c r="BT42" s="67"/>
+      <c r="BU42" s="67"/>
+      <c r="BV42" s="68"/>
     </row>
-    <row r="43" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="117"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="73"/>
-      <c r="M43" s="237"/>
-      <c r="N43" s="231"/>
-      <c r="O43" s="231"/>
-      <c r="P43" s="231"/>
-      <c r="Q43" s="231"/>
-      <c r="R43" s="231"/>
-      <c r="S43" s="231"/>
-      <c r="T43" s="231"/>
-      <c r="U43" s="238"/>
-      <c r="AF43" s="237"/>
-      <c r="AG43" s="231"/>
-      <c r="AH43" s="231"/>
-      <c r="AI43" s="231"/>
-      <c r="AJ43" s="231"/>
-      <c r="AK43" s="238"/>
-      <c r="AP43" s="198"/>
-      <c r="AQ43" s="198"/>
+    <row r="43" spans="1:74" ht="17.25" thickBot="1">
+      <c r="B43" s="69"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71"/>
+      <c r="M43" s="113"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="114"/>
+      <c r="Q43" s="114"/>
+      <c r="R43" s="114"/>
+      <c r="S43" s="114"/>
+      <c r="T43" s="114"/>
+      <c r="U43" s="115"/>
+      <c r="AF43" s="113"/>
+      <c r="AG43" s="114"/>
+      <c r="AH43" s="114"/>
+      <c r="AI43" s="114"/>
+      <c r="AJ43" s="114"/>
+      <c r="AK43" s="115"/>
+      <c r="AP43" s="128"/>
+      <c r="AQ43" s="128"/>
       <c r="AR43" s="52"/>
       <c r="AS43" s="52"/>
       <c r="AU43" s="52"/>
       <c r="AV43" s="52"/>
-      <c r="AW43" s="119"/>
-      <c r="AX43" s="75"/>
-      <c r="BC43" s="237"/>
-      <c r="BD43" s="231"/>
-      <c r="BE43" s="231"/>
-      <c r="BF43" s="231"/>
-      <c r="BG43" s="231"/>
-      <c r="BH43" s="238"/>
-      <c r="BQ43" s="117"/>
-      <c r="BR43" s="72"/>
-      <c r="BS43" s="72"/>
-      <c r="BT43" s="72"/>
-      <c r="BU43" s="72"/>
-      <c r="BV43" s="73"/>
+      <c r="AW43" s="72"/>
+      <c r="AX43" s="74"/>
+      <c r="BC43" s="113"/>
+      <c r="BD43" s="114"/>
+      <c r="BE43" s="114"/>
+      <c r="BF43" s="114"/>
+      <c r="BG43" s="114"/>
+      <c r="BH43" s="115"/>
+      <c r="BQ43" s="69"/>
+      <c r="BR43" s="70"/>
+      <c r="BS43" s="70"/>
+      <c r="BT43" s="70"/>
+      <c r="BU43" s="70"/>
+      <c r="BV43" s="71"/>
     </row>
-    <row r="44" spans="1:74" x14ac:dyDescent="0.3">
-      <c r="B44" s="117"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="73"/>
-      <c r="BQ44" s="117"/>
-      <c r="BR44" s="72"/>
-      <c r="BS44" s="72"/>
-      <c r="BT44" s="72"/>
-      <c r="BU44" s="72"/>
-      <c r="BV44" s="73"/>
+    <row r="44" spans="1:74">
+      <c r="B44" s="69"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="71"/>
+      <c r="BQ44" s="69"/>
+      <c r="BR44" s="70"/>
+      <c r="BS44" s="70"/>
+      <c r="BT44" s="70"/>
+      <c r="BU44" s="70"/>
+      <c r="BV44" s="71"/>
     </row>
-    <row r="45" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="119"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="75"/>
+    <row r="45" spans="1:74" ht="17.25" thickBot="1">
+      <c r="B45" s="72"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
+      <c r="G45" s="74"/>
       <c r="H45" s="33"/>
       <c r="I45" s="33"/>
       <c r="J45" s="33"/>
@@ -6582,14 +6577,14 @@
       <c r="Q45" s="33"/>
       <c r="R45" s="33"/>
       <c r="S45" s="33"/>
-      <c r="BQ45" s="119"/>
-      <c r="BR45" s="74"/>
-      <c r="BS45" s="74"/>
-      <c r="BT45" s="74"/>
-      <c r="BU45" s="74"/>
-      <c r="BV45" s="75"/>
+      <c r="BQ45" s="72"/>
+      <c r="BR45" s="73"/>
+      <c r="BS45" s="73"/>
+      <c r="BT45" s="73"/>
+      <c r="BU45" s="73"/>
+      <c r="BV45" s="74"/>
     </row>
-    <row r="46" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:74" ht="17.25" thickBot="1">
       <c r="A46" s="19"/>
       <c r="B46" s="23"/>
       <c r="C46" s="16"/>
@@ -6603,107 +6598,107 @@
       <c r="K46" s="16"/>
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
-      <c r="N46" s="198" t="s">
+      <c r="N46" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="O46" s="198"/>
-      <c r="T46" s="112" t="s">
+      <c r="O46" s="128"/>
+      <c r="T46" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="U46" s="113"/>
-      <c r="V46" s="113"/>
-      <c r="W46" s="113"/>
-      <c r="X46" s="113"/>
-      <c r="Y46" s="114" t="s">
+      <c r="U46" s="138"/>
+      <c r="V46" s="138"/>
+      <c r="W46" s="138"/>
+      <c r="X46" s="138"/>
+      <c r="Y46" s="66" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z46" s="67"/>
+      <c r="AA46" s="67"/>
+      <c r="AB46" s="67"/>
+      <c r="AC46" s="248"/>
+      <c r="AD46" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="Z46" s="115"/>
-      <c r="AA46" s="115"/>
-      <c r="AB46" s="115"/>
-      <c r="AC46" s="116"/>
-      <c r="AD46" s="115" t="s">
+      <c r="AE46" s="248"/>
+      <c r="AF46" s="251" t="s">
         <v>232</v>
       </c>
-      <c r="AE46" s="116"/>
-      <c r="AF46" s="127" t="s">
+      <c r="AG46" s="67"/>
+      <c r="AH46" s="67"/>
+      <c r="AI46" s="67"/>
+      <c r="AJ46" s="251" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK46" s="67"/>
+      <c r="AL46" s="67"/>
+      <c r="AM46" s="67"/>
+      <c r="AN46" s="67"/>
+      <c r="AO46" s="67"/>
+      <c r="AP46" s="67"/>
+      <c r="AQ46" s="68"/>
+      <c r="AR46" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="138"/>
+      <c r="AT46" s="138"/>
+      <c r="AU46" s="138"/>
+      <c r="AV46" s="253"/>
+      <c r="AW46" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX46" s="67"/>
+      <c r="AY46" s="67"/>
+      <c r="AZ46" s="251" t="s">
         <v>233</v>
       </c>
-      <c r="AG46" s="115"/>
-      <c r="AH46" s="115"/>
-      <c r="AI46" s="115"/>
-      <c r="AJ46" s="127" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK46" s="115"/>
-      <c r="AL46" s="115"/>
-      <c r="AM46" s="115"/>
-      <c r="AN46" s="115"/>
-      <c r="AO46" s="115"/>
-      <c r="AP46" s="115"/>
-      <c r="AQ46" s="129"/>
-      <c r="AR46" s="112" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS46" s="113"/>
-      <c r="AT46" s="113"/>
-      <c r="AU46" s="113"/>
-      <c r="AV46" s="130"/>
-      <c r="AW46" s="114" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX46" s="115"/>
-      <c r="AY46" s="115"/>
-      <c r="AZ46" s="127" t="s">
+      <c r="BA46" s="67"/>
+      <c r="BB46" s="67"/>
+      <c r="BC46" s="248"/>
+      <c r="BD46" s="241" t="s">
+        <v>107</v>
+      </c>
+      <c r="BE46" s="242"/>
+      <c r="BF46" s="242"/>
+      <c r="BG46" s="242"/>
+      <c r="BH46" s="242"/>
+      <c r="BI46" s="241" t="s">
+        <v>3</v>
+      </c>
+      <c r="BJ46" s="242"/>
+      <c r="BK46" s="242"/>
+      <c r="BL46" s="245"/>
+      <c r="BM46" s="263" t="s">
         <v>234</v>
       </c>
-      <c r="BA46" s="115"/>
-      <c r="BB46" s="115"/>
-      <c r="BC46" s="116"/>
-      <c r="BD46" s="123" t="s">
-        <v>3</v>
-      </c>
-      <c r="BE46" s="77"/>
-      <c r="BF46" s="77"/>
-      <c r="BG46" s="77"/>
-      <c r="BH46" s="77"/>
-      <c r="BI46" s="123" t="s">
-        <v>4</v>
-      </c>
-      <c r="BJ46" s="77"/>
-      <c r="BK46" s="77"/>
-      <c r="BL46" s="124"/>
-      <c r="BM46" s="76" t="s">
+      <c r="BN46" s="242"/>
+      <c r="BO46" s="242"/>
+      <c r="BP46" s="242"/>
+      <c r="BQ46" s="264"/>
+      <c r="BR46" s="269" t="s">
         <v>235</v>
       </c>
-      <c r="BN46" s="77"/>
-      <c r="BO46" s="77"/>
-      <c r="BP46" s="77"/>
-      <c r="BQ46" s="78"/>
-      <c r="BR46" s="85" t="s">
-        <v>236</v>
-      </c>
-      <c r="BS46" s="86"/>
-      <c r="BT46" s="86"/>
-      <c r="BU46" s="86"/>
-      <c r="BV46" s="87"/>
+      <c r="BS46" s="270"/>
+      <c r="BT46" s="270"/>
+      <c r="BU46" s="270"/>
+      <c r="BV46" s="271"/>
     </row>
-    <row r="47" spans="1:74" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:74" ht="20.25">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
-      <c r="C47" s="72" t="s">
+      <c r="C47" s="70" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="72"/>
-      <c r="I47" s="72"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="L47" s="72"/>
+      <c r="L47" s="70"/>
       <c r="M47" s="19"/>
       <c r="N47" s="19"/>
       <c r="O47" s="24"/>
@@ -6711,154 +6706,154 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
-      <c r="Y47" s="117"/>
-      <c r="Z47" s="72"/>
-      <c r="AA47" s="72"/>
-      <c r="AB47" s="72"/>
-      <c r="AC47" s="118"/>
-      <c r="AD47" s="72"/>
-      <c r="AE47" s="118"/>
-      <c r="AF47" s="122"/>
-      <c r="AG47" s="72"/>
-      <c r="AH47" s="72"/>
-      <c r="AI47" s="72"/>
-      <c r="AJ47" s="122"/>
-      <c r="AK47" s="72"/>
-      <c r="AL47" s="72"/>
-      <c r="AM47" s="72"/>
-      <c r="AN47" s="72"/>
-      <c r="AO47" s="72"/>
-      <c r="AP47" s="72"/>
-      <c r="AQ47" s="73"/>
-      <c r="AW47" s="117"/>
-      <c r="AX47" s="72"/>
-      <c r="AY47" s="72"/>
-      <c r="AZ47" s="122"/>
-      <c r="BA47" s="72"/>
-      <c r="BB47" s="72"/>
-      <c r="BC47" s="118"/>
-      <c r="BD47" s="80"/>
-      <c r="BE47" s="80"/>
-      <c r="BF47" s="80"/>
-      <c r="BG47" s="80"/>
-      <c r="BH47" s="80"/>
-      <c r="BI47" s="80"/>
-      <c r="BJ47" s="80"/>
-      <c r="BK47" s="80"/>
-      <c r="BL47" s="125"/>
-      <c r="BM47" s="79"/>
-      <c r="BN47" s="80"/>
-      <c r="BO47" s="80"/>
-      <c r="BP47" s="80"/>
-      <c r="BQ47" s="81"/>
-      <c r="BR47" s="88"/>
-      <c r="BS47" s="89"/>
-      <c r="BT47" s="89"/>
-      <c r="BU47" s="89"/>
-      <c r="BV47" s="90"/>
+      <c r="Y47" s="69"/>
+      <c r="Z47" s="70"/>
+      <c r="AA47" s="70"/>
+      <c r="AB47" s="70"/>
+      <c r="AC47" s="249"/>
+      <c r="AD47" s="70"/>
+      <c r="AE47" s="249"/>
+      <c r="AF47" s="240"/>
+      <c r="AG47" s="70"/>
+      <c r="AH47" s="70"/>
+      <c r="AI47" s="70"/>
+      <c r="AJ47" s="240"/>
+      <c r="AK47" s="70"/>
+      <c r="AL47" s="70"/>
+      <c r="AM47" s="70"/>
+      <c r="AN47" s="70"/>
+      <c r="AO47" s="70"/>
+      <c r="AP47" s="70"/>
+      <c r="AQ47" s="71"/>
+      <c r="AW47" s="69"/>
+      <c r="AX47" s="70"/>
+      <c r="AY47" s="70"/>
+      <c r="AZ47" s="240"/>
+      <c r="BA47" s="70"/>
+      <c r="BB47" s="70"/>
+      <c r="BC47" s="249"/>
+      <c r="BD47" s="243"/>
+      <c r="BE47" s="243"/>
+      <c r="BF47" s="243"/>
+      <c r="BG47" s="243"/>
+      <c r="BH47" s="243"/>
+      <c r="BI47" s="243"/>
+      <c r="BJ47" s="243"/>
+      <c r="BK47" s="243"/>
+      <c r="BL47" s="246"/>
+      <c r="BM47" s="265"/>
+      <c r="BN47" s="243"/>
+      <c r="BO47" s="243"/>
+      <c r="BP47" s="243"/>
+      <c r="BQ47" s="266"/>
+      <c r="BR47" s="234"/>
+      <c r="BS47" s="232"/>
+      <c r="BT47" s="232"/>
+      <c r="BU47" s="232"/>
+      <c r="BV47" s="233"/>
     </row>
-    <row r="48" spans="1:74" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:74" ht="33.75" customHeight="1" thickBot="1">
       <c r="A48" s="19"/>
       <c r="B48" s="18"/>
       <c r="C48" s="52"/>
       <c r="D48" s="52"/>
-      <c r="E48" s="121" t="s">
+      <c r="E48" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="F48" s="63"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="I48" s="63"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="F48" s="121"/>
-      <c r="G48" s="52"/>
-      <c r="H48" s="121" t="s">
-        <v>112</v>
-      </c>
-      <c r="I48" s="121"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="121" t="s">
-        <v>114</v>
-      </c>
-      <c r="L48" s="121"/>
+      <c r="L48" s="63"/>
       <c r="M48" s="19"/>
       <c r="N48" s="19"/>
       <c r="O48" s="34"/>
       <c r="P48" s="3"/>
-      <c r="Y48" s="119"/>
-      <c r="Z48" s="74"/>
-      <c r="AA48" s="74"/>
-      <c r="AB48" s="74"/>
-      <c r="AC48" s="120"/>
-      <c r="AD48" s="74"/>
-      <c r="AE48" s="120"/>
-      <c r="AF48" s="128"/>
-      <c r="AG48" s="74"/>
-      <c r="AH48" s="74"/>
-      <c r="AI48" s="74"/>
-      <c r="AJ48" s="128"/>
-      <c r="AK48" s="74"/>
-      <c r="AL48" s="74"/>
-      <c r="AM48" s="74"/>
-      <c r="AN48" s="74"/>
-      <c r="AO48" s="74"/>
-      <c r="AP48" s="74"/>
-      <c r="AQ48" s="75"/>
-      <c r="AW48" s="119"/>
-      <c r="AX48" s="74"/>
-      <c r="AY48" s="74"/>
-      <c r="AZ48" s="128"/>
-      <c r="BA48" s="74"/>
-      <c r="BB48" s="74"/>
-      <c r="BC48" s="120"/>
-      <c r="BD48" s="83"/>
-      <c r="BE48" s="83"/>
-      <c r="BF48" s="83"/>
-      <c r="BG48" s="83"/>
-      <c r="BH48" s="83"/>
-      <c r="BI48" s="83"/>
-      <c r="BJ48" s="83"/>
-      <c r="BK48" s="83"/>
-      <c r="BL48" s="126"/>
-      <c r="BM48" s="82"/>
-      <c r="BN48" s="83"/>
-      <c r="BO48" s="83"/>
-      <c r="BP48" s="83"/>
-      <c r="BQ48" s="84"/>
-      <c r="BR48" s="88"/>
-      <c r="BS48" s="89"/>
-      <c r="BT48" s="89"/>
-      <c r="BU48" s="89"/>
-      <c r="BV48" s="90"/>
+      <c r="Y48" s="72"/>
+      <c r="Z48" s="73"/>
+      <c r="AA48" s="73"/>
+      <c r="AB48" s="73"/>
+      <c r="AC48" s="250"/>
+      <c r="AD48" s="73"/>
+      <c r="AE48" s="250"/>
+      <c r="AF48" s="252"/>
+      <c r="AG48" s="73"/>
+      <c r="AH48" s="73"/>
+      <c r="AI48" s="73"/>
+      <c r="AJ48" s="252"/>
+      <c r="AK48" s="73"/>
+      <c r="AL48" s="73"/>
+      <c r="AM48" s="73"/>
+      <c r="AN48" s="73"/>
+      <c r="AO48" s="73"/>
+      <c r="AP48" s="73"/>
+      <c r="AQ48" s="74"/>
+      <c r="AW48" s="72"/>
+      <c r="AX48" s="73"/>
+      <c r="AY48" s="73"/>
+      <c r="AZ48" s="252"/>
+      <c r="BA48" s="73"/>
+      <c r="BB48" s="73"/>
+      <c r="BC48" s="250"/>
+      <c r="BD48" s="244"/>
+      <c r="BE48" s="244"/>
+      <c r="BF48" s="244"/>
+      <c r="BG48" s="244"/>
+      <c r="BH48" s="244"/>
+      <c r="BI48" s="244"/>
+      <c r="BJ48" s="244"/>
+      <c r="BK48" s="244"/>
+      <c r="BL48" s="247"/>
+      <c r="BM48" s="267"/>
+      <c r="BN48" s="244"/>
+      <c r="BO48" s="244"/>
+      <c r="BP48" s="244"/>
+      <c r="BQ48" s="268"/>
+      <c r="BR48" s="234"/>
+      <c r="BS48" s="232"/>
+      <c r="BT48" s="232"/>
+      <c r="BU48" s="232"/>
+      <c r="BV48" s="233"/>
     </row>
-    <row r="49" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:74" ht="17.25" thickBot="1">
       <c r="A49" s="19"/>
       <c r="B49" s="18"/>
-      <c r="C49" s="199"/>
-      <c r="D49" s="137" t="s">
+      <c r="C49" s="127"/>
+      <c r="D49" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="E49" s="131" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49" s="130" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="19"/>
+      <c r="H49" s="132" t="s">
+        <v>89</v>
+      </c>
+      <c r="I49" s="198" t="s">
+        <v>97</v>
+      </c>
+      <c r="J49" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="E49" s="200" t="s">
-        <v>83</v>
-      </c>
-      <c r="F49" s="193" t="s">
-        <v>89</v>
-      </c>
-      <c r="G49" s="19"/>
-      <c r="H49" s="196" t="s">
-        <v>90</v>
-      </c>
-      <c r="I49" s="201" t="s">
+      <c r="K49" s="199"/>
+      <c r="L49" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="J49" s="137" t="s">
+      <c r="M49" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="K49" s="202"/>
-      <c r="L49" s="191" t="s">
-        <v>99</v>
-      </c>
-      <c r="M49" s="122" t="s">
-        <v>111</v>
-      </c>
       <c r="N49" s="19"/>
-      <c r="O49" s="192" t="s">
-        <v>105</v>
+      <c r="O49" s="200" t="s">
+        <v>104</v>
       </c>
       <c r="P49" s="3"/>
       <c r="Y49" s="5"/>
@@ -6896,28 +6891,28 @@
       <c r="BO49" s="5"/>
       <c r="BP49" s="5"/>
       <c r="BQ49" s="5"/>
-      <c r="BR49" s="88"/>
-      <c r="BS49" s="89"/>
-      <c r="BT49" s="89"/>
-      <c r="BU49" s="89"/>
-      <c r="BV49" s="90"/>
+      <c r="BR49" s="234"/>
+      <c r="BS49" s="232"/>
+      <c r="BT49" s="232"/>
+      <c r="BU49" s="232"/>
+      <c r="BV49" s="233"/>
     </row>
-    <row r="50" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:74" ht="17.25" thickBot="1">
       <c r="A50" s="19"/>
       <c r="B50" s="18"/>
-      <c r="C50" s="199"/>
-      <c r="D50" s="137"/>
-      <c r="E50" s="200"/>
-      <c r="F50" s="193"/>
+      <c r="C50" s="127"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="131"/>
+      <c r="F50" s="130"/>
       <c r="G50" s="19"/>
-      <c r="H50" s="196"/>
-      <c r="I50" s="201"/>
-      <c r="J50" s="137"/>
-      <c r="K50" s="202"/>
-      <c r="L50" s="191"/>
-      <c r="M50" s="122"/>
+      <c r="H50" s="132"/>
+      <c r="I50" s="198"/>
+      <c r="J50" s="64"/>
+      <c r="K50" s="199"/>
+      <c r="L50" s="129"/>
+      <c r="M50" s="240"/>
       <c r="N50" s="19"/>
-      <c r="O50" s="192"/>
+      <c r="O50" s="200"/>
       <c r="P50" s="3"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
@@ -6954,70 +6949,70 @@
       <c r="BO50" s="5"/>
       <c r="BP50" s="5"/>
       <c r="BQ50" s="5"/>
-      <c r="BR50" s="88"/>
-      <c r="BS50" s="89"/>
-      <c r="BT50" s="89"/>
-      <c r="BU50" s="89"/>
-      <c r="BV50" s="90"/>
+      <c r="BR50" s="234"/>
+      <c r="BS50" s="232"/>
+      <c r="BT50" s="232"/>
+      <c r="BU50" s="232"/>
+      <c r="BV50" s="233"/>
     </row>
-    <row r="51" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:74" ht="17.25" thickBot="1">
       <c r="A51" s="19"/>
       <c r="B51" s="18"/>
-      <c r="C51" s="199"/>
+      <c r="C51" s="127"/>
       <c r="D51" s="19"/>
-      <c r="E51" s="200"/>
-      <c r="F51" s="193"/>
+      <c r="E51" s="131"/>
+      <c r="F51" s="130"/>
       <c r="G51" s="19"/>
-      <c r="H51" s="196"/>
-      <c r="I51" s="201"/>
+      <c r="H51" s="132"/>
+      <c r="I51" s="198"/>
       <c r="J51" s="19"/>
-      <c r="K51" s="202"/>
-      <c r="L51" s="191"/>
+      <c r="K51" s="199"/>
+      <c r="L51" s="129"/>
       <c r="M51" s="19"/>
       <c r="N51" s="19"/>
-      <c r="O51" s="192"/>
-      <c r="AZ51" s="131" t="s">
-        <v>269</v>
-      </c>
-      <c r="BA51" s="131"/>
-      <c r="BH51" s="131" t="s">
-        <v>273</v>
-      </c>
-      <c r="BK51" s="131" t="s">
-        <v>275</v>
-      </c>
-      <c r="BR51" s="88"/>
-      <c r="BS51" s="89"/>
-      <c r="BT51" s="89"/>
-      <c r="BU51" s="89"/>
-      <c r="BV51" s="90"/>
+      <c r="O51" s="200"/>
+      <c r="AZ51" s="103" t="s">
+        <v>268</v>
+      </c>
+      <c r="BA51" s="103"/>
+      <c r="BH51" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="BK51" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="BR51" s="234"/>
+      <c r="BS51" s="232"/>
+      <c r="BT51" s="232"/>
+      <c r="BU51" s="232"/>
+      <c r="BV51" s="233"/>
     </row>
-    <row r="52" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:74" ht="17.25" thickBot="1">
       <c r="A52" s="19"/>
       <c r="B52" s="18"/>
-      <c r="C52" s="199"/>
+      <c r="C52" s="127"/>
       <c r="D52" s="19"/>
-      <c r="E52" s="200" t="s">
-        <v>84</v>
-      </c>
-      <c r="F52" s="193" t="s">
-        <v>88</v>
+      <c r="E52" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" s="130" t="s">
+        <v>87</v>
       </c>
       <c r="G52" s="19"/>
-      <c r="H52" s="196" t="s">
-        <v>91</v>
-      </c>
-      <c r="I52" s="201" t="s">
-        <v>97</v>
+      <c r="H52" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="I52" s="198" t="s">
+        <v>96</v>
       </c>
       <c r="J52" s="19"/>
-      <c r="K52" s="197" t="s">
-        <v>100</v>
-      </c>
-      <c r="L52" s="202"/>
+      <c r="K52" s="133" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="199"/>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
-      <c r="O52" s="192"/>
+      <c r="O52" s="200"/>
       <c r="R52" s="26"/>
       <c r="V52" s="6"/>
       <c r="Y52" s="6"/>
@@ -7035,844 +7030,844 @@
       <c r="AW52" s="6"/>
       <c r="AX52" s="6"/>
       <c r="AY52" s="6"/>
-      <c r="AZ52" s="121"/>
-      <c r="BA52" s="121"/>
+      <c r="AZ52" s="63"/>
+      <c r="BA52" s="63"/>
       <c r="BB52" s="6"/>
       <c r="BE52" s="6"/>
       <c r="BF52" s="6"/>
       <c r="BG52" s="6"/>
-      <c r="BH52" s="121"/>
+      <c r="BH52" s="63"/>
       <c r="BJ52" s="6"/>
-      <c r="BK52" s="121"/>
-      <c r="BR52" s="88"/>
-      <c r="BS52" s="89"/>
-      <c r="BT52" s="89"/>
-      <c r="BU52" s="89"/>
-      <c r="BV52" s="90"/>
+      <c r="BK52" s="63"/>
+      <c r="BR52" s="234"/>
+      <c r="BS52" s="232"/>
+      <c r="BT52" s="232"/>
+      <c r="BU52" s="232"/>
+      <c r="BV52" s="233"/>
     </row>
-    <row r="53" spans="1:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="A53" s="19"/>
       <c r="B53" s="18"/>
-      <c r="C53" s="199"/>
+      <c r="C53" s="127"/>
       <c r="D53" s="19"/>
-      <c r="E53" s="200"/>
-      <c r="F53" s="193"/>
+      <c r="E53" s="131"/>
+      <c r="F53" s="130"/>
       <c r="G53" s="19"/>
-      <c r="H53" s="196"/>
-      <c r="I53" s="201"/>
+      <c r="H53" s="132"/>
+      <c r="I53" s="198"/>
       <c r="J53" s="19"/>
-      <c r="K53" s="197"/>
-      <c r="L53" s="202"/>
+      <c r="K53" s="133"/>
+      <c r="L53" s="199"/>
       <c r="M53" s="19"/>
       <c r="N53" s="19"/>
-      <c r="O53" s="192"/>
+      <c r="O53" s="200"/>
       <c r="R53" s="26"/>
       <c r="S53" s="42"/>
-      <c r="T53" s="103"/>
-      <c r="U53" s="94"/>
+      <c r="T53" s="124"/>
+      <c r="U53" s="100"/>
       <c r="V53" s="6"/>
-      <c r="W53" s="106" t="s">
-        <v>263</v>
-      </c>
-      <c r="X53" s="106"/>
+      <c r="W53" s="142" t="s">
+        <v>262</v>
+      </c>
+      <c r="X53" s="142"/>
       <c r="Y53" s="6"/>
       <c r="Z53" s="42"/>
       <c r="AA53" s="6"/>
-      <c r="AB53" s="106" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC53" s="103"/>
+      <c r="AB53" s="142" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC53" s="124"/>
       <c r="AD53" s="6"/>
-      <c r="AE53" s="103"/>
-      <c r="AF53" s="103"/>
+      <c r="AE53" s="124"/>
+      <c r="AF53" s="124"/>
       <c r="AG53" s="6"/>
       <c r="AH53" s="42"/>
       <c r="AI53" s="6"/>
-      <c r="AJ53" s="94"/>
-      <c r="AK53" s="94"/>
+      <c r="AJ53" s="100"/>
+      <c r="AK53" s="100"/>
       <c r="AL53" s="6"/>
-      <c r="AM53" s="132" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN53" s="94"/>
+      <c r="AM53" s="145" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN53" s="100"/>
       <c r="AO53" s="6"/>
       <c r="AP53" s="42"/>
       <c r="AQ53" s="6"/>
-      <c r="AR53" s="109" t="s">
+      <c r="AR53" s="224" t="s">
+        <v>6</v>
+      </c>
+      <c r="AS53" s="224" t="s">
+        <v>302</v>
+      </c>
+      <c r="AT53" s="6"/>
+      <c r="AU53" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="AS53" s="109" t="s">
-        <v>303</v>
-      </c>
-      <c r="AT53" s="6"/>
-      <c r="AU53" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV53" s="94"/>
+      <c r="AV53" s="100"/>
       <c r="AW53" s="6"/>
       <c r="AX53" s="42"/>
       <c r="AY53" s="6"/>
-      <c r="AZ53" s="91" t="s">
+      <c r="AZ53" s="228" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA53" s="228" t="s">
+        <v>236</v>
+      </c>
+      <c r="BB53" s="6"/>
+      <c r="BC53" s="228" t="s">
         <v>9</v>
       </c>
-      <c r="BA53" s="91" t="s">
-        <v>237</v>
-      </c>
-      <c r="BB53" s="6"/>
-      <c r="BC53" s="91" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD53" s="94"/>
+      <c r="BD53" s="100"/>
       <c r="BE53" s="6"/>
       <c r="BF53" s="42"/>
       <c r="BG53" s="6"/>
-      <c r="BH53" s="97" t="s">
+      <c r="BH53" s="193" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI53" s="193" t="s">
         <v>11</v>
       </c>
-      <c r="BI53" s="97" t="s">
+      <c r="BJ53" s="6"/>
+      <c r="BK53" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="BJ53" s="6"/>
-      <c r="BK53" s="164" t="s">
+      <c r="BL53" s="217" t="s">
         <v>13</v>
       </c>
-      <c r="BL53" s="160" t="s">
-        <v>14</v>
-      </c>
       <c r="BN53" s="42"/>
-      <c r="BR53" s="88"/>
-      <c r="BS53" s="89"/>
-      <c r="BT53" s="89"/>
-      <c r="BU53" s="89"/>
-      <c r="BV53" s="90"/>
+      <c r="BR53" s="234"/>
+      <c r="BS53" s="232"/>
+      <c r="BT53" s="232"/>
+      <c r="BU53" s="232"/>
+      <c r="BV53" s="233"/>
     </row>
-    <row r="54" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:74" ht="17.25" thickBot="1">
       <c r="A54" s="19"/>
       <c r="B54" s="18"/>
-      <c r="C54" s="199"/>
+      <c r="C54" s="127"/>
       <c r="D54" s="19"/>
-      <c r="E54" s="200"/>
-      <c r="F54" s="193"/>
+      <c r="E54" s="131"/>
+      <c r="F54" s="130"/>
       <c r="G54" s="19"/>
-      <c r="H54" s="196"/>
-      <c r="I54" s="201"/>
+      <c r="H54" s="132"/>
+      <c r="I54" s="198"/>
       <c r="J54" s="19"/>
-      <c r="K54" s="197"/>
-      <c r="L54" s="202"/>
+      <c r="K54" s="133"/>
+      <c r="L54" s="199"/>
       <c r="M54" s="19"/>
       <c r="N54" s="19"/>
-      <c r="O54" s="192"/>
+      <c r="O54" s="200"/>
       <c r="Q54" s="6"/>
       <c r="R54" s="26"/>
-      <c r="T54" s="104"/>
-      <c r="U54" s="95"/>
+      <c r="T54" s="125"/>
+      <c r="U54" s="101"/>
       <c r="V54" s="6"/>
-      <c r="W54" s="107"/>
-      <c r="X54" s="107"/>
+      <c r="W54" s="143"/>
+      <c r="X54" s="143"/>
       <c r="Y54" s="7"/>
       <c r="Z54" s="6"/>
       <c r="AA54" s="6"/>
-      <c r="AB54" s="107"/>
-      <c r="AC54" s="104"/>
+      <c r="AB54" s="143"/>
+      <c r="AC54" s="125"/>
       <c r="AD54" s="7"/>
-      <c r="AE54" s="104"/>
-      <c r="AF54" s="104"/>
+      <c r="AE54" s="125"/>
+      <c r="AF54" s="125"/>
       <c r="AG54" s="6"/>
       <c r="AH54" s="6"/>
       <c r="AI54" s="6"/>
-      <c r="AJ54" s="95"/>
-      <c r="AK54" s="95"/>
+      <c r="AJ54" s="101"/>
+      <c r="AK54" s="101"/>
       <c r="AL54" s="6"/>
-      <c r="AM54" s="133"/>
-      <c r="AN54" s="95"/>
+      <c r="AM54" s="146"/>
+      <c r="AN54" s="101"/>
       <c r="AO54" s="6"/>
       <c r="AP54" s="6"/>
       <c r="AQ54" s="6"/>
-      <c r="AR54" s="110"/>
-      <c r="AS54" s="110"/>
+      <c r="AR54" s="225"/>
+      <c r="AS54" s="225"/>
       <c r="AT54" s="6"/>
-      <c r="AU54" s="110"/>
-      <c r="AV54" s="95"/>
+      <c r="AU54" s="225"/>
+      <c r="AV54" s="101"/>
       <c r="AW54" s="6"/>
       <c r="AX54" s="6"/>
       <c r="AY54" s="6"/>
-      <c r="AZ54" s="92"/>
-      <c r="BA54" s="92"/>
+      <c r="AZ54" s="229"/>
+      <c r="BA54" s="229"/>
       <c r="BB54" s="6"/>
-      <c r="BC54" s="92"/>
-      <c r="BD54" s="95"/>
+      <c r="BC54" s="229"/>
+      <c r="BD54" s="101"/>
       <c r="BE54" s="6"/>
       <c r="BF54" s="6"/>
       <c r="BG54" s="6"/>
-      <c r="BH54" s="98"/>
-      <c r="BI54" s="98"/>
+      <c r="BH54" s="194"/>
+      <c r="BI54" s="194"/>
       <c r="BJ54" s="6"/>
-      <c r="BK54" s="165"/>
-      <c r="BL54" s="161"/>
-      <c r="BN54" s="160" t="s">
+      <c r="BK54" s="215"/>
+      <c r="BL54" s="218"/>
+      <c r="BN54" s="217" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO54" s="21"/>
+      <c r="BR54" s="231" t="s">
         <v>15</v>
       </c>
-      <c r="BO54" s="21"/>
-      <c r="BR54" s="163" t="s">
-        <v>16</v>
-      </c>
-      <c r="BS54" s="89"/>
-      <c r="BT54" s="89"/>
-      <c r="BU54" s="89"/>
-      <c r="BV54" s="90"/>
+      <c r="BS54" s="232"/>
+      <c r="BT54" s="232"/>
+      <c r="BU54" s="232"/>
+      <c r="BV54" s="233"/>
     </row>
-    <row r="55" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:74" ht="17.25" thickBot="1">
       <c r="A55" s="19"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
-      <c r="E55" s="199"/>
-      <c r="F55" s="193" t="s">
-        <v>87</v>
+      <c r="E55" s="127"/>
+      <c r="F55" s="130" t="s">
+        <v>86</v>
       </c>
       <c r="G55" s="19"/>
-      <c r="H55" s="196" t="s">
-        <v>92</v>
-      </c>
-      <c r="I55" s="196" t="s">
-        <v>96</v>
+      <c r="H55" s="132" t="s">
+        <v>91</v>
+      </c>
+      <c r="I55" s="132" t="s">
+        <v>95</v>
       </c>
       <c r="J55" s="19"/>
-      <c r="K55" s="197" t="s">
+      <c r="K55" s="133" t="s">
+        <v>100</v>
+      </c>
+      <c r="L55" s="129" t="s">
         <v>101</v>
-      </c>
-      <c r="L55" s="191" t="s">
-        <v>102</v>
       </c>
       <c r="M55" s="19"/>
       <c r="N55" s="19"/>
-      <c r="O55" s="192"/>
+      <c r="O55" s="200"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="26"/>
-      <c r="T55" s="105"/>
-      <c r="U55" s="96"/>
+      <c r="T55" s="126"/>
+      <c r="U55" s="102"/>
       <c r="V55" s="6"/>
-      <c r="W55" s="108"/>
-      <c r="X55" s="108"/>
+      <c r="W55" s="144"/>
+      <c r="X55" s="144"/>
       <c r="Y55" s="6"/>
       <c r="Z55" s="6"/>
       <c r="AA55" s="6"/>
-      <c r="AB55" s="108"/>
-      <c r="AC55" s="105"/>
+      <c r="AB55" s="144"/>
+      <c r="AC55" s="126"/>
       <c r="AD55" s="6"/>
-      <c r="AE55" s="105"/>
-      <c r="AF55" s="105"/>
+      <c r="AE55" s="126"/>
+      <c r="AF55" s="126"/>
       <c r="AG55" s="6"/>
       <c r="AH55" s="6"/>
       <c r="AI55" s="6"/>
-      <c r="AJ55" s="96"/>
-      <c r="AK55" s="96"/>
+      <c r="AJ55" s="102"/>
+      <c r="AK55" s="102"/>
       <c r="AL55" s="6"/>
-      <c r="AM55" s="134"/>
-      <c r="AN55" s="96"/>
+      <c r="AM55" s="147"/>
+      <c r="AN55" s="102"/>
       <c r="AO55" s="6"/>
       <c r="AP55" s="6"/>
       <c r="AQ55" s="6"/>
-      <c r="AR55" s="111"/>
-      <c r="AS55" s="111"/>
+      <c r="AR55" s="226"/>
+      <c r="AS55" s="226"/>
       <c r="AT55" s="6"/>
-      <c r="AU55" s="111"/>
-      <c r="AV55" s="96"/>
+      <c r="AU55" s="226"/>
+      <c r="AV55" s="102"/>
       <c r="AW55" s="6"/>
       <c r="AX55" s="6"/>
       <c r="AY55" s="6"/>
-      <c r="AZ55" s="93"/>
-      <c r="BA55" s="93"/>
+      <c r="AZ55" s="230"/>
+      <c r="BA55" s="230"/>
       <c r="BB55" s="6"/>
-      <c r="BC55" s="93"/>
-      <c r="BD55" s="96"/>
+      <c r="BC55" s="230"/>
+      <c r="BD55" s="102"/>
       <c r="BE55" s="6"/>
       <c r="BF55" s="6"/>
       <c r="BG55" s="6"/>
-      <c r="BH55" s="99"/>
-      <c r="BI55" s="99"/>
+      <c r="BH55" s="195"/>
+      <c r="BI55" s="195"/>
       <c r="BJ55" s="6"/>
-      <c r="BK55" s="166"/>
-      <c r="BL55" s="162"/>
-      <c r="BN55" s="161"/>
+      <c r="BK55" s="216"/>
+      <c r="BL55" s="219"/>
+      <c r="BN55" s="218"/>
       <c r="BO55" s="21"/>
-      <c r="BR55" s="88"/>
-      <c r="BS55" s="89"/>
-      <c r="BT55" s="89"/>
-      <c r="BU55" s="89"/>
-      <c r="BV55" s="90"/>
+      <c r="BR55" s="234"/>
+      <c r="BS55" s="232"/>
+      <c r="BT55" s="232"/>
+      <c r="BU55" s="232"/>
+      <c r="BV55" s="233"/>
     </row>
-    <row r="56" spans="1:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="A56" s="19"/>
       <c r="B56" s="46"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
-      <c r="E56" s="199"/>
-      <c r="F56" s="193"/>
+      <c r="E56" s="127"/>
+      <c r="F56" s="130"/>
       <c r="G56" s="19"/>
-      <c r="H56" s="196"/>
-      <c r="I56" s="196"/>
+      <c r="H56" s="132"/>
+      <c r="I56" s="132"/>
       <c r="J56" s="19"/>
-      <c r="K56" s="197"/>
-      <c r="L56" s="191"/>
+      <c r="K56" s="133"/>
+      <c r="L56" s="129"/>
       <c r="M56" s="19"/>
       <c r="N56" s="19"/>
-      <c r="O56" s="192"/>
+      <c r="O56" s="200"/>
       <c r="Q56" s="8"/>
       <c r="R56" s="59"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="100" t="s">
+      <c r="T56" s="139" t="s">
+        <v>16</v>
+      </c>
+      <c r="U56" s="124"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="U56" s="103"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="106" t="s">
+      <c r="X56" s="142" t="s">
         <v>18</v>
-      </c>
-      <c r="X56" s="106" t="s">
-        <v>19</v>
       </c>
       <c r="Y56" s="6"/>
       <c r="Z56" s="6"/>
       <c r="AA56" s="6"/>
-      <c r="AB56" s="103"/>
-      <c r="AC56" s="141" t="s">
-        <v>20</v>
+      <c r="AB56" s="124"/>
+      <c r="AC56" s="104" t="s">
+        <v>19</v>
       </c>
       <c r="AD56" s="6"/>
-      <c r="AE56" s="103"/>
-      <c r="AF56" s="103"/>
+      <c r="AE56" s="124"/>
+      <c r="AF56" s="124"/>
       <c r="AG56" s="6"/>
       <c r="AH56" s="6"/>
       <c r="AI56" s="6"/>
-      <c r="AJ56" s="103"/>
-      <c r="AK56" s="132" t="s">
+      <c r="AJ56" s="124"/>
+      <c r="AK56" s="145" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL56" s="6"/>
+      <c r="AM56" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="AL56" s="6"/>
-      <c r="AM56" s="132" t="s">
-        <v>22</v>
-      </c>
-      <c r="AN56" s="94"/>
+      <c r="AN56" s="100"/>
       <c r="AO56" s="6"/>
       <c r="AP56" s="6"/>
       <c r="AQ56" s="6"/>
-      <c r="AR56" s="109" t="s">
+      <c r="AR56" s="224" t="s">
+        <v>22</v>
+      </c>
+      <c r="AS56" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="AS56" s="109" t="s">
+      <c r="AT56" s="6"/>
+      <c r="AU56" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="AT56" s="6"/>
-      <c r="AU56" s="109" t="s">
-        <v>25</v>
-      </c>
-      <c r="AV56" s="94"/>
+      <c r="AV56" s="100"/>
       <c r="AW56" s="6"/>
       <c r="AX56" s="6"/>
       <c r="AY56" s="6"/>
-      <c r="AZ56" s="91" t="s">
+      <c r="AZ56" s="228" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA56" s="228" t="s">
         <v>26</v>
       </c>
-      <c r="BA56" s="91" t="s">
-        <v>27</v>
-      </c>
       <c r="BB56" s="6"/>
-      <c r="BC56" s="94"/>
-      <c r="BD56" s="94"/>
+      <c r="BC56" s="100"/>
+      <c r="BD56" s="100"/>
       <c r="BE56" s="6"/>
       <c r="BF56" s="6"/>
       <c r="BG56" s="6"/>
-      <c r="BH56" s="97" t="s">
-        <v>304</v>
-      </c>
-      <c r="BI56" s="97" t="s">
-        <v>272</v>
+      <c r="BH56" s="193" t="s">
+        <v>303</v>
+      </c>
+      <c r="BI56" s="193" t="s">
+        <v>271</v>
       </c>
       <c r="BJ56" s="6"/>
-      <c r="BK56" s="164" t="s">
+      <c r="BK56" s="214" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL56" s="217" t="s">
         <v>28</v>
       </c>
-      <c r="BL56" s="160" t="s">
-        <v>29</v>
-      </c>
-      <c r="BN56" s="162"/>
+      <c r="BN56" s="219"/>
       <c r="BO56" s="21"/>
-      <c r="BR56" s="88"/>
-      <c r="BS56" s="89"/>
-      <c r="BT56" s="89"/>
-      <c r="BU56" s="89"/>
-      <c r="BV56" s="90"/>
+      <c r="BR56" s="234"/>
+      <c r="BS56" s="232"/>
+      <c r="BT56" s="232"/>
+      <c r="BU56" s="232"/>
+      <c r="BV56" s="233"/>
     </row>
-    <row r="57" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:74" ht="17.25" thickBot="1">
       <c r="A57" s="19"/>
       <c r="B57" s="58"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
-      <c r="E57" s="199"/>
-      <c r="F57" s="193"/>
+      <c r="E57" s="127"/>
+      <c r="F57" s="130"/>
       <c r="G57" s="19"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
+      <c r="H57" s="132"/>
+      <c r="I57" s="132"/>
       <c r="J57" s="19"/>
-      <c r="K57" s="197"/>
-      <c r="L57" s="191"/>
+      <c r="K57" s="133"/>
+      <c r="L57" s="129"/>
       <c r="M57" s="19"/>
       <c r="N57" s="19"/>
-      <c r="O57" s="192"/>
+      <c r="O57" s="200"/>
       <c r="Q57" s="8"/>
       <c r="R57" s="26"/>
-      <c r="T57" s="101"/>
-      <c r="U57" s="104"/>
+      <c r="T57" s="140"/>
+      <c r="U57" s="125"/>
       <c r="V57" s="6"/>
-      <c r="W57" s="107"/>
-      <c r="X57" s="107"/>
+      <c r="W57" s="143"/>
+      <c r="X57" s="143"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="6"/>
       <c r="AA57" s="6"/>
-      <c r="AB57" s="104"/>
-      <c r="AC57" s="142"/>
+      <c r="AB57" s="125"/>
+      <c r="AC57" s="105"/>
       <c r="AD57" s="7"/>
-      <c r="AE57" s="104"/>
-      <c r="AF57" s="104"/>
+      <c r="AE57" s="125"/>
+      <c r="AF57" s="125"/>
       <c r="AG57" s="6"/>
       <c r="AH57" s="6"/>
       <c r="AI57" s="6"/>
-      <c r="AJ57" s="104"/>
-      <c r="AK57" s="133"/>
+      <c r="AJ57" s="125"/>
+      <c r="AK57" s="146"/>
       <c r="AL57" s="6"/>
-      <c r="AM57" s="133"/>
-      <c r="AN57" s="95"/>
+      <c r="AM57" s="146"/>
+      <c r="AN57" s="101"/>
       <c r="AO57" s="6"/>
       <c r="AP57" s="6"/>
       <c r="AQ57" s="6"/>
-      <c r="AR57" s="110"/>
-      <c r="AS57" s="110"/>
+      <c r="AR57" s="225"/>
+      <c r="AS57" s="225"/>
       <c r="AT57" s="6"/>
-      <c r="AU57" s="110"/>
-      <c r="AV57" s="95"/>
+      <c r="AU57" s="225"/>
+      <c r="AV57" s="101"/>
       <c r="AW57" s="6"/>
       <c r="AX57" s="6"/>
       <c r="AY57" s="6"/>
-      <c r="AZ57" s="92"/>
-      <c r="BA57" s="92"/>
+      <c r="AZ57" s="229"/>
+      <c r="BA57" s="229"/>
       <c r="BB57" s="6"/>
-      <c r="BC57" s="95"/>
-      <c r="BD57" s="95"/>
+      <c r="BC57" s="101"/>
+      <c r="BD57" s="101"/>
       <c r="BE57" s="6"/>
       <c r="BF57" s="6"/>
       <c r="BG57" s="6"/>
-      <c r="BH57" s="98"/>
-      <c r="BI57" s="98"/>
+      <c r="BH57" s="194"/>
+      <c r="BI57" s="194"/>
       <c r="BJ57" s="6"/>
-      <c r="BK57" s="165"/>
-      <c r="BL57" s="161"/>
-      <c r="BN57" s="160" t="s">
-        <v>30</v>
-      </c>
-      <c r="BR57" s="88"/>
-      <c r="BS57" s="89"/>
-      <c r="BT57" s="89"/>
-      <c r="BU57" s="89"/>
-      <c r="BV57" s="90"/>
+      <c r="BK57" s="215"/>
+      <c r="BL57" s="218"/>
+      <c r="BN57" s="217" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR57" s="234"/>
+      <c r="BS57" s="232"/>
+      <c r="BT57" s="232"/>
+      <c r="BU57" s="232"/>
+      <c r="BV57" s="233"/>
     </row>
-    <row r="58" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:74" ht="17.25" thickBot="1">
       <c r="B58" s="46"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
-      <c r="E58" s="193" t="s">
-        <v>85</v>
+      <c r="E58" s="130" t="s">
+        <v>84</v>
       </c>
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
-      <c r="H58" s="200" t="s">
-        <v>93</v>
-      </c>
-      <c r="I58" s="196" t="s">
-        <v>95</v>
+      <c r="H58" s="131" t="s">
+        <v>92</v>
+      </c>
+      <c r="I58" s="132" t="s">
+        <v>94</v>
       </c>
       <c r="J58" s="19"/>
-      <c r="K58" s="197" t="s">
-        <v>301</v>
-      </c>
-      <c r="L58" s="191" t="s">
-        <v>103</v>
+      <c r="K58" s="133" t="s">
+        <v>300</v>
+      </c>
+      <c r="L58" s="129" t="s">
+        <v>102</v>
       </c>
       <c r="M58" s="19"/>
       <c r="N58" s="19"/>
-      <c r="O58" s="192" t="s">
-        <v>106</v>
+      <c r="O58" s="200" t="s">
+        <v>105</v>
       </c>
       <c r="Q58" s="9"/>
       <c r="R58" s="26"/>
-      <c r="T58" s="102"/>
-      <c r="U58" s="105"/>
+      <c r="T58" s="141"/>
+      <c r="U58" s="126"/>
       <c r="V58" s="6"/>
-      <c r="W58" s="108"/>
-      <c r="X58" s="108"/>
+      <c r="W58" s="144"/>
+      <c r="X58" s="144"/>
       <c r="Y58" s="6"/>
       <c r="Z58" s="6"/>
       <c r="AA58" s="6"/>
-      <c r="AB58" s="105"/>
-      <c r="AC58" s="143"/>
+      <c r="AB58" s="126"/>
+      <c r="AC58" s="106"/>
       <c r="AD58" s="6"/>
-      <c r="AE58" s="105"/>
-      <c r="AF58" s="105"/>
+      <c r="AE58" s="126"/>
+      <c r="AF58" s="126"/>
       <c r="AG58" s="6"/>
       <c r="AH58" s="6"/>
       <c r="AI58" s="6"/>
-      <c r="AJ58" s="105"/>
-      <c r="AK58" s="134"/>
+      <c r="AJ58" s="126"/>
+      <c r="AK58" s="147"/>
       <c r="AL58" s="6"/>
-      <c r="AM58" s="134"/>
-      <c r="AN58" s="96"/>
+      <c r="AM58" s="147"/>
+      <c r="AN58" s="102"/>
       <c r="AO58" s="6"/>
       <c r="AP58" s="6"/>
       <c r="AQ58" s="6"/>
-      <c r="AR58" s="111"/>
-      <c r="AS58" s="111"/>
+      <c r="AR58" s="226"/>
+      <c r="AS58" s="226"/>
       <c r="AT58" s="6"/>
-      <c r="AU58" s="111"/>
-      <c r="AV58" s="96"/>
+      <c r="AU58" s="226"/>
+      <c r="AV58" s="102"/>
       <c r="AW58" s="6"/>
       <c r="AX58" s="6"/>
       <c r="AY58" s="6"/>
-      <c r="AZ58" s="93"/>
-      <c r="BA58" s="93"/>
+      <c r="AZ58" s="230"/>
+      <c r="BA58" s="230"/>
       <c r="BB58" s="6"/>
-      <c r="BC58" s="96"/>
-      <c r="BD58" s="96"/>
+      <c r="BC58" s="102"/>
+      <c r="BD58" s="102"/>
       <c r="BE58" s="6"/>
       <c r="BF58" s="6"/>
       <c r="BG58" s="6"/>
-      <c r="BH58" s="99"/>
-      <c r="BI58" s="99"/>
+      <c r="BH58" s="195"/>
+      <c r="BI58" s="195"/>
       <c r="BJ58" s="6"/>
-      <c r="BK58" s="166"/>
-      <c r="BL58" s="162"/>
-      <c r="BN58" s="161"/>
-      <c r="BR58" s="88"/>
-      <c r="BS58" s="89"/>
-      <c r="BT58" s="89"/>
-      <c r="BU58" s="89"/>
-      <c r="BV58" s="90"/>
+      <c r="BK58" s="216"/>
+      <c r="BL58" s="219"/>
+      <c r="BN58" s="218"/>
+      <c r="BR58" s="234"/>
+      <c r="BS58" s="232"/>
+      <c r="BT58" s="232"/>
+      <c r="BU58" s="232"/>
+      <c r="BV58" s="233"/>
     </row>
-    <row r="59" spans="1:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="B59" s="46"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
-      <c r="E59" s="193"/>
+      <c r="E59" s="130"/>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
-      <c r="H59" s="200"/>
-      <c r="I59" s="196"/>
+      <c r="H59" s="131"/>
+      <c r="I59" s="132"/>
       <c r="J59" s="19"/>
-      <c r="K59" s="197"/>
-      <c r="L59" s="191"/>
+      <c r="K59" s="133"/>
+      <c r="L59" s="129"/>
       <c r="M59" s="19"/>
       <c r="N59" s="19"/>
-      <c r="O59" s="192"/>
+      <c r="O59" s="200"/>
       <c r="P59" s="32"/>
       <c r="Q59" s="60"/>
       <c r="R59" s="61"/>
       <c r="S59" s="9"/>
-      <c r="T59" s="100" t="s">
+      <c r="T59" s="139" t="s">
+        <v>30</v>
+      </c>
+      <c r="U59" s="124"/>
+      <c r="V59" s="6"/>
+      <c r="W59" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="U59" s="103"/>
-      <c r="V59" s="6"/>
-      <c r="W59" s="106" t="s">
+      <c r="X59" s="142" t="s">
         <v>32</v>
-      </c>
-      <c r="X59" s="106" t="s">
-        <v>33</v>
       </c>
       <c r="Y59" s="6"/>
       <c r="Z59" s="6"/>
       <c r="AA59" s="6"/>
-      <c r="AB59" s="103"/>
-      <c r="AC59" s="141" t="s">
-        <v>34</v>
+      <c r="AB59" s="124"/>
+      <c r="AC59" s="104" t="s">
+        <v>33</v>
       </c>
       <c r="AD59" s="6"/>
-      <c r="AE59" s="94"/>
-      <c r="AF59" s="103"/>
+      <c r="AE59" s="100"/>
+      <c r="AF59" s="124"/>
       <c r="AG59" s="6"/>
       <c r="AH59" s="6"/>
       <c r="AI59" s="6"/>
-      <c r="AJ59" s="103"/>
-      <c r="AK59" s="132" t="s">
+      <c r="AJ59" s="124"/>
+      <c r="AK59" s="145" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL59" s="6"/>
+      <c r="AM59" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="AL59" s="6"/>
-      <c r="AM59" s="132" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN59" s="94"/>
+      <c r="AN59" s="100"/>
       <c r="AO59" s="6"/>
       <c r="AP59" s="6"/>
       <c r="AQ59" s="6"/>
-      <c r="AR59" s="94"/>
-      <c r="AS59" s="109" t="s">
+      <c r="AR59" s="100"/>
+      <c r="AS59" s="224" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT59" s="6"/>
+      <c r="AU59" s="224" t="s">
         <v>37</v>
       </c>
-      <c r="AT59" s="6"/>
-      <c r="AU59" s="109" t="s">
-        <v>38</v>
-      </c>
-      <c r="AV59" s="94"/>
+      <c r="AV59" s="100"/>
       <c r="AW59" s="6"/>
       <c r="AX59" s="6"/>
       <c r="AY59" s="6"/>
-      <c r="AZ59" s="91" t="s">
-        <v>39</v>
-      </c>
-      <c r="BA59" s="91" t="s">
-        <v>238</v>
+      <c r="AZ59" s="228" t="s">
+        <v>38</v>
+      </c>
+      <c r="BA59" s="228" t="s">
+        <v>237</v>
       </c>
       <c r="BB59" s="6"/>
-      <c r="BC59" s="94"/>
-      <c r="BD59" s="94"/>
+      <c r="BC59" s="100"/>
+      <c r="BD59" s="100"/>
       <c r="BE59" s="6"/>
       <c r="BF59" s="6"/>
       <c r="BG59" s="6"/>
-      <c r="BH59" s="97" t="s">
-        <v>40</v>
-      </c>
-      <c r="BI59" s="164" t="s">
-        <v>75</v>
+      <c r="BH59" s="193" t="s">
+        <v>39</v>
+      </c>
+      <c r="BI59" s="214" t="s">
+        <v>74</v>
       </c>
       <c r="BJ59" s="6"/>
-      <c r="BK59" s="164" t="s">
-        <v>274</v>
-      </c>
-      <c r="BL59" s="160" t="s">
+      <c r="BK59" s="214" t="s">
+        <v>273</v>
+      </c>
+      <c r="BL59" s="217" t="s">
+        <v>41</v>
+      </c>
+      <c r="BN59" s="219"/>
+      <c r="BR59" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="BN59" s="162"/>
-      <c r="BR59" s="88" t="s">
-        <v>43</v>
-      </c>
-      <c r="BS59" s="89"/>
-      <c r="BT59" s="89"/>
-      <c r="BU59" s="89"/>
-      <c r="BV59" s="90"/>
+      <c r="BS59" s="232"/>
+      <c r="BT59" s="232"/>
+      <c r="BU59" s="232"/>
+      <c r="BV59" s="233"/>
     </row>
-    <row r="60" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:74" ht="17.25" thickBot="1">
       <c r="B60" s="46"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
-      <c r="E60" s="193"/>
+      <c r="E60" s="130"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
-      <c r="H60" s="200"/>
-      <c r="I60" s="196"/>
+      <c r="H60" s="131"/>
+      <c r="I60" s="132"/>
       <c r="J60" s="19"/>
-      <c r="K60" s="197"/>
-      <c r="L60" s="191"/>
+      <c r="K60" s="133"/>
+      <c r="L60" s="129"/>
       <c r="M60" s="19"/>
       <c r="N60" s="19"/>
-      <c r="O60" s="192"/>
-      <c r="P60" s="72"/>
-      <c r="Q60" s="72"/>
-      <c r="R60" s="72"/>
+      <c r="O60" s="200"/>
+      <c r="P60" s="70"/>
+      <c r="Q60" s="70"/>
+      <c r="R60" s="70"/>
       <c r="S60" s="10"/>
-      <c r="T60" s="101"/>
-      <c r="U60" s="104"/>
+      <c r="T60" s="140"/>
+      <c r="U60" s="125"/>
       <c r="V60" s="6"/>
-      <c r="W60" s="107"/>
-      <c r="X60" s="107"/>
+      <c r="W60" s="143"/>
+      <c r="X60" s="143"/>
       <c r="Y60" s="7"/>
       <c r="Z60" s="6"/>
       <c r="AA60" s="6"/>
-      <c r="AB60" s="104"/>
-      <c r="AC60" s="142"/>
+      <c r="AB60" s="125"/>
+      <c r="AC60" s="105"/>
       <c r="AD60" s="7"/>
-      <c r="AE60" s="95"/>
-      <c r="AF60" s="104"/>
+      <c r="AE60" s="101"/>
+      <c r="AF60" s="125"/>
       <c r="AG60" s="6"/>
       <c r="AH60" s="6"/>
       <c r="AI60" s="6"/>
-      <c r="AJ60" s="104"/>
-      <c r="AK60" s="133"/>
+      <c r="AJ60" s="125"/>
+      <c r="AK60" s="146"/>
       <c r="AL60" s="6"/>
-      <c r="AM60" s="133"/>
-      <c r="AN60" s="95"/>
+      <c r="AM60" s="146"/>
+      <c r="AN60" s="101"/>
       <c r="AO60" s="6"/>
       <c r="AP60" s="6"/>
       <c r="AQ60" s="6"/>
-      <c r="AR60" s="95"/>
-      <c r="AS60" s="110"/>
+      <c r="AR60" s="101"/>
+      <c r="AS60" s="225"/>
       <c r="AT60" s="6"/>
-      <c r="AU60" s="110"/>
-      <c r="AV60" s="95"/>
+      <c r="AU60" s="225"/>
+      <c r="AV60" s="101"/>
       <c r="AW60" s="6"/>
       <c r="AX60" s="6"/>
       <c r="AY60" s="6"/>
-      <c r="AZ60" s="92"/>
-      <c r="BA60" s="92"/>
+      <c r="AZ60" s="229"/>
+      <c r="BA60" s="229"/>
       <c r="BB60" s="6"/>
-      <c r="BC60" s="95"/>
-      <c r="BD60" s="95"/>
+      <c r="BC60" s="101"/>
+      <c r="BD60" s="101"/>
       <c r="BE60" s="6"/>
       <c r="BF60" s="6"/>
       <c r="BG60" s="6"/>
-      <c r="BH60" s="98"/>
-      <c r="BI60" s="165"/>
+      <c r="BH60" s="194"/>
+      <c r="BI60" s="215"/>
       <c r="BJ60" s="6"/>
-      <c r="BK60" s="165"/>
-      <c r="BL60" s="161"/>
-      <c r="BN60" s="174" t="s">
-        <v>44</v>
-      </c>
-      <c r="BR60" s="88"/>
-      <c r="BS60" s="89"/>
-      <c r="BT60" s="89"/>
-      <c r="BU60" s="89"/>
-      <c r="BV60" s="90"/>
+      <c r="BK60" s="215"/>
+      <c r="BL60" s="218"/>
+      <c r="BN60" s="227" t="s">
+        <v>43</v>
+      </c>
+      <c r="BR60" s="234"/>
+      <c r="BS60" s="232"/>
+      <c r="BT60" s="232"/>
+      <c r="BU60" s="232"/>
+      <c r="BV60" s="233"/>
     </row>
-    <row r="61" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:74" ht="17.25" thickBot="1">
       <c r="B61" s="46"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
-      <c r="E61" s="193" t="s">
-        <v>86</v>
+      <c r="E61" s="130" t="s">
+        <v>85</v>
       </c>
       <c r="F61" s="19"/>
       <c r="G61" s="19"/>
-      <c r="H61" s="194" t="s">
-        <v>94</v>
-      </c>
-      <c r="I61" s="194"/>
+      <c r="H61" s="201" t="s">
+        <v>93</v>
+      </c>
+      <c r="I61" s="201"/>
       <c r="J61" s="19"/>
-      <c r="K61" s="194" t="s">
-        <v>104</v>
-      </c>
-      <c r="L61" s="194"/>
+      <c r="K61" s="201" t="s">
+        <v>103</v>
+      </c>
+      <c r="L61" s="201"/>
       <c r="M61" s="19"/>
       <c r="N61" s="19"/>
-      <c r="O61" s="192"/>
+      <c r="O61" s="200"/>
       <c r="P61" s="19"/>
       <c r="Q61" s="51"/>
       <c r="R61" s="19"/>
-      <c r="T61" s="102"/>
-      <c r="U61" s="105"/>
+      <c r="T61" s="141"/>
+      <c r="U61" s="126"/>
       <c r="V61" s="6"/>
-      <c r="W61" s="108"/>
-      <c r="X61" s="108"/>
+      <c r="W61" s="144"/>
+      <c r="X61" s="144"/>
       <c r="Y61" s="6"/>
       <c r="Z61" s="6"/>
       <c r="AA61" s="6"/>
-      <c r="AB61" s="105"/>
-      <c r="AC61" s="143"/>
+      <c r="AB61" s="126"/>
+      <c r="AC61" s="106"/>
       <c r="AD61" s="6"/>
-      <c r="AE61" s="96"/>
-      <c r="AF61" s="105"/>
+      <c r="AE61" s="102"/>
+      <c r="AF61" s="126"/>
       <c r="AG61" s="6"/>
       <c r="AH61" s="6"/>
       <c r="AI61" s="6"/>
-      <c r="AJ61" s="105"/>
-      <c r="AK61" s="134"/>
+      <c r="AJ61" s="126"/>
+      <c r="AK61" s="147"/>
       <c r="AL61" s="6"/>
-      <c r="AM61" s="134"/>
-      <c r="AN61" s="96"/>
+      <c r="AM61" s="147"/>
+      <c r="AN61" s="102"/>
       <c r="AO61" s="6"/>
       <c r="AP61" s="6"/>
       <c r="AQ61" s="6"/>
-      <c r="AR61" s="96"/>
-      <c r="AS61" s="111"/>
+      <c r="AR61" s="102"/>
+      <c r="AS61" s="226"/>
       <c r="AT61" s="6"/>
-      <c r="AU61" s="111"/>
-      <c r="AV61" s="96"/>
+      <c r="AU61" s="226"/>
+      <c r="AV61" s="102"/>
       <c r="AW61" s="6"/>
       <c r="AX61" s="6"/>
       <c r="AY61" s="6"/>
-      <c r="AZ61" s="93"/>
-      <c r="BA61" s="93"/>
+      <c r="AZ61" s="230"/>
+      <c r="BA61" s="230"/>
       <c r="BB61" s="6"/>
-      <c r="BC61" s="96"/>
-      <c r="BD61" s="96"/>
+      <c r="BC61" s="102"/>
+      <c r="BD61" s="102"/>
       <c r="BE61" s="6"/>
       <c r="BF61" s="6"/>
       <c r="BG61" s="6"/>
-      <c r="BH61" s="99"/>
-      <c r="BI61" s="166"/>
+      <c r="BH61" s="195"/>
+      <c r="BI61" s="216"/>
       <c r="BJ61" s="6"/>
-      <c r="BK61" s="166"/>
-      <c r="BL61" s="162"/>
-      <c r="BN61" s="161"/>
-      <c r="BR61" s="88"/>
-      <c r="BS61" s="89"/>
-      <c r="BT61" s="89"/>
-      <c r="BU61" s="89"/>
-      <c r="BV61" s="90"/>
+      <c r="BK61" s="216"/>
+      <c r="BL61" s="219"/>
+      <c r="BN61" s="218"/>
+      <c r="BR61" s="234"/>
+      <c r="BS61" s="232"/>
+      <c r="BT61" s="232"/>
+      <c r="BU61" s="232"/>
+      <c r="BV61" s="233"/>
     </row>
-    <row r="62" spans="1:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:74" ht="17.25" thickBot="1">
       <c r="B62" s="46"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
-      <c r="E62" s="193"/>
+      <c r="E62" s="130"/>
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
-      <c r="H62" s="194"/>
-      <c r="I62" s="194"/>
+      <c r="H62" s="201"/>
+      <c r="I62" s="201"/>
       <c r="J62" s="19"/>
-      <c r="K62" s="194"/>
-      <c r="L62" s="194"/>
+      <c r="K62" s="201"/>
+      <c r="L62" s="201"/>
       <c r="M62" s="19"/>
       <c r="N62" s="19"/>
-      <c r="O62" s="192"/>
-      <c r="P62" s="232" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q62" s="242" t="s">
-        <v>239</v>
-      </c>
-      <c r="R62" s="243"/>
+      <c r="O62" s="200"/>
+      <c r="P62" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q62" s="116" t="s">
+        <v>238</v>
+      </c>
+      <c r="R62" s="117"/>
       <c r="S62" s="9"/>
-      <c r="T62" s="248" t="s">
-        <v>262</v>
-      </c>
-      <c r="U62" s="248"/>
+      <c r="T62" s="122" t="s">
+        <v>261</v>
+      </c>
+      <c r="U62" s="122"/>
       <c r="V62" s="6"/>
-      <c r="W62" s="173" t="s">
-        <v>264</v>
-      </c>
-      <c r="X62" s="173"/>
+      <c r="W62" s="65" t="s">
+        <v>263</v>
+      </c>
+      <c r="X62" s="65"/>
       <c r="Y62" s="6"/>
       <c r="Z62" s="6"/>
       <c r="AA62" s="6"/>
-      <c r="AB62" s="141" t="s">
+      <c r="AB62" s="104" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC62" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="AC62" s="141" t="s">
-        <v>46</v>
-      </c>
       <c r="AD62" s="6"/>
-      <c r="AE62" s="103"/>
-      <c r="AF62" s="103"/>
+      <c r="AE62" s="124"/>
+      <c r="AF62" s="124"/>
       <c r="AG62" s="6"/>
       <c r="AH62" s="6"/>
       <c r="AI62" s="6"/>
       <c r="AJ62" s="6"/>
       <c r="AK62" s="6"/>
-      <c r="AL62" s="131" t="s">
-        <v>266</v>
-      </c>
-      <c r="AM62" s="131"/>
+      <c r="AL62" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="AM62" s="103"/>
       <c r="AN62" s="6"/>
       <c r="AO62" s="6"/>
       <c r="AP62" s="6"/>
       <c r="AQ62" s="6"/>
-      <c r="AR62" s="131" t="s">
-        <v>268</v>
-      </c>
-      <c r="AS62" s="131"/>
+      <c r="AR62" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="AS62" s="103"/>
       <c r="AT62" s="6"/>
-      <c r="AU62" s="173" t="s">
-        <v>267</v>
-      </c>
-      <c r="AV62" s="173"/>
+      <c r="AU62" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV62" s="65"/>
       <c r="AW62" s="6"/>
       <c r="AX62" s="6"/>
       <c r="AY62" s="6"/>
@@ -7888,63 +7883,63 @@
       <c r="BI62" s="6"/>
       <c r="BJ62" s="6"/>
       <c r="BK62" s="6"/>
-      <c r="BL62" s="173" t="s">
-        <v>276</v>
-      </c>
-      <c r="BN62" s="162"/>
-      <c r="BR62" s="88"/>
-      <c r="BS62" s="89"/>
-      <c r="BT62" s="89"/>
-      <c r="BU62" s="89"/>
-      <c r="BV62" s="90"/>
+      <c r="BL62" s="65" t="s">
+        <v>275</v>
+      </c>
+      <c r="BN62" s="219"/>
+      <c r="BR62" s="234"/>
+      <c r="BS62" s="232"/>
+      <c r="BT62" s="232"/>
+      <c r="BU62" s="232"/>
+      <c r="BV62" s="233"/>
     </row>
-    <row r="63" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:74">
       <c r="B63" s="46"/>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
-      <c r="E63" s="193"/>
+      <c r="E63" s="130"/>
       <c r="F63" s="19"/>
       <c r="G63" s="19"/>
-      <c r="H63" s="194"/>
-      <c r="I63" s="194"/>
+      <c r="H63" s="201"/>
+      <c r="I63" s="201"/>
       <c r="J63" s="19"/>
-      <c r="K63" s="194"/>
-      <c r="L63" s="194"/>
+      <c r="K63" s="201"/>
+      <c r="L63" s="201"/>
       <c r="M63" s="19"/>
       <c r="N63" s="19"/>
       <c r="O63" s="24"/>
-      <c r="P63" s="235"/>
-      <c r="Q63" s="244"/>
-      <c r="R63" s="245"/>
-      <c r="T63" s="249"/>
-      <c r="U63" s="249"/>
+      <c r="P63" s="110"/>
+      <c r="Q63" s="118"/>
+      <c r="R63" s="119"/>
+      <c r="T63" s="123"/>
+      <c r="U63" s="123"/>
       <c r="V63" s="6"/>
-      <c r="W63" s="121"/>
-      <c r="X63" s="121"/>
+      <c r="W63" s="63"/>
+      <c r="X63" s="63"/>
       <c r="Y63" s="6"/>
       <c r="Z63" s="6"/>
       <c r="AA63" s="6"/>
-      <c r="AB63" s="142"/>
-      <c r="AC63" s="142"/>
+      <c r="AB63" s="105"/>
+      <c r="AC63" s="105"/>
       <c r="AD63" s="6"/>
-      <c r="AE63" s="104"/>
-      <c r="AF63" s="104"/>
+      <c r="AE63" s="125"/>
+      <c r="AF63" s="125"/>
       <c r="AG63" s="6"/>
       <c r="AH63" s="6"/>
       <c r="AI63" s="6"/>
       <c r="AJ63" s="6"/>
       <c r="AK63" s="6"/>
-      <c r="AL63" s="131"/>
-      <c r="AM63" s="131"/>
+      <c r="AL63" s="103"/>
+      <c r="AM63" s="103"/>
       <c r="AN63" s="6"/>
       <c r="AO63" s="6"/>
       <c r="AP63" s="6"/>
       <c r="AQ63" s="6"/>
-      <c r="AR63" s="131"/>
-      <c r="AS63" s="131"/>
+      <c r="AR63" s="103"/>
+      <c r="AS63" s="103"/>
       <c r="AT63" s="6"/>
-      <c r="AU63" s="121"/>
-      <c r="AV63" s="121"/>
+      <c r="AU63" s="63"/>
+      <c r="AV63" s="63"/>
       <c r="AW63" s="6"/>
       <c r="AX63" s="6"/>
       <c r="AY63" s="6"/>
@@ -7960,17 +7955,17 @@
       <c r="BI63" s="6"/>
       <c r="BJ63" s="6"/>
       <c r="BK63" s="6"/>
-      <c r="BL63" s="121"/>
-      <c r="BN63" s="160" t="s">
-        <v>47</v>
-      </c>
-      <c r="BR63" s="88"/>
-      <c r="BS63" s="89"/>
-      <c r="BT63" s="89"/>
-      <c r="BU63" s="89"/>
-      <c r="BV63" s="90"/>
+      <c r="BL63" s="63"/>
+      <c r="BN63" s="217" t="s">
+        <v>46</v>
+      </c>
+      <c r="BR63" s="234"/>
+      <c r="BS63" s="232"/>
+      <c r="BT63" s="232"/>
+      <c r="BU63" s="232"/>
+      <c r="BV63" s="233"/>
     </row>
-    <row r="64" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:74">
       <c r="B64" s="46"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
@@ -7985,87 +7980,87 @@
       <c r="M64" s="19"/>
       <c r="N64" s="19"/>
       <c r="O64" s="26"/>
-      <c r="P64" s="235"/>
-      <c r="Q64" s="244"/>
-      <c r="R64" s="245"/>
-      <c r="T64" s="100" t="s">
+      <c r="P64" s="110"/>
+      <c r="Q64" s="118"/>
+      <c r="R64" s="119"/>
+      <c r="T64" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="U64" s="100"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="142" t="s">
         <v>49</v>
       </c>
-      <c r="U64" s="94"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="106" t="s">
+      <c r="X64" s="142" t="s">
         <v>50</v>
-      </c>
-      <c r="X64" s="106" t="s">
-        <v>51</v>
       </c>
       <c r="Y64" s="6"/>
       <c r="Z64" s="6"/>
       <c r="AA64" s="6"/>
-      <c r="AB64" s="143"/>
-      <c r="AC64" s="143"/>
+      <c r="AB64" s="106"/>
+      <c r="AC64" s="106"/>
       <c r="AD64" s="6"/>
-      <c r="AE64" s="105"/>
-      <c r="AF64" s="105"/>
+      <c r="AE64" s="126"/>
+      <c r="AF64" s="126"/>
       <c r="AG64" s="6"/>
       <c r="AH64" s="6"/>
       <c r="AI64" s="6"/>
-      <c r="AJ64" s="103"/>
-      <c r="AK64" s="132" t="s">
-        <v>302</v>
+      <c r="AJ64" s="124"/>
+      <c r="AK64" s="145" t="s">
+        <v>301</v>
       </c>
       <c r="AL64" s="6"/>
-      <c r="AM64" s="132" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN64" s="103"/>
+      <c r="AM64" s="145" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN64" s="124"/>
       <c r="AO64" s="6"/>
       <c r="AP64" s="6"/>
       <c r="AQ64" s="6"/>
-      <c r="AR64" s="109" t="s">
+      <c r="AR64" s="224" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS64" s="100"/>
+      <c r="AT64" s="6"/>
+      <c r="AU64" s="221" t="s">
         <v>53</v>
       </c>
-      <c r="AS64" s="94"/>
-      <c r="AT64" s="6"/>
-      <c r="AU64" s="175" t="s">
+      <c r="AV64" s="221" t="s">
         <v>54</v>
-      </c>
-      <c r="AV64" s="175" t="s">
-        <v>55</v>
       </c>
       <c r="AW64" s="6"/>
       <c r="AY64" s="6"/>
-      <c r="AZ64" s="103"/>
-      <c r="BA64" s="138" t="s">
+      <c r="AZ64" s="124"/>
+      <c r="BA64" s="180" t="s">
+        <v>55</v>
+      </c>
+      <c r="BB64" s="6"/>
+      <c r="BC64" s="100"/>
+      <c r="BD64" s="148" t="s">
         <v>56</v>
-      </c>
-      <c r="BB64" s="6"/>
-      <c r="BC64" s="94"/>
-      <c r="BD64" s="170" t="s">
-        <v>57</v>
       </c>
       <c r="BE64" s="6"/>
       <c r="BF64" s="6"/>
       <c r="BG64" s="6"/>
-      <c r="BH64" s="170" t="s">
+      <c r="BH64" s="148" t="s">
+        <v>57</v>
+      </c>
+      <c r="BI64" s="100"/>
+      <c r="BJ64" s="6"/>
+      <c r="BK64" s="214" t="s">
         <v>58</v>
       </c>
-      <c r="BI64" s="94"/>
-      <c r="BJ64" s="6"/>
-      <c r="BK64" s="164" t="s">
+      <c r="BL64" s="217" t="s">
         <v>59</v>
       </c>
-      <c r="BL64" s="160" t="s">
-        <v>60</v>
-      </c>
-      <c r="BN64" s="161"/>
-      <c r="BR64" s="88"/>
-      <c r="BS64" s="89"/>
-      <c r="BT64" s="89"/>
-      <c r="BU64" s="89"/>
-      <c r="BV64" s="90"/>
+      <c r="BN64" s="218"/>
+      <c r="BR64" s="234"/>
+      <c r="BS64" s="232"/>
+      <c r="BT64" s="232"/>
+      <c r="BU64" s="232"/>
+      <c r="BV64" s="233"/>
     </row>
-    <row r="65" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:74" ht="17.25" thickBot="1">
       <c r="B65" s="46"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -8080,459 +8075,459 @@
       <c r="M65" s="33"/>
       <c r="N65" s="33"/>
       <c r="O65" s="34"/>
-      <c r="P65" s="235"/>
-      <c r="Q65" s="244"/>
-      <c r="R65" s="245"/>
-      <c r="T65" s="101"/>
-      <c r="U65" s="95"/>
+      <c r="P65" s="110"/>
+      <c r="Q65" s="118"/>
+      <c r="R65" s="119"/>
+      <c r="T65" s="140"/>
+      <c r="U65" s="101"/>
       <c r="V65" s="6"/>
-      <c r="W65" s="107"/>
-      <c r="X65" s="107"/>
+      <c r="W65" s="143"/>
+      <c r="X65" s="143"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="6"/>
       <c r="AA65" s="6"/>
-      <c r="AB65" s="141" t="s">
+      <c r="AB65" s="104" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC65" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="AC65" s="141" t="s">
-        <v>62</v>
-      </c>
       <c r="AD65" s="7"/>
-      <c r="AE65" s="103"/>
-      <c r="AF65" s="103"/>
+      <c r="AE65" s="124"/>
+      <c r="AF65" s="124"/>
       <c r="AG65" s="6"/>
       <c r="AH65" s="6"/>
       <c r="AI65" s="6"/>
-      <c r="AJ65" s="104"/>
-      <c r="AK65" s="133"/>
+      <c r="AJ65" s="125"/>
+      <c r="AK65" s="146"/>
       <c r="AL65" s="6"/>
-      <c r="AM65" s="133"/>
-      <c r="AN65" s="104"/>
+      <c r="AM65" s="146"/>
+      <c r="AN65" s="125"/>
       <c r="AO65" s="6"/>
       <c r="AP65" s="6"/>
       <c r="AQ65" s="6"/>
-      <c r="AR65" s="110"/>
-      <c r="AS65" s="95"/>
+      <c r="AR65" s="225"/>
+      <c r="AS65" s="101"/>
       <c r="AT65" s="6"/>
-      <c r="AU65" s="176"/>
-      <c r="AV65" s="176"/>
+      <c r="AU65" s="222"/>
+      <c r="AV65" s="222"/>
       <c r="AW65" s="6"/>
       <c r="AX65" s="6"/>
       <c r="AY65" s="6"/>
-      <c r="AZ65" s="104"/>
-      <c r="BA65" s="139"/>
+      <c r="AZ65" s="125"/>
+      <c r="BA65" s="181"/>
       <c r="BB65" s="6"/>
-      <c r="BC65" s="95"/>
-      <c r="BD65" s="171"/>
+      <c r="BC65" s="101"/>
+      <c r="BD65" s="149"/>
       <c r="BE65" s="6"/>
       <c r="BF65" s="6"/>
       <c r="BG65" s="6"/>
-      <c r="BH65" s="171"/>
-      <c r="BI65" s="95"/>
+      <c r="BH65" s="149"/>
+      <c r="BI65" s="101"/>
       <c r="BJ65" s="6"/>
-      <c r="BK65" s="165"/>
-      <c r="BL65" s="161"/>
-      <c r="BN65" s="162"/>
-      <c r="BR65" s="88"/>
-      <c r="BS65" s="89"/>
-      <c r="BT65" s="89"/>
-      <c r="BU65" s="89"/>
-      <c r="BV65" s="90"/>
+      <c r="BK65" s="215"/>
+      <c r="BL65" s="218"/>
+      <c r="BN65" s="219"/>
+      <c r="BR65" s="234"/>
+      <c r="BS65" s="232"/>
+      <c r="BT65" s="232"/>
+      <c r="BU65" s="232"/>
+      <c r="BV65" s="233"/>
     </row>
-    <row r="66" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:74" ht="17.25" thickBot="1">
       <c r="B66" s="18"/>
-      <c r="C66" s="198" t="s">
+      <c r="C66" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="128"/>
+      <c r="E66" s="128"/>
+      <c r="F66" s="128"/>
+      <c r="G66" s="128" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="198"/>
-      <c r="E66" s="198"/>
-      <c r="F66" s="198"/>
-      <c r="G66" s="198" t="s">
-        <v>108</v>
-      </c>
-      <c r="H66" s="198"/>
-      <c r="I66" s="63"/>
-      <c r="J66" s="64"/>
-      <c r="K66" s="64"/>
-      <c r="L66" s="64"/>
-      <c r="M66" s="64"/>
-      <c r="N66" s="64"/>
-      <c r="O66" s="65"/>
-      <c r="P66" s="235"/>
-      <c r="Q66" s="244"/>
-      <c r="R66" s="245"/>
-      <c r="T66" s="102"/>
-      <c r="U66" s="96"/>
+      <c r="H66" s="128"/>
+      <c r="I66" s="254"/>
+      <c r="J66" s="255"/>
+      <c r="K66" s="255"/>
+      <c r="L66" s="255"/>
+      <c r="M66" s="255"/>
+      <c r="N66" s="255"/>
+      <c r="O66" s="256"/>
+      <c r="P66" s="110"/>
+      <c r="Q66" s="118"/>
+      <c r="R66" s="119"/>
+      <c r="T66" s="141"/>
+      <c r="U66" s="102"/>
       <c r="V66" s="6"/>
-      <c r="W66" s="108"/>
-      <c r="X66" s="108"/>
+      <c r="W66" s="144"/>
+      <c r="X66" s="144"/>
       <c r="Y66" s="6"/>
       <c r="Z66" s="6"/>
       <c r="AA66" s="6"/>
-      <c r="AB66" s="142"/>
-      <c r="AC66" s="142"/>
+      <c r="AB66" s="105"/>
+      <c r="AC66" s="105"/>
       <c r="AD66" s="6"/>
-      <c r="AE66" s="104"/>
-      <c r="AF66" s="104"/>
+      <c r="AE66" s="125"/>
+      <c r="AF66" s="125"/>
       <c r="AG66" s="6"/>
       <c r="AH66" s="6"/>
       <c r="AI66" s="6"/>
-      <c r="AJ66" s="105"/>
-      <c r="AK66" s="134"/>
+      <c r="AJ66" s="126"/>
+      <c r="AK66" s="147"/>
       <c r="AL66" s="6"/>
-      <c r="AM66" s="134"/>
-      <c r="AN66" s="105"/>
+      <c r="AM66" s="147"/>
+      <c r="AN66" s="126"/>
       <c r="AO66" s="6"/>
       <c r="AP66" s="6"/>
       <c r="AQ66" s="6"/>
-      <c r="AR66" s="111"/>
-      <c r="AS66" s="96"/>
+      <c r="AR66" s="226"/>
+      <c r="AS66" s="102"/>
       <c r="AT66" s="6"/>
-      <c r="AU66" s="177"/>
-      <c r="AV66" s="177"/>
+      <c r="AU66" s="223"/>
+      <c r="AV66" s="223"/>
       <c r="AW66" s="6"/>
       <c r="AX66" s="6"/>
       <c r="AY66" s="6"/>
-      <c r="AZ66" s="105"/>
-      <c r="BA66" s="140"/>
+      <c r="AZ66" s="126"/>
+      <c r="BA66" s="182"/>
       <c r="BB66" s="6"/>
-      <c r="BC66" s="96"/>
-      <c r="BD66" s="172"/>
+      <c r="BC66" s="102"/>
+      <c r="BD66" s="150"/>
       <c r="BE66" s="6"/>
       <c r="BF66" s="6"/>
       <c r="BG66" s="6"/>
-      <c r="BH66" s="172"/>
-      <c r="BI66" s="95"/>
+      <c r="BH66" s="150"/>
+      <c r="BI66" s="101"/>
       <c r="BJ66" s="6"/>
-      <c r="BK66" s="166"/>
-      <c r="BL66" s="162"/>
+      <c r="BK66" s="216"/>
+      <c r="BL66" s="219"/>
       <c r="BN66" s="21"/>
-      <c r="BR66" s="88"/>
-      <c r="BS66" s="89"/>
-      <c r="BT66" s="89"/>
-      <c r="BU66" s="89"/>
-      <c r="BV66" s="90"/>
+      <c r="BR66" s="234"/>
+      <c r="BS66" s="232"/>
+      <c r="BT66" s="232"/>
+      <c r="BU66" s="232"/>
+      <c r="BV66" s="233"/>
     </row>
-    <row r="67" spans="2:74" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:74" ht="17.25" customHeight="1" thickBot="1">
       <c r="B67" s="18"/>
-      <c r="C67" s="198"/>
-      <c r="D67" s="198"/>
-      <c r="E67" s="198"/>
-      <c r="F67" s="198"/>
-      <c r="G67" s="198"/>
-      <c r="H67" s="198"/>
-      <c r="I67" s="66"/>
-      <c r="J67" s="67"/>
-      <c r="K67" s="67"/>
-      <c r="L67" s="67"/>
-      <c r="M67" s="67"/>
-      <c r="N67" s="67"/>
-      <c r="O67" s="68"/>
-      <c r="P67" s="235"/>
-      <c r="Q67" s="244"/>
-      <c r="R67" s="245"/>
-      <c r="T67" s="100" t="s">
+      <c r="C67" s="128"/>
+      <c r="D67" s="128"/>
+      <c r="E67" s="128"/>
+      <c r="F67" s="128"/>
+      <c r="G67" s="128"/>
+      <c r="H67" s="128"/>
+      <c r="I67" s="257"/>
+      <c r="J67" s="258"/>
+      <c r="K67" s="258"/>
+      <c r="L67" s="258"/>
+      <c r="M67" s="258"/>
+      <c r="N67" s="258"/>
+      <c r="O67" s="259"/>
+      <c r="P67" s="110"/>
+      <c r="Q67" s="118"/>
+      <c r="R67" s="119"/>
+      <c r="T67" s="139" t="s">
+        <v>62</v>
+      </c>
+      <c r="U67" s="139" t="s">
         <v>63</v>
       </c>
-      <c r="U67" s="100" t="s">
+      <c r="V67" s="6"/>
+      <c r="W67" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="V67" s="6"/>
-      <c r="W67" s="106" t="s">
+      <c r="X67" s="142" t="s">
         <v>65</v>
-      </c>
-      <c r="X67" s="106" t="s">
-        <v>66</v>
       </c>
       <c r="Y67" s="6"/>
       <c r="Z67" s="6"/>
       <c r="AA67" s="6"/>
-      <c r="AB67" s="142"/>
-      <c r="AC67" s="142"/>
+      <c r="AB67" s="105"/>
+      <c r="AC67" s="105"/>
       <c r="AD67" s="6"/>
-      <c r="AE67" s="104"/>
-      <c r="AF67" s="104"/>
+      <c r="AE67" s="125"/>
+      <c r="AF67" s="125"/>
       <c r="AG67" s="6"/>
       <c r="AH67" s="6"/>
       <c r="AI67" s="6"/>
-      <c r="AJ67" s="94"/>
-      <c r="AK67" s="132" t="s">
+      <c r="AJ67" s="100"/>
+      <c r="AK67" s="145" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL67" s="6"/>
+      <c r="AM67" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="AL67" s="6"/>
-      <c r="AM67" s="132" t="s">
+      <c r="AN67" s="145" t="s">
         <v>68</v>
-      </c>
-      <c r="AN67" s="132" t="s">
-        <v>69</v>
       </c>
       <c r="AO67" s="6"/>
       <c r="AP67" s="6"/>
       <c r="AQ67" s="6"/>
-      <c r="AR67" s="109" t="s">
+      <c r="AR67" s="224" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS67" s="100"/>
+      <c r="AT67" s="6"/>
+      <c r="AU67" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="AS67" s="94"/>
-      <c r="AT67" s="6"/>
-      <c r="AU67" s="175" t="s">
-        <v>71</v>
-      </c>
-      <c r="AV67" s="175" t="s">
-        <v>298</v>
+      <c r="AV67" s="221" t="s">
+        <v>297</v>
       </c>
       <c r="AW67" s="6"/>
       <c r="AX67" s="6"/>
       <c r="AY67" s="6"/>
-      <c r="AZ67" s="138" t="s">
+      <c r="AZ67" s="180" t="s">
+        <v>71</v>
+      </c>
+      <c r="BA67" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="BA67" s="138" t="s">
+      <c r="BB67" s="6"/>
+      <c r="BC67" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="BB67" s="6"/>
-      <c r="BC67" s="170" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD67" s="94"/>
+      <c r="BD67" s="100"/>
       <c r="BE67" s="6"/>
       <c r="BF67" s="6"/>
       <c r="BG67" s="6"/>
-      <c r="BH67" s="94"/>
-      <c r="BI67" s="94"/>
+      <c r="BH67" s="100"/>
+      <c r="BI67" s="100"/>
       <c r="BJ67" s="6"/>
-      <c r="BK67" s="164" t="s">
-        <v>41</v>
-      </c>
-      <c r="BL67" s="160" t="s">
-        <v>76</v>
+      <c r="BK67" s="214" t="s">
+        <v>40</v>
+      </c>
+      <c r="BL67" s="217" t="s">
+        <v>75</v>
       </c>
       <c r="BN67" s="21"/>
-      <c r="BR67" s="88"/>
-      <c r="BS67" s="89"/>
-      <c r="BT67" s="89"/>
-      <c r="BU67" s="89"/>
-      <c r="BV67" s="90"/>
+      <c r="BR67" s="234"/>
+      <c r="BS67" s="232"/>
+      <c r="BT67" s="232"/>
+      <c r="BU67" s="232"/>
+      <c r="BV67" s="233"/>
     </row>
-    <row r="68" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:74" ht="17.25" thickBot="1">
       <c r="B68" s="18"/>
-      <c r="C68" s="198"/>
-      <c r="D68" s="198"/>
-      <c r="E68" s="198"/>
-      <c r="F68" s="198"/>
-      <c r="G68" s="198"/>
-      <c r="H68" s="198"/>
-      <c r="I68" s="66"/>
-      <c r="J68" s="67"/>
-      <c r="K68" s="67"/>
-      <c r="L68" s="67"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="67"/>
-      <c r="O68" s="68"/>
-      <c r="P68" s="235"/>
-      <c r="Q68" s="244"/>
-      <c r="R68" s="245"/>
-      <c r="T68" s="101"/>
-      <c r="U68" s="101"/>
+      <c r="C68" s="128"/>
+      <c r="D68" s="128"/>
+      <c r="E68" s="128"/>
+      <c r="F68" s="128"/>
+      <c r="G68" s="128"/>
+      <c r="H68" s="128"/>
+      <c r="I68" s="257"/>
+      <c r="J68" s="258"/>
+      <c r="K68" s="258"/>
+      <c r="L68" s="258"/>
+      <c r="M68" s="258"/>
+      <c r="N68" s="258"/>
+      <c r="O68" s="259"/>
+      <c r="P68" s="110"/>
+      <c r="Q68" s="118"/>
+      <c r="R68" s="119"/>
+      <c r="T68" s="140"/>
+      <c r="U68" s="140"/>
       <c r="V68" s="6"/>
-      <c r="W68" s="107"/>
-      <c r="X68" s="107"/>
+      <c r="W68" s="143"/>
+      <c r="X68" s="143"/>
       <c r="Y68" s="7"/>
       <c r="Z68" s="6"/>
       <c r="AA68" s="6"/>
-      <c r="AB68" s="190" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC68" s="190"/>
+      <c r="AB68" s="220" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC68" s="220"/>
       <c r="AD68" s="7"/>
-      <c r="AE68" s="180"/>
-      <c r="AF68" s="180"/>
+      <c r="AE68" s="204"/>
+      <c r="AF68" s="204"/>
       <c r="AG68" s="6"/>
       <c r="AH68" s="6"/>
       <c r="AI68" s="6"/>
-      <c r="AJ68" s="95"/>
-      <c r="AK68" s="133"/>
+      <c r="AJ68" s="101"/>
+      <c r="AK68" s="146"/>
       <c r="AL68" s="6"/>
-      <c r="AM68" s="133"/>
-      <c r="AN68" s="133"/>
+      <c r="AM68" s="146"/>
+      <c r="AN68" s="146"/>
       <c r="AO68" s="6"/>
       <c r="AP68" s="6"/>
       <c r="AQ68" s="6"/>
-      <c r="AR68" s="110"/>
-      <c r="AS68" s="95"/>
+      <c r="AR68" s="225"/>
+      <c r="AS68" s="101"/>
       <c r="AT68" s="6"/>
-      <c r="AU68" s="176"/>
-      <c r="AV68" s="176"/>
+      <c r="AU68" s="222"/>
+      <c r="AV68" s="222"/>
       <c r="AW68" s="6"/>
       <c r="AX68" s="6"/>
       <c r="AY68" s="6"/>
-      <c r="AZ68" s="139"/>
-      <c r="BA68" s="139"/>
+      <c r="AZ68" s="181"/>
+      <c r="BA68" s="181"/>
       <c r="BB68" s="6"/>
-      <c r="BC68" s="171"/>
-      <c r="BD68" s="95"/>
+      <c r="BC68" s="149"/>
+      <c r="BD68" s="101"/>
       <c r="BE68" s="6"/>
       <c r="BF68" s="6"/>
       <c r="BG68" s="6"/>
-      <c r="BH68" s="95"/>
-      <c r="BI68" s="95"/>
+      <c r="BH68" s="101"/>
+      <c r="BI68" s="101"/>
       <c r="BJ68" s="6"/>
-      <c r="BK68" s="165"/>
-      <c r="BL68" s="161"/>
+      <c r="BK68" s="215"/>
+      <c r="BL68" s="218"/>
       <c r="BN68" s="21"/>
-      <c r="BR68" s="88"/>
-      <c r="BS68" s="89"/>
-      <c r="BT68" s="89"/>
-      <c r="BU68" s="89"/>
-      <c r="BV68" s="90"/>
+      <c r="BR68" s="234"/>
+      <c r="BS68" s="232"/>
+      <c r="BT68" s="232"/>
+      <c r="BU68" s="232"/>
+      <c r="BV68" s="233"/>
     </row>
-    <row r="69" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:74" ht="17.25" thickBot="1">
       <c r="B69" s="18"/>
-      <c r="C69" s="198"/>
-      <c r="D69" s="198"/>
-      <c r="E69" s="198"/>
-      <c r="F69" s="198"/>
-      <c r="G69" s="198"/>
-      <c r="H69" s="198"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="67"/>
-      <c r="L69" s="67"/>
-      <c r="M69" s="67"/>
-      <c r="N69" s="67"/>
-      <c r="O69" s="68"/>
-      <c r="P69" s="235"/>
-      <c r="Q69" s="244"/>
-      <c r="R69" s="245"/>
-      <c r="T69" s="101"/>
-      <c r="U69" s="101"/>
+      <c r="C69" s="128"/>
+      <c r="D69" s="128"/>
+      <c r="E69" s="128"/>
+      <c r="F69" s="128"/>
+      <c r="G69" s="128"/>
+      <c r="H69" s="128"/>
+      <c r="I69" s="257"/>
+      <c r="J69" s="258"/>
+      <c r="K69" s="258"/>
+      <c r="L69" s="258"/>
+      <c r="M69" s="258"/>
+      <c r="N69" s="258"/>
+      <c r="O69" s="259"/>
+      <c r="P69" s="110"/>
+      <c r="Q69" s="118"/>
+      <c r="R69" s="119"/>
+      <c r="T69" s="140"/>
+      <c r="U69" s="140"/>
       <c r="V69" s="6"/>
-      <c r="W69" s="107"/>
-      <c r="X69" s="107"/>
+      <c r="W69" s="143"/>
+      <c r="X69" s="143"/>
       <c r="Y69" s="6"/>
       <c r="Z69" s="6"/>
       <c r="AA69" s="6"/>
-      <c r="AB69" s="190"/>
-      <c r="AC69" s="190"/>
+      <c r="AB69" s="220"/>
+      <c r="AC69" s="220"/>
       <c r="AD69" s="6"/>
-      <c r="AE69" s="180"/>
-      <c r="AF69" s="180"/>
+      <c r="AE69" s="204"/>
+      <c r="AF69" s="204"/>
       <c r="AG69" s="6"/>
       <c r="AH69" s="6"/>
       <c r="AI69" s="6"/>
-      <c r="AJ69" s="95"/>
-      <c r="AK69" s="133"/>
+      <c r="AJ69" s="101"/>
+      <c r="AK69" s="146"/>
       <c r="AL69" s="6"/>
-      <c r="AM69" s="133"/>
-      <c r="AN69" s="133"/>
+      <c r="AM69" s="146"/>
+      <c r="AN69" s="146"/>
       <c r="AO69" s="6"/>
       <c r="AP69" s="6"/>
       <c r="AQ69" s="6"/>
-      <c r="AR69" s="111"/>
-      <c r="AS69" s="96"/>
+      <c r="AR69" s="226"/>
+      <c r="AS69" s="102"/>
       <c r="AT69" s="6"/>
-      <c r="AU69" s="177"/>
-      <c r="AV69" s="177"/>
+      <c r="AU69" s="223"/>
+      <c r="AV69" s="223"/>
       <c r="AW69" s="6"/>
       <c r="AX69" s="6"/>
       <c r="AY69" s="6"/>
-      <c r="AZ69" s="139"/>
-      <c r="BA69" s="139"/>
+      <c r="AZ69" s="181"/>
+      <c r="BA69" s="181"/>
       <c r="BB69" s="6"/>
-      <c r="BC69" s="172"/>
-      <c r="BD69" s="96"/>
+      <c r="BC69" s="150"/>
+      <c r="BD69" s="102"/>
       <c r="BE69" s="6"/>
       <c r="BF69" s="6"/>
       <c r="BG69" s="6"/>
-      <c r="BH69" s="95"/>
-      <c r="BI69" s="95"/>
+      <c r="BH69" s="101"/>
+      <c r="BI69" s="101"/>
       <c r="BJ69" s="6"/>
-      <c r="BK69" s="166"/>
-      <c r="BL69" s="162"/>
+      <c r="BK69" s="216"/>
+      <c r="BL69" s="219"/>
       <c r="BN69" s="21"/>
       <c r="BQ69" s="19"/>
-      <c r="BR69" s="88"/>
-      <c r="BS69" s="89"/>
-      <c r="BT69" s="89"/>
-      <c r="BU69" s="89"/>
-      <c r="BV69" s="90"/>
+      <c r="BR69" s="234"/>
+      <c r="BS69" s="232"/>
+      <c r="BT69" s="232"/>
+      <c r="BU69" s="232"/>
+      <c r="BV69" s="233"/>
     </row>
-    <row r="70" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:74" ht="17.25" thickBot="1">
       <c r="B70" s="18"/>
-      <c r="C70" s="198"/>
-      <c r="D70" s="198"/>
-      <c r="E70" s="198"/>
-      <c r="F70" s="198"/>
-      <c r="G70" s="198"/>
-      <c r="H70" s="198"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="67"/>
-      <c r="L70" s="67"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="67"/>
-      <c r="O70" s="68"/>
-      <c r="P70" s="235"/>
-      <c r="Q70" s="244"/>
-      <c r="R70" s="245"/>
-      <c r="T70" s="178" t="s">
+      <c r="C70" s="128"/>
+      <c r="D70" s="128"/>
+      <c r="E70" s="128"/>
+      <c r="F70" s="128"/>
+      <c r="G70" s="128"/>
+      <c r="H70" s="128"/>
+      <c r="I70" s="257"/>
+      <c r="J70" s="258"/>
+      <c r="K70" s="258"/>
+      <c r="L70" s="258"/>
+      <c r="M70" s="258"/>
+      <c r="N70" s="258"/>
+      <c r="O70" s="259"/>
+      <c r="P70" s="110"/>
+      <c r="Q70" s="118"/>
+      <c r="R70" s="119"/>
+      <c r="T70" s="202" t="s">
+        <v>77</v>
+      </c>
+      <c r="U70" s="202"/>
+      <c r="W70" s="203" t="s">
         <v>78</v>
       </c>
-      <c r="U70" s="178"/>
-      <c r="W70" s="179" t="s">
-        <v>79</v>
-      </c>
-      <c r="X70" s="179"/>
-      <c r="AB70" s="173" t="s">
-        <v>265</v>
-      </c>
-      <c r="AC70" s="173"/>
+      <c r="X70" s="203"/>
+      <c r="AB70" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC70" s="65"/>
       <c r="AD70" s="7"/>
       <c r="AF70" s="9"/>
-      <c r="AJ70" s="180"/>
-      <c r="AK70" s="180"/>
-      <c r="AM70" s="181" t="s">
-        <v>300</v>
-      </c>
-      <c r="AN70" s="181"/>
-      <c r="AU70" s="182" t="s">
+      <c r="AJ70" s="204"/>
+      <c r="AK70" s="204"/>
+      <c r="AM70" s="205" t="s">
+        <v>299</v>
+      </c>
+      <c r="AN70" s="205"/>
+      <c r="AU70" s="206" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV70" s="207"/>
+      <c r="AZ70" s="208"/>
+      <c r="BA70" s="209"/>
+      <c r="BH70" s="210" t="s">
         <v>80</v>
       </c>
-      <c r="AV70" s="183"/>
-      <c r="AZ70" s="184"/>
-      <c r="BA70" s="185"/>
-      <c r="BH70" s="186" t="s">
+      <c r="BI70" s="211"/>
+      <c r="BK70" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="BI70" s="187"/>
-      <c r="BK70" s="188" t="s">
-        <v>82</v>
-      </c>
-      <c r="BL70" s="189"/>
+      <c r="BL70" s="213"/>
       <c r="BN70" s="21"/>
-      <c r="BR70" s="88"/>
-      <c r="BS70" s="89"/>
-      <c r="BT70" s="89"/>
-      <c r="BU70" s="89"/>
-      <c r="BV70" s="90"/>
+      <c r="BR70" s="234"/>
+      <c r="BS70" s="232"/>
+      <c r="BT70" s="232"/>
+      <c r="BU70" s="232"/>
+      <c r="BV70" s="233"/>
     </row>
-    <row r="71" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:74" ht="17.25" thickBot="1">
       <c r="B71" s="18"/>
-      <c r="C71" s="198"/>
-      <c r="D71" s="198"/>
-      <c r="E71" s="198"/>
-      <c r="F71" s="198"/>
-      <c r="G71" s="198"/>
-      <c r="H71" s="198"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="67"/>
-      <c r="K71" s="67"/>
-      <c r="L71" s="67"/>
-      <c r="M71" s="67"/>
-      <c r="N71" s="67"/>
-      <c r="O71" s="68"/>
-      <c r="P71" s="235"/>
-      <c r="Q71" s="244"/>
-      <c r="R71" s="245"/>
+      <c r="C71" s="128"/>
+      <c r="D71" s="128"/>
+      <c r="E71" s="128"/>
+      <c r="F71" s="128"/>
+      <c r="G71" s="128"/>
+      <c r="H71" s="128"/>
+      <c r="I71" s="257"/>
+      <c r="J71" s="258"/>
+      <c r="K71" s="258"/>
+      <c r="L71" s="258"/>
+      <c r="M71" s="258"/>
+      <c r="N71" s="258"/>
+      <c r="O71" s="259"/>
+      <c r="P71" s="110"/>
+      <c r="Q71" s="118"/>
+      <c r="R71" s="119"/>
       <c r="U71" s="9"/>
       <c r="W71" s="9"/>
       <c r="X71" s="9"/>
@@ -8542,40 +8537,40 @@
       <c r="AN71" s="9"/>
       <c r="AS71" s="9"/>
       <c r="AV71" s="9"/>
-      <c r="AZ71" s="173" t="s">
+      <c r="AZ71" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="BA71" s="65"/>
+      <c r="BH71" s="65" t="s">
         <v>270</v>
       </c>
-      <c r="BA71" s="173"/>
-      <c r="BH71" s="173" t="s">
-        <v>271</v>
-      </c>
-      <c r="BI71" s="173"/>
+      <c r="BI71" s="65"/>
       <c r="BL71" s="9"/>
       <c r="BN71" s="21"/>
-      <c r="BR71" s="88"/>
-      <c r="BS71" s="89"/>
-      <c r="BT71" s="89"/>
-      <c r="BU71" s="89"/>
-      <c r="BV71" s="90"/>
+      <c r="BR71" s="234"/>
+      <c r="BS71" s="232"/>
+      <c r="BT71" s="232"/>
+      <c r="BU71" s="232"/>
+      <c r="BV71" s="233"/>
     </row>
-    <row r="72" spans="2:74" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:74" ht="18" thickTop="1" thickBot="1">
       <c r="B72" s="18"/>
-      <c r="C72" s="198"/>
-      <c r="D72" s="198"/>
-      <c r="E72" s="198"/>
-      <c r="F72" s="198"/>
-      <c r="G72" s="198"/>
-      <c r="H72" s="198"/>
-      <c r="I72" s="66"/>
-      <c r="J72" s="67"/>
-      <c r="K72" s="67"/>
-      <c r="L72" s="67"/>
-      <c r="M72" s="67"/>
-      <c r="N72" s="67"/>
-      <c r="O72" s="68"/>
-      <c r="P72" s="237"/>
-      <c r="Q72" s="246"/>
-      <c r="R72" s="247"/>
+      <c r="C72" s="128"/>
+      <c r="D72" s="128"/>
+      <c r="E72" s="128"/>
+      <c r="F72" s="128"/>
+      <c r="G72" s="128"/>
+      <c r="H72" s="128"/>
+      <c r="I72" s="257"/>
+      <c r="J72" s="258"/>
+      <c r="K72" s="258"/>
+      <c r="L72" s="258"/>
+      <c r="M72" s="258"/>
+      <c r="N72" s="258"/>
+      <c r="O72" s="259"/>
+      <c r="P72" s="113"/>
+      <c r="Q72" s="120"/>
+      <c r="R72" s="121"/>
       <c r="S72" s="42"/>
       <c r="U72" s="9"/>
       <c r="W72" s="9"/>
@@ -8589,51 +8584,51 @@
       <c r="AH72" s="42"/>
       <c r="AP72" s="42"/>
       <c r="AX72" s="42"/>
-      <c r="AZ72" s="131"/>
-      <c r="BA72" s="131"/>
+      <c r="AZ72" s="103"/>
+      <c r="BA72" s="103"/>
       <c r="BF72" s="42"/>
-      <c r="BH72" s="131"/>
-      <c r="BI72" s="131"/>
+      <c r="BH72" s="103"/>
+      <c r="BI72" s="103"/>
       <c r="BN72" s="22"/>
-      <c r="BR72" s="167"/>
-      <c r="BS72" s="168"/>
-      <c r="BT72" s="168"/>
-      <c r="BU72" s="168"/>
-      <c r="BV72" s="169"/>
+      <c r="BR72" s="235"/>
+      <c r="BS72" s="236"/>
+      <c r="BT72" s="236"/>
+      <c r="BU72" s="236"/>
+      <c r="BV72" s="237"/>
     </row>
-    <row r="73" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:74" ht="17.25" thickBot="1">
       <c r="B73" s="18"/>
-      <c r="C73" s="198"/>
-      <c r="D73" s="198"/>
-      <c r="E73" s="198"/>
-      <c r="F73" s="198"/>
-      <c r="G73" s="198"/>
-      <c r="H73" s="198"/>
-      <c r="I73" s="66"/>
-      <c r="J73" s="67"/>
-      <c r="K73" s="67"/>
-      <c r="L73" s="67"/>
-      <c r="M73" s="67"/>
-      <c r="N73" s="67"/>
-      <c r="O73" s="68"/>
+      <c r="C73" s="128"/>
+      <c r="D73" s="128"/>
+      <c r="E73" s="128"/>
+      <c r="F73" s="128"/>
+      <c r="G73" s="128"/>
+      <c r="H73" s="128"/>
+      <c r="I73" s="257"/>
+      <c r="J73" s="258"/>
+      <c r="K73" s="258"/>
+      <c r="L73" s="258"/>
+      <c r="M73" s="258"/>
+      <c r="N73" s="258"/>
+      <c r="O73" s="259"/>
       <c r="AB73" s="14"/>
       <c r="AF73" s="15"/>
     </row>
-    <row r="74" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:74" ht="17.25" thickBot="1">
       <c r="B74" s="18"/>
-      <c r="C74" s="198"/>
-      <c r="D74" s="198"/>
-      <c r="E74" s="198"/>
-      <c r="F74" s="198"/>
-      <c r="G74" s="198"/>
-      <c r="H74" s="198"/>
-      <c r="I74" s="66"/>
-      <c r="J74" s="67"/>
-      <c r="K74" s="67"/>
-      <c r="L74" s="67"/>
-      <c r="M74" s="67"/>
-      <c r="N74" s="67"/>
-      <c r="O74" s="68"/>
+      <c r="C74" s="128"/>
+      <c r="D74" s="128"/>
+      <c r="E74" s="128"/>
+      <c r="F74" s="128"/>
+      <c r="G74" s="128"/>
+      <c r="H74" s="128"/>
+      <c r="I74" s="257"/>
+      <c r="J74" s="258"/>
+      <c r="K74" s="258"/>
+      <c r="L74" s="258"/>
+      <c r="M74" s="258"/>
+      <c r="N74" s="258"/>
+      <c r="O74" s="259"/>
       <c r="P74" s="16"/>
       <c r="Q74" s="16"/>
       <c r="R74" s="16"/>
@@ -8689,24 +8684,397 @@
       <c r="BU74" s="16"/>
       <c r="BV74" s="16"/>
     </row>
-    <row r="75" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:74" ht="17.25" thickBot="1">
       <c r="B75" s="32"/>
-      <c r="C75" s="198"/>
-      <c r="D75" s="198"/>
-      <c r="E75" s="198"/>
-      <c r="F75" s="198"/>
-      <c r="G75" s="198"/>
-      <c r="H75" s="198"/>
-      <c r="I75" s="69"/>
-      <c r="J75" s="70"/>
-      <c r="K75" s="70"/>
-      <c r="L75" s="70"/>
-      <c r="M75" s="70"/>
-      <c r="N75" s="70"/>
-      <c r="O75" s="71"/>
+      <c r="C75" s="128"/>
+      <c r="D75" s="128"/>
+      <c r="E75" s="128"/>
+      <c r="F75" s="128"/>
+      <c r="G75" s="128"/>
+      <c r="H75" s="128"/>
+      <c r="I75" s="260"/>
+      <c r="J75" s="261"/>
+      <c r="K75" s="261"/>
+      <c r="L75" s="261"/>
+      <c r="M75" s="261"/>
+      <c r="N75" s="261"/>
+      <c r="O75" s="262"/>
     </row>
   </sheetData>
   <mergeCells count="397">
+    <mergeCell ref="I66:O75"/>
+    <mergeCell ref="BS4:BV6"/>
+    <mergeCell ref="BM46:BQ48"/>
+    <mergeCell ref="BR46:BV53"/>
+    <mergeCell ref="BC53:BC55"/>
+    <mergeCell ref="BD53:BD55"/>
+    <mergeCell ref="BH53:BH55"/>
+    <mergeCell ref="BI53:BI55"/>
+    <mergeCell ref="T56:T58"/>
+    <mergeCell ref="U56:U58"/>
+    <mergeCell ref="W56:W58"/>
+    <mergeCell ref="X56:X58"/>
+    <mergeCell ref="AB56:AB58"/>
+    <mergeCell ref="AR53:AR55"/>
+    <mergeCell ref="AS53:AS55"/>
+    <mergeCell ref="AU53:AU55"/>
+    <mergeCell ref="AV53:AV55"/>
+    <mergeCell ref="AE53:AE55"/>
+    <mergeCell ref="T53:T55"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="Y46:AC48"/>
+    <mergeCell ref="X53:X55"/>
+    <mergeCell ref="AB53:AB55"/>
+    <mergeCell ref="AC53:AC55"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="BD46:BH48"/>
+    <mergeCell ref="BI46:BL48"/>
+    <mergeCell ref="AD46:AE48"/>
+    <mergeCell ref="AF46:AI48"/>
+    <mergeCell ref="AJ46:AQ48"/>
+    <mergeCell ref="AR46:AV46"/>
+    <mergeCell ref="AW46:AY48"/>
+    <mergeCell ref="AZ46:BC48"/>
+    <mergeCell ref="BH51:BH52"/>
+    <mergeCell ref="BK51:BK52"/>
+    <mergeCell ref="AF53:AF55"/>
+    <mergeCell ref="AJ53:AJ55"/>
+    <mergeCell ref="AK53:AK55"/>
+    <mergeCell ref="AM53:AM55"/>
+    <mergeCell ref="AN53:AN55"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="M10:M12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="W10:W12"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="J24:J26"/>
+    <mergeCell ref="N24:N26"/>
+    <mergeCell ref="Q24:Q26"/>
+    <mergeCell ref="T13:T15"/>
+    <mergeCell ref="X13:X15"/>
+    <mergeCell ref="T10:T12"/>
+    <mergeCell ref="X10:X12"/>
+    <mergeCell ref="Q10:Q12"/>
+    <mergeCell ref="U10:U12"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="BN54:BN56"/>
+    <mergeCell ref="BR54:BV58"/>
+    <mergeCell ref="AZ53:AZ55"/>
+    <mergeCell ref="BA53:BA55"/>
+    <mergeCell ref="BL56:BL58"/>
+    <mergeCell ref="BN57:BN59"/>
+    <mergeCell ref="BD56:BD58"/>
+    <mergeCell ref="BH56:BH58"/>
+    <mergeCell ref="BI56:BI58"/>
+    <mergeCell ref="BK56:BK58"/>
+    <mergeCell ref="BR59:BV72"/>
+    <mergeCell ref="BD64:BD66"/>
+    <mergeCell ref="BH64:BH66"/>
+    <mergeCell ref="BI64:BI66"/>
+    <mergeCell ref="BK64:BK66"/>
+    <mergeCell ref="AZ71:BA72"/>
+    <mergeCell ref="BH71:BI72"/>
+    <mergeCell ref="BL62:BL63"/>
+    <mergeCell ref="BK53:BK55"/>
+    <mergeCell ref="BL53:BL55"/>
+    <mergeCell ref="X59:X61"/>
+    <mergeCell ref="AB59:AB61"/>
+    <mergeCell ref="AC59:AC61"/>
+    <mergeCell ref="AE59:AE61"/>
+    <mergeCell ref="BA56:BA58"/>
+    <mergeCell ref="BC56:BC58"/>
+    <mergeCell ref="AN56:AN58"/>
+    <mergeCell ref="AR56:AR58"/>
+    <mergeCell ref="AS56:AS58"/>
+    <mergeCell ref="AU56:AU58"/>
+    <mergeCell ref="AV56:AV58"/>
+    <mergeCell ref="AZ56:AZ58"/>
+    <mergeCell ref="AC56:AC58"/>
+    <mergeCell ref="AE56:AE58"/>
+    <mergeCell ref="AS59:AS61"/>
+    <mergeCell ref="AU59:AU61"/>
+    <mergeCell ref="AV59:AV61"/>
+    <mergeCell ref="AZ59:AZ61"/>
+    <mergeCell ref="BA59:BA61"/>
+    <mergeCell ref="BC59:BC61"/>
+    <mergeCell ref="AF56:AF58"/>
+    <mergeCell ref="AJ56:AJ58"/>
+    <mergeCell ref="AK56:AK58"/>
+    <mergeCell ref="AM56:AM58"/>
+    <mergeCell ref="P60:R60"/>
+    <mergeCell ref="BN60:BN62"/>
+    <mergeCell ref="AB62:AB64"/>
+    <mergeCell ref="AC62:AC64"/>
+    <mergeCell ref="AE62:AE64"/>
+    <mergeCell ref="AF62:AF64"/>
+    <mergeCell ref="BN63:BN65"/>
+    <mergeCell ref="T64:T66"/>
+    <mergeCell ref="U64:U66"/>
+    <mergeCell ref="W64:W66"/>
+    <mergeCell ref="BD59:BD61"/>
+    <mergeCell ref="BH59:BH61"/>
+    <mergeCell ref="BI59:BI61"/>
+    <mergeCell ref="BK59:BK61"/>
+    <mergeCell ref="BL59:BL61"/>
+    <mergeCell ref="AF59:AF61"/>
+    <mergeCell ref="AJ59:AJ61"/>
+    <mergeCell ref="AK59:AK61"/>
+    <mergeCell ref="AM59:AM61"/>
+    <mergeCell ref="AN59:AN61"/>
+    <mergeCell ref="AR59:AR61"/>
+    <mergeCell ref="T59:T61"/>
+    <mergeCell ref="U59:U61"/>
+    <mergeCell ref="W59:W61"/>
+    <mergeCell ref="AJ67:AJ69"/>
+    <mergeCell ref="AK67:AK69"/>
+    <mergeCell ref="BL64:BL66"/>
+    <mergeCell ref="AB65:AB67"/>
+    <mergeCell ref="AC65:AC67"/>
+    <mergeCell ref="AE65:AE67"/>
+    <mergeCell ref="AF65:AF67"/>
+    <mergeCell ref="X64:X66"/>
+    <mergeCell ref="AJ64:AJ66"/>
+    <mergeCell ref="AK64:AK66"/>
+    <mergeCell ref="AR67:AR69"/>
+    <mergeCell ref="AS67:AS69"/>
+    <mergeCell ref="AS64:AS66"/>
+    <mergeCell ref="AU64:AU66"/>
+    <mergeCell ref="AV64:AV66"/>
+    <mergeCell ref="AZ64:AZ66"/>
+    <mergeCell ref="BA64:BA66"/>
+    <mergeCell ref="BC64:BC66"/>
+    <mergeCell ref="AM64:AM66"/>
+    <mergeCell ref="AN64:AN66"/>
+    <mergeCell ref="AR64:AR66"/>
+    <mergeCell ref="AM67:AM69"/>
+    <mergeCell ref="AN67:AN69"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="W70:X70"/>
+    <mergeCell ref="AJ70:AK70"/>
+    <mergeCell ref="AM70:AN70"/>
+    <mergeCell ref="AU70:AV70"/>
+    <mergeCell ref="AZ70:BA70"/>
+    <mergeCell ref="BH70:BI70"/>
+    <mergeCell ref="BK70:BL70"/>
+    <mergeCell ref="BH67:BH69"/>
+    <mergeCell ref="BI67:BI69"/>
+    <mergeCell ref="BK67:BK69"/>
+    <mergeCell ref="BL67:BL69"/>
+    <mergeCell ref="AB68:AC69"/>
+    <mergeCell ref="AE68:AF69"/>
+    <mergeCell ref="AU67:AU69"/>
+    <mergeCell ref="AV67:AV69"/>
+    <mergeCell ref="AZ67:AZ69"/>
+    <mergeCell ref="BA67:BA69"/>
+    <mergeCell ref="BC67:BC69"/>
+    <mergeCell ref="BD67:BD69"/>
+    <mergeCell ref="T67:T69"/>
+    <mergeCell ref="U67:U69"/>
+    <mergeCell ref="W67:W69"/>
+    <mergeCell ref="X67:X69"/>
+    <mergeCell ref="L58:L60"/>
+    <mergeCell ref="O58:O62"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="H61:I63"/>
+    <mergeCell ref="K61:L63"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="K55:K57"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="C47:I47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="I49:I51"/>
+    <mergeCell ref="K49:K51"/>
+    <mergeCell ref="L49:L51"/>
+    <mergeCell ref="O49:O57"/>
+    <mergeCell ref="B21:C26"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="L52:L54"/>
+    <mergeCell ref="U53:U55"/>
+    <mergeCell ref="W53:W55"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="N13:N15"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="M13:M15"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="M24:M26"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="I8:J9"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="N10:N12"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="T24:T26"/>
+    <mergeCell ref="T21:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="Q7:Q9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="U24:U26"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="W13:W15"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="P24:P26"/>
+    <mergeCell ref="W24:W26"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="U13:U15"/>
+    <mergeCell ref="Q18:Q20"/>
+    <mergeCell ref="P18:P20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="U18:U20"/>
+    <mergeCell ref="W18:W20"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="Q21:Q23"/>
+    <mergeCell ref="U21:U23"/>
+    <mergeCell ref="P21:P23"/>
+    <mergeCell ref="W21:W23"/>
+    <mergeCell ref="BT9:BU9"/>
+    <mergeCell ref="BB10:BB12"/>
+    <mergeCell ref="BC10:BC12"/>
+    <mergeCell ref="BG10:BG12"/>
+    <mergeCell ref="BH10:BH12"/>
+    <mergeCell ref="BJ10:BJ12"/>
+    <mergeCell ref="BK10:BK12"/>
+    <mergeCell ref="BO10:BO12"/>
+    <mergeCell ref="BP10:BP12"/>
+    <mergeCell ref="BT10:BT12"/>
+    <mergeCell ref="BU10:BU12"/>
+    <mergeCell ref="BG7:BG9"/>
+    <mergeCell ref="BH7:BH9"/>
+    <mergeCell ref="BB9:BC9"/>
+    <mergeCell ref="BJ9:BK9"/>
+    <mergeCell ref="BR30:BV35"/>
+    <mergeCell ref="BM30:BQ35"/>
+    <mergeCell ref="BK30:BL35"/>
+    <mergeCell ref="BO13:BO15"/>
+    <mergeCell ref="BP13:BP15"/>
+    <mergeCell ref="BT13:BT15"/>
+    <mergeCell ref="BU13:BU15"/>
+    <mergeCell ref="BB18:BB20"/>
+    <mergeCell ref="BC18:BC20"/>
+    <mergeCell ref="BG18:BG20"/>
+    <mergeCell ref="BH18:BH20"/>
+    <mergeCell ref="BJ18:BJ20"/>
+    <mergeCell ref="BK18:BK20"/>
+    <mergeCell ref="BO18:BO20"/>
+    <mergeCell ref="BP18:BP20"/>
+    <mergeCell ref="BT18:BT20"/>
+    <mergeCell ref="BU18:BU20"/>
+    <mergeCell ref="BO16:BP16"/>
+    <mergeCell ref="BB13:BB15"/>
+    <mergeCell ref="BC13:BC15"/>
+    <mergeCell ref="BG13:BG15"/>
+    <mergeCell ref="BH13:BH15"/>
+    <mergeCell ref="BJ13:BJ15"/>
+    <mergeCell ref="BK13:BK15"/>
+    <mergeCell ref="BT21:BT23"/>
+    <mergeCell ref="BU21:BU23"/>
+    <mergeCell ref="BB24:BB26"/>
+    <mergeCell ref="BC24:BC26"/>
+    <mergeCell ref="BG24:BG26"/>
+    <mergeCell ref="BH24:BH26"/>
+    <mergeCell ref="BJ24:BJ26"/>
+    <mergeCell ref="BK24:BK26"/>
+    <mergeCell ref="BO24:BO26"/>
+    <mergeCell ref="BP24:BP26"/>
+    <mergeCell ref="BJ21:BJ23"/>
+    <mergeCell ref="BK21:BK23"/>
+    <mergeCell ref="BO21:BO23"/>
+    <mergeCell ref="BP21:BP23"/>
+    <mergeCell ref="BT24:BT26"/>
+    <mergeCell ref="BU24:BU26"/>
+    <mergeCell ref="BB21:BB23"/>
+    <mergeCell ref="BC21:BC23"/>
+    <mergeCell ref="BG21:BG23"/>
+    <mergeCell ref="BH21:BH23"/>
+    <mergeCell ref="BQ36:BV39"/>
+    <mergeCell ref="BQ42:BV45"/>
+    <mergeCell ref="AC31:AI31"/>
+    <mergeCell ref="AA32:AB35"/>
+    <mergeCell ref="Y31:Z35"/>
+    <mergeCell ref="U31:X35"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="K29:K31"/>
+    <mergeCell ref="K32:K34"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="BC41:BH43"/>
+    <mergeCell ref="BE38:BH40"/>
+    <mergeCell ref="AC32:AC35"/>
+    <mergeCell ref="AD32:AD35"/>
+    <mergeCell ref="AE32:AE35"/>
+    <mergeCell ref="AF32:AF35"/>
+    <mergeCell ref="AG32:AG35"/>
+    <mergeCell ref="AH32:AH35"/>
+    <mergeCell ref="AI32:AI35"/>
+    <mergeCell ref="AR35:AV35"/>
+    <mergeCell ref="AP38:AQ43"/>
+    <mergeCell ref="AW38:AX43"/>
+    <mergeCell ref="AF41:AK43"/>
+    <mergeCell ref="AB70:AC70"/>
+    <mergeCell ref="AL62:AM63"/>
+    <mergeCell ref="AR62:AS63"/>
+    <mergeCell ref="AU62:AV63"/>
+    <mergeCell ref="AZ51:BA52"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="M38:U40"/>
+    <mergeCell ref="M41:U43"/>
+    <mergeCell ref="B36:G39"/>
+    <mergeCell ref="B42:G45"/>
+    <mergeCell ref="P62:P72"/>
+    <mergeCell ref="Q62:R72"/>
+    <mergeCell ref="T62:U63"/>
+    <mergeCell ref="W62:X63"/>
+    <mergeCell ref="J32:J34"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="C66:F75"/>
+    <mergeCell ref="G66:H75"/>
+    <mergeCell ref="L55:L57"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="H58:H60"/>
+    <mergeCell ref="I58:I60"/>
+    <mergeCell ref="K58:K60"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="D49:D50"/>
     <mergeCell ref="BB16:BC17"/>
@@ -8731,379 +9099,6 @@
     <mergeCell ref="X24:X26"/>
     <mergeCell ref="J29:J31"/>
     <mergeCell ref="N18:N20"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AL62:AM63"/>
-    <mergeCell ref="AR62:AS63"/>
-    <mergeCell ref="AU62:AV63"/>
-    <mergeCell ref="AZ51:BA52"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="M38:U40"/>
-    <mergeCell ref="M41:U43"/>
-    <mergeCell ref="B36:G39"/>
-    <mergeCell ref="B42:G45"/>
-    <mergeCell ref="P62:P72"/>
-    <mergeCell ref="Q62:R72"/>
-    <mergeCell ref="T62:U63"/>
-    <mergeCell ref="W62:X63"/>
-    <mergeCell ref="J32:J34"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="C66:F75"/>
-    <mergeCell ref="G66:H75"/>
-    <mergeCell ref="L55:L57"/>
-    <mergeCell ref="E58:E60"/>
-    <mergeCell ref="H58:H60"/>
-    <mergeCell ref="I58:I60"/>
-    <mergeCell ref="K58:K60"/>
-    <mergeCell ref="BQ36:BV39"/>
-    <mergeCell ref="BQ42:BV45"/>
-    <mergeCell ref="AC31:AI31"/>
-    <mergeCell ref="AA32:AB35"/>
-    <mergeCell ref="Y31:Z35"/>
-    <mergeCell ref="U31:X35"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="K29:K31"/>
-    <mergeCell ref="K32:K34"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="BC41:BH43"/>
-    <mergeCell ref="BE38:BH40"/>
-    <mergeCell ref="AC32:AC35"/>
-    <mergeCell ref="AD32:AD35"/>
-    <mergeCell ref="AE32:AE35"/>
-    <mergeCell ref="AF32:AF35"/>
-    <mergeCell ref="AG32:AG35"/>
-    <mergeCell ref="AH32:AH35"/>
-    <mergeCell ref="AI32:AI35"/>
-    <mergeCell ref="AR35:AV35"/>
-    <mergeCell ref="AP38:AQ43"/>
-    <mergeCell ref="AW38:AX43"/>
-    <mergeCell ref="AF41:AK43"/>
-    <mergeCell ref="BT21:BT23"/>
-    <mergeCell ref="BU21:BU23"/>
-    <mergeCell ref="BB24:BB26"/>
-    <mergeCell ref="BC24:BC26"/>
-    <mergeCell ref="BG24:BG26"/>
-    <mergeCell ref="BH24:BH26"/>
-    <mergeCell ref="BJ24:BJ26"/>
-    <mergeCell ref="BK24:BK26"/>
-    <mergeCell ref="BO24:BO26"/>
-    <mergeCell ref="BP24:BP26"/>
-    <mergeCell ref="BJ21:BJ23"/>
-    <mergeCell ref="BK21:BK23"/>
-    <mergeCell ref="BO21:BO23"/>
-    <mergeCell ref="BP21:BP23"/>
-    <mergeCell ref="BT24:BT26"/>
-    <mergeCell ref="BU24:BU26"/>
-    <mergeCell ref="BB21:BB23"/>
-    <mergeCell ref="BC21:BC23"/>
-    <mergeCell ref="BG21:BG23"/>
-    <mergeCell ref="BH21:BH23"/>
-    <mergeCell ref="BR30:BV35"/>
-    <mergeCell ref="BM30:BQ35"/>
-    <mergeCell ref="BK30:BL35"/>
-    <mergeCell ref="BO13:BO15"/>
-    <mergeCell ref="BP13:BP15"/>
-    <mergeCell ref="BT13:BT15"/>
-    <mergeCell ref="BU13:BU15"/>
-    <mergeCell ref="BB18:BB20"/>
-    <mergeCell ref="BC18:BC20"/>
-    <mergeCell ref="BG18:BG20"/>
-    <mergeCell ref="BH18:BH20"/>
-    <mergeCell ref="BJ18:BJ20"/>
-    <mergeCell ref="BK18:BK20"/>
-    <mergeCell ref="BO18:BO20"/>
-    <mergeCell ref="BP18:BP20"/>
-    <mergeCell ref="BT18:BT20"/>
-    <mergeCell ref="BU18:BU20"/>
-    <mergeCell ref="BO16:BP16"/>
-    <mergeCell ref="BB13:BB15"/>
-    <mergeCell ref="BC13:BC15"/>
-    <mergeCell ref="BG13:BG15"/>
-    <mergeCell ref="BH13:BH15"/>
-    <mergeCell ref="BJ13:BJ15"/>
-    <mergeCell ref="BK13:BK15"/>
-    <mergeCell ref="BT9:BU9"/>
-    <mergeCell ref="BB10:BB12"/>
-    <mergeCell ref="BC10:BC12"/>
-    <mergeCell ref="BG10:BG12"/>
-    <mergeCell ref="BH10:BH12"/>
-    <mergeCell ref="BJ10:BJ12"/>
-    <mergeCell ref="BK10:BK12"/>
-    <mergeCell ref="BO10:BO12"/>
-    <mergeCell ref="BP10:BP12"/>
-    <mergeCell ref="BT10:BT12"/>
-    <mergeCell ref="BU10:BU12"/>
-    <mergeCell ref="BG7:BG9"/>
-    <mergeCell ref="BH7:BH9"/>
-    <mergeCell ref="BB9:BC9"/>
-    <mergeCell ref="BJ9:BK9"/>
-    <mergeCell ref="Q18:Q20"/>
-    <mergeCell ref="P18:P20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="U18:U20"/>
-    <mergeCell ref="W18:W20"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="Q21:Q23"/>
-    <mergeCell ref="U21:U23"/>
-    <mergeCell ref="P21:P23"/>
-    <mergeCell ref="W21:W23"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="T24:T26"/>
-    <mergeCell ref="T21:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="Q7:Q9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="U24:U26"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="W13:W15"/>
-    <mergeCell ref="T7:T9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="P24:P26"/>
-    <mergeCell ref="W24:W26"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="U13:U15"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="N13:N15"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="M13:M15"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="M24:M26"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="I8:J9"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="N10:N12"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="L52:L54"/>
-    <mergeCell ref="U53:U55"/>
-    <mergeCell ref="W53:W55"/>
-    <mergeCell ref="L58:L60"/>
-    <mergeCell ref="O58:O62"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="H61:I63"/>
-    <mergeCell ref="K61:L63"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="H55:H57"/>
-    <mergeCell ref="I55:I57"/>
-    <mergeCell ref="K55:K57"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="C47:I47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="I49:I51"/>
-    <mergeCell ref="K49:K51"/>
-    <mergeCell ref="L49:L51"/>
-    <mergeCell ref="O49:O57"/>
-    <mergeCell ref="B21:C26"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="W70:X70"/>
-    <mergeCell ref="AJ70:AK70"/>
-    <mergeCell ref="AM70:AN70"/>
-    <mergeCell ref="AU70:AV70"/>
-    <mergeCell ref="AZ70:BA70"/>
-    <mergeCell ref="BH70:BI70"/>
-    <mergeCell ref="BK70:BL70"/>
-    <mergeCell ref="BH67:BH69"/>
-    <mergeCell ref="BI67:BI69"/>
-    <mergeCell ref="BK67:BK69"/>
-    <mergeCell ref="BL67:BL69"/>
-    <mergeCell ref="AB68:AC69"/>
-    <mergeCell ref="AE68:AF69"/>
-    <mergeCell ref="AU67:AU69"/>
-    <mergeCell ref="AV67:AV69"/>
-    <mergeCell ref="AZ67:AZ69"/>
-    <mergeCell ref="BA67:BA69"/>
-    <mergeCell ref="BC67:BC69"/>
-    <mergeCell ref="BD67:BD69"/>
-    <mergeCell ref="T67:T69"/>
-    <mergeCell ref="U67:U69"/>
-    <mergeCell ref="W67:W69"/>
-    <mergeCell ref="X67:X69"/>
-    <mergeCell ref="AJ67:AJ69"/>
-    <mergeCell ref="AK67:AK69"/>
-    <mergeCell ref="BL64:BL66"/>
-    <mergeCell ref="AB65:AB67"/>
-    <mergeCell ref="AC65:AC67"/>
-    <mergeCell ref="AE65:AE67"/>
-    <mergeCell ref="AF65:AF67"/>
-    <mergeCell ref="X64:X66"/>
-    <mergeCell ref="AJ64:AJ66"/>
-    <mergeCell ref="AK64:AK66"/>
-    <mergeCell ref="AR67:AR69"/>
-    <mergeCell ref="AS67:AS69"/>
-    <mergeCell ref="AS64:AS66"/>
-    <mergeCell ref="AU64:AU66"/>
-    <mergeCell ref="AV64:AV66"/>
-    <mergeCell ref="AZ64:AZ66"/>
-    <mergeCell ref="BA64:BA66"/>
-    <mergeCell ref="BC64:BC66"/>
-    <mergeCell ref="AM64:AM66"/>
-    <mergeCell ref="AN64:AN66"/>
-    <mergeCell ref="AR64:AR66"/>
-    <mergeCell ref="AM67:AM69"/>
-    <mergeCell ref="AN67:AN69"/>
-    <mergeCell ref="P60:R60"/>
-    <mergeCell ref="BN60:BN62"/>
-    <mergeCell ref="AB62:AB64"/>
-    <mergeCell ref="AC62:AC64"/>
-    <mergeCell ref="AE62:AE64"/>
-    <mergeCell ref="AF62:AF64"/>
-    <mergeCell ref="BN63:BN65"/>
-    <mergeCell ref="T64:T66"/>
-    <mergeCell ref="U64:U66"/>
-    <mergeCell ref="W64:W66"/>
-    <mergeCell ref="BD59:BD61"/>
-    <mergeCell ref="BH59:BH61"/>
-    <mergeCell ref="BI59:BI61"/>
-    <mergeCell ref="BK59:BK61"/>
-    <mergeCell ref="BL59:BL61"/>
-    <mergeCell ref="AF59:AF61"/>
-    <mergeCell ref="AJ59:AJ61"/>
-    <mergeCell ref="AK59:AK61"/>
-    <mergeCell ref="AM59:AM61"/>
-    <mergeCell ref="AN59:AN61"/>
-    <mergeCell ref="AR59:AR61"/>
-    <mergeCell ref="T59:T61"/>
-    <mergeCell ref="U59:U61"/>
-    <mergeCell ref="W59:W61"/>
-    <mergeCell ref="X59:X61"/>
-    <mergeCell ref="AB59:AB61"/>
-    <mergeCell ref="AC59:AC61"/>
-    <mergeCell ref="AE59:AE61"/>
-    <mergeCell ref="BA56:BA58"/>
-    <mergeCell ref="BC56:BC58"/>
-    <mergeCell ref="AN56:AN58"/>
-    <mergeCell ref="AR56:AR58"/>
-    <mergeCell ref="AS56:AS58"/>
-    <mergeCell ref="AU56:AU58"/>
-    <mergeCell ref="AV56:AV58"/>
-    <mergeCell ref="AZ56:AZ58"/>
-    <mergeCell ref="AC56:AC58"/>
-    <mergeCell ref="AE56:AE58"/>
-    <mergeCell ref="AS59:AS61"/>
-    <mergeCell ref="AU59:AU61"/>
-    <mergeCell ref="AV59:AV61"/>
-    <mergeCell ref="AZ59:AZ61"/>
-    <mergeCell ref="BA59:BA61"/>
-    <mergeCell ref="BC59:BC61"/>
-    <mergeCell ref="AF56:AF58"/>
-    <mergeCell ref="AJ56:AJ58"/>
-    <mergeCell ref="AK56:AK58"/>
-    <mergeCell ref="AM56:AM58"/>
-    <mergeCell ref="BN54:BN56"/>
-    <mergeCell ref="BR54:BV58"/>
-    <mergeCell ref="AZ53:AZ55"/>
-    <mergeCell ref="BA53:BA55"/>
-    <mergeCell ref="BL56:BL58"/>
-    <mergeCell ref="BN57:BN59"/>
-    <mergeCell ref="BD56:BD58"/>
-    <mergeCell ref="BH56:BH58"/>
-    <mergeCell ref="BI56:BI58"/>
-    <mergeCell ref="BK56:BK58"/>
-    <mergeCell ref="BR59:BV72"/>
-    <mergeCell ref="BD64:BD66"/>
-    <mergeCell ref="BH64:BH66"/>
-    <mergeCell ref="BI64:BI66"/>
-    <mergeCell ref="BK64:BK66"/>
-    <mergeCell ref="AZ71:BA72"/>
-    <mergeCell ref="BH71:BI72"/>
-    <mergeCell ref="BL62:BL63"/>
-    <mergeCell ref="BK53:BK55"/>
-    <mergeCell ref="BL53:BL55"/>
-    <mergeCell ref="BH51:BH52"/>
-    <mergeCell ref="BK51:BK52"/>
-    <mergeCell ref="AF53:AF55"/>
-    <mergeCell ref="AJ53:AJ55"/>
-    <mergeCell ref="AK53:AK55"/>
-    <mergeCell ref="AM53:AM55"/>
-    <mergeCell ref="AN53:AN55"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="M10:M12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="W10:W12"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="N24:N26"/>
-    <mergeCell ref="Q24:Q26"/>
-    <mergeCell ref="T13:T15"/>
-    <mergeCell ref="X13:X15"/>
-    <mergeCell ref="T10:T12"/>
-    <mergeCell ref="X10:X12"/>
-    <mergeCell ref="Q10:Q12"/>
-    <mergeCell ref="U10:U12"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="BD46:BH48"/>
-    <mergeCell ref="BI46:BL48"/>
-    <mergeCell ref="AD46:AE48"/>
-    <mergeCell ref="AF46:AI48"/>
-    <mergeCell ref="AJ46:AQ48"/>
-    <mergeCell ref="AR46:AV46"/>
-    <mergeCell ref="AW46:AY48"/>
-    <mergeCell ref="AZ46:BC48"/>
-    <mergeCell ref="I66:O75"/>
-    <mergeCell ref="BS4:BV6"/>
-    <mergeCell ref="BM46:BQ48"/>
-    <mergeCell ref="BR46:BV53"/>
-    <mergeCell ref="BC53:BC55"/>
-    <mergeCell ref="BD53:BD55"/>
-    <mergeCell ref="BH53:BH55"/>
-    <mergeCell ref="BI53:BI55"/>
-    <mergeCell ref="T56:T58"/>
-    <mergeCell ref="U56:U58"/>
-    <mergeCell ref="W56:W58"/>
-    <mergeCell ref="X56:X58"/>
-    <mergeCell ref="AB56:AB58"/>
-    <mergeCell ref="AR53:AR55"/>
-    <mergeCell ref="AS53:AS55"/>
-    <mergeCell ref="AU53:AU55"/>
-    <mergeCell ref="AV53:AV55"/>
-    <mergeCell ref="AE53:AE55"/>
-    <mergeCell ref="T53:T55"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="Y46:AC48"/>
-    <mergeCell ref="X53:X55"/>
-    <mergeCell ref="AB53:AB55"/>
-    <mergeCell ref="AC53:AC55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/daerung.xlsx
+++ b/daerung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\수정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A2EDF5-9F9C-4B11-8CB9-024CE6820B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFA219F-9FD7-4A78-8722-9DC9705480E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="308">
   <si>
     <t/>
   </si>
@@ -793,9 +793,6 @@
   </si>
   <si>
     <t>김지용B</t>
-  </si>
-  <si>
-    <t>인지희</t>
   </si>
   <si>
     <t>신기동</t>
@@ -979,6 +976,22 @@
   </si>
   <si>
     <t>천진아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이다현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신의진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박연우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김수지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1709,6 +1722,165 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1716,142 +1888,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1888,30 +1925,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2253,14 +2266,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:BV76"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="100" width="5.28515625" style="1" customWidth="1"/>
     <col min="101" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:74" ht="26.1" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="1" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2338,34 +2351,34 @@
       <c r="AB2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="AC2" s="95" t="s">
-        <v>278</v>
-      </c>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="95"/>
-      <c r="AH2" s="95"/>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="86" t="s">
-        <v>272</v>
-      </c>
-      <c r="AK2" s="87"/>
-      <c r="AL2" s="87"/>
-      <c r="AM2" s="87"/>
-      <c r="AN2" s="87"/>
-      <c r="AO2" s="87"/>
-      <c r="AP2" s="87"/>
-      <c r="AQ2" s="87"/>
-      <c r="AR2" s="87"/>
-      <c r="AS2" s="87"/>
-      <c r="AT2" s="87"/>
-      <c r="AU2" s="87"/>
-      <c r="AV2" s="87"/>
-      <c r="AW2" s="87"/>
-      <c r="AX2" s="87"/>
-      <c r="AY2" s="87"/>
-      <c r="AZ2" s="88"/>
+      <c r="AC2" s="101" t="s">
+        <v>277</v>
+      </c>
+      <c r="AD2" s="101"/>
+      <c r="AE2" s="101"/>
+      <c r="AF2" s="101"/>
+      <c r="AG2" s="101"/>
+      <c r="AH2" s="101"/>
+      <c r="AI2" s="101"/>
+      <c r="AJ2" s="89" t="s">
+        <v>271</v>
+      </c>
+      <c r="AK2" s="90"/>
+      <c r="AL2" s="90"/>
+      <c r="AM2" s="90"/>
+      <c r="AN2" s="90"/>
+      <c r="AO2" s="90"/>
+      <c r="AP2" s="90"/>
+      <c r="AQ2" s="90"/>
+      <c r="AR2" s="90"/>
+      <c r="AS2" s="90"/>
+      <c r="AT2" s="90"/>
+      <c r="AU2" s="90"/>
+      <c r="AV2" s="90"/>
+      <c r="AW2" s="90"/>
+      <c r="AX2" s="90"/>
+      <c r="AY2" s="90"/>
+      <c r="AZ2" s="91"/>
       <c r="BA2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2433,113 +2446,113 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="3" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="Y3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="101"/>
+      <c r="AD3" s="101"/>
+      <c r="AE3" s="101"/>
+      <c r="AF3" s="101"/>
+      <c r="AG3" s="101"/>
+      <c r="AH3" s="101"/>
+      <c r="AI3" s="101"/>
+      <c r="AJ3" s="92"/>
+      <c r="AK3" s="93"/>
+      <c r="AL3" s="93"/>
+      <c r="AM3" s="93"/>
+      <c r="AN3" s="93"/>
+      <c r="AO3" s="93"/>
+      <c r="AP3" s="93"/>
+      <c r="AQ3" s="93"/>
+      <c r="AR3" s="93"/>
+      <c r="AS3" s="93"/>
+      <c r="AT3" s="93"/>
+      <c r="AU3" s="93"/>
+      <c r="AV3" s="93"/>
+      <c r="AW3" s="93"/>
+      <c r="AX3" s="93"/>
+      <c r="AY3" s="93"/>
+      <c r="AZ3" s="94"/>
+      <c r="BA3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="103" t="s">
         <v>270</v>
       </c>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="Y3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="95"/>
-      <c r="AD3" s="95"/>
-      <c r="AE3" s="95"/>
-      <c r="AF3" s="95"/>
-      <c r="AG3" s="95"/>
-      <c r="AH3" s="95"/>
-      <c r="AI3" s="95"/>
-      <c r="AJ3" s="89"/>
-      <c r="AK3" s="90"/>
-      <c r="AL3" s="90"/>
-      <c r="AM3" s="90"/>
-      <c r="AN3" s="90"/>
-      <c r="AO3" s="90"/>
-      <c r="AP3" s="90"/>
-      <c r="AQ3" s="90"/>
-      <c r="AR3" s="90"/>
-      <c r="AS3" s="90"/>
-      <c r="AT3" s="90"/>
-      <c r="AU3" s="90"/>
-      <c r="AV3" s="90"/>
-      <c r="AW3" s="90"/>
-      <c r="AX3" s="90"/>
-      <c r="AY3" s="90"/>
-      <c r="AZ3" s="91"/>
-      <c r="BA3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC3" s="97" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD3" s="97"/>
-      <c r="BE3" s="97"/>
-      <c r="BF3" s="97"/>
-      <c r="BG3" s="97"/>
-      <c r="BH3" s="97"/>
-      <c r="BI3" s="97"/>
-      <c r="BJ3" s="97"/>
-      <c r="BK3" s="97"/>
-      <c r="BL3" s="97"/>
-      <c r="BM3" s="97"/>
-      <c r="BN3" s="97"/>
-      <c r="BO3" s="97"/>
-      <c r="BP3" s="97"/>
-      <c r="BQ3" s="97"/>
-      <c r="BR3" s="97"/>
-      <c r="BS3" s="97"/>
-      <c r="BT3" s="97"/>
+      <c r="BD3" s="103"/>
+      <c r="BE3" s="103"/>
+      <c r="BF3" s="103"/>
+      <c r="BG3" s="103"/>
+      <c r="BH3" s="103"/>
+      <c r="BI3" s="103"/>
+      <c r="BJ3" s="103"/>
+      <c r="BK3" s="103"/>
+      <c r="BL3" s="103"/>
+      <c r="BM3" s="103"/>
+      <c r="BN3" s="103"/>
+      <c r="BO3" s="103"/>
+      <c r="BP3" s="103"/>
+      <c r="BQ3" s="103"/>
+      <c r="BR3" s="103"/>
+      <c r="BS3" s="103"/>
+      <c r="BT3" s="103"/>
       <c r="BV3" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="4" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="97"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="97"/>
-      <c r="W4" s="97"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="103"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
       <c r="Y4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2552,51 +2565,51 @@
       <c r="AB4" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="AC4" s="95"/>
-      <c r="AD4" s="95"/>
-      <c r="AE4" s="95"/>
-      <c r="AF4" s="95"/>
-      <c r="AG4" s="95"/>
-      <c r="AH4" s="95"/>
-      <c r="AI4" s="95"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="90"/>
-      <c r="AL4" s="90"/>
-      <c r="AM4" s="90"/>
-      <c r="AN4" s="90"/>
-      <c r="AO4" s="90"/>
-      <c r="AP4" s="90"/>
-      <c r="AQ4" s="90"/>
-      <c r="AR4" s="90"/>
-      <c r="AS4" s="90"/>
-      <c r="AT4" s="90"/>
-      <c r="AU4" s="90"/>
-      <c r="AV4" s="90"/>
-      <c r="AW4" s="90"/>
-      <c r="AX4" s="90"/>
-      <c r="AY4" s="90"/>
-      <c r="AZ4" s="91"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="92"/>
+      <c r="AK4" s="93"/>
+      <c r="AL4" s="93"/>
+      <c r="AM4" s="93"/>
+      <c r="AN4" s="93"/>
+      <c r="AO4" s="93"/>
+      <c r="AP4" s="93"/>
+      <c r="AQ4" s="93"/>
+      <c r="AR4" s="93"/>
+      <c r="AS4" s="93"/>
+      <c r="AT4" s="93"/>
+      <c r="AU4" s="93"/>
+      <c r="AV4" s="93"/>
+      <c r="AW4" s="93"/>
+      <c r="AX4" s="93"/>
+      <c r="AY4" s="93"/>
+      <c r="AZ4" s="94"/>
       <c r="BA4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="BC4" s="97"/>
-      <c r="BD4" s="97"/>
-      <c r="BE4" s="97"/>
-      <c r="BF4" s="97"/>
-      <c r="BG4" s="97"/>
-      <c r="BH4" s="97"/>
-      <c r="BI4" s="97"/>
-      <c r="BJ4" s="97"/>
-      <c r="BK4" s="97"/>
-      <c r="BL4" s="97"/>
-      <c r="BM4" s="97"/>
-      <c r="BN4" s="97"/>
-      <c r="BO4" s="97"/>
-      <c r="BP4" s="97"/>
-      <c r="BQ4" s="97"/>
-      <c r="BR4" s="97"/>
-      <c r="BS4" s="97"/>
-      <c r="BT4" s="97"/>
+      <c r="BC4" s="103"/>
+      <c r="BD4" s="103"/>
+      <c r="BE4" s="103"/>
+      <c r="BF4" s="103"/>
+      <c r="BG4" s="103"/>
+      <c r="BH4" s="103"/>
+      <c r="BI4" s="103"/>
+      <c r="BJ4" s="103"/>
+      <c r="BK4" s="103"/>
+      <c r="BL4" s="103"/>
+      <c r="BM4" s="103"/>
+      <c r="BN4" s="103"/>
+      <c r="BO4" s="103"/>
+      <c r="BP4" s="103"/>
+      <c r="BQ4" s="103"/>
+      <c r="BR4" s="103"/>
+      <c r="BS4" s="103"/>
+      <c r="BT4" s="103"/>
       <c r="BU4" s="10" t="s">
         <v>0</v>
       </c>
@@ -2604,75 +2617,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="5" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="97"/>
-      <c r="V5" s="97"/>
-      <c r="W5" s="97"/>
-      <c r="AC5" s="95"/>
-      <c r="AD5" s="95"/>
-      <c r="AE5" s="95"/>
-      <c r="AF5" s="95"/>
-      <c r="AG5" s="95"/>
-      <c r="AH5" s="95"/>
-      <c r="AI5" s="95"/>
-      <c r="AJ5" s="89"/>
-      <c r="AK5" s="90"/>
-      <c r="AL5" s="90"/>
-      <c r="AM5" s="90"/>
-      <c r="AN5" s="90"/>
-      <c r="AO5" s="90"/>
-      <c r="AP5" s="90"/>
-      <c r="AQ5" s="90"/>
-      <c r="AR5" s="90"/>
-      <c r="AS5" s="90"/>
-      <c r="AT5" s="90"/>
-      <c r="AU5" s="90"/>
-      <c r="AV5" s="90"/>
-      <c r="AW5" s="90"/>
-      <c r="AX5" s="90"/>
-      <c r="AY5" s="90"/>
-      <c r="AZ5" s="91"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="AC5" s="101"/>
+      <c r="AD5" s="101"/>
+      <c r="AE5" s="101"/>
+      <c r="AF5" s="101"/>
+      <c r="AG5" s="101"/>
+      <c r="AH5" s="101"/>
+      <c r="AI5" s="101"/>
+      <c r="AJ5" s="92"/>
+      <c r="AK5" s="93"/>
+      <c r="AL5" s="93"/>
+      <c r="AM5" s="93"/>
+      <c r="AN5" s="93"/>
+      <c r="AO5" s="93"/>
+      <c r="AP5" s="93"/>
+      <c r="AQ5" s="93"/>
+      <c r="AR5" s="93"/>
+      <c r="AS5" s="93"/>
+      <c r="AT5" s="93"/>
+      <c r="AU5" s="93"/>
+      <c r="AV5" s="93"/>
+      <c r="AW5" s="93"/>
+      <c r="AX5" s="93"/>
+      <c r="AY5" s="93"/>
+      <c r="AZ5" s="94"/>
       <c r="BA5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="BC5" s="97"/>
-      <c r="BD5" s="97"/>
-      <c r="BE5" s="97"/>
-      <c r="BF5" s="97"/>
-      <c r="BG5" s="97"/>
-      <c r="BH5" s="97"/>
-      <c r="BI5" s="97"/>
-      <c r="BJ5" s="97"/>
-      <c r="BK5" s="97"/>
-      <c r="BL5" s="97"/>
-      <c r="BM5" s="97"/>
-      <c r="BN5" s="97"/>
-      <c r="BO5" s="97"/>
-      <c r="BP5" s="97"/>
-      <c r="BQ5" s="97"/>
-      <c r="BR5" s="97"/>
-      <c r="BS5" s="97"/>
-      <c r="BT5" s="97"/>
+      <c r="BC5" s="103"/>
+      <c r="BD5" s="103"/>
+      <c r="BE5" s="103"/>
+      <c r="BF5" s="103"/>
+      <c r="BG5" s="103"/>
+      <c r="BH5" s="103"/>
+      <c r="BI5" s="103"/>
+      <c r="BJ5" s="103"/>
+      <c r="BK5" s="103"/>
+      <c r="BL5" s="103"/>
+      <c r="BM5" s="103"/>
+      <c r="BN5" s="103"/>
+      <c r="BO5" s="103"/>
+      <c r="BP5" s="103"/>
+      <c r="BQ5" s="103"/>
+      <c r="BR5" s="103"/>
+      <c r="BS5" s="103"/>
+      <c r="BT5" s="103"/>
       <c r="BU5" s="10" t="s">
         <v>0</v>
       </c>
@@ -2680,37 +2693,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="6" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="AC6" s="95"/>
-      <c r="AD6" s="95"/>
-      <c r="AE6" s="95"/>
-      <c r="AF6" s="95"/>
-      <c r="AG6" s="95"/>
-      <c r="AH6" s="95"/>
-      <c r="AI6" s="95"/>
-      <c r="AJ6" s="89"/>
-      <c r="AK6" s="90"/>
-      <c r="AL6" s="90"/>
-      <c r="AM6" s="90"/>
-      <c r="AN6" s="90"/>
-      <c r="AO6" s="90"/>
-      <c r="AP6" s="90"/>
-      <c r="AQ6" s="90"/>
-      <c r="AR6" s="90"/>
-      <c r="AS6" s="90"/>
-      <c r="AT6" s="90"/>
-      <c r="AU6" s="90"/>
-      <c r="AV6" s="90"/>
-      <c r="AW6" s="90"/>
-      <c r="AX6" s="90"/>
-      <c r="AY6" s="90"/>
-      <c r="AZ6" s="91"/>
+      <c r="AC6" s="101"/>
+      <c r="AD6" s="101"/>
+      <c r="AE6" s="101"/>
+      <c r="AF6" s="101"/>
+      <c r="AG6" s="101"/>
+      <c r="AH6" s="101"/>
+      <c r="AI6" s="101"/>
+      <c r="AJ6" s="92"/>
+      <c r="AK6" s="93"/>
+      <c r="AL6" s="93"/>
+      <c r="AM6" s="93"/>
+      <c r="AN6" s="93"/>
+      <c r="AO6" s="93"/>
+      <c r="AP6" s="93"/>
+      <c r="AQ6" s="93"/>
+      <c r="AR6" s="93"/>
+      <c r="AS6" s="93"/>
+      <c r="AT6" s="93"/>
+      <c r="AU6" s="93"/>
+      <c r="AV6" s="93"/>
+      <c r="AW6" s="93"/>
+      <c r="AX6" s="93"/>
+      <c r="AY6" s="93"/>
+      <c r="AZ6" s="94"/>
       <c r="BA6" s="14" t="s">
         <v>0</v>
       </c>
@@ -2727,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="7" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="14" t="s">
         <v>0</v>
       </c>
@@ -2737,7 +2750,7 @@
       <c r="G7" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="136" t="s">
+      <c r="M7" s="86" t="s">
         <v>2</v>
       </c>
       <c r="N7" s="71" t="s">
@@ -2759,38 +2772,38 @@
         <v>7</v>
       </c>
       <c r="W7" s="71" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X7" s="71" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="AC7" s="95"/>
-      <c r="AD7" s="95"/>
-      <c r="AE7" s="95"/>
-      <c r="AF7" s="95"/>
-      <c r="AG7" s="95"/>
-      <c r="AH7" s="95"/>
-      <c r="AI7" s="95"/>
-      <c r="AJ7" s="89"/>
-      <c r="AK7" s="90"/>
-      <c r="AL7" s="90"/>
-      <c r="AM7" s="90"/>
-      <c r="AN7" s="90"/>
-      <c r="AO7" s="90"/>
-      <c r="AP7" s="90"/>
-      <c r="AQ7" s="90"/>
-      <c r="AR7" s="90"/>
-      <c r="AS7" s="90"/>
-      <c r="AT7" s="90"/>
-      <c r="AU7" s="90"/>
-      <c r="AV7" s="90"/>
-      <c r="AW7" s="90"/>
-      <c r="AX7" s="90"/>
-      <c r="AY7" s="90"/>
-      <c r="AZ7" s="91"/>
+      <c r="AC7" s="101"/>
+      <c r="AD7" s="101"/>
+      <c r="AE7" s="101"/>
+      <c r="AF7" s="101"/>
+      <c r="AG7" s="101"/>
+      <c r="AH7" s="101"/>
+      <c r="AI7" s="101"/>
+      <c r="AJ7" s="92"/>
+      <c r="AK7" s="93"/>
+      <c r="AL7" s="93"/>
+      <c r="AM7" s="93"/>
+      <c r="AN7" s="93"/>
+      <c r="AO7" s="93"/>
+      <c r="AP7" s="93"/>
+      <c r="AQ7" s="93"/>
+      <c r="AR7" s="93"/>
+      <c r="AS7" s="93"/>
+      <c r="AT7" s="93"/>
+      <c r="AU7" s="93"/>
+      <c r="AV7" s="93"/>
+      <c r="AW7" s="93"/>
+      <c r="AX7" s="93"/>
+      <c r="AY7" s="93"/>
+      <c r="AZ7" s="94"/>
       <c r="BA7" s="14" t="s">
         <v>0</v>
       </c>
@@ -2801,13 +2814,13 @@
         <v>9</v>
       </c>
       <c r="BS7" s="85" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BT7" s="85"/>
       <c r="BU7" s="85"/>
-      <c r="BV7" s="96"/>
+      <c r="BV7" s="102"/>
     </row>
-    <row r="8" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="8" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="14" t="s">
         <v>0</v>
       </c>
@@ -2820,16 +2833,16 @@
       <c r="G8" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="I8" s="134" t="s">
+      <c r="I8" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="135" t="s">
+      <c r="J8" s="75" t="s">
         <v>0</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M8" s="137" t="s">
+      <c r="M8" s="87" t="s">
         <v>0</v>
       </c>
       <c r="N8" s="72" t="s">
@@ -2862,30 +2875,30 @@
       <c r="AB8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="AC8" s="95"/>
-      <c r="AD8" s="95"/>
-      <c r="AE8" s="95"/>
-      <c r="AF8" s="95"/>
-      <c r="AG8" s="95"/>
-      <c r="AH8" s="95"/>
-      <c r="AI8" s="95"/>
-      <c r="AJ8" s="89"/>
-      <c r="AK8" s="90"/>
-      <c r="AL8" s="90"/>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="90"/>
-      <c r="AO8" s="90"/>
-      <c r="AP8" s="90"/>
-      <c r="AQ8" s="90"/>
-      <c r="AR8" s="90"/>
-      <c r="AS8" s="90"/>
-      <c r="AT8" s="90"/>
-      <c r="AU8" s="90"/>
-      <c r="AV8" s="90"/>
-      <c r="AW8" s="90"/>
-      <c r="AX8" s="90"/>
-      <c r="AY8" s="90"/>
-      <c r="AZ8" s="91"/>
+      <c r="AC8" s="101"/>
+      <c r="AD8" s="101"/>
+      <c r="AE8" s="101"/>
+      <c r="AF8" s="101"/>
+      <c r="AG8" s="101"/>
+      <c r="AH8" s="101"/>
+      <c r="AI8" s="101"/>
+      <c r="AJ8" s="92"/>
+      <c r="AK8" s="93"/>
+      <c r="AL8" s="93"/>
+      <c r="AM8" s="93"/>
+      <c r="AN8" s="93"/>
+      <c r="AO8" s="93"/>
+      <c r="AP8" s="93"/>
+      <c r="AQ8" s="93"/>
+      <c r="AR8" s="93"/>
+      <c r="AS8" s="93"/>
+      <c r="AT8" s="93"/>
+      <c r="AU8" s="93"/>
+      <c r="AV8" s="93"/>
+      <c r="AW8" s="93"/>
+      <c r="AX8" s="93"/>
+      <c r="AY8" s="93"/>
+      <c r="AZ8" s="94"/>
       <c r="BA8" s="14" t="s">
         <v>0</v>
       </c>
@@ -2911,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="9" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="16" t="s">
         <v>0</v>
       </c>
@@ -2924,13 +2937,13 @@
       <c r="G9" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="J9" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="M9" s="138" t="s">
+      <c r="I9" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="M9" s="88" t="s">
         <v>0</v>
       </c>
       <c r="N9" s="73" t="s">
@@ -2963,30 +2976,30 @@
       <c r="AB9" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="AC9" s="95"/>
-      <c r="AD9" s="95"/>
-      <c r="AE9" s="95"/>
-      <c r="AF9" s="95"/>
-      <c r="AG9" s="95"/>
-      <c r="AH9" s="95"/>
-      <c r="AI9" s="95"/>
-      <c r="AJ9" s="89"/>
-      <c r="AK9" s="90"/>
-      <c r="AL9" s="90"/>
-      <c r="AM9" s="90"/>
-      <c r="AN9" s="90"/>
-      <c r="AO9" s="90"/>
-      <c r="AP9" s="90"/>
-      <c r="AQ9" s="90"/>
-      <c r="AR9" s="90"/>
-      <c r="AS9" s="90"/>
-      <c r="AT9" s="90"/>
-      <c r="AU9" s="90"/>
-      <c r="AV9" s="90"/>
-      <c r="AW9" s="90"/>
-      <c r="AX9" s="90"/>
-      <c r="AY9" s="90"/>
-      <c r="AZ9" s="91"/>
+      <c r="AC9" s="101"/>
+      <c r="AD9" s="101"/>
+      <c r="AE9" s="101"/>
+      <c r="AF9" s="101"/>
+      <c r="AG9" s="101"/>
+      <c r="AH9" s="101"/>
+      <c r="AI9" s="101"/>
+      <c r="AJ9" s="92"/>
+      <c r="AK9" s="93"/>
+      <c r="AL9" s="93"/>
+      <c r="AM9" s="93"/>
+      <c r="AN9" s="93"/>
+      <c r="AO9" s="93"/>
+      <c r="AP9" s="93"/>
+      <c r="AQ9" s="93"/>
+      <c r="AR9" s="93"/>
+      <c r="AS9" s="93"/>
+      <c r="AT9" s="93"/>
+      <c r="AU9" s="93"/>
+      <c r="AV9" s="93"/>
+      <c r="AW9" s="93"/>
+      <c r="AX9" s="93"/>
+      <c r="AY9" s="93"/>
+      <c r="AZ9" s="94"/>
       <c r="BA9" s="14" t="s">
         <v>0</v>
       </c>
@@ -3027,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="10" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
@@ -3063,10 +3076,10 @@
       </c>
       <c r="U10" s="71"/>
       <c r="W10" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="X10" s="71" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AA10" s="81" t="s">
         <v>25</v>
@@ -3074,30 +3087,30 @@
       <c r="AB10" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="AC10" s="95"/>
-      <c r="AD10" s="95"/>
-      <c r="AE10" s="95"/>
-      <c r="AF10" s="95"/>
-      <c r="AG10" s="95"/>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="95"/>
-      <c r="AJ10" s="89"/>
-      <c r="AK10" s="90"/>
-      <c r="AL10" s="90"/>
-      <c r="AM10" s="90"/>
-      <c r="AN10" s="90"/>
-      <c r="AO10" s="90"/>
-      <c r="AP10" s="90"/>
-      <c r="AQ10" s="90"/>
-      <c r="AR10" s="90"/>
-      <c r="AS10" s="90"/>
-      <c r="AT10" s="90"/>
-      <c r="AU10" s="90"/>
-      <c r="AV10" s="90"/>
-      <c r="AW10" s="90"/>
-      <c r="AX10" s="90"/>
-      <c r="AY10" s="90"/>
-      <c r="AZ10" s="91"/>
+      <c r="AC10" s="101"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="101"/>
+      <c r="AF10" s="101"/>
+      <c r="AG10" s="101"/>
+      <c r="AH10" s="101"/>
+      <c r="AI10" s="101"/>
+      <c r="AJ10" s="92"/>
+      <c r="AK10" s="93"/>
+      <c r="AL10" s="93"/>
+      <c r="AM10" s="93"/>
+      <c r="AN10" s="93"/>
+      <c r="AO10" s="93"/>
+      <c r="AP10" s="93"/>
+      <c r="AQ10" s="93"/>
+      <c r="AR10" s="93"/>
+      <c r="AS10" s="93"/>
+      <c r="AT10" s="93"/>
+      <c r="AU10" s="93"/>
+      <c r="AV10" s="93"/>
+      <c r="AW10" s="93"/>
+      <c r="AX10" s="93"/>
+      <c r="AY10" s="93"/>
+      <c r="AZ10" s="94"/>
       <c r="BA10" s="14" t="s">
         <v>0</v>
       </c>
@@ -3138,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="11" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="16" t="s">
         <v>0</v>
       </c>
@@ -3185,30 +3198,30 @@
       <c r="AB11" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="AC11" s="95"/>
-      <c r="AD11" s="95"/>
-      <c r="AE11" s="95"/>
-      <c r="AF11" s="95"/>
-      <c r="AG11" s="95"/>
-      <c r="AH11" s="95"/>
-      <c r="AI11" s="95"/>
-      <c r="AJ11" s="89"/>
-      <c r="AK11" s="90"/>
-      <c r="AL11" s="90"/>
-      <c r="AM11" s="90"/>
-      <c r="AN11" s="90"/>
-      <c r="AO11" s="90"/>
-      <c r="AP11" s="90"/>
-      <c r="AQ11" s="90"/>
-      <c r="AR11" s="90"/>
-      <c r="AS11" s="90"/>
-      <c r="AT11" s="90"/>
-      <c r="AU11" s="90"/>
-      <c r="AV11" s="90"/>
-      <c r="AW11" s="90"/>
-      <c r="AX11" s="90"/>
-      <c r="AY11" s="90"/>
-      <c r="AZ11" s="91"/>
+      <c r="AC11" s="101"/>
+      <c r="AD11" s="101"/>
+      <c r="AE11" s="101"/>
+      <c r="AF11" s="101"/>
+      <c r="AG11" s="101"/>
+      <c r="AH11" s="101"/>
+      <c r="AI11" s="101"/>
+      <c r="AJ11" s="92"/>
+      <c r="AK11" s="93"/>
+      <c r="AL11" s="93"/>
+      <c r="AM11" s="93"/>
+      <c r="AN11" s="93"/>
+      <c r="AO11" s="93"/>
+      <c r="AP11" s="93"/>
+      <c r="AQ11" s="93"/>
+      <c r="AR11" s="93"/>
+      <c r="AS11" s="93"/>
+      <c r="AT11" s="93"/>
+      <c r="AU11" s="93"/>
+      <c r="AV11" s="93"/>
+      <c r="AW11" s="93"/>
+      <c r="AX11" s="93"/>
+      <c r="AY11" s="93"/>
+      <c r="AZ11" s="94"/>
       <c r="BA11" s="14" t="s">
         <v>0</v>
       </c>
@@ -3249,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="12" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="16" t="s">
         <v>0</v>
       </c>
@@ -3290,33 +3303,33 @@
       <c r="X12" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="AB12" s="92" t="s">
+      <c r="AB12" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="AC12" s="95"/>
-      <c r="AD12" s="95"/>
-      <c r="AE12" s="95"/>
-      <c r="AF12" s="95"/>
-      <c r="AG12" s="95"/>
-      <c r="AH12" s="95"/>
-      <c r="AI12" s="95"/>
-      <c r="AJ12" s="89"/>
-      <c r="AK12" s="90"/>
-      <c r="AL12" s="90"/>
-      <c r="AM12" s="90"/>
-      <c r="AN12" s="90"/>
-      <c r="AO12" s="90"/>
-      <c r="AP12" s="90"/>
-      <c r="AQ12" s="90"/>
-      <c r="AR12" s="90"/>
-      <c r="AS12" s="90"/>
-      <c r="AT12" s="90"/>
-      <c r="AU12" s="90"/>
-      <c r="AV12" s="90"/>
-      <c r="AW12" s="90"/>
-      <c r="AX12" s="90"/>
-      <c r="AY12" s="90"/>
-      <c r="AZ12" s="91"/>
+      <c r="AC12" s="101"/>
+      <c r="AD12" s="101"/>
+      <c r="AE12" s="101"/>
+      <c r="AF12" s="101"/>
+      <c r="AG12" s="101"/>
+      <c r="AH12" s="101"/>
+      <c r="AI12" s="101"/>
+      <c r="AJ12" s="92"/>
+      <c r="AK12" s="93"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="93"/>
+      <c r="AN12" s="93"/>
+      <c r="AO12" s="93"/>
+      <c r="AP12" s="93"/>
+      <c r="AQ12" s="93"/>
+      <c r="AR12" s="93"/>
+      <c r="AS12" s="93"/>
+      <c r="AT12" s="93"/>
+      <c r="AU12" s="93"/>
+      <c r="AV12" s="93"/>
+      <c r="AW12" s="93"/>
+      <c r="AX12" s="93"/>
+      <c r="AY12" s="93"/>
+      <c r="AZ12" s="94"/>
       <c r="BA12" s="14" t="s">
         <v>0</v>
       </c>
@@ -3357,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="13" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="16" t="s">
         <v>0</v>
       </c>
@@ -3395,38 +3408,38 @@
         <v>0</v>
       </c>
       <c r="W13" s="71" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="X13" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="AB13" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="95"/>
-      <c r="AD13" s="95"/>
-      <c r="AE13" s="95"/>
-      <c r="AF13" s="95"/>
-      <c r="AG13" s="95"/>
-      <c r="AH13" s="95"/>
-      <c r="AI13" s="95"/>
-      <c r="AJ13" s="89"/>
-      <c r="AK13" s="90"/>
-      <c r="AL13" s="90"/>
-      <c r="AM13" s="90"/>
-      <c r="AN13" s="90"/>
-      <c r="AO13" s="90"/>
-      <c r="AP13" s="90"/>
-      <c r="AQ13" s="90"/>
-      <c r="AR13" s="90"/>
-      <c r="AS13" s="90"/>
-      <c r="AT13" s="90"/>
-      <c r="AU13" s="90"/>
-      <c r="AV13" s="90"/>
-      <c r="AW13" s="90"/>
-      <c r="AX13" s="90"/>
-      <c r="AY13" s="90"/>
-      <c r="AZ13" s="91"/>
+      <c r="AB13" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="101"/>
+      <c r="AD13" s="101"/>
+      <c r="AE13" s="101"/>
+      <c r="AF13" s="101"/>
+      <c r="AG13" s="101"/>
+      <c r="AH13" s="101"/>
+      <c r="AI13" s="101"/>
+      <c r="AJ13" s="92"/>
+      <c r="AK13" s="93"/>
+      <c r="AL13" s="93"/>
+      <c r="AM13" s="93"/>
+      <c r="AN13" s="93"/>
+      <c r="AO13" s="93"/>
+      <c r="AP13" s="93"/>
+      <c r="AQ13" s="93"/>
+      <c r="AR13" s="93"/>
+      <c r="AS13" s="93"/>
+      <c r="AT13" s="93"/>
+      <c r="AU13" s="93"/>
+      <c r="AV13" s="93"/>
+      <c r="AW13" s="93"/>
+      <c r="AX13" s="93"/>
+      <c r="AY13" s="93"/>
+      <c r="AZ13" s="94"/>
       <c r="BA13" s="14" t="s">
         <v>0</v>
       </c>
@@ -3467,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="14" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
         <v>0</v>
       </c>
@@ -3510,33 +3523,33 @@
       <c r="X14" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB14" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="95"/>
-      <c r="AD14" s="95"/>
-      <c r="AE14" s="95"/>
-      <c r="AF14" s="95"/>
-      <c r="AG14" s="95"/>
-      <c r="AH14" s="95"/>
-      <c r="AI14" s="95"/>
-      <c r="AJ14" s="89"/>
-      <c r="AK14" s="90"/>
-      <c r="AL14" s="90"/>
-      <c r="AM14" s="90"/>
-      <c r="AN14" s="90"/>
-      <c r="AO14" s="90"/>
-      <c r="AP14" s="90"/>
-      <c r="AQ14" s="90"/>
-      <c r="AR14" s="90"/>
-      <c r="AS14" s="90"/>
-      <c r="AT14" s="90"/>
-      <c r="AU14" s="90"/>
-      <c r="AV14" s="90"/>
-      <c r="AW14" s="90"/>
-      <c r="AX14" s="90"/>
-      <c r="AY14" s="90"/>
-      <c r="AZ14" s="91"/>
+      <c r="AB14" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="101"/>
+      <c r="AD14" s="101"/>
+      <c r="AE14" s="101"/>
+      <c r="AF14" s="101"/>
+      <c r="AG14" s="101"/>
+      <c r="AH14" s="101"/>
+      <c r="AI14" s="101"/>
+      <c r="AJ14" s="92"/>
+      <c r="AK14" s="93"/>
+      <c r="AL14" s="93"/>
+      <c r="AM14" s="93"/>
+      <c r="AN14" s="93"/>
+      <c r="AO14" s="93"/>
+      <c r="AP14" s="93"/>
+      <c r="AQ14" s="93"/>
+      <c r="AR14" s="93"/>
+      <c r="AS14" s="93"/>
+      <c r="AT14" s="93"/>
+      <c r="AU14" s="93"/>
+      <c r="AV14" s="93"/>
+      <c r="AW14" s="93"/>
+      <c r="AX14" s="93"/>
+      <c r="AY14" s="93"/>
+      <c r="AZ14" s="94"/>
       <c r="BA14" s="14" t="s">
         <v>0</v>
       </c>
@@ -3577,7 +3590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="15" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="16" t="s">
         <v>0</v>
       </c>
@@ -3620,33 +3633,33 @@
       <c r="X15" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="AB15" s="92" t="s">
+      <c r="AB15" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="AC15" s="95"/>
-      <c r="AD15" s="95"/>
-      <c r="AE15" s="95"/>
-      <c r="AF15" s="95"/>
-      <c r="AG15" s="95"/>
-      <c r="AH15" s="95"/>
-      <c r="AI15" s="95"/>
-      <c r="AJ15" s="89"/>
-      <c r="AK15" s="90"/>
-      <c r="AL15" s="90"/>
-      <c r="AM15" s="90"/>
-      <c r="AN15" s="90"/>
-      <c r="AO15" s="90"/>
-      <c r="AP15" s="90"/>
-      <c r="AQ15" s="90"/>
-      <c r="AR15" s="90"/>
-      <c r="AS15" s="90"/>
-      <c r="AT15" s="90"/>
-      <c r="AU15" s="90"/>
-      <c r="AV15" s="90"/>
-      <c r="AW15" s="90"/>
-      <c r="AX15" s="90"/>
-      <c r="AY15" s="90"/>
-      <c r="AZ15" s="91"/>
+      <c r="AC15" s="101"/>
+      <c r="AD15" s="101"/>
+      <c r="AE15" s="101"/>
+      <c r="AF15" s="101"/>
+      <c r="AG15" s="101"/>
+      <c r="AH15" s="101"/>
+      <c r="AI15" s="101"/>
+      <c r="AJ15" s="92"/>
+      <c r="AK15" s="93"/>
+      <c r="AL15" s="93"/>
+      <c r="AM15" s="93"/>
+      <c r="AN15" s="93"/>
+      <c r="AO15" s="93"/>
+      <c r="AP15" s="93"/>
+      <c r="AQ15" s="93"/>
+      <c r="AR15" s="93"/>
+      <c r="AS15" s="93"/>
+      <c r="AT15" s="93"/>
+      <c r="AU15" s="93"/>
+      <c r="AV15" s="93"/>
+      <c r="AW15" s="93"/>
+      <c r="AX15" s="93"/>
+      <c r="AY15" s="93"/>
+      <c r="AZ15" s="94"/>
       <c r="BA15" s="14" t="s">
         <v>0</v>
       </c>
@@ -3687,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="16" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="16" t="s">
         <v>0</v>
       </c>
@@ -3726,33 +3739,33 @@
       <c r="X16" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="AB16" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="95"/>
-      <c r="AD16" s="95"/>
-      <c r="AE16" s="95"/>
-      <c r="AF16" s="95"/>
-      <c r="AG16" s="95"/>
-      <c r="AH16" s="95"/>
-      <c r="AI16" s="95"/>
-      <c r="AJ16" s="89"/>
-      <c r="AK16" s="90"/>
-      <c r="AL16" s="90"/>
-      <c r="AM16" s="90"/>
-      <c r="AN16" s="90"/>
-      <c r="AO16" s="90"/>
-      <c r="AP16" s="90"/>
-      <c r="AQ16" s="90"/>
-      <c r="AR16" s="90"/>
-      <c r="AS16" s="90"/>
-      <c r="AT16" s="90"/>
-      <c r="AU16" s="90"/>
-      <c r="AV16" s="90"/>
-      <c r="AW16" s="90"/>
-      <c r="AX16" s="90"/>
-      <c r="AY16" s="90"/>
-      <c r="AZ16" s="91"/>
+      <c r="AB16" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="101"/>
+      <c r="AD16" s="101"/>
+      <c r="AE16" s="101"/>
+      <c r="AF16" s="101"/>
+      <c r="AG16" s="101"/>
+      <c r="AH16" s="101"/>
+      <c r="AI16" s="101"/>
+      <c r="AJ16" s="92"/>
+      <c r="AK16" s="93"/>
+      <c r="AL16" s="93"/>
+      <c r="AM16" s="93"/>
+      <c r="AN16" s="93"/>
+      <c r="AO16" s="93"/>
+      <c r="AP16" s="93"/>
+      <c r="AQ16" s="93"/>
+      <c r="AR16" s="93"/>
+      <c r="AS16" s="93"/>
+      <c r="AT16" s="93"/>
+      <c r="AU16" s="93"/>
+      <c r="AV16" s="93"/>
+      <c r="AW16" s="93"/>
+      <c r="AX16" s="93"/>
+      <c r="AY16" s="93"/>
+      <c r="AZ16" s="94"/>
       <c r="BA16" s="14" t="s">
         <v>0</v>
       </c>
@@ -3784,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="17" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="16" t="s">
         <v>0</v>
       </c>
@@ -3815,33 +3828,33 @@
       <c r="U17" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="AB17" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="95"/>
-      <c r="AD17" s="95"/>
-      <c r="AE17" s="95"/>
-      <c r="AF17" s="95"/>
-      <c r="AG17" s="95"/>
-      <c r="AH17" s="95"/>
-      <c r="AI17" s="95"/>
-      <c r="AJ17" s="89"/>
-      <c r="AK17" s="90"/>
-      <c r="AL17" s="90"/>
-      <c r="AM17" s="90"/>
-      <c r="AN17" s="90"/>
-      <c r="AO17" s="90"/>
-      <c r="AP17" s="90"/>
-      <c r="AQ17" s="90"/>
-      <c r="AR17" s="90"/>
-      <c r="AS17" s="90"/>
-      <c r="AT17" s="90"/>
-      <c r="AU17" s="90"/>
-      <c r="AV17" s="90"/>
-      <c r="AW17" s="90"/>
-      <c r="AX17" s="90"/>
-      <c r="AY17" s="90"/>
-      <c r="AZ17" s="91"/>
+      <c r="AB17" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="101"/>
+      <c r="AD17" s="101"/>
+      <c r="AE17" s="101"/>
+      <c r="AF17" s="101"/>
+      <c r="AG17" s="101"/>
+      <c r="AH17" s="101"/>
+      <c r="AI17" s="101"/>
+      <c r="AJ17" s="92"/>
+      <c r="AK17" s="93"/>
+      <c r="AL17" s="93"/>
+      <c r="AM17" s="93"/>
+      <c r="AN17" s="93"/>
+      <c r="AO17" s="93"/>
+      <c r="AP17" s="93"/>
+      <c r="AQ17" s="93"/>
+      <c r="AR17" s="93"/>
+      <c r="AS17" s="93"/>
+      <c r="AT17" s="93"/>
+      <c r="AU17" s="93"/>
+      <c r="AV17" s="93"/>
+      <c r="AW17" s="93"/>
+      <c r="AX17" s="93"/>
+      <c r="AY17" s="93"/>
+      <c r="AZ17" s="94"/>
       <c r="BA17" s="14" t="s">
         <v>0</v>
       </c>
@@ -3867,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="18" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="14" t="s">
         <v>0</v>
       </c>
@@ -3881,7 +3894,7 @@
       <c r="I18" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="J18" s="136" t="s">
+      <c r="J18" s="86" t="s">
         <v>0</v>
       </c>
       <c r="M18" s="71" t="s">
@@ -3908,33 +3921,33 @@
       <c r="X18" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="AB18" s="92" t="s">
+      <c r="AB18" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="AC18" s="95"/>
-      <c r="AD18" s="95"/>
-      <c r="AE18" s="95"/>
-      <c r="AF18" s="95"/>
-      <c r="AG18" s="95"/>
-      <c r="AH18" s="95"/>
-      <c r="AI18" s="95"/>
-      <c r="AJ18" s="89"/>
-      <c r="AK18" s="90"/>
-      <c r="AL18" s="90"/>
-      <c r="AM18" s="90"/>
-      <c r="AN18" s="90"/>
-      <c r="AO18" s="90"/>
-      <c r="AP18" s="90"/>
-      <c r="AQ18" s="90"/>
-      <c r="AR18" s="90"/>
-      <c r="AS18" s="90"/>
-      <c r="AT18" s="90"/>
-      <c r="AU18" s="90"/>
-      <c r="AV18" s="90"/>
-      <c r="AW18" s="90"/>
-      <c r="AX18" s="90"/>
-      <c r="AY18" s="90"/>
-      <c r="AZ18" s="91"/>
+      <c r="AC18" s="101"/>
+      <c r="AD18" s="101"/>
+      <c r="AE18" s="101"/>
+      <c r="AF18" s="101"/>
+      <c r="AG18" s="101"/>
+      <c r="AH18" s="101"/>
+      <c r="AI18" s="101"/>
+      <c r="AJ18" s="92"/>
+      <c r="AK18" s="93"/>
+      <c r="AL18" s="93"/>
+      <c r="AM18" s="93"/>
+      <c r="AN18" s="93"/>
+      <c r="AO18" s="93"/>
+      <c r="AP18" s="93"/>
+      <c r="AQ18" s="93"/>
+      <c r="AR18" s="93"/>
+      <c r="AS18" s="93"/>
+      <c r="AT18" s="93"/>
+      <c r="AU18" s="93"/>
+      <c r="AV18" s="93"/>
+      <c r="AW18" s="93"/>
+      <c r="AX18" s="93"/>
+      <c r="AY18" s="93"/>
+      <c r="AZ18" s="94"/>
       <c r="BA18" s="14" t="s">
         <v>0</v>
       </c>
@@ -3954,7 +3967,7 @@
         <v>80</v>
       </c>
       <c r="BK18" s="71" t="s">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="BO18" s="71" t="s">
         <v>0</v>
@@ -3975,7 +3988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="19" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="14" t="s">
         <v>0</v>
       </c>
@@ -3991,7 +4004,7 @@
       <c r="I19" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="J19" s="137" t="s">
+      <c r="J19" s="87" t="s">
         <v>0</v>
       </c>
       <c r="M19" s="72" t="s">
@@ -4018,33 +4031,33 @@
       <c r="X19" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB19" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="95"/>
-      <c r="AD19" s="95"/>
-      <c r="AE19" s="95"/>
-      <c r="AF19" s="95"/>
-      <c r="AG19" s="95"/>
-      <c r="AH19" s="95"/>
-      <c r="AI19" s="95"/>
-      <c r="AJ19" s="89"/>
-      <c r="AK19" s="90"/>
-      <c r="AL19" s="90"/>
-      <c r="AM19" s="90"/>
-      <c r="AN19" s="90"/>
-      <c r="AO19" s="90"/>
-      <c r="AP19" s="90"/>
-      <c r="AQ19" s="90"/>
-      <c r="AR19" s="90"/>
-      <c r="AS19" s="90"/>
-      <c r="AT19" s="90"/>
-      <c r="AU19" s="90"/>
-      <c r="AV19" s="90"/>
-      <c r="AW19" s="90"/>
-      <c r="AX19" s="90"/>
-      <c r="AY19" s="90"/>
-      <c r="AZ19" s="91"/>
+      <c r="AB19" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="101"/>
+      <c r="AD19" s="101"/>
+      <c r="AE19" s="101"/>
+      <c r="AF19" s="101"/>
+      <c r="AG19" s="101"/>
+      <c r="AH19" s="101"/>
+      <c r="AI19" s="101"/>
+      <c r="AJ19" s="92"/>
+      <c r="AK19" s="93"/>
+      <c r="AL19" s="93"/>
+      <c r="AM19" s="93"/>
+      <c r="AN19" s="93"/>
+      <c r="AO19" s="93"/>
+      <c r="AP19" s="93"/>
+      <c r="AQ19" s="93"/>
+      <c r="AR19" s="93"/>
+      <c r="AS19" s="93"/>
+      <c r="AT19" s="93"/>
+      <c r="AU19" s="93"/>
+      <c r="AV19" s="93"/>
+      <c r="AW19" s="93"/>
+      <c r="AX19" s="93"/>
+      <c r="AY19" s="93"/>
+      <c r="AZ19" s="94"/>
       <c r="BA19" s="14" t="s">
         <v>0</v>
       </c>
@@ -4085,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="20" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="14" t="s">
         <v>0</v>
       </c>
@@ -4101,7 +4114,7 @@
       <c r="I20" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="J20" s="138" t="s">
+      <c r="J20" s="88" t="s">
         <v>0</v>
       </c>
       <c r="M20" s="73" t="s">
@@ -4128,33 +4141,33 @@
       <c r="X20" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="AB20" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="95"/>
-      <c r="AD20" s="95"/>
-      <c r="AE20" s="95"/>
-      <c r="AF20" s="95"/>
-      <c r="AG20" s="95"/>
-      <c r="AH20" s="95"/>
-      <c r="AI20" s="95"/>
-      <c r="AJ20" s="89"/>
-      <c r="AK20" s="90"/>
-      <c r="AL20" s="90"/>
-      <c r="AM20" s="90"/>
-      <c r="AN20" s="90"/>
-      <c r="AO20" s="90"/>
-      <c r="AP20" s="90"/>
-      <c r="AQ20" s="90"/>
-      <c r="AR20" s="90"/>
-      <c r="AS20" s="90"/>
-      <c r="AT20" s="90"/>
-      <c r="AU20" s="90"/>
-      <c r="AV20" s="90"/>
-      <c r="AW20" s="90"/>
-      <c r="AX20" s="90"/>
-      <c r="AY20" s="90"/>
-      <c r="AZ20" s="91"/>
+      <c r="AB20" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="101"/>
+      <c r="AD20" s="101"/>
+      <c r="AE20" s="101"/>
+      <c r="AF20" s="101"/>
+      <c r="AG20" s="101"/>
+      <c r="AH20" s="101"/>
+      <c r="AI20" s="101"/>
+      <c r="AJ20" s="92"/>
+      <c r="AK20" s="93"/>
+      <c r="AL20" s="93"/>
+      <c r="AM20" s="93"/>
+      <c r="AN20" s="93"/>
+      <c r="AO20" s="93"/>
+      <c r="AP20" s="93"/>
+      <c r="AQ20" s="93"/>
+      <c r="AR20" s="93"/>
+      <c r="AS20" s="93"/>
+      <c r="AT20" s="93"/>
+      <c r="AU20" s="93"/>
+      <c r="AV20" s="93"/>
+      <c r="AW20" s="93"/>
+      <c r="AX20" s="93"/>
+      <c r="AY20" s="93"/>
+      <c r="AZ20" s="94"/>
       <c r="BA20" s="14" t="s">
         <v>0</v>
       </c>
@@ -4195,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="21" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="19"/>
       <c r="F21" s="71" t="s">
         <v>84</v>
@@ -4215,7 +4228,7 @@
       <c r="N21" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="P21" s="139" t="s">
+      <c r="P21" s="98" t="s">
         <v>90</v>
       </c>
       <c r="Q21" s="71" t="s">
@@ -4233,33 +4246,33 @@
       <c r="X21" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="AB21" s="92" t="s">
+      <c r="AB21" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="AC21" s="95"/>
-      <c r="AD21" s="95"/>
-      <c r="AE21" s="95"/>
-      <c r="AF21" s="95"/>
-      <c r="AG21" s="95"/>
-      <c r="AH21" s="95"/>
-      <c r="AI21" s="95"/>
-      <c r="AJ21" s="89"/>
-      <c r="AK21" s="90"/>
-      <c r="AL21" s="90"/>
-      <c r="AM21" s="90"/>
-      <c r="AN21" s="90"/>
-      <c r="AO21" s="90"/>
-      <c r="AP21" s="90"/>
-      <c r="AQ21" s="90"/>
-      <c r="AR21" s="90"/>
-      <c r="AS21" s="90"/>
-      <c r="AT21" s="90"/>
-      <c r="AU21" s="90"/>
-      <c r="AV21" s="90"/>
-      <c r="AW21" s="90"/>
-      <c r="AX21" s="90"/>
-      <c r="AY21" s="90"/>
-      <c r="AZ21" s="91"/>
+      <c r="AC21" s="101"/>
+      <c r="AD21" s="101"/>
+      <c r="AE21" s="101"/>
+      <c r="AF21" s="101"/>
+      <c r="AG21" s="101"/>
+      <c r="AH21" s="101"/>
+      <c r="AI21" s="101"/>
+      <c r="AJ21" s="92"/>
+      <c r="AK21" s="93"/>
+      <c r="AL21" s="93"/>
+      <c r="AM21" s="93"/>
+      <c r="AN21" s="93"/>
+      <c r="AO21" s="93"/>
+      <c r="AP21" s="93"/>
+      <c r="AQ21" s="93"/>
+      <c r="AR21" s="93"/>
+      <c r="AS21" s="93"/>
+      <c r="AT21" s="93"/>
+      <c r="AU21" s="93"/>
+      <c r="AV21" s="93"/>
+      <c r="AW21" s="93"/>
+      <c r="AX21" s="93"/>
+      <c r="AY21" s="93"/>
+      <c r="AZ21" s="94"/>
       <c r="BA21" s="14" t="s">
         <v>0</v>
       </c>
@@ -4279,7 +4292,7 @@
         <v>100</v>
       </c>
       <c r="BK21" s="71" t="s">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="BO21" s="71" t="s">
         <v>0</v>
@@ -4300,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="22" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="19"/>
       <c r="F22" s="72" t="s">
         <v>0</v>
@@ -4320,7 +4333,7 @@
       <c r="N22" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="P22" s="140" t="s">
+      <c r="P22" s="99" t="s">
         <v>0</v>
       </c>
       <c r="Q22" s="72" t="s">
@@ -4338,47 +4351,47 @@
       <c r="X22" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB22" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="95" t="s">
+      <c r="AB22" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="AD22" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="95" t="s">
+      <c r="AD22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="AH22" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="89"/>
-      <c r="AK22" s="90"/>
-      <c r="AL22" s="90"/>
-      <c r="AM22" s="90"/>
-      <c r="AN22" s="90"/>
-      <c r="AO22" s="90"/>
-      <c r="AP22" s="90"/>
-      <c r="AQ22" s="90"/>
-      <c r="AR22" s="90"/>
-      <c r="AS22" s="90"/>
-      <c r="AT22" s="90"/>
-      <c r="AU22" s="90"/>
-      <c r="AV22" s="90"/>
-      <c r="AW22" s="90"/>
-      <c r="AX22" s="90"/>
-      <c r="AY22" s="90"/>
-      <c r="AZ22" s="91"/>
+      <c r="AH22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="92"/>
+      <c r="AK22" s="93"/>
+      <c r="AL22" s="93"/>
+      <c r="AM22" s="93"/>
+      <c r="AN22" s="93"/>
+      <c r="AO22" s="93"/>
+      <c r="AP22" s="93"/>
+      <c r="AQ22" s="93"/>
+      <c r="AR22" s="93"/>
+      <c r="AS22" s="93"/>
+      <c r="AT22" s="93"/>
+      <c r="AU22" s="93"/>
+      <c r="AV22" s="93"/>
+      <c r="AW22" s="93"/>
+      <c r="AX22" s="93"/>
+      <c r="AY22" s="93"/>
+      <c r="AZ22" s="94"/>
       <c r="BA22" s="14" t="s">
         <v>0</v>
       </c>
@@ -4419,7 +4432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="23" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="19"/>
       <c r="F23" s="73" t="s">
         <v>0</v>
@@ -4439,7 +4452,7 @@
       <c r="N23" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="P23" s="141" t="s">
+      <c r="P23" s="100" t="s">
         <v>0</v>
       </c>
       <c r="Q23" s="73" t="s">
@@ -4457,47 +4470,47 @@
       <c r="X23" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="AB23" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="89"/>
-      <c r="AK23" s="90"/>
-      <c r="AL23" s="90"/>
-      <c r="AM23" s="90"/>
-      <c r="AN23" s="90"/>
-      <c r="AO23" s="90"/>
-      <c r="AP23" s="90"/>
-      <c r="AQ23" s="90"/>
-      <c r="AR23" s="90"/>
-      <c r="AS23" s="90"/>
-      <c r="AT23" s="90"/>
-      <c r="AU23" s="90"/>
-      <c r="AV23" s="90"/>
-      <c r="AW23" s="90"/>
-      <c r="AX23" s="90"/>
-      <c r="AY23" s="90"/>
-      <c r="AZ23" s="91"/>
+      <c r="AB23" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="92"/>
+      <c r="AK23" s="93"/>
+      <c r="AL23" s="93"/>
+      <c r="AM23" s="93"/>
+      <c r="AN23" s="93"/>
+      <c r="AO23" s="93"/>
+      <c r="AP23" s="93"/>
+      <c r="AQ23" s="93"/>
+      <c r="AR23" s="93"/>
+      <c r="AS23" s="93"/>
+      <c r="AT23" s="93"/>
+      <c r="AU23" s="93"/>
+      <c r="AV23" s="93"/>
+      <c r="AW23" s="93"/>
+      <c r="AX23" s="93"/>
+      <c r="AY23" s="93"/>
+      <c r="AZ23" s="94"/>
       <c r="BA23" s="14" t="s">
         <v>0</v>
       </c>
@@ -4538,9 +4551,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="24" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="19"/>
-      <c r="F24" s="136" t="s">
+      <c r="F24" s="86" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="71" t="s">
@@ -4552,7 +4565,7 @@
       <c r="J24" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="136" t="s">
+      <c r="M24" s="86" t="s">
         <v>0</v>
       </c>
       <c r="N24" s="71" t="s">
@@ -4561,7 +4574,7 @@
       <c r="P24" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="Q24" s="136" t="s">
+      <c r="Q24" s="86" t="s">
         <v>0</v>
       </c>
       <c r="T24" s="71" t="s">
@@ -4576,47 +4589,47 @@
       <c r="X24" s="71" t="s">
         <v>114</v>
       </c>
-      <c r="AB24" s="92" t="s">
+      <c r="AB24" s="95" t="s">
         <v>115</v>
       </c>
-      <c r="AC24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="89"/>
-      <c r="AK24" s="90"/>
-      <c r="AL24" s="90"/>
-      <c r="AM24" s="90"/>
-      <c r="AN24" s="90"/>
-      <c r="AO24" s="90"/>
-      <c r="AP24" s="90"/>
-      <c r="AQ24" s="90"/>
-      <c r="AR24" s="90"/>
-      <c r="AS24" s="90"/>
-      <c r="AT24" s="90"/>
-      <c r="AU24" s="90"/>
-      <c r="AV24" s="90"/>
-      <c r="AW24" s="90"/>
-      <c r="AX24" s="90"/>
-      <c r="AY24" s="90"/>
-      <c r="AZ24" s="91"/>
+      <c r="AC24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="92"/>
+      <c r="AK24" s="93"/>
+      <c r="AL24" s="93"/>
+      <c r="AM24" s="93"/>
+      <c r="AN24" s="93"/>
+      <c r="AO24" s="93"/>
+      <c r="AP24" s="93"/>
+      <c r="AQ24" s="93"/>
+      <c r="AR24" s="93"/>
+      <c r="AS24" s="93"/>
+      <c r="AT24" s="93"/>
+      <c r="AU24" s="93"/>
+      <c r="AV24" s="93"/>
+      <c r="AW24" s="93"/>
+      <c r="AX24" s="93"/>
+      <c r="AY24" s="93"/>
+      <c r="AZ24" s="94"/>
       <c r="BA24" s="14" t="s">
         <v>0</v>
       </c>
@@ -4636,7 +4649,7 @@
         <v>119</v>
       </c>
       <c r="BK24" s="71" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="BO24" s="71" t="s">
         <v>120</v>
@@ -4657,9 +4670,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="25" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="19"/>
-      <c r="F25" s="137" t="s">
+      <c r="F25" s="87" t="s">
         <v>0</v>
       </c>
       <c r="G25" s="72" t="s">
@@ -4671,7 +4684,7 @@
       <c r="J25" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="M25" s="137" t="s">
+      <c r="M25" s="87" t="s">
         <v>0</v>
       </c>
       <c r="N25" s="72" t="s">
@@ -4680,7 +4693,7 @@
       <c r="P25" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="Q25" s="137" t="s">
+      <c r="Q25" s="87" t="s">
         <v>0</v>
       </c>
       <c r="T25" s="72" t="s">
@@ -4695,47 +4708,47 @@
       <c r="X25" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB25" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="89"/>
-      <c r="AK25" s="90"/>
-      <c r="AL25" s="90"/>
-      <c r="AM25" s="90"/>
-      <c r="AN25" s="90"/>
-      <c r="AO25" s="90"/>
-      <c r="AP25" s="90"/>
-      <c r="AQ25" s="90"/>
-      <c r="AR25" s="90"/>
-      <c r="AS25" s="90"/>
-      <c r="AT25" s="90"/>
-      <c r="AU25" s="90"/>
-      <c r="AV25" s="90"/>
-      <c r="AW25" s="90"/>
-      <c r="AX25" s="90"/>
-      <c r="AY25" s="90"/>
-      <c r="AZ25" s="91"/>
+      <c r="AB25" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="92"/>
+      <c r="AK25" s="93"/>
+      <c r="AL25" s="93"/>
+      <c r="AM25" s="93"/>
+      <c r="AN25" s="93"/>
+      <c r="AO25" s="93"/>
+      <c r="AP25" s="93"/>
+      <c r="AQ25" s="93"/>
+      <c r="AR25" s="93"/>
+      <c r="AS25" s="93"/>
+      <c r="AT25" s="93"/>
+      <c r="AU25" s="93"/>
+      <c r="AV25" s="93"/>
+      <c r="AW25" s="93"/>
+      <c r="AX25" s="93"/>
+      <c r="AY25" s="93"/>
+      <c r="AZ25" s="94"/>
       <c r="BA25" s="14" t="s">
         <v>0</v>
       </c>
@@ -4776,12 +4789,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="26" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="19"/>
       <c r="D26" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F26" s="138" t="s">
+      <c r="F26" s="88" t="s">
         <v>0</v>
       </c>
       <c r="G26" s="73" t="s">
@@ -4796,7 +4809,7 @@
       <c r="K26" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="M26" s="138" t="s">
+      <c r="M26" s="88" t="s">
         <v>0</v>
       </c>
       <c r="N26" s="73" t="s">
@@ -4805,7 +4818,7 @@
       <c r="P26" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="Q26" s="138" t="s">
+      <c r="Q26" s="88" t="s">
         <v>0</v>
       </c>
       <c r="S26" s="8" t="s">
@@ -4826,47 +4839,47 @@
       <c r="Y26" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AB26" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="89"/>
-      <c r="AK26" s="90"/>
-      <c r="AL26" s="90"/>
-      <c r="AM26" s="90"/>
-      <c r="AN26" s="90"/>
-      <c r="AO26" s="90"/>
-      <c r="AP26" s="90"/>
-      <c r="AQ26" s="90"/>
-      <c r="AR26" s="90"/>
-      <c r="AS26" s="90"/>
-      <c r="AT26" s="90"/>
-      <c r="AU26" s="90"/>
-      <c r="AV26" s="90"/>
-      <c r="AW26" s="90"/>
-      <c r="AX26" s="90"/>
-      <c r="AY26" s="90"/>
-      <c r="AZ26" s="91"/>
+      <c r="AB26" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="92"/>
+      <c r="AK26" s="93"/>
+      <c r="AL26" s="93"/>
+      <c r="AM26" s="93"/>
+      <c r="AN26" s="93"/>
+      <c r="AO26" s="93"/>
+      <c r="AP26" s="93"/>
+      <c r="AQ26" s="93"/>
+      <c r="AR26" s="93"/>
+      <c r="AS26" s="93"/>
+      <c r="AT26" s="93"/>
+      <c r="AU26" s="93"/>
+      <c r="AV26" s="93"/>
+      <c r="AW26" s="93"/>
+      <c r="AX26" s="93"/>
+      <c r="AY26" s="93"/>
+      <c r="AZ26" s="94"/>
       <c r="BA26" s="14" t="s">
         <v>0</v>
       </c>
@@ -4916,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:74" ht="26.1" customHeight="1">
+    <row r="27" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="s">
         <v>0</v>
       </c>
@@ -4924,17 +4937,17 @@
       <c r="N27" s="82"/>
       <c r="T27" s="82"/>
       <c r="U27" s="82"/>
-      <c r="AB27" s="118" t="s">
-        <v>285</v>
-      </c>
-      <c r="BA27" s="118" t="s">
-        <v>285</v>
+      <c r="AB27" s="126" t="s">
+        <v>284</v>
+      </c>
+      <c r="BA27" s="126" t="s">
+        <v>284</v>
       </c>
       <c r="BV27" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="28" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="14" t="s">
         <v>0</v>
       </c>
@@ -4944,17 +4957,17 @@
       <c r="N28" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="AB28" s="104"/>
-      <c r="BA28" s="104"/>
+      <c r="AB28" s="110"/>
+      <c r="BA28" s="110"/>
       <c r="BV28" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B29" s="109" t="s">
-        <v>284</v>
-      </c>
-      <c r="C29" s="111"/>
+    <row r="29" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="117" t="s">
+        <v>283</v>
+      </c>
+      <c r="C29" s="119"/>
       <c r="F29" s="71" t="s">
         <v>126</v>
       </c>
@@ -4970,15 +4983,15 @@
       <c r="M29" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="AB29" s="104"/>
-      <c r="BA29" s="104"/>
+      <c r="AB29" s="110"/>
+      <c r="BA29" s="110"/>
       <c r="BV29" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
-      <c r="B30" s="112"/>
-      <c r="C30" s="114"/>
+    <row r="30" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="120"/>
+      <c r="C30" s="122"/>
       <c r="F30" s="72" t="s">
         <v>0</v>
       </c>
@@ -4994,7 +5007,7 @@
       <c r="M30" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB30" s="104"/>
+      <c r="AB30" s="110"/>
       <c r="AC30" s="85" t="s">
         <v>131</v>
       </c>
@@ -5016,12 +5029,12 @@
       <c r="AI30" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="BA30" s="122"/>
+      <c r="BA30" s="130"/>
       <c r="BV30" s="33"/>
     </row>
-    <row r="31" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B31" s="112"/>
-      <c r="C31" s="114"/>
+    <row r="31" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="120"/>
+      <c r="C31" s="122"/>
       <c r="F31" s="73" t="s">
         <v>0</v>
       </c>
@@ -5037,70 +5050,70 @@
       <c r="M31" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="U31" s="98" t="s">
+      <c r="U31" s="104" t="s">
         <v>129</v>
       </c>
-      <c r="V31" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="W31" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="X31" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="109" t="s">
+      <c r="V31" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="W31" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="X31" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="Z31" s="110"/>
-      <c r="AA31" s="110"/>
-      <c r="AB31" s="111"/>
-      <c r="AC31" s="98" t="s">
+      <c r="Z31" s="118"/>
+      <c r="AA31" s="118"/>
+      <c r="AB31" s="119"/>
+      <c r="AC31" s="104" t="s">
         <v>134</v>
       </c>
-      <c r="AD31" s="98" t="s">
+      <c r="AD31" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="AE31" s="98" t="s">
+      <c r="AE31" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="AF31" s="98" t="s">
+      <c r="AF31" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="AG31" s="98" t="s">
+      <c r="AG31" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="AH31" s="98" t="s">
+      <c r="AH31" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="AI31" s="98" t="s">
+      <c r="AI31" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="AW31" s="109" t="s">
+      <c r="AW31" s="117" t="s">
+        <v>280</v>
+      </c>
+      <c r="AX31" s="118"/>
+      <c r="AY31" s="118"/>
+      <c r="AZ31" s="118"/>
+      <c r="BA31" s="119"/>
+      <c r="BM31" s="117" t="s">
         <v>281</v>
       </c>
-      <c r="AX31" s="110"/>
-      <c r="AY31" s="110"/>
-      <c r="AZ31" s="110"/>
-      <c r="BA31" s="111"/>
-      <c r="BM31" s="109" t="s">
+      <c r="BN31" s="118"/>
+      <c r="BO31" s="118"/>
+      <c r="BP31" s="118"/>
+      <c r="BQ31" s="119"/>
+      <c r="BR31" s="117" t="s">
         <v>282</v>
       </c>
-      <c r="BN31" s="110"/>
-      <c r="BO31" s="110"/>
-      <c r="BP31" s="110"/>
-      <c r="BQ31" s="111"/>
-      <c r="BR31" s="109" t="s">
-        <v>283</v>
-      </c>
-      <c r="BS31" s="110"/>
-      <c r="BT31" s="110"/>
-      <c r="BU31" s="110"/>
-      <c r="BV31" s="111"/>
+      <c r="BS31" s="118"/>
+      <c r="BT31" s="118"/>
+      <c r="BU31" s="118"/>
+      <c r="BV31" s="119"/>
     </row>
-    <row r="32" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B32" s="112"/>
-      <c r="C32" s="114"/>
+    <row r="32" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="120"/>
+      <c r="C32" s="122"/>
       <c r="F32" s="71" t="s">
         <v>132</v>
       </c>
@@ -5116,48 +5129,48 @@
       <c r="M32" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="U32" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="V32" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="W32" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="X32" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="112"/>
-      <c r="Z32" s="113"/>
-      <c r="AA32" s="113"/>
-      <c r="AB32" s="114"/>
-      <c r="AC32" s="99"/>
-      <c r="AD32" s="99"/>
-      <c r="AE32" s="99"/>
-      <c r="AF32" s="99"/>
-      <c r="AG32" s="99"/>
-      <c r="AH32" s="99"/>
-      <c r="AI32" s="99"/>
-      <c r="AW32" s="112"/>
-      <c r="AX32" s="113"/>
-      <c r="AY32" s="113"/>
-      <c r="AZ32" s="113"/>
-      <c r="BA32" s="114"/>
-      <c r="BM32" s="112"/>
-      <c r="BN32" s="113"/>
-      <c r="BO32" s="113"/>
-      <c r="BP32" s="113"/>
-      <c r="BQ32" s="114"/>
-      <c r="BR32" s="112"/>
-      <c r="BS32" s="113"/>
-      <c r="BT32" s="113"/>
-      <c r="BU32" s="113"/>
-      <c r="BV32" s="114"/>
+      <c r="U32" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="V32" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="W32" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="X32" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="120"/>
+      <c r="Z32" s="121"/>
+      <c r="AA32" s="121"/>
+      <c r="AB32" s="122"/>
+      <c r="AC32" s="105"/>
+      <c r="AD32" s="105"/>
+      <c r="AE32" s="105"/>
+      <c r="AF32" s="105"/>
+      <c r="AG32" s="105"/>
+      <c r="AH32" s="105"/>
+      <c r="AI32" s="105"/>
+      <c r="AW32" s="120"/>
+      <c r="AX32" s="121"/>
+      <c r="AY32" s="121"/>
+      <c r="AZ32" s="121"/>
+      <c r="BA32" s="122"/>
+      <c r="BM32" s="120"/>
+      <c r="BN32" s="121"/>
+      <c r="BO32" s="121"/>
+      <c r="BP32" s="121"/>
+      <c r="BQ32" s="122"/>
+      <c r="BR32" s="120"/>
+      <c r="BS32" s="121"/>
+      <c r="BT32" s="121"/>
+      <c r="BU32" s="121"/>
+      <c r="BV32" s="122"/>
     </row>
-    <row r="33" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B33" s="112"/>
-      <c r="C33" s="114"/>
+    <row r="33" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="120"/>
+      <c r="C33" s="122"/>
       <c r="F33" s="72" t="s">
         <v>0</v>
       </c>
@@ -5173,48 +5186,48 @@
       <c r="M33" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="U33" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="V33" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="W33" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="X33" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="112"/>
-      <c r="Z33" s="113"/>
-      <c r="AA33" s="113"/>
-      <c r="AB33" s="114"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="99"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="99"/>
-      <c r="AG33" s="99"/>
-      <c r="AH33" s="99"/>
-      <c r="AI33" s="99"/>
-      <c r="AW33" s="112"/>
-      <c r="AX33" s="113"/>
-      <c r="AY33" s="113"/>
-      <c r="AZ33" s="113"/>
-      <c r="BA33" s="114"/>
-      <c r="BM33" s="112"/>
-      <c r="BN33" s="113"/>
-      <c r="BO33" s="113"/>
-      <c r="BP33" s="113"/>
-      <c r="BQ33" s="114"/>
-      <c r="BR33" s="112"/>
-      <c r="BS33" s="113"/>
-      <c r="BT33" s="113"/>
-      <c r="BU33" s="113"/>
-      <c r="BV33" s="114"/>
+      <c r="U33" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="V33" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="W33" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="X33" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="120"/>
+      <c r="Z33" s="121"/>
+      <c r="AA33" s="121"/>
+      <c r="AB33" s="122"/>
+      <c r="AC33" s="105"/>
+      <c r="AD33" s="105"/>
+      <c r="AE33" s="105"/>
+      <c r="AF33" s="105"/>
+      <c r="AG33" s="105"/>
+      <c r="AH33" s="105"/>
+      <c r="AI33" s="105"/>
+      <c r="AW33" s="120"/>
+      <c r="AX33" s="121"/>
+      <c r="AY33" s="121"/>
+      <c r="AZ33" s="121"/>
+      <c r="BA33" s="122"/>
+      <c r="BM33" s="120"/>
+      <c r="BN33" s="121"/>
+      <c r="BO33" s="121"/>
+      <c r="BP33" s="121"/>
+      <c r="BQ33" s="122"/>
+      <c r="BR33" s="120"/>
+      <c r="BS33" s="121"/>
+      <c r="BT33" s="121"/>
+      <c r="BU33" s="121"/>
+      <c r="BV33" s="122"/>
     </row>
-    <row r="34" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B34" s="112"/>
-      <c r="C34" s="114"/>
+    <row r="34" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="120"/>
+      <c r="C34" s="122"/>
       <c r="F34" s="73" t="s">
         <v>0</v>
       </c>
@@ -5230,48 +5243,48 @@
       <c r="M34" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="U34" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="V34" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="W34" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="X34" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="112"/>
-      <c r="Z34" s="113"/>
-      <c r="AA34" s="113"/>
-      <c r="AB34" s="114"/>
-      <c r="AC34" s="99"/>
-      <c r="AD34" s="99"/>
-      <c r="AE34" s="99"/>
-      <c r="AF34" s="99"/>
-      <c r="AG34" s="99"/>
-      <c r="AH34" s="99"/>
-      <c r="AI34" s="99"/>
-      <c r="AW34" s="112"/>
-      <c r="AX34" s="113"/>
-      <c r="AY34" s="113"/>
-      <c r="AZ34" s="113"/>
-      <c r="BA34" s="114"/>
-      <c r="BM34" s="112"/>
-      <c r="BN34" s="113"/>
-      <c r="BO34" s="113"/>
-      <c r="BP34" s="113"/>
-      <c r="BQ34" s="114"/>
-      <c r="BR34" s="112"/>
-      <c r="BS34" s="113"/>
-      <c r="BT34" s="113"/>
-      <c r="BU34" s="113"/>
-      <c r="BV34" s="114"/>
+      <c r="U34" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="V34" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="W34" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="X34" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="120"/>
+      <c r="Z34" s="121"/>
+      <c r="AA34" s="121"/>
+      <c r="AB34" s="122"/>
+      <c r="AC34" s="105"/>
+      <c r="AD34" s="105"/>
+      <c r="AE34" s="105"/>
+      <c r="AF34" s="105"/>
+      <c r="AG34" s="105"/>
+      <c r="AH34" s="105"/>
+      <c r="AI34" s="105"/>
+      <c r="AW34" s="120"/>
+      <c r="AX34" s="121"/>
+      <c r="AY34" s="121"/>
+      <c r="AZ34" s="121"/>
+      <c r="BA34" s="122"/>
+      <c r="BM34" s="120"/>
+      <c r="BN34" s="121"/>
+      <c r="BO34" s="121"/>
+      <c r="BP34" s="121"/>
+      <c r="BQ34" s="122"/>
+      <c r="BR34" s="120"/>
+      <c r="BS34" s="121"/>
+      <c r="BT34" s="121"/>
+      <c r="BU34" s="121"/>
+      <c r="BV34" s="122"/>
     </row>
-    <row r="35" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
-      <c r="B35" s="115"/>
-      <c r="C35" s="117"/>
+    <row r="35" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="123"/>
+      <c r="C35" s="125"/>
       <c r="D35" s="18" t="s">
         <v>0</v>
       </c>
@@ -5302,42 +5315,42 @@
       <c r="M35" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="N35" s="104" t="s">
+      <c r="N35" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="O35" s="104"/>
-      <c r="P35" s="104"/>
-      <c r="Q35" s="104"/>
-      <c r="R35" s="104"/>
+      <c r="O35" s="110"/>
+      <c r="P35" s="110"/>
+      <c r="Q35" s="110"/>
+      <c r="R35" s="110"/>
       <c r="S35" s="18" t="s">
         <v>0</v>
       </c>
       <c r="T35" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="U35" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="V35" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="W35" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="X35" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="115"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="116"/>
-      <c r="AB35" s="117"/>
-      <c r="AC35" s="100"/>
-      <c r="AD35" s="100"/>
-      <c r="AE35" s="100"/>
-      <c r="AF35" s="100"/>
-      <c r="AG35" s="100"/>
-      <c r="AH35" s="100"/>
-      <c r="AI35" s="100"/>
+      <c r="U35" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="V35" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="W35" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="X35" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="123"/>
+      <c r="Z35" s="124"/>
+      <c r="AA35" s="124"/>
+      <c r="AB35" s="125"/>
+      <c r="AC35" s="106"/>
+      <c r="AD35" s="106"/>
+      <c r="AE35" s="106"/>
+      <c r="AF35" s="106"/>
+      <c r="AG35" s="106"/>
+      <c r="AH35" s="106"/>
+      <c r="AI35" s="106"/>
       <c r="AJ35" s="18" t="s">
         <v>0</v>
       </c>
@@ -5362,26 +5375,26 @@
       <c r="AQ35" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="AR35" s="104" t="s">
+      <c r="AR35" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="AS35" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AT35" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU35" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW35" s="115"/>
-      <c r="AX35" s="116"/>
-      <c r="AY35" s="116"/>
-      <c r="AZ35" s="116"/>
-      <c r="BA35" s="117"/>
+      <c r="AS35" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT35" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU35" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW35" s="123"/>
+      <c r="AX35" s="124"/>
+      <c r="AY35" s="124"/>
+      <c r="AZ35" s="124"/>
+      <c r="BA35" s="125"/>
       <c r="BB35" s="18" t="s">
         <v>0</v>
       </c>
@@ -5415,18 +5428,18 @@
       <c r="BL35" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="BM35" s="115"/>
-      <c r="BN35" s="116"/>
-      <c r="BO35" s="116"/>
-      <c r="BP35" s="116"/>
-      <c r="BQ35" s="117"/>
-      <c r="BR35" s="115"/>
-      <c r="BS35" s="116"/>
-      <c r="BT35" s="116"/>
-      <c r="BU35" s="116"/>
-      <c r="BV35" s="117"/>
+      <c r="BM35" s="123"/>
+      <c r="BN35" s="124"/>
+      <c r="BO35" s="124"/>
+      <c r="BP35" s="124"/>
+      <c r="BQ35" s="125"/>
+      <c r="BR35" s="123"/>
+      <c r="BS35" s="124"/>
+      <c r="BT35" s="124"/>
+      <c r="BU35" s="124"/>
+      <c r="BV35" s="125"/>
     </row>
-    <row r="36" spans="2:74" ht="26.1" customHeight="1">
+    <row r="36" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="39"/>
       <c r="C36" s="40"/>
       <c r="D36" s="40"/>
@@ -5503,7 +5516,7 @@
       <c r="BU36" s="34"/>
       <c r="BV36" s="35"/>
     </row>
-    <row r="37" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="37" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="42"/>
       <c r="C37" s="43"/>
       <c r="D37" s="46"/>
@@ -5578,17 +5591,17 @@
       <c r="BU37" s="36"/>
       <c r="BV37" s="37"/>
     </row>
-    <row r="38" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="38" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="42"/>
       <c r="C38" s="43"/>
-      <c r="D38" s="133" t="s">
+      <c r="D38" s="141" t="s">
         <v>142</v>
       </c>
-      <c r="E38" s="133"/>
-      <c r="F38" s="133"/>
-      <c r="G38" s="133"/>
-      <c r="H38" s="133"/>
-      <c r="I38" s="133"/>
+      <c r="E38" s="141"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="141"/>
+      <c r="H38" s="141"/>
+      <c r="I38" s="141"/>
       <c r="J38" s="43"/>
       <c r="K38" s="43"/>
       <c r="L38" s="43"/>
@@ -5599,7 +5612,7 @@
       <c r="Q38" s="43"/>
       <c r="R38" s="43"/>
       <c r="S38" s="39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T38" s="40"/>
       <c r="U38" s="40"/>
@@ -5611,7 +5624,7 @@
       <c r="AA38" s="51"/>
       <c r="AB38" s="52"/>
       <c r="AC38" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AD38" s="48"/>
       <c r="AE38" s="48"/>
@@ -5633,7 +5646,7 @@
       <c r="AU38" s="36"/>
       <c r="AV38" s="36"/>
       <c r="AW38" s="68" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AX38" s="69"/>
       <c r="AY38" s="69"/>
@@ -5663,15 +5676,15 @@
       <c r="BU38" s="42"/>
       <c r="BV38" s="44"/>
     </row>
-    <row r="39" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="39" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="45"/>
       <c r="C39" s="46"/>
-      <c r="D39" s="133"/>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="133"/>
-      <c r="I39" s="133"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="141"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="141"/>
+      <c r="I39" s="141"/>
       <c r="J39" s="43"/>
       <c r="K39" s="43"/>
       <c r="L39" s="43"/>
@@ -5738,13 +5751,13 @@
       <c r="BU39" s="45"/>
       <c r="BV39" s="47"/>
     </row>
-    <row r="40" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
-      <c r="D40" s="133"/>
-      <c r="E40" s="133"/>
-      <c r="F40" s="133"/>
-      <c r="G40" s="133"/>
-      <c r="H40" s="133"/>
-      <c r="I40" s="133"/>
+    <row r="40" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D40" s="141"/>
+      <c r="E40" s="141"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="141"/>
+      <c r="I40" s="141"/>
       <c r="J40" s="43"/>
       <c r="K40" s="43"/>
       <c r="L40" s="43"/>
@@ -5810,15 +5823,15 @@
       <c r="BT40" s="47"/>
       <c r="BU40" s="19"/>
     </row>
-    <row r="41" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
-      <c r="D41" s="133" t="s">
+    <row r="41" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D41" s="141" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="133"/>
-      <c r="F41" s="133"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="133"/>
-      <c r="I41" s="133"/>
+      <c r="E41" s="141"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="141"/>
+      <c r="I41" s="141"/>
       <c r="J41" s="43"/>
       <c r="K41" s="43"/>
       <c r="L41" s="43"/>
@@ -5845,7 +5858,7 @@
       <c r="AG41" s="57"/>
       <c r="AH41" s="58"/>
       <c r="AI41" s="48" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AJ41" s="48"/>
       <c r="AK41" s="48"/>
@@ -5861,7 +5874,7 @@
       <c r="AU41" s="36"/>
       <c r="AV41" s="36"/>
       <c r="AW41" s="68" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AX41" s="69"/>
       <c r="AY41" s="69"/>
@@ -5899,15 +5912,15 @@
       <c r="BS41" s="57"/>
       <c r="BT41" s="58"/>
     </row>
-    <row r="42" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="42" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="39"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="133"/>
-      <c r="E42" s="133"/>
-      <c r="F42" s="133"/>
-      <c r="G42" s="133"/>
-      <c r="H42" s="133"/>
-      <c r="I42" s="133"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="141"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="141"/>
+      <c r="I42" s="141"/>
       <c r="J42" s="43"/>
       <c r="K42" s="43"/>
       <c r="L42" s="43"/>
@@ -5986,15 +5999,15 @@
       <c r="BU42" s="40"/>
       <c r="BV42" s="41"/>
     </row>
-    <row r="43" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="43" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="42"/>
       <c r="C43" s="43"/>
-      <c r="D43" s="133"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="133"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="133"/>
-      <c r="I43" s="133"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="141"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="141"/>
+      <c r="H43" s="141"/>
+      <c r="I43" s="141"/>
       <c r="J43" s="43"/>
       <c r="K43" s="43"/>
       <c r="L43" s="43"/>
@@ -6073,7 +6086,7 @@
       <c r="BU43" s="43"/>
       <c r="BV43" s="44"/>
     </row>
-    <row r="44" spans="2:74" ht="26.1" customHeight="1">
+    <row r="44" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
       <c r="C44" s="43"/>
       <c r="D44" s="40" t="s">
@@ -6150,7 +6163,7 @@
       <c r="BU44" s="43"/>
       <c r="BV44" s="44"/>
     </row>
-    <row r="45" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="45" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="45"/>
       <c r="C45" s="46"/>
       <c r="D45" s="46"/>
@@ -6225,7 +6238,7 @@
       <c r="BU45" s="46"/>
       <c r="BV45" s="47"/>
     </row>
-    <row r="46" spans="2:74" ht="26.1" customHeight="1">
+    <row r="46" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="12" t="s">
         <v>0</v>
       </c>
@@ -6253,192 +6266,192 @@
       <c r="J46" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="K46" s="104" t="s">
+      <c r="K46" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="L46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="M46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="N46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="O46" s="104" t="s">
+      <c r="L46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="M46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="O46" s="110" t="s">
         <v>0</v>
       </c>
       <c r="P46" s="26"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
-      <c r="T46" s="104" t="s">
+      <c r="T46" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="U46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="V46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="W46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="X46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="98" t="s">
+      <c r="U46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="V46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="W46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="X46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="Z46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="98" t="s">
+      <c r="Z46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="AE46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="98" t="s">
+      <c r="AE46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="104" t="s">
         <v>148</v>
       </c>
-      <c r="AG46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="98" t="s">
-        <v>287</v>
-      </c>
-      <c r="AK46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR46" s="104" t="s">
+      <c r="AG46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="104" t="s">
+        <v>286</v>
+      </c>
+      <c r="AK46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR46" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="AS46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW46" s="98" t="s">
-        <v>280</v>
-      </c>
-      <c r="AX46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="98" t="s">
+      <c r="AS46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="104" t="s">
+        <v>279</v>
+      </c>
+      <c r="AX46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="BA46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC46" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD46" s="98" t="s">
-        <v>274</v>
-      </c>
-      <c r="BE46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="98" t="s">
-        <v>274</v>
-      </c>
-      <c r="BJ46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM46" s="98" t="s">
+      <c r="BA46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="104" t="s">
+        <v>273</v>
+      </c>
+      <c r="BE46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="104" t="s">
+        <v>273</v>
+      </c>
+      <c r="BJ46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM46" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="BN46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR46" s="98" t="s">
+      <c r="BN46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR46" s="104" t="s">
         <v>151</v>
       </c>
-      <c r="BS46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU46" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV46" s="101" t="s">
+      <c r="BS46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV46" s="107" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:74" ht="26.1" customHeight="1">
+    <row r="47" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="14" t="s">
         <v>0</v>
       </c>
@@ -6455,328 +6468,328 @@
         <v>0</v>
       </c>
       <c r="P47" s="19"/>
-      <c r="Y47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AX47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC47" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BE47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV47" s="102" t="s">
+      <c r="Y47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC47" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU47" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV47" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="48" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E48" s="97" t="s">
-        <v>286</v>
-      </c>
-      <c r="F48" s="97"/>
-      <c r="G48" s="97"/>
-      <c r="H48" s="97"/>
-      <c r="I48" s="97"/>
-      <c r="J48" s="97"/>
-      <c r="K48" s="97"/>
-      <c r="L48" s="97"/>
+      <c r="E48" s="103" t="s">
+        <v>285</v>
+      </c>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
       <c r="O48" s="2" t="s">
         <v>0</v>
       </c>
       <c r="P48" s="19"/>
-      <c r="Y48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AX48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC48" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BE48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ48" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR48" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS48" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT48" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU48" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV48" s="102" t="s">
+      <c r="Y48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC48" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ48" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR48" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS48" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT48" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU48" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV48" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:74" ht="26.1" customHeight="1">
+    <row r="49" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E49" s="97"/>
-      <c r="F49" s="97"/>
-      <c r="G49" s="97"/>
-      <c r="H49" s="97"/>
-      <c r="I49" s="97"/>
-      <c r="J49" s="97"/>
-      <c r="K49" s="97"/>
-      <c r="L49" s="97"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="103"/>
+      <c r="J49" s="103"/>
+      <c r="K49" s="103"/>
+      <c r="L49" s="103"/>
       <c r="O49" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="BR49" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS49" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT49" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU49" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV49" s="102" t="s">
+      <c r="BR49" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS49" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT49" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU49" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV49" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:74" ht="26.1" customHeight="1">
+    <row r="50" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="14" t="s">
         <v>0</v>
       </c>
@@ -6793,71 +6806,71 @@
       </c>
       <c r="L50" s="84"/>
       <c r="O50" s="22"/>
-      <c r="AH50" s="105" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI50" s="105"/>
-      <c r="AJ50" s="105"/>
-      <c r="AK50" s="105"/>
-      <c r="AL50" s="105"/>
-      <c r="AM50" s="105"/>
-      <c r="AN50" s="105"/>
-      <c r="AO50" s="105"/>
-      <c r="AP50" s="105"/>
-      <c r="AQ50" s="105"/>
-      <c r="AR50" s="105"/>
-      <c r="AS50" s="105"/>
-      <c r="AT50" s="105"/>
-      <c r="AU50" s="105"/>
-      <c r="AV50" s="105"/>
-      <c r="BR50" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS50" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT50" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU50" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV50" s="102" t="s">
+      <c r="AH50" s="113" t="s">
+        <v>272</v>
+      </c>
+      <c r="AI50" s="113"/>
+      <c r="AJ50" s="113"/>
+      <c r="AK50" s="113"/>
+      <c r="AL50" s="113"/>
+      <c r="AM50" s="113"/>
+      <c r="AN50" s="113"/>
+      <c r="AO50" s="113"/>
+      <c r="AP50" s="113"/>
+      <c r="AQ50" s="113"/>
+      <c r="AR50" s="113"/>
+      <c r="AS50" s="113"/>
+      <c r="AT50" s="113"/>
+      <c r="AU50" s="113"/>
+      <c r="AV50" s="113"/>
+      <c r="BR50" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS50" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT50" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU50" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV50" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:74" ht="26.1" customHeight="1">
+    <row r="51" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="130" t="s">
+      <c r="C51" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="138" t="s">
         <v>155</v>
       </c>
-      <c r="E51" s="129" t="s">
+      <c r="E51" s="137" t="s">
         <v>156</v>
       </c>
-      <c r="F51" s="129" t="s">
+      <c r="F51" s="137" t="s">
         <v>157</v>
       </c>
-      <c r="H51" s="129" t="s">
+      <c r="H51" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="I51" s="129" t="s">
+      <c r="I51" s="137" t="s">
         <v>159</v>
       </c>
-      <c r="J51" s="130" t="s">
+      <c r="J51" s="138" t="s">
         <v>160</v>
       </c>
-      <c r="K51" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="L51" s="129" t="s">
+      <c r="K51" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" s="137" t="s">
         <v>161</v>
       </c>
-      <c r="M51" s="128" t="s">
+      <c r="M51" s="136" t="s">
         <v>162</v>
       </c>
       <c r="O51" s="22"/>
@@ -6867,21 +6880,21 @@
       <c r="X51" s="31"/>
       <c r="AB51" s="10"/>
       <c r="AC51" s="10"/>
-      <c r="AH51" s="105"/>
-      <c r="AI51" s="105"/>
-      <c r="AJ51" s="105"/>
-      <c r="AK51" s="105"/>
-      <c r="AL51" s="105"/>
-      <c r="AM51" s="105"/>
-      <c r="AN51" s="105"/>
-      <c r="AO51" s="105"/>
-      <c r="AP51" s="105"/>
-      <c r="AQ51" s="105"/>
-      <c r="AR51" s="105"/>
-      <c r="AS51" s="105"/>
-      <c r="AT51" s="105"/>
-      <c r="AU51" s="105"/>
-      <c r="AV51" s="105"/>
+      <c r="AH51" s="113"/>
+      <c r="AI51" s="113"/>
+      <c r="AJ51" s="113"/>
+      <c r="AK51" s="113"/>
+      <c r="AL51" s="113"/>
+      <c r="AM51" s="113"/>
+      <c r="AN51" s="113"/>
+      <c r="AO51" s="113"/>
+      <c r="AP51" s="113"/>
+      <c r="AQ51" s="113"/>
+      <c r="AR51" s="113"/>
+      <c r="AS51" s="113"/>
+      <c r="AT51" s="113"/>
+      <c r="AU51" s="113"/>
+      <c r="AV51" s="113"/>
       <c r="AZ51" s="10"/>
       <c r="BA51" s="10" t="s">
         <v>0</v>
@@ -6890,66 +6903,66 @@
       <c r="BI51" s="10"/>
       <c r="BK51" s="10"/>
       <c r="BL51" s="10"/>
-      <c r="BR51" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS51" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT51" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU51" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV51" s="102" t="s">
+      <c r="BR51" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS51" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT51" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU51" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV51" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:74" ht="26.1" customHeight="1">
+    <row r="52" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="126"/>
-      <c r="D52" s="130"/>
-      <c r="E52" s="130"/>
-      <c r="F52" s="130"/>
-      <c r="H52" s="130"/>
-      <c r="I52" s="130"/>
-      <c r="J52" s="130"/>
-      <c r="K52" s="126"/>
-      <c r="L52" s="130"/>
-      <c r="M52" s="128"/>
+      <c r="C52" s="134"/>
+      <c r="D52" s="138"/>
+      <c r="E52" s="138"/>
+      <c r="F52" s="138"/>
+      <c r="H52" s="138"/>
+      <c r="I52" s="138"/>
+      <c r="J52" s="138"/>
+      <c r="K52" s="134"/>
+      <c r="L52" s="138"/>
+      <c r="M52" s="136"/>
       <c r="O52" s="22"/>
       <c r="R52" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="T52" s="120" t="s">
+      <c r="T52" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="U52" s="120"/>
-      <c r="W52" s="120" t="s">
+      <c r="U52" s="112"/>
+      <c r="W52" s="112" t="s">
         <v>226</v>
       </c>
-      <c r="X52" s="120"/>
+      <c r="X52" s="112"/>
       <c r="AB52" s="85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AC52" s="85"/>
       <c r="AD52" s="85"/>
-      <c r="AK52" s="121" t="s">
+      <c r="AK52" s="111" t="s">
+        <v>288</v>
+      </c>
+      <c r="AL52" s="111"/>
+      <c r="AM52" s="111"/>
+      <c r="AR52" s="112" t="s">
+        <v>287</v>
+      </c>
+      <c r="AS52" s="112"/>
+      <c r="AU52" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="AL52" s="121"/>
-      <c r="AM52" s="121"/>
-      <c r="AR52" s="120" t="s">
-        <v>288</v>
-      </c>
-      <c r="AS52" s="120"/>
-      <c r="AU52" s="120" t="s">
-        <v>290</v>
-      </c>
-      <c r="AV52" s="120"/>
+      <c r="AV52" s="112"/>
       <c r="AZ52" s="84" t="s">
         <v>163</v>
       </c>
@@ -6959,36 +6972,36 @@
       </c>
       <c r="BI52" s="84"/>
       <c r="BK52" s="84" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BL52" s="84"/>
-      <c r="BR52" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS52" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT52" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU52" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV52" s="102" t="s">
+      <c r="BR52" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS52" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT52" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU52" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV52" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="53" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C53" s="127"/>
-      <c r="E53" s="131"/>
-      <c r="F53" s="131"/>
-      <c r="H53" s="131"/>
-      <c r="I53" s="131"/>
-      <c r="K53" s="127"/>
-      <c r="L53" s="131"/>
+      <c r="C53" s="135"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
+      <c r="K53" s="135"/>
+      <c r="L53" s="139"/>
       <c r="O53" s="22"/>
       <c r="R53" s="2" t="s">
         <v>0</v>
@@ -7078,7 +7091,7 @@
         <v>180</v>
       </c>
       <c r="BK53" s="71" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BL53" s="71" t="s">
         <v>181</v>
@@ -7086,45 +7099,45 @@
       <c r="BN53" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="BR53" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS53" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT53" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU53" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV53" s="103" t="s">
+      <c r="BR53" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS53" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT53" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU53" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV53" s="109" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:74" ht="26.1" customHeight="1">
+    <row r="54" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C54" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="E54" s="129" t="s">
+      <c r="C54" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="E54" s="137" t="s">
         <v>165</v>
       </c>
-      <c r="F54" s="129" t="s">
+      <c r="F54" s="137" t="s">
         <v>166</v>
       </c>
-      <c r="H54" s="129" t="s">
+      <c r="H54" s="137" t="s">
         <v>167</v>
       </c>
-      <c r="I54" s="129" t="s">
+      <c r="I54" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="K54" s="129" t="s">
+      <c r="K54" s="137" t="s">
         <v>169</v>
       </c>
-      <c r="L54" s="125" t="s">
+      <c r="L54" s="133" t="s">
         <v>0</v>
       </c>
       <c r="O54" s="22"/>
@@ -7204,33 +7217,33 @@
       <c r="BN54" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="BR54" s="98" t="s">
-        <v>277</v>
-      </c>
-      <c r="BS54" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT54" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU54" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV54" s="101" t="s">
+      <c r="BR54" s="104" t="s">
+        <v>276</v>
+      </c>
+      <c r="BS54" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT54" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU54" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV54" s="107" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:74" ht="26.1" customHeight="1">
+    <row r="55" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C55" s="126"/>
-      <c r="E55" s="130"/>
-      <c r="F55" s="130"/>
-      <c r="H55" s="130"/>
-      <c r="I55" s="130"/>
-      <c r="K55" s="130"/>
-      <c r="L55" s="126"/>
+      <c r="C55" s="134"/>
+      <c r="E55" s="138"/>
+      <c r="F55" s="138"/>
+      <c r="H55" s="138"/>
+      <c r="I55" s="138"/>
+      <c r="K55" s="138"/>
+      <c r="L55" s="134"/>
       <c r="O55" s="22"/>
       <c r="R55" s="2" t="s">
         <v>0</v>
@@ -7308,33 +7321,33 @@
       <c r="BN55" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="BR55" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS55" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT55" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU55" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV55" s="102" t="s">
+      <c r="BR55" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS55" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT55" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU55" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV55" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:74" ht="26.1" customHeight="1">
+    <row r="56" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="127"/>
-      <c r="E56" s="131"/>
-      <c r="F56" s="131"/>
-      <c r="H56" s="131"/>
-      <c r="I56" s="131"/>
-      <c r="K56" s="131"/>
-      <c r="L56" s="127"/>
+      <c r="C56" s="135"/>
+      <c r="E56" s="139"/>
+      <c r="F56" s="139"/>
+      <c r="H56" s="139"/>
+      <c r="I56" s="139"/>
+      <c r="K56" s="139"/>
+      <c r="L56" s="135"/>
       <c r="O56" s="22"/>
       <c r="R56" s="2" t="s">
         <v>0</v>
@@ -7414,42 +7427,42 @@
       <c r="BN56" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BR56" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS56" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT56" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU56" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV56" s="102" t="s">
+      <c r="BR56" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS56" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT56" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU56" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV56" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:74" ht="26.1" customHeight="1">
+    <row r="57" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E57" s="125" t="s">
-        <v>299</v>
-      </c>
-      <c r="F57" s="129" t="s">
+      <c r="E57" s="133" t="s">
+        <v>298</v>
+      </c>
+      <c r="F57" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="H57" s="129" t="s">
+      <c r="H57" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="I57" s="129" t="s">
+      <c r="I57" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="K57" s="129" t="s">
+      <c r="K57" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="L57" s="129" t="s">
+      <c r="L57" s="137" t="s">
         <v>187</v>
       </c>
       <c r="O57" s="22"/>
@@ -7531,32 +7544,32 @@
       <c r="BN57" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="BR57" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS57" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT57" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU57" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV57" s="102" t="s">
+      <c r="BR57" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS57" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT57" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU57" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV57" s="108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="58" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E58" s="126"/>
-      <c r="F58" s="130"/>
-      <c r="H58" s="130"/>
-      <c r="I58" s="130"/>
-      <c r="K58" s="130"/>
-      <c r="L58" s="130"/>
+      <c r="E58" s="134"/>
+      <c r="F58" s="138"/>
+      <c r="H58" s="138"/>
+      <c r="I58" s="138"/>
+      <c r="K58" s="138"/>
+      <c r="L58" s="138"/>
       <c r="O58" s="22"/>
       <c r="R58" s="2" t="s">
         <v>0</v>
@@ -7636,32 +7649,32 @@
       <c r="BN58" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="BR58" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS58" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT58" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU58" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV58" s="103" t="s">
+      <c r="BR58" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS58" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT58" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU58" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV58" s="109" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:74" ht="26.1" customHeight="1">
+    <row r="59" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E59" s="127"/>
-      <c r="F59" s="131"/>
-      <c r="H59" s="131"/>
-      <c r="I59" s="131"/>
-      <c r="K59" s="131"/>
-      <c r="L59" s="131"/>
+      <c r="E59" s="135"/>
+      <c r="F59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="K59" s="139"/>
+      <c r="L59" s="139"/>
       <c r="O59" s="22"/>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -7747,34 +7760,34 @@
       <c r="BN59" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BR59" s="109" t="s">
-        <v>276</v>
-      </c>
-      <c r="BS59" s="110"/>
-      <c r="BT59" s="110"/>
-      <c r="BU59" s="110"/>
-      <c r="BV59" s="111"/>
+      <c r="BR59" s="117" t="s">
+        <v>275</v>
+      </c>
+      <c r="BS59" s="118"/>
+      <c r="BT59" s="118"/>
+      <c r="BU59" s="118"/>
+      <c r="BV59" s="119"/>
     </row>
-    <row r="60" spans="2:74" ht="26.1" customHeight="1">
+    <row r="60" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E60" s="129" t="s">
+      <c r="E60" s="137" t="s">
         <v>204</v>
       </c>
-      <c r="F60" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="H60" s="129" t="s">
+      <c r="F60" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="H60" s="137" t="s">
         <v>205</v>
       </c>
-      <c r="I60" s="129" t="s">
+      <c r="I60" s="137" t="s">
         <v>206</v>
       </c>
-      <c r="K60" s="129" t="s">
+      <c r="K60" s="137" t="s">
         <v>207</v>
       </c>
-      <c r="L60" s="129"/>
+      <c r="L60" s="137"/>
       <c r="O60" s="22"/>
       <c r="P60" s="10" t="s">
         <v>0</v>
@@ -7860,22 +7873,22 @@
       <c r="BN60" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="BR60" s="112"/>
-      <c r="BS60" s="113"/>
-      <c r="BT60" s="113"/>
-      <c r="BU60" s="113"/>
-      <c r="BV60" s="114"/>
+      <c r="BR60" s="120"/>
+      <c r="BS60" s="121"/>
+      <c r="BT60" s="121"/>
+      <c r="BU60" s="121"/>
+      <c r="BV60" s="122"/>
     </row>
-    <row r="61" spans="2:74" ht="26.1" customHeight="1">
+    <row r="61" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E61" s="130"/>
-      <c r="F61" s="126"/>
-      <c r="H61" s="130"/>
-      <c r="I61" s="130"/>
-      <c r="K61" s="130"/>
-      <c r="L61" s="130"/>
+      <c r="E61" s="138"/>
+      <c r="F61" s="134"/>
+      <c r="H61" s="138"/>
+      <c r="I61" s="138"/>
+      <c r="K61" s="138"/>
+      <c r="L61" s="138"/>
       <c r="O61" s="22"/>
       <c r="T61" s="73" t="s">
         <v>0</v>
@@ -7952,22 +7965,22 @@
       <c r="BN61" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="BR61" s="112"/>
-      <c r="BS61" s="113"/>
-      <c r="BT61" s="113"/>
-      <c r="BU61" s="113"/>
-      <c r="BV61" s="114"/>
+      <c r="BR61" s="120"/>
+      <c r="BS61" s="121"/>
+      <c r="BT61" s="121"/>
+      <c r="BU61" s="121"/>
+      <c r="BV61" s="122"/>
     </row>
-    <row r="62" spans="2:74" ht="26.1" customHeight="1">
+    <row r="62" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E62" s="131"/>
-      <c r="F62" s="127"/>
-      <c r="H62" s="131"/>
-      <c r="I62" s="131"/>
-      <c r="K62" s="131"/>
-      <c r="L62" s="131"/>
+      <c r="E62" s="139"/>
+      <c r="F62" s="135"/>
+      <c r="H62" s="139"/>
+      <c r="I62" s="139"/>
+      <c r="K62" s="139"/>
+      <c r="L62" s="139"/>
       <c r="O62" s="22"/>
       <c r="P62" s="10"/>
       <c r="Q62" s="10"/>
@@ -7993,18 +8006,18 @@
         <v>0</v>
       </c>
       <c r="BL62" s="82" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BN62" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BR62" s="112"/>
-      <c r="BS62" s="113"/>
-      <c r="BT62" s="113"/>
-      <c r="BU62" s="113"/>
-      <c r="BV62" s="114"/>
+      <c r="BR62" s="120"/>
+      <c r="BS62" s="121"/>
+      <c r="BT62" s="121"/>
+      <c r="BU62" s="121"/>
+      <c r="BV62" s="122"/>
     </row>
-    <row r="63" spans="2:74" ht="26.1" customHeight="1">
+    <row r="63" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="14" t="s">
         <v>0</v>
       </c>
@@ -8052,13 +8065,13 @@
       <c r="BN63" s="71" t="s">
         <v>229</v>
       </c>
-      <c r="BR63" s="112"/>
-      <c r="BS63" s="113"/>
-      <c r="BT63" s="113"/>
-      <c r="BU63" s="113"/>
-      <c r="BV63" s="114"/>
+      <c r="BR63" s="120"/>
+      <c r="BS63" s="121"/>
+      <c r="BT63" s="121"/>
+      <c r="BU63" s="121"/>
+      <c r="BV63" s="122"/>
     </row>
-    <row r="64" spans="2:74" ht="26.1" customHeight="1">
+    <row r="64" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="14" t="s">
         <v>0</v>
       </c>
@@ -8149,13 +8162,13 @@
       <c r="BN64" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="BR64" s="112"/>
-      <c r="BS64" s="113"/>
-      <c r="BT64" s="113"/>
-      <c r="BU64" s="113"/>
-      <c r="BV64" s="114"/>
+      <c r="BR64" s="120"/>
+      <c r="BS64" s="121"/>
+      <c r="BT64" s="121"/>
+      <c r="BU64" s="121"/>
+      <c r="BV64" s="122"/>
     </row>
-    <row r="65" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
+    <row r="65" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="14" t="s">
         <v>0</v>
       </c>
@@ -8256,31 +8269,31 @@
       <c r="BN65" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BR65" s="112"/>
-      <c r="BS65" s="113"/>
-      <c r="BT65" s="113"/>
-      <c r="BU65" s="113"/>
-      <c r="BV65" s="114"/>
+      <c r="BR65" s="120"/>
+      <c r="BS65" s="121"/>
+      <c r="BT65" s="121"/>
+      <c r="BU65" s="121"/>
+      <c r="BV65" s="122"/>
     </row>
-    <row r="66" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B66" s="98" t="s">
-        <v>275</v>
-      </c>
-      <c r="C66" s="98"/>
-      <c r="D66" s="98"/>
-      <c r="E66" s="98"/>
-      <c r="F66" s="98"/>
-      <c r="G66" s="98"/>
-      <c r="H66" s="98"/>
-      <c r="I66" s="106" t="s">
+    <row r="66" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="104" t="s">
         <v>274</v>
       </c>
-      <c r="J66" s="106"/>
-      <c r="K66" s="106"/>
-      <c r="L66" s="106"/>
-      <c r="M66" s="106"/>
-      <c r="N66" s="106"/>
-      <c r="O66" s="106"/>
+      <c r="C66" s="104"/>
+      <c r="D66" s="104"/>
+      <c r="E66" s="104"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="114" t="s">
+        <v>273</v>
+      </c>
+      <c r="J66" s="114"/>
+      <c r="K66" s="114"/>
+      <c r="L66" s="114"/>
+      <c r="M66" s="114"/>
+      <c r="N66" s="114"/>
+      <c r="O66" s="114"/>
       <c r="P66" s="10"/>
       <c r="Q66" s="10"/>
       <c r="R66" s="10"/>
@@ -8356,27 +8369,27 @@
       <c r="BL66" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BR66" s="112"/>
-      <c r="BS66" s="113"/>
-      <c r="BT66" s="113"/>
-      <c r="BU66" s="113"/>
-      <c r="BV66" s="114"/>
+      <c r="BR66" s="120"/>
+      <c r="BS66" s="121"/>
+      <c r="BT66" s="121"/>
+      <c r="BU66" s="121"/>
+      <c r="BV66" s="122"/>
     </row>
-    <row r="67" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B67" s="99"/>
-      <c r="C67" s="99"/>
-      <c r="D67" s="99"/>
-      <c r="E67" s="99"/>
-      <c r="F67" s="99"/>
-      <c r="G67" s="99"/>
-      <c r="H67" s="99"/>
-      <c r="I67" s="107"/>
-      <c r="J67" s="107"/>
-      <c r="K67" s="107"/>
-      <c r="L67" s="107"/>
-      <c r="M67" s="107"/>
-      <c r="N67" s="107"/>
-      <c r="O67" s="107"/>
+    <row r="67" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="105"/>
+      <c r="C67" s="105"/>
+      <c r="D67" s="105"/>
+      <c r="E67" s="105"/>
+      <c r="F67" s="105"/>
+      <c r="G67" s="105"/>
+      <c r="H67" s="105"/>
+      <c r="I67" s="115"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="115"/>
+      <c r="L67" s="115"/>
+      <c r="M67" s="115"/>
+      <c r="N67" s="115"/>
+      <c r="O67" s="115"/>
       <c r="P67" s="10"/>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -8429,50 +8442,50 @@
         <v>254</v>
       </c>
       <c r="AZ67" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="BA67" s="71" t="s">
         <v>255</v>
       </c>
-      <c r="BA67" s="71" t="s">
+      <c r="BC67" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="BC67" s="71" t="s">
+      <c r="BD67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK67" s="71" t="s">
         <v>257</v>
       </c>
-      <c r="BD67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK67" s="71" t="s">
+      <c r="BL67" s="71" t="s">
         <v>258</v>
       </c>
-      <c r="BL67" s="71" t="s">
-        <v>259</v>
-      </c>
-      <c r="BR67" s="112"/>
-      <c r="BS67" s="113"/>
-      <c r="BT67" s="113"/>
-      <c r="BU67" s="113"/>
-      <c r="BV67" s="114"/>
+      <c r="BR67" s="120"/>
+      <c r="BS67" s="121"/>
+      <c r="BT67" s="121"/>
+      <c r="BU67" s="121"/>
+      <c r="BV67" s="122"/>
     </row>
-    <row r="68" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B68" s="99"/>
-      <c r="C68" s="99"/>
-      <c r="D68" s="99"/>
-      <c r="E68" s="99"/>
-      <c r="F68" s="99"/>
-      <c r="G68" s="99"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="107"/>
-      <c r="J68" s="107"/>
-      <c r="K68" s="107"/>
-      <c r="L68" s="107"/>
-      <c r="M68" s="107"/>
-      <c r="N68" s="107"/>
-      <c r="O68" s="107"/>
+    <row r="68" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="105"/>
+      <c r="C68" s="105"/>
+      <c r="D68" s="105"/>
+      <c r="E68" s="105"/>
+      <c r="F68" s="105"/>
+      <c r="G68" s="105"/>
+      <c r="H68" s="105"/>
+      <c r="I68" s="115"/>
+      <c r="J68" s="115"/>
+      <c r="K68" s="115"/>
+      <c r="L68" s="115"/>
+      <c r="M68" s="115"/>
+      <c r="N68" s="115"/>
+      <c r="O68" s="115"/>
       <c r="P68" s="10"/>
       <c r="Q68" s="10"/>
       <c r="R68" s="10"/>
@@ -8488,16 +8501,16 @@
       <c r="X68" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB68" s="74" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC68" s="75" t="s">
+      <c r="AB68" s="127" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC68" s="128" t="s">
         <v>0</v>
       </c>
       <c r="AE68" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="AF68" s="119" t="s">
+      <c r="AF68" s="129" t="s">
         <v>0</v>
       </c>
       <c r="AJ68" s="72" t="s">
@@ -8548,27 +8561,27 @@
       <c r="BL68" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="BR68" s="112"/>
-      <c r="BS68" s="113"/>
-      <c r="BT68" s="113"/>
-      <c r="BU68" s="113"/>
-      <c r="BV68" s="114"/>
+      <c r="BR68" s="120"/>
+      <c r="BS68" s="121"/>
+      <c r="BT68" s="121"/>
+      <c r="BU68" s="121"/>
+      <c r="BV68" s="122"/>
     </row>
-    <row r="69" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B69" s="99"/>
-      <c r="C69" s="99"/>
-      <c r="D69" s="99"/>
-      <c r="E69" s="99"/>
-      <c r="F69" s="99"/>
-      <c r="G69" s="99"/>
-      <c r="H69" s="99"/>
-      <c r="I69" s="107"/>
-      <c r="J69" s="107"/>
-      <c r="K69" s="107"/>
-      <c r="L69" s="107"/>
-      <c r="M69" s="107"/>
-      <c r="N69" s="107"/>
-      <c r="O69" s="107"/>
+    <row r="69" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="105"/>
+      <c r="C69" s="105"/>
+      <c r="D69" s="105"/>
+      <c r="E69" s="105"/>
+      <c r="F69" s="105"/>
+      <c r="G69" s="105"/>
+      <c r="H69" s="105"/>
+      <c r="I69" s="115"/>
+      <c r="J69" s="115"/>
+      <c r="K69" s="115"/>
+      <c r="L69" s="115"/>
+      <c r="M69" s="115"/>
+      <c r="N69" s="115"/>
+      <c r="O69" s="115"/>
       <c r="P69" s="10"/>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -8584,16 +8597,16 @@
       <c r="X69" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="AB69" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC69" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE69" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF69" s="119" t="s">
+      <c r="AB69" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="129" t="s">
         <v>0</v>
       </c>
       <c r="AJ69" s="72" t="s">
@@ -8644,40 +8657,40 @@
       <c r="BL69" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BR69" s="112"/>
-      <c r="BS69" s="113"/>
-      <c r="BT69" s="113"/>
-      <c r="BU69" s="113"/>
-      <c r="BV69" s="114"/>
+      <c r="BR69" s="120"/>
+      <c r="BS69" s="121"/>
+      <c r="BT69" s="121"/>
+      <c r="BU69" s="121"/>
+      <c r="BV69" s="122"/>
     </row>
-    <row r="70" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B70" s="99"/>
-      <c r="C70" s="99"/>
-      <c r="D70" s="99"/>
-      <c r="E70" s="99"/>
-      <c r="F70" s="99"/>
-      <c r="G70" s="99"/>
-      <c r="H70" s="99"/>
-      <c r="I70" s="107"/>
-      <c r="J70" s="107"/>
-      <c r="K70" s="107"/>
-      <c r="L70" s="107"/>
-      <c r="M70" s="107"/>
-      <c r="N70" s="107"/>
-      <c r="O70" s="107"/>
+    <row r="70" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="105"/>
+      <c r="C70" s="105"/>
+      <c r="D70" s="105"/>
+      <c r="E70" s="105"/>
+      <c r="F70" s="105"/>
+      <c r="G70" s="105"/>
+      <c r="H70" s="105"/>
+      <c r="I70" s="115"/>
+      <c r="J70" s="115"/>
+      <c r="K70" s="115"/>
+      <c r="L70" s="115"/>
+      <c r="M70" s="115"/>
+      <c r="N70" s="115"/>
+      <c r="O70" s="115"/>
       <c r="P70" s="10"/>
       <c r="Q70" s="10"/>
       <c r="R70" s="10"/>
       <c r="T70" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="U70" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="W70" s="79" t="s">
         <v>261</v>
       </c>
-      <c r="U70" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="W70" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="X70" s="119" t="s">
+      <c r="X70" s="129" t="s">
         <v>0</v>
       </c>
       <c r="AB70" s="29"/>
@@ -8685,60 +8698,60 @@
       <c r="AJ70" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="AK70" s="119" t="s">
+      <c r="AK70" s="129" t="s">
         <v>0</v>
       </c>
       <c r="AM70" s="79" t="s">
+        <v>263</v>
+      </c>
+      <c r="AN70" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="83" t="s">
         <v>264</v>
       </c>
-      <c r="AN70" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU70" s="83" t="s">
+      <c r="AV70" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ70" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA70" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH70" s="79" t="s">
         <v>265</v>
       </c>
-      <c r="AV70" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ70" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA70" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH70" s="79" t="s">
+      <c r="BI70" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK70" s="131" t="s">
         <v>266</v>
       </c>
-      <c r="BI70" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK70" s="123" t="s">
-        <v>267</v>
-      </c>
-      <c r="BL70" s="124" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR70" s="112"/>
-      <c r="BS70" s="113"/>
-      <c r="BT70" s="113"/>
-      <c r="BU70" s="113"/>
-      <c r="BV70" s="114"/>
+      <c r="BL70" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR70" s="120"/>
+      <c r="BS70" s="121"/>
+      <c r="BT70" s="121"/>
+      <c r="BU70" s="121"/>
+      <c r="BV70" s="122"/>
     </row>
-    <row r="71" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B71" s="99"/>
-      <c r="C71" s="99"/>
-      <c r="D71" s="99"/>
-      <c r="E71" s="99"/>
-      <c r="F71" s="99"/>
-      <c r="G71" s="99"/>
-      <c r="H71" s="99"/>
-      <c r="I71" s="107"/>
-      <c r="J71" s="107"/>
-      <c r="K71" s="107"/>
-      <c r="L71" s="107"/>
-      <c r="M71" s="107"/>
-      <c r="N71" s="107"/>
-      <c r="O71" s="107"/>
+    <row r="71" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="105"/>
+      <c r="C71" s="105"/>
+      <c r="D71" s="105"/>
+      <c r="E71" s="105"/>
+      <c r="F71" s="105"/>
+      <c r="G71" s="105"/>
+      <c r="H71" s="105"/>
+      <c r="I71" s="115"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="115"/>
+      <c r="L71" s="115"/>
+      <c r="M71" s="115"/>
+      <c r="N71" s="115"/>
+      <c r="O71" s="115"/>
       <c r="P71" s="10"/>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -8746,34 +8759,34 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="BA71" s="82"/>
       <c r="BH71" s="82" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BI71" s="82"/>
-      <c r="BR71" s="112"/>
-      <c r="BS71" s="113"/>
-      <c r="BT71" s="113"/>
-      <c r="BU71" s="113"/>
-      <c r="BV71" s="114"/>
+      <c r="BR71" s="120"/>
+      <c r="BS71" s="121"/>
+      <c r="BT71" s="121"/>
+      <c r="BU71" s="121"/>
+      <c r="BV71" s="122"/>
     </row>
-    <row r="72" spans="2:74" ht="26.1" customHeight="1">
-      <c r="B72" s="99"/>
-      <c r="C72" s="99"/>
-      <c r="D72" s="99"/>
-      <c r="E72" s="99"/>
-      <c r="F72" s="99"/>
-      <c r="G72" s="99"/>
-      <c r="H72" s="99"/>
-      <c r="I72" s="107"/>
-      <c r="J72" s="107"/>
-      <c r="K72" s="107"/>
-      <c r="L72" s="107"/>
-      <c r="M72" s="107"/>
-      <c r="N72" s="107"/>
-      <c r="O72" s="107"/>
+    <row r="72" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="105"/>
+      <c r="C72" s="105"/>
+      <c r="D72" s="105"/>
+      <c r="E72" s="105"/>
+      <c r="F72" s="105"/>
+      <c r="G72" s="105"/>
+      <c r="H72" s="105"/>
+      <c r="I72" s="115"/>
+      <c r="J72" s="115"/>
+      <c r="K72" s="115"/>
+      <c r="L72" s="115"/>
+      <c r="M72" s="115"/>
+      <c r="N72" s="115"/>
+      <c r="O72" s="115"/>
       <c r="P72" s="10"/>
       <c r="Q72" s="10"/>
       <c r="R72" s="10"/>
@@ -8825,27 +8838,27 @@
       <c r="BN72" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="BR72" s="112"/>
-      <c r="BS72" s="113"/>
-      <c r="BT72" s="113"/>
-      <c r="BU72" s="113"/>
-      <c r="BV72" s="114"/>
+      <c r="BR72" s="120"/>
+      <c r="BS72" s="121"/>
+      <c r="BT72" s="121"/>
+      <c r="BU72" s="121"/>
+      <c r="BV72" s="122"/>
     </row>
-    <row r="73" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
-      <c r="B73" s="100"/>
-      <c r="C73" s="100"/>
-      <c r="D73" s="100"/>
-      <c r="E73" s="100"/>
-      <c r="F73" s="100"/>
-      <c r="G73" s="100"/>
-      <c r="H73" s="100"/>
-      <c r="I73" s="108"/>
-      <c r="J73" s="108"/>
-      <c r="K73" s="108"/>
-      <c r="L73" s="108"/>
-      <c r="M73" s="108"/>
-      <c r="N73" s="108"/>
-      <c r="O73" s="108"/>
+    <row r="73" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="106"/>
+      <c r="C73" s="106"/>
+      <c r="D73" s="106"/>
+      <c r="E73" s="106"/>
+      <c r="F73" s="106"/>
+      <c r="G73" s="106"/>
+      <c r="H73" s="106"/>
+      <c r="I73" s="116"/>
+      <c r="J73" s="116"/>
+      <c r="K73" s="116"/>
+      <c r="L73" s="116"/>
+      <c r="M73" s="116"/>
+      <c r="N73" s="116"/>
+      <c r="O73" s="116"/>
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
       <c r="R73" s="25"/>
@@ -8858,13 +8871,13 @@
       <c r="AF73" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="BR73" s="115"/>
-      <c r="BS73" s="116"/>
-      <c r="BT73" s="116"/>
-      <c r="BU73" s="116"/>
-      <c r="BV73" s="117"/>
+      <c r="BR73" s="123"/>
+      <c r="BS73" s="124"/>
+      <c r="BT73" s="124"/>
+      <c r="BU73" s="124"/>
+      <c r="BV73" s="125"/>
     </row>
-    <row r="74" spans="2:74" ht="26.1" customHeight="1">
+    <row r="74" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="13" t="s">
         <v>0</v>
       </c>
@@ -9070,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:74" ht="26.1" customHeight="1">
+    <row r="75" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="2" t="s">
         <v>0</v>
       </c>
@@ -9114,7 +9127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:74" ht="26.1" customHeight="1"/>
+    <row r="76" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="411">
     <mergeCell ref="T59:T61"/>
@@ -9533,7 +9546,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV21 BU4:CV4 BA8:CV12 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:CV58 P53:BJ53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:CV57 P54:BJ54 S66:BQ66 S67:BQ69 S64:BQ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D22:AI26 A21 D21:AB21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:AA29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BJ55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A18:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV26 AW36 BE46:BH46 BJ46:CV46 A10:T12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV12 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:CV58 P53:BJ53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:CV57 P54:BJ54 S66:BQ66 S68:BQ69 S64:BQ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D22:AI26 A21 D21:AB21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:AA29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BJ55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A18:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV23 AW36 BE46:BH46 BJ46:CV46 A10:T12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:CV20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:CV26 BA24:BJ24 BL24:CV24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/daerung.xlsx
+++ b/daerung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\수정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFA219F-9FD7-4A78-8722-9DC9705480E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83785BF4-78D0-4F53-BB8F-283800753F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="309">
   <si>
     <t/>
   </si>
@@ -289,9 +289,6 @@
   </si>
   <si>
     <t>주창륜</t>
-  </si>
-  <si>
-    <t>이재민</t>
   </si>
   <si>
     <t>유지현</t>
@@ -570,9 +567,6 @@
     <t>김윤석</t>
   </si>
   <si>
-    <t>백지윤</t>
-  </si>
-  <si>
     <t>신하늬</t>
   </si>
   <si>
@@ -861,10 +855,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CEO실</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>탕비실</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -890,10 +880,6 @@
   </si>
   <si>
     <t>C802</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CTO실</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -992,6 +978,26 @@
   </si>
   <si>
     <t>김수지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총괄대표실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부문대표실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김채현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이원용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이재민</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -999,7 +1005,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2266,14 +2272,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:BV76"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="100" width="5.28515625" style="1" customWidth="1"/>
     <col min="101" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:74" ht="26.1" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="101" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AD2" s="101"/>
       <c r="AE2" s="101"/>
@@ -2361,7 +2367,7 @@
       <c r="AH2" s="101"/>
       <c r="AI2" s="101"/>
       <c r="AJ2" s="89" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AK2" s="90"/>
       <c r="AL2" s="90"/>
@@ -2446,12 +2452,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="103" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E3" s="103"/>
       <c r="F3" s="103"/>
@@ -2506,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BC3" s="103" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BD3" s="103"/>
       <c r="BE3" s="103"/>
@@ -2529,7 +2535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B4" s="14" t="s">
         <v>0</v>
       </c>
@@ -2617,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -2693,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B6" s="14" t="s">
         <v>0</v>
       </c>
@@ -2740,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B7" s="14" t="s">
         <v>0</v>
       </c>
@@ -2772,10 +2778,10 @@
         <v>7</v>
       </c>
       <c r="W7" s="71" t="s">
+        <v>295</v>
+      </c>
+      <c r="X7" s="71" t="s">
         <v>299</v>
-      </c>
-      <c r="X7" s="71" t="s">
-        <v>303</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>0</v>
@@ -2814,13 +2820,13 @@
         <v>9</v>
       </c>
       <c r="BS7" s="85" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="BT7" s="85"/>
       <c r="BU7" s="85"/>
       <c r="BV7" s="102"/>
     </row>
-    <row r="8" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B8" s="14" t="s">
         <v>0</v>
       </c>
@@ -2924,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B9" s="16" t="s">
         <v>0</v>
       </c>
@@ -3040,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
@@ -3076,10 +3082,10 @@
       </c>
       <c r="U10" s="71"/>
       <c r="W10" s="71" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="X10" s="71" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AA10" s="81" t="s">
         <v>25</v>
@@ -3151,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B11" s="16" t="s">
         <v>0</v>
       </c>
@@ -3262,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B12" s="16" t="s">
         <v>0</v>
       </c>
@@ -3370,7 +3376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B13" s="16" t="s">
         <v>0</v>
       </c>
@@ -3408,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="71" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="X13" s="71" t="s">
         <v>0</v>
@@ -3480,7 +3486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B14" s="16" t="s">
         <v>0</v>
       </c>
@@ -3590,7 +3596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B15" s="16" t="s">
         <v>0</v>
       </c>
@@ -3700,7 +3706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B16" s="16" t="s">
         <v>0</v>
       </c>
@@ -3797,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B17" s="16" t="s">
         <v>0</v>
       </c>
@@ -3817,13 +3823,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="N17" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" s="85" t="s">
         <v>123</v>
-      </c>
-      <c r="N17" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="T17" s="85" t="s">
-        <v>124</v>
       </c>
       <c r="U17" s="85" t="s">
         <v>0</v>
@@ -3880,7 +3886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B18" s="14" t="s">
         <v>0</v>
       </c>
@@ -3901,7 +3907,7 @@
         <v>70</v>
       </c>
       <c r="N18" s="71" t="s">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="P18" s="71" t="s">
         <v>0</v>
@@ -3967,7 +3973,7 @@
         <v>80</v>
       </c>
       <c r="BK18" s="71" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="BO18" s="71" t="s">
         <v>0</v>
@@ -3988,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B19" s="14" t="s">
         <v>0</v>
       </c>
@@ -4098,7 +4104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B20" s="14" t="s">
         <v>0</v>
       </c>
@@ -4208,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B21" s="19"/>
       <c r="F21" s="71" t="s">
         <v>84</v>
@@ -4223,31 +4229,31 @@
         <v>87</v>
       </c>
       <c r="M21" s="71" t="s">
+        <v>307</v>
+      </c>
+      <c r="N21" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="N21" s="71" t="s">
+      <c r="P21" s="98" t="s">
         <v>89</v>
       </c>
-      <c r="P21" s="98" t="s">
+      <c r="Q21" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="Q21" s="71" t="s">
+      <c r="T21" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="U21" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="T21" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="U21" s="71" t="s">
+      <c r="W21" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="W21" s="71" t="s">
+      <c r="X21" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="X21" s="71" t="s">
+      <c r="AB21" s="95" t="s">
         <v>94</v>
-      </c>
-      <c r="AB21" s="95" t="s">
-        <v>95</v>
       </c>
       <c r="AC21" s="101"/>
       <c r="AD21" s="101"/>
@@ -4277,43 +4283,43 @@
         <v>0</v>
       </c>
       <c r="BB21" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC21" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="BC21" s="71" t="s">
+      <c r="BG21" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="BG21" s="71" t="s">
+      <c r="BH21" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="BH21" s="71" t="s">
+      <c r="BJ21" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="BJ21" s="71" t="s">
+      <c r="BK21" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="BO21" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP21" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="BK21" s="71" t="s">
-        <v>306</v>
-      </c>
-      <c r="BO21" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP21" s="71" t="s">
+      <c r="BS21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT21" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="BS21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT21" s="71" t="s">
+      <c r="BU21" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="BU21" s="71" t="s">
-        <v>103</v>
-      </c>
       <c r="BV21" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B22" s="19"/>
       <c r="F22" s="72" t="s">
         <v>0</v>
@@ -4355,19 +4361,19 @@
         <v>0</v>
       </c>
       <c r="AC22" s="101" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="101" t="s">
         <v>104</v>
-      </c>
-      <c r="AD22" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="101" t="s">
-        <v>105</v>
       </c>
       <c r="AH22" s="101" t="s">
         <v>0</v>
@@ -4432,7 +4438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B23" s="19"/>
       <c r="F23" s="73" t="s">
         <v>0</v>
@@ -4551,46 +4557,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B24" s="19"/>
       <c r="F24" s="86" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="I24" s="71" t="s">
+      <c r="J24" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="J24" s="71" t="s">
+      <c r="M24" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="N24" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="N24" s="71" t="s">
+      <c r="P24" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="P24" s="71" t="s">
+      <c r="Q24" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="Q24" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="T24" s="71" t="s">
+      <c r="U24" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="U24" s="71" t="s">
+      <c r="W24" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="W24" s="71" t="s">
+      <c r="X24" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="X24" s="71" t="s">
+      <c r="AB24" s="95" t="s">
         <v>114</v>
-      </c>
-      <c r="AB24" s="95" t="s">
-        <v>115</v>
       </c>
       <c r="AC24" s="101" t="s">
         <v>0</v>
@@ -4637,32 +4643,32 @@
         <v>0</v>
       </c>
       <c r="BC24" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG24" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="BG24" s="71" t="s">
+      <c r="BH24" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="BH24" s="71" t="s">
+      <c r="BJ24" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="BJ24" s="71" t="s">
+      <c r="BK24" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="BO24" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="BK24" s="71" t="s">
-        <v>307</v>
-      </c>
-      <c r="BO24" s="71" t="s">
+      <c r="BP24" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="BP24" s="71" t="s">
+      <c r="BS24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT24" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="BS24" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT24" s="71" t="s">
-        <v>122</v>
-      </c>
       <c r="BU24" s="71" t="s">
         <v>0</v>
       </c>
@@ -4670,7 +4676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B25" s="19"/>
       <c r="F25" s="87" t="s">
         <v>0</v>
@@ -4789,7 +4795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B26" s="19"/>
       <c r="D26" s="3" t="s">
         <v>0</v>
@@ -4929,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:74" ht="26.1" customHeight="1">
       <c r="B27" s="14" t="s">
         <v>0</v>
       </c>
@@ -4938,21 +4944,21 @@
       <c r="T27" s="82"/>
       <c r="U27" s="82"/>
       <c r="AB27" s="126" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="BA27" s="126" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="BV27" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B28" s="14" t="s">
         <v>0</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N28" s="85" t="s">
         <v>0</v>
@@ -4963,25 +4969,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:74" ht="26.1" customHeight="1">
       <c r="B29" s="117" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C29" s="119"/>
       <c r="F29" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G29" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="J29" s="71" t="s">
+      <c r="K29" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="M29" s="71" t="s">
         <v>127</v>
-      </c>
-      <c r="K29" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="M29" s="71" t="s">
-        <v>128</v>
       </c>
       <c r="AB29" s="110"/>
       <c r="BA29" s="110"/>
@@ -4989,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B30" s="120"/>
       <c r="C30" s="122"/>
       <c r="F30" s="72" t="s">
@@ -5009,7 +5015,7 @@
       </c>
       <c r="AB30" s="110"/>
       <c r="AC30" s="85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD30" s="85" t="s">
         <v>0</v>
@@ -5032,7 +5038,7 @@
       <c r="BA30" s="130"/>
       <c r="BV30" s="33"/>
     </row>
-    <row r="31" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:74" ht="26.1" customHeight="1">
       <c r="B31" s="120"/>
       <c r="C31" s="122"/>
       <c r="F31" s="73" t="s">
@@ -5051,83 +5057,83 @@
         <v>0</v>
       </c>
       <c r="U31" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V31" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="W31" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="X31" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="117" t="s">
         <v>129</v>
-      </c>
-      <c r="V31" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="W31" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="X31" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="117" t="s">
-        <v>130</v>
       </c>
       <c r="Z31" s="118"/>
       <c r="AA31" s="118"/>
       <c r="AB31" s="119"/>
       <c r="AC31" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD31" s="104" t="s">
         <v>134</v>
       </c>
-      <c r="AD31" s="104" t="s">
+      <c r="AE31" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="AE31" s="104" t="s">
+      <c r="AF31" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="AF31" s="104" t="s">
+      <c r="AG31" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="AG31" s="104" t="s">
+      <c r="AH31" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="AH31" s="104" t="s">
+      <c r="AI31" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="AI31" s="104" t="s">
-        <v>140</v>
-      </c>
       <c r="AW31" s="117" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AX31" s="118"/>
       <c r="AY31" s="118"/>
       <c r="AZ31" s="118"/>
       <c r="BA31" s="119"/>
       <c r="BM31" s="117" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="BN31" s="118"/>
       <c r="BO31" s="118"/>
       <c r="BP31" s="118"/>
       <c r="BQ31" s="119"/>
       <c r="BR31" s="117" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="BS31" s="118"/>
       <c r="BT31" s="118"/>
       <c r="BU31" s="118"/>
       <c r="BV31" s="119"/>
     </row>
-    <row r="32" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:74" ht="26.1" customHeight="1">
       <c r="B32" s="120"/>
       <c r="C32" s="122"/>
       <c r="F32" s="71" t="s">
+        <v>131</v>
+      </c>
+      <c r="G32" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="J32" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="M32" s="71" t="s">
         <v>132</v>
-      </c>
-      <c r="G32" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="J32" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="M32" s="71" t="s">
-        <v>133</v>
       </c>
       <c r="U32" s="105" t="s">
         <v>0</v>
@@ -5168,7 +5174,7 @@
       <c r="BU32" s="121"/>
       <c r="BV32" s="122"/>
     </row>
-    <row r="33" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:74" ht="26.1" customHeight="1">
       <c r="B33" s="120"/>
       <c r="C33" s="122"/>
       <c r="F33" s="72" t="s">
@@ -5225,7 +5231,7 @@
       <c r="BU33" s="121"/>
       <c r="BV33" s="122"/>
     </row>
-    <row r="34" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:74" ht="26.1" customHeight="1">
       <c r="B34" s="120"/>
       <c r="C34" s="122"/>
       <c r="F34" s="73" t="s">
@@ -5282,7 +5288,7 @@
       <c r="BU34" s="121"/>
       <c r="BV34" s="122"/>
     </row>
-    <row r="35" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B35" s="123"/>
       <c r="C35" s="125"/>
       <c r="D35" s="18" t="s">
@@ -5316,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O35" s="110"/>
       <c r="P35" s="110"/>
@@ -5376,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="AR35" s="110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AS35" s="110" t="s">
         <v>0</v>
@@ -5439,7 +5445,7 @@
       <c r="BU35" s="124"/>
       <c r="BV35" s="125"/>
     </row>
-    <row r="36" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:74" ht="26.1" customHeight="1">
       <c r="B36" s="39"/>
       <c r="C36" s="40"/>
       <c r="D36" s="40"/>
@@ -5516,7 +5522,7 @@
       <c r="BU36" s="34"/>
       <c r="BV36" s="35"/>
     </row>
-    <row r="37" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B37" s="42"/>
       <c r="C37" s="43"/>
       <c r="D37" s="46"/>
@@ -5591,11 +5597,11 @@
       <c r="BU37" s="36"/>
       <c r="BV37" s="37"/>
     </row>
-    <row r="38" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B38" s="42"/>
       <c r="C38" s="43"/>
       <c r="D38" s="141" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E38" s="141"/>
       <c r="F38" s="141"/>
@@ -5612,7 +5618,7 @@
       <c r="Q38" s="43"/>
       <c r="R38" s="43"/>
       <c r="S38" s="39" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="T38" s="40"/>
       <c r="U38" s="40"/>
@@ -5624,7 +5630,7 @@
       <c r="AA38" s="51"/>
       <c r="AB38" s="52"/>
       <c r="AC38" s="48" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AD38" s="48"/>
       <c r="AE38" s="48"/>
@@ -5646,7 +5652,7 @@
       <c r="AU38" s="36"/>
       <c r="AV38" s="36"/>
       <c r="AW38" s="68" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AX38" s="69"/>
       <c r="AY38" s="69"/>
@@ -5666,7 +5672,7 @@
       <c r="BM38" s="63"/>
       <c r="BN38" s="64"/>
       <c r="BO38" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BP38" s="40"/>
       <c r="BQ38" s="40"/>
@@ -5676,7 +5682,7 @@
       <c r="BU38" s="42"/>
       <c r="BV38" s="44"/>
     </row>
-    <row r="39" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B39" s="45"/>
       <c r="C39" s="46"/>
       <c r="D39" s="141"/>
@@ -5751,7 +5757,7 @@
       <c r="BU39" s="45"/>
       <c r="BV39" s="47"/>
     </row>
-    <row r="40" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="D40" s="141"/>
       <c r="E40" s="141"/>
       <c r="F40" s="141"/>
@@ -5823,9 +5829,9 @@
       <c r="BT40" s="47"/>
       <c r="BU40" s="19"/>
     </row>
-    <row r="41" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="D41" s="141" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E41" s="141"/>
       <c r="F41" s="141"/>
@@ -5858,7 +5864,7 @@
       <c r="AG41" s="57"/>
       <c r="AH41" s="58"/>
       <c r="AI41" s="48" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AJ41" s="48"/>
       <c r="AK41" s="48"/>
@@ -5874,7 +5880,7 @@
       <c r="AU41" s="36"/>
       <c r="AV41" s="36"/>
       <c r="AW41" s="68" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AX41" s="69"/>
       <c r="AY41" s="69"/>
@@ -5882,7 +5888,7 @@
       <c r="BA41" s="69"/>
       <c r="BB41" s="70"/>
       <c r="BC41" s="39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BD41" s="40" t="s">
         <v>0</v>
@@ -5912,7 +5918,7 @@
       <c r="BS41" s="57"/>
       <c r="BT41" s="58"/>
     </row>
-    <row r="42" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B42" s="39"/>
       <c r="C42" s="40"/>
       <c r="D42" s="141"/>
@@ -5999,7 +6005,7 @@
       <c r="BU42" s="40"/>
       <c r="BV42" s="41"/>
     </row>
-    <row r="43" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B43" s="42"/>
       <c r="C43" s="43"/>
       <c r="D43" s="141"/>
@@ -6086,7 +6092,7 @@
       <c r="BU43" s="43"/>
       <c r="BV43" s="44"/>
     </row>
-    <row r="44" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:74" ht="26.1" customHeight="1">
       <c r="B44" s="42"/>
       <c r="C44" s="43"/>
       <c r="D44" s="40" t="s">
@@ -6163,7 +6169,7 @@
       <c r="BU44" s="43"/>
       <c r="BV44" s="44"/>
     </row>
-    <row r="45" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B45" s="45"/>
       <c r="C45" s="46"/>
       <c r="D45" s="46"/>
@@ -6238,7 +6244,7 @@
       <c r="BU45" s="46"/>
       <c r="BV45" s="47"/>
     </row>
-    <row r="46" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:74" ht="26.1" customHeight="1">
       <c r="B46" s="12" t="s">
         <v>0</v>
       </c>
@@ -6267,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L46" s="110" t="s">
         <v>0</v>
@@ -6286,7 +6292,7 @@
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
       <c r="T46" s="110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U46" s="110" t="s">
         <v>0</v>
@@ -6301,143 +6307,143 @@
         <v>0</v>
       </c>
       <c r="Y46" s="104" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="Z46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="104" t="s">
+      <c r="AE46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="AE46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="104" t="s">
+      <c r="AG46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="104" t="s">
+        <v>282</v>
+      </c>
+      <c r="AK46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR46" s="110" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="104" t="s">
+        <v>276</v>
+      </c>
+      <c r="AX46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="104" t="s">
         <v>148</v>
       </c>
-      <c r="AG46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="104" t="s">
-        <v>286</v>
-      </c>
-      <c r="AK46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR46" s="110" t="s">
-        <v>141</v>
-      </c>
-      <c r="AS46" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU46" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW46" s="104" t="s">
-        <v>279</v>
-      </c>
-      <c r="AX46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="104" t="s">
+      <c r="BA46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC46" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="104" t="s">
+        <v>271</v>
+      </c>
+      <c r="BE46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="104" t="s">
+        <v>271</v>
+      </c>
+      <c r="BJ46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM46" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="BA46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC46" s="104" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD46" s="104" t="s">
-        <v>273</v>
-      </c>
-      <c r="BE46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="104" t="s">
-        <v>273</v>
-      </c>
-      <c r="BJ46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM46" s="104" t="s">
+      <c r="BN46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ46" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR46" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="BN46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ46" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR46" s="104" t="s">
-        <v>151</v>
-      </c>
       <c r="BS46" s="107" t="s">
         <v>0</v>
       </c>
@@ -6451,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:74" ht="26.1" customHeight="1">
       <c r="B47" s="14" t="s">
         <v>0</v>
       </c>
@@ -6604,12 +6610,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B48" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E48" s="103" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F48" s="103"/>
       <c r="G48" s="103"/>
@@ -6758,7 +6764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:74" ht="26.1" customHeight="1">
       <c r="B49" s="14" t="s">
         <v>0</v>
       </c>
@@ -6789,25 +6795,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:74" ht="26.1" customHeight="1">
       <c r="B50" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E50" s="84" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F50" s="84"/>
       <c r="H50" s="84" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I50" s="84"/>
       <c r="K50" s="84" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L50" s="84"/>
       <c r="O50" s="22"/>
       <c r="AH50" s="113" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AI50" s="113"/>
       <c r="AJ50" s="113"/>
@@ -6839,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:74" ht="26.1" customHeight="1">
       <c r="B51" s="14" t="s">
         <v>0</v>
       </c>
@@ -6847,31 +6853,31 @@
         <v>0</v>
       </c>
       <c r="D51" s="138" t="s">
+        <v>154</v>
+      </c>
+      <c r="E51" s="137" t="s">
         <v>155</v>
       </c>
-      <c r="E51" s="137" t="s">
+      <c r="F51" s="137" t="s">
         <v>156</v>
       </c>
-      <c r="F51" s="137" t="s">
+      <c r="H51" s="137" t="s">
         <v>157</v>
       </c>
-      <c r="H51" s="137" t="s">
+      <c r="I51" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="I51" s="137" t="s">
+      <c r="J51" s="138" t="s">
         <v>159</v>
       </c>
-      <c r="J51" s="138" t="s">
+      <c r="K51" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" s="137" t="s">
         <v>160</v>
       </c>
-      <c r="K51" s="133" t="s">
-        <v>0</v>
-      </c>
-      <c r="L51" s="137" t="s">
+      <c r="M51" s="136" t="s">
         <v>161</v>
-      </c>
-      <c r="M51" s="136" t="s">
-        <v>162</v>
       </c>
       <c r="O51" s="22"/>
       <c r="T51" s="31"/>
@@ -6919,7 +6925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:74" ht="26.1" customHeight="1">
       <c r="B52" s="14" t="s">
         <v>0</v>
       </c>
@@ -6938,41 +6944,41 @@
         <v>0</v>
       </c>
       <c r="T52" s="112" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U52" s="112"/>
       <c r="W52" s="112" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X52" s="112"/>
       <c r="AB52" s="85" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AC52" s="85"/>
       <c r="AD52" s="85"/>
       <c r="AK52" s="111" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AL52" s="111"/>
       <c r="AM52" s="111"/>
       <c r="AR52" s="112" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AS52" s="112"/>
       <c r="AU52" s="112" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AV52" s="112"/>
       <c r="AZ52" s="84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BA52" s="84"/>
       <c r="BH52" s="84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BI52" s="84"/>
       <c r="BK52" s="84" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="BL52" s="84"/>
       <c r="BR52" s="108" t="s">
@@ -6991,7 +6997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B53" s="14" t="s">
         <v>0</v>
       </c>
@@ -7016,86 +7022,86 @@
         <v>0</v>
       </c>
       <c r="W53" s="71" t="s">
+        <v>169</v>
+      </c>
+      <c r="X53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="X53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="71" t="s">
+      <c r="AC53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="71" t="s">
         <v>171</v>
       </c>
-      <c r="AC53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM53" s="71" t="s">
+      <c r="AN53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR53" s="71" t="s">
         <v>172</v>
       </c>
-      <c r="AN53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR53" s="71" t="s">
+      <c r="AS53" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="AS53" s="71" t="s">
+      <c r="AU53" s="71" t="s">
         <v>174</v>
       </c>
-      <c r="AU53" s="71" t="s">
+      <c r="AV53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="AV53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AX53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="71" t="s">
+      <c r="BA53" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="BA53" s="71" t="s">
+      <c r="BC53" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="BC53" s="71" t="s">
+      <c r="BD53" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH53" s="71" t="s">
         <v>178</v>
       </c>
-      <c r="BD53" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH53" s="71" t="s">
+      <c r="BI53" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="BK53" s="71" t="s">
+        <v>288</v>
+      </c>
+      <c r="BL53" s="71" t="s">
         <v>179</v>
       </c>
-      <c r="BI53" s="71" t="s">
-        <v>180</v>
-      </c>
-      <c r="BK53" s="71" t="s">
-        <v>292</v>
-      </c>
-      <c r="BL53" s="71" t="s">
-        <v>181</v>
-      </c>
       <c r="BN53" s="3" t="s">
         <v>0</v>
       </c>
@@ -7115,7 +7121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:74" ht="26.1" customHeight="1">
       <c r="B54" s="14" t="s">
         <v>0</v>
       </c>
@@ -7123,19 +7129,19 @@
         <v>0</v>
       </c>
       <c r="E54" s="137" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" s="137" t="s">
         <v>165</v>
       </c>
-      <c r="F54" s="137" t="s">
+      <c r="H54" s="137" t="s">
         <v>166</v>
       </c>
-      <c r="H54" s="137" t="s">
+      <c r="I54" s="137" t="s">
         <v>167</v>
       </c>
-      <c r="I54" s="137" t="s">
+      <c r="K54" s="137" t="s">
         <v>168</v>
-      </c>
-      <c r="K54" s="137" t="s">
-        <v>169</v>
       </c>
       <c r="L54" s="133" t="s">
         <v>0</v>
@@ -7215,10 +7221,10 @@
         <v>0</v>
       </c>
       <c r="BN54" s="71" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="BR54" s="104" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="BS54" s="107" t="s">
         <v>0</v>
@@ -7233,7 +7239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:74" ht="26.1" customHeight="1">
       <c r="B55" s="14" t="s">
         <v>0</v>
       </c>
@@ -7337,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:74" ht="26.1" customHeight="1">
       <c r="B56" s="14" t="s">
         <v>0</v>
       </c>
@@ -7353,77 +7359,75 @@
         <v>0</v>
       </c>
       <c r="T56" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="U56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="W56" s="71" t="s">
+        <v>187</v>
+      </c>
+      <c r="X56" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="U56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="W56" s="71" t="s">
+      <c r="AB56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="X56" s="71" t="s">
+      <c r="AE56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="AB56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="71" t="s">
+      <c r="AM56" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="AE56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="71" t="s">
+      <c r="AN56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR56" s="71" t="s">
         <v>192</v>
       </c>
-      <c r="AM56" s="71" t="s">
+      <c r="AS56" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="AN56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="71" t="s">
+      <c r="AU56" s="71" t="s">
         <v>194</v>
       </c>
-      <c r="AS56" s="71" t="s">
+      <c r="AV56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ56" s="71" t="s">
         <v>195</v>
       </c>
-      <c r="AU56" s="71" t="s">
+      <c r="BA56" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="AV56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ56" s="71" t="s">
+      <c r="BC56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD56" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH56" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="BA56" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="BC56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD56" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH56" s="71" t="s">
+      <c r="BI56" s="71"/>
+      <c r="BK56" s="71" t="s">
         <v>199</v>
       </c>
-      <c r="BI56" s="71" t="s">
+      <c r="BL56" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="BK56" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="BL56" s="71" t="s">
-        <v>202</v>
-      </c>
       <c r="BN56" s="73" t="s">
         <v>0</v>
       </c>
@@ -7443,27 +7447,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:74" ht="26.1" customHeight="1">
       <c r="B57" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E57" s="133" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F57" s="137" t="s">
+        <v>181</v>
+      </c>
+      <c r="H57" s="137" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="H57" s="137" t="s">
+      <c r="K57" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="I57" s="137" t="s">
+      <c r="L57" s="137" t="s">
         <v>185</v>
-      </c>
-      <c r="K57" s="137" t="s">
-        <v>186</v>
-      </c>
-      <c r="L57" s="137" t="s">
-        <v>187</v>
       </c>
       <c r="O57" s="22"/>
       <c r="R57" s="2" t="s">
@@ -7532,9 +7536,7 @@
       <c r="BH57" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="BI57" s="72" t="s">
-        <v>0</v>
-      </c>
+      <c r="BI57" s="72"/>
       <c r="BK57" s="72" t="s">
         <v>0</v>
       </c>
@@ -7542,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="BN57" s="71" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="BR57" s="108" t="s">
         <v>0</v>
@@ -7560,7 +7562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B58" s="14" t="s">
         <v>0</v>
       </c>
@@ -7637,9 +7639,7 @@
       <c r="BH58" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="BI58" s="73" t="s">
-        <v>0</v>
-      </c>
+      <c r="BI58" s="73"/>
       <c r="BK58" s="73" t="s">
         <v>0</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:74" ht="26.1" customHeight="1">
       <c r="B59" s="14" t="s">
         <v>0</v>
       </c>
@@ -7686,106 +7686,106 @@
         <v>0</v>
       </c>
       <c r="T59" s="71" t="s">
+        <v>206</v>
+      </c>
+      <c r="U59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="W59" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="X59" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="U59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="W59" s="71" t="s">
+      <c r="AB59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="71" t="s">
         <v>209</v>
       </c>
-      <c r="X59" s="71" t="s">
+      <c r="AE59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="71" t="s">
         <v>210</v>
       </c>
-      <c r="AB59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="71" t="s">
+      <c r="AM59" s="71" t="s">
         <v>211</v>
       </c>
-      <c r="AE59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="71" t="s">
+      <c r="AN59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="71" t="s">
         <v>212</v>
       </c>
-      <c r="AM59" s="71" t="s">
+      <c r="AU59" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="AN59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="71" t="s">
+      <c r="AV59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ59" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="AU59" s="71" t="s">
+      <c r="BA59" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="AV59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="71" t="s">
+      <c r="BC59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH59" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="BA59" s="71" t="s">
+      <c r="BI59" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="BC59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH59" s="71" t="s">
+      <c r="BK59" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="BI59" s="71" t="s">
+      <c r="BL59" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="BK59" s="71" t="s">
-        <v>220</v>
-      </c>
-      <c r="BL59" s="71" t="s">
-        <v>221</v>
-      </c>
       <c r="BN59" s="73" t="s">
         <v>0</v>
       </c>
       <c r="BR59" s="117" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="BS59" s="118"/>
       <c r="BT59" s="118"/>
       <c r="BU59" s="118"/>
       <c r="BV59" s="119"/>
     </row>
-    <row r="60" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:74" ht="26.1" customHeight="1">
       <c r="B60" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E60" s="137" t="s">
+        <v>202</v>
+      </c>
+      <c r="F60" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="H60" s="137" t="s">
+        <v>203</v>
+      </c>
+      <c r="I60" s="137" t="s">
         <v>204</v>
       </c>
-      <c r="F60" s="133" t="s">
-        <v>0</v>
-      </c>
-      <c r="H60" s="137" t="s">
+      <c r="K60" s="137" t="s">
         <v>205</v>
-      </c>
-      <c r="I60" s="137" t="s">
-        <v>206</v>
-      </c>
-      <c r="K60" s="137" t="s">
-        <v>207</v>
       </c>
       <c r="L60" s="137"/>
       <c r="O60" s="22"/>
@@ -7871,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="BN60" s="71" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BR60" s="120"/>
       <c r="BS60" s="121"/>
@@ -7879,7 +7879,7 @@
       <c r="BU60" s="121"/>
       <c r="BV60" s="122"/>
     </row>
-    <row r="61" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:74" ht="26.1" customHeight="1">
       <c r="B61" s="14" t="s">
         <v>0</v>
       </c>
@@ -7971,7 +7971,7 @@
       <c r="BU61" s="121"/>
       <c r="BV61" s="122"/>
     </row>
-    <row r="62" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:74" ht="26.1" customHeight="1">
       <c r="B62" s="14" t="s">
         <v>0</v>
       </c>
@@ -7994,10 +7994,10 @@
         <v>0</v>
       </c>
       <c r="AB62" s="71" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AC62" s="71" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AE62" s="71" t="s">
         <v>0</v>
@@ -8006,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="BL62" s="82" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="BN62" s="73" t="s">
         <v>0</v>
@@ -8017,18 +8017,18 @@
       <c r="BU62" s="121"/>
       <c r="BV62" s="122"/>
     </row>
-    <row r="63" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:74" ht="26.1" customHeight="1">
       <c r="B63" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E63" s="79"/>
       <c r="F63" s="80"/>
       <c r="H63" s="79" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I63" s="80"/>
       <c r="K63" s="79" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L63" s="80"/>
       <c r="O63" s="22"/>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="BN63" s="71" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="BR63" s="120"/>
       <c r="BS63" s="121"/>
@@ -8071,7 +8071,7 @@
       <c r="BU63" s="121"/>
       <c r="BV63" s="122"/>
     </row>
-    <row r="64" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:74" ht="26.1" customHeight="1">
       <c r="B64" s="14" t="s">
         <v>0</v>
       </c>
@@ -8088,76 +8088,76 @@
       <c r="Q64" s="10"/>
       <c r="R64" s="10"/>
       <c r="T64" s="71" t="s">
+        <v>228</v>
+      </c>
+      <c r="U64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="W64" s="71" t="s">
+        <v>229</v>
+      </c>
+      <c r="X64" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="U64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="W64" s="71" t="s">
+      <c r="AB64" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="71" t="s">
         <v>231</v>
       </c>
-      <c r="X64" s="71" t="s">
+      <c r="AM64" s="71" t="s">
         <v>232</v>
       </c>
-      <c r="AB64" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF64" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="71" t="s">
+      <c r="AN64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR64" s="71" t="s">
         <v>233</v>
       </c>
-      <c r="AM64" s="71" t="s">
+      <c r="AS64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU64" s="71" t="s">
         <v>234</v>
       </c>
-      <c r="AN64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR64" s="71" t="s">
+      <c r="AV64" s="71" t="s">
         <v>235</v>
       </c>
-      <c r="AS64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU64" s="71" t="s">
+      <c r="AZ64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA64" s="71" t="s">
         <v>236</v>
       </c>
-      <c r="AV64" s="71" t="s">
+      <c r="BC64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD64" s="71" t="s">
         <v>237</v>
       </c>
-      <c r="AZ64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA64" s="71" t="s">
+      <c r="BH64" s="71" t="s">
         <v>238</v>
       </c>
-      <c r="BC64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD64" s="71" t="s">
+      <c r="BI64" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK64" s="71" t="s">
         <v>239</v>
       </c>
-      <c r="BH64" s="71" t="s">
+      <c r="BL64" s="71" t="s">
         <v>240</v>
-      </c>
-      <c r="BI64" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK64" s="71" t="s">
-        <v>241</v>
-      </c>
-      <c r="BL64" s="71" t="s">
-        <v>242</v>
       </c>
       <c r="BN64" s="72" t="s">
         <v>0</v>
@@ -8168,7 +8168,7 @@
       <c r="BU64" s="121"/>
       <c r="BV64" s="122"/>
     </row>
-    <row r="65" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B65" s="14" t="s">
         <v>0</v>
       </c>
@@ -8207,10 +8207,10 @@
         <v>0</v>
       </c>
       <c r="AB65" s="71" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AC65" s="71" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AE65" s="71" t="s">
         <v>0</v>
@@ -8275,9 +8275,9 @@
       <c r="BU65" s="121"/>
       <c r="BV65" s="122"/>
     </row>
-    <row r="66" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:74" ht="26.1" customHeight="1">
       <c r="B66" s="104" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C66" s="104"/>
       <c r="D66" s="104"/>
@@ -8286,7 +8286,7 @@
       <c r="G66" s="104"/>
       <c r="H66" s="104"/>
       <c r="I66" s="114" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="J66" s="114"/>
       <c r="K66" s="114"/>
@@ -8375,7 +8375,7 @@
       <c r="BU66" s="121"/>
       <c r="BV66" s="122"/>
     </row>
-    <row r="67" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:74" ht="26.1" customHeight="1">
       <c r="B67" s="105"/>
       <c r="C67" s="105"/>
       <c r="D67" s="105"/>
@@ -8394,76 +8394,76 @@
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
       <c r="T67" s="71" t="s">
+        <v>243</v>
+      </c>
+      <c r="U67" s="71" t="s">
+        <v>244</v>
+      </c>
+      <c r="W67" s="71" t="s">
         <v>245</v>
       </c>
-      <c r="U67" s="71" t="s">
+      <c r="X67" s="71" t="s">
         <v>246</v>
       </c>
-      <c r="W67" s="71" t="s">
+      <c r="AB67" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="71" t="s">
         <v>247</v>
       </c>
-      <c r="X67" s="71" t="s">
+      <c r="AM67" s="71" t="s">
         <v>248</v>
       </c>
-      <c r="AB67" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF67" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK67" s="71" t="s">
+      <c r="AN67" s="71" t="s">
         <v>249</v>
       </c>
-      <c r="AM67" s="71" t="s">
+      <c r="AR67" s="71" t="s">
         <v>250</v>
       </c>
-      <c r="AN67" s="71" t="s">
+      <c r="AS67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="71" t="s">
         <v>251</v>
       </c>
-      <c r="AR67" s="71" t="s">
+      <c r="AV67" s="71" t="s">
         <v>252</v>
       </c>
-      <c r="AS67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="71" t="s">
+      <c r="AZ67" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="BA67" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="AV67" s="71" t="s">
+      <c r="BC67" s="71" t="s">
         <v>254</v>
       </c>
-      <c r="AZ67" s="71" t="s">
-        <v>304</v>
-      </c>
-      <c r="BA67" s="71" t="s">
+      <c r="BD67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK67" s="71" t="s">
         <v>255</v>
       </c>
-      <c r="BC67" s="71" t="s">
+      <c r="BL67" s="71" t="s">
         <v>256</v>
-      </c>
-      <c r="BD67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK67" s="71" t="s">
-        <v>257</v>
-      </c>
-      <c r="BL67" s="71" t="s">
-        <v>258</v>
       </c>
       <c r="BR67" s="120"/>
       <c r="BS67" s="121"/>
@@ -8471,7 +8471,7 @@
       <c r="BU67" s="121"/>
       <c r="BV67" s="122"/>
     </row>
-    <row r="68" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:74" ht="26.1" customHeight="1">
       <c r="B68" s="105"/>
       <c r="C68" s="105"/>
       <c r="D68" s="105"/>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="127" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AC68" s="128" t="s">
         <v>0</v>
@@ -8567,7 +8567,7 @@
       <c r="BU68" s="121"/>
       <c r="BV68" s="122"/>
     </row>
-    <row r="69" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:74" ht="26.1" customHeight="1">
       <c r="B69" s="105"/>
       <c r="C69" s="105"/>
       <c r="D69" s="105"/>
@@ -8663,7 +8663,7 @@
       <c r="BU69" s="121"/>
       <c r="BV69" s="122"/>
     </row>
-    <row r="70" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:74" ht="26.1" customHeight="1">
       <c r="B70" s="105"/>
       <c r="C70" s="105"/>
       <c r="D70" s="105"/>
@@ -8682,13 +8682,13 @@
       <c r="Q70" s="10"/>
       <c r="R70" s="10"/>
       <c r="T70" s="79" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="U70" s="129" t="s">
         <v>0</v>
       </c>
       <c r="W70" s="79" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X70" s="129" t="s">
         <v>0</v>
@@ -8702,31 +8702,31 @@
         <v>0</v>
       </c>
       <c r="AM70" s="79" t="s">
+        <v>261</v>
+      </c>
+      <c r="AN70" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="AV70" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ70" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA70" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH70" s="79" t="s">
         <v>263</v>
       </c>
-      <c r="AN70" s="129" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU70" s="83" t="s">
+      <c r="BI70" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK70" s="131" t="s">
         <v>264</v>
-      </c>
-      <c r="AV70" s="140" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ70" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA70" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH70" s="79" t="s">
-        <v>265</v>
-      </c>
-      <c r="BI70" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK70" s="131" t="s">
-        <v>266</v>
       </c>
       <c r="BL70" s="132" t="s">
         <v>0</v>
@@ -8737,7 +8737,7 @@
       <c r="BU70" s="121"/>
       <c r="BV70" s="122"/>
     </row>
-    <row r="71" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:74" ht="26.1" customHeight="1">
       <c r="B71" s="105"/>
       <c r="C71" s="105"/>
       <c r="D71" s="105"/>
@@ -8759,11 +8759,11 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="82" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="BA71" s="82"/>
       <c r="BH71" s="82" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BI71" s="82"/>
       <c r="BR71" s="120"/>
@@ -8772,7 +8772,7 @@
       <c r="BU71" s="121"/>
       <c r="BV71" s="122"/>
     </row>
-    <row r="72" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:74" ht="26.1" customHeight="1">
       <c r="B72" s="105"/>
       <c r="C72" s="105"/>
       <c r="D72" s="105"/>
@@ -8844,7 +8844,7 @@
       <c r="BU72" s="121"/>
       <c r="BV72" s="122"/>
     </row>
-    <row r="73" spans="2:74" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B73" s="106"/>
       <c r="C73" s="106"/>
       <c r="D73" s="106"/>
@@ -8877,7 +8877,7 @@
       <c r="BU73" s="124"/>
       <c r="BV73" s="125"/>
     </row>
-    <row r="74" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:74" ht="26.1" customHeight="1">
       <c r="B74" s="13" t="s">
         <v>0</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:74" ht="26.1" customHeight="1">
       <c r="B75" s="2" t="s">
         <v>0</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:74" ht="26.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="2:74" ht="26.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="411">
     <mergeCell ref="T59:T61"/>
@@ -9546,7 +9546,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV12 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:CV58 P53:BJ53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:CV57 P54:BJ54 S66:BQ66 S68:BQ69 S64:BQ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D22:AI26 A21 D21:AB21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:AA29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BJ55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A18:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV23 AW36 BE46:BH46 BJ46:CV46 A10:T12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:CV20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:CV26 BA24:BJ24 BL24:CV24" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV12 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:BH58 P53:BH53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:BH57 P54:BH54 S66:BQ66 S68:BQ69 S64:BQ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D24:AI26 A21 D21:L21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:J29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BH55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A19:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV23 AW36 BE46:BH46 BJ46:CV46 A10:T12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:CV20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:CV26 BA24:BJ24 BL24:CV24 BJ53 BJ54 BJ55 BJ58:CV58 BJ56:CV57 L29:AA29 A18:M18 O18:AB18 D22:L23 N22:AI23 N21:AB21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/daerung.xlsx
+++ b/daerung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\수정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D293583-7767-4F4D-AAD6-10A8B265543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD023B8D-88C5-4600-9651-B58B3EA6C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="304">
   <si>
     <t/>
   </si>
@@ -123,9 +123,6 @@
     <t>유다빈</t>
   </si>
   <si>
-    <t>김혜선</t>
-  </si>
-  <si>
     <t>김나현A</t>
   </si>
   <si>
@@ -303,9 +300,6 @@
     <t>손광현</t>
   </si>
   <si>
-    <t>손예진</t>
-  </si>
-  <si>
     <t>김다영</t>
   </si>
   <si>
@@ -354,16 +348,10 @@
     <t>김성우</t>
   </si>
   <si>
-    <t>신대환</t>
-  </si>
-  <si>
     <t>장민규</t>
   </si>
   <si>
     <t>이민수</t>
-  </si>
-  <si>
-    <t>김선호</t>
   </si>
   <si>
     <t>김건희</t>
@@ -742,9 +730,6 @@
   </si>
   <si>
     <t>이상호B</t>
-  </si>
-  <si>
-    <t>배유미</t>
   </si>
   <si>
     <t>김보결</t>
@@ -995,6 +980,10 @@
   </si>
   <si>
     <t>이재민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김영삼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2355,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="95" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AD2" s="95"/>
       <c r="AE2" s="95"/>
@@ -2364,7 +2353,7 @@
       <c r="AH2" s="95"/>
       <c r="AI2" s="95"/>
       <c r="AJ2" s="109" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AK2" s="110"/>
       <c r="AL2" s="110"/>
@@ -2454,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E3" s="46"/>
       <c r="F3" s="46"/>
@@ -2509,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="BC3" s="46" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="BD3" s="46"/>
       <c r="BE3" s="46"/>
@@ -2775,10 +2764,10 @@
         <v>7</v>
       </c>
       <c r="W7" s="34" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="X7" s="34" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>0</v>
@@ -2817,7 +2806,7 @@
         <v>9</v>
       </c>
       <c r="BS7" s="78" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="BT7" s="78"/>
       <c r="BU7" s="78"/>
@@ -3077,10 +3066,10 @@
       </c>
       <c r="U10" s="34"/>
       <c r="W10" s="34" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="X10" s="34" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AA10" s="90" t="s">
         <v>24</v>
@@ -3142,11 +3131,9 @@
       <c r="BS10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BT10" s="35" t="s">
+      <c r="BT10" s="35"/>
+      <c r="BU10" s="35" t="s">
         <v>32</v>
-      </c>
-      <c r="BU10" s="35" t="s">
-        <v>33</v>
       </c>
       <c r="BV10" s="20" t="s">
         <v>0</v>
@@ -3251,9 +3238,7 @@
       <c r="BS11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BT11" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="BT11" s="35"/>
       <c r="BU11" s="35" t="s">
         <v>0</v>
       </c>
@@ -3266,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="36" t="s">
         <v>0</v>
@@ -3301,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC12" s="95"/>
       <c r="AD12" s="95"/>
@@ -3357,9 +3342,7 @@
       <c r="BS12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BT12" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="BT12" s="36"/>
       <c r="BU12" s="36" t="s">
         <v>0</v>
       </c>
@@ -3375,37 +3358,37 @@
         <v>0</v>
       </c>
       <c r="F13" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="I13" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="34" t="s">
+      <c r="J13" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="34" t="s">
+      <c r="M13" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="N13" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="34" t="s">
+      <c r="P13" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="P13" s="34" t="s">
+      <c r="Q13" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="Q13" s="34" t="s">
+      <c r="T13" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="T13" s="34" t="s">
-        <v>44</v>
-      </c>
       <c r="U13" s="34" t="s">
         <v>0</v>
       </c>
       <c r="W13" s="34" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="X13" s="34" t="s">
         <v>0</v>
@@ -3441,37 +3424,37 @@
         <v>0</v>
       </c>
       <c r="BB13" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="BC13" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="BC13" s="34" t="s">
+      <c r="BG13" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="BG13" s="34" t="s">
+      <c r="BH13" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="BH13" s="34" t="s">
+      <c r="BJ13" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="BJ13" s="34" t="s">
+      <c r="BK13" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="BK13" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO13" s="34" t="s">
+      <c r="BP13" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="BP13" s="34" t="s">
+      <c r="BS13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="BS13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT13" s="34" t="s">
+      <c r="BU13" s="34" t="s">
         <v>52</v>
-      </c>
-      <c r="BU13" s="34" t="s">
-        <v>53</v>
       </c>
       <c r="BV13" s="20" t="s">
         <v>0</v>
@@ -3592,46 +3575,46 @@
         <v>0</v>
       </c>
       <c r="C15" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="J15" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="M15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="U15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="W15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="X15" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="96" t="s">
         <v>54</v>
-      </c>
-      <c r="F15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="I15" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="J15" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="M15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="P15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="T15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="U15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="W15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="X15" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="96" t="s">
-        <v>55</v>
       </c>
       <c r="AC15" s="95"/>
       <c r="AD15" s="95"/>
@@ -3705,22 +3688,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="47" t="s">
+      <c r="J16" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="M16" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J16" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="M16" s="47" t="s">
+      <c r="N16" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" s="78" t="s">
         <v>58</v>
-      </c>
-      <c r="N16" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="P16" s="78" t="s">
-        <v>59</v>
       </c>
       <c r="Q16" s="78" t="s">
         <v>0</v>
@@ -3731,7 +3714,7 @@
       <c r="T16" s="15"/>
       <c r="U16" s="15"/>
       <c r="W16" s="47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X16" s="47" t="s">
         <v>0</v>
@@ -3767,22 +3750,22 @@
         <v>0</v>
       </c>
       <c r="BB16" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="BC16" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG16" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="BC16" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG16" s="47" t="s">
+      <c r="BJ16" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="BJ16" s="47" t="s">
+      <c r="BK16" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO16" s="47" t="s">
         <v>63</v>
-      </c>
-      <c r="BK16" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO16" s="47" t="s">
-        <v>64</v>
       </c>
       <c r="BP16" s="47" t="s">
         <v>0</v>
@@ -3805,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H17" s="78" t="s">
         <v>0</v>
@@ -3814,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="78" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N17" s="78" t="s">
         <v>0</v>
       </c>
       <c r="T17" s="78" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="U17" s="78" t="s">
         <v>0</v>
@@ -3883,43 +3866,43 @@
       </c>
       <c r="C18" s="15"/>
       <c r="F18" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="I18" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="34" t="s">
+      <c r="J18" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="M18" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="J18" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="M18" s="34" t="s">
+      <c r="N18" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="P18" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="T18" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="N18" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="P18" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="T18" s="34" t="s">
+      <c r="U18" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="U18" s="34" t="s">
+      <c r="W18" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="W18" s="34" t="s">
+      <c r="X18" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="X18" s="34" t="s">
+      <c r="AB18" s="96" t="s">
         <v>73</v>
-      </c>
-      <c r="AB18" s="96" t="s">
-        <v>74</v>
       </c>
       <c r="AC18" s="95"/>
       <c r="AD18" s="95"/>
@@ -3949,37 +3932,37 @@
         <v>0</v>
       </c>
       <c r="BB18" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC18" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="BC18" s="34" t="s">
+      <c r="BG18" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="BG18" s="34" t="s">
+      <c r="BH18" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="BH18" s="34" t="s">
+      <c r="BJ18" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="BJ18" s="34" t="s">
+      <c r="BK18" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="BO18" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP18" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="BK18" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="BO18" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP18" s="34" t="s">
+      <c r="BS18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT18" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="BS18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT18" s="34" t="s">
+      <c r="BU18" s="34" t="s">
         <v>81</v>
-      </c>
-      <c r="BU18" s="34" t="s">
-        <v>82</v>
       </c>
       <c r="BV18" s="20" t="s">
         <v>0</v>
@@ -4208,43 +4191,41 @@
     <row r="21" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="B21" s="19"/>
       <c r="F21" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="I21" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="J21" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="J21" s="34" t="s">
+      <c r="M21" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="N21" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="M21" s="34" t="s">
-        <v>306</v>
-      </c>
-      <c r="N21" s="34" t="s">
+      <c r="P21" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="P21" s="103" t="s">
+      <c r="Q21" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="Q21" s="34" t="s">
+      <c r="T21" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="U21" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="T21" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="U21" s="34" t="s">
+      <c r="W21" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="W21" s="34" t="s">
+      <c r="X21" s="34"/>
+      <c r="AB21" s="96" t="s">
         <v>91</v>
-      </c>
-      <c r="X21" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB21" s="96" t="s">
-        <v>93</v>
       </c>
       <c r="AC21" s="95"/>
       <c r="AD21" s="95"/>
@@ -4274,37 +4255,37 @@
         <v>0</v>
       </c>
       <c r="BB21" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC21" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="BG21" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="BC21" s="34" t="s">
+      <c r="BH21" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="BG21" s="34" t="s">
+      <c r="BJ21" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="BH21" s="34" t="s">
+      <c r="BK21" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="BO21" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP21" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="BJ21" s="34" t="s">
+      <c r="BS21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT21" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="BK21" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="BO21" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP21" s="34" t="s">
+      <c r="BU21" s="34" t="s">
         <v>99</v>
-      </c>
-      <c r="BS21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT21" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="BU21" s="34" t="s">
-        <v>101</v>
       </c>
       <c r="BV21" s="20" t="s">
         <v>0</v>
@@ -4345,14 +4326,12 @@
       <c r="W22" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="X22" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="X22" s="35"/>
       <c r="AB22" s="97" t="s">
         <v>0</v>
       </c>
       <c r="AC22" s="95" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="95" t="s">
         <v>0</v>
@@ -4364,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="AG22" s="95" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AH22" s="95" t="s">
         <v>0</v>
@@ -4464,9 +4443,7 @@
       <c r="W23" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="X23" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="X23" s="36"/>
       <c r="AB23" s="98" t="s">
         <v>0</v>
       </c>
@@ -4554,40 +4531,36 @@
         <v>0</v>
       </c>
       <c r="G24" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="J24" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="34" t="s">
+      <c r="M24" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="N24" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="34" t="s">
+      <c r="P24" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="M24" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="N24" s="34" t="s">
+      <c r="Q24" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="P24" s="34" t="s">
+      <c r="W24" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="Q24" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="T24" s="34" t="s">
+      <c r="X24" s="34"/>
+      <c r="AB24" s="96" t="s">
         <v>109</v>
-      </c>
-      <c r="U24" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="W24" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="X24" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB24" s="96" t="s">
-        <v>113</v>
       </c>
       <c r="AC24" s="95" t="s">
         <v>0</v>
@@ -4634,31 +4607,31 @@
         <v>0</v>
       </c>
       <c r="BC24" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="BG24" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH24" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ24" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK24" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="BO24" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="BG24" s="34" t="s">
+      <c r="BP24" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="BH24" s="34" t="s">
+      <c r="BS24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT24" s="34" t="s">
         <v>116</v>
-      </c>
-      <c r="BJ24" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK24" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="BO24" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP24" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS24" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT24" s="34" t="s">
-        <v>120</v>
       </c>
       <c r="BU24" s="34" t="s">
         <v>0</v>
@@ -4693,18 +4666,14 @@
       <c r="Q25" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="T25" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="T25" s="35"/>
       <c r="U25" s="35" t="s">
         <v>0</v>
       </c>
       <c r="W25" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="X25" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="X25" s="35"/>
       <c r="AB25" s="97" t="s">
         <v>0</v>
       </c>
@@ -4821,18 +4790,14 @@
       <c r="S26" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="T26" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="T26" s="36"/>
       <c r="U26" s="36" t="s">
         <v>0</v>
       </c>
       <c r="W26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="X26" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="X26" s="36"/>
       <c r="Y26" s="3" t="s">
         <v>0</v>
       </c>
@@ -4935,10 +4900,10 @@
       <c r="T27" s="47"/>
       <c r="U27" s="47"/>
       <c r="AB27" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="BA27" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="BV27" s="20" t="s">
         <v>0</v>
@@ -4949,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="78" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N28" s="78" t="s">
         <v>0</v>
@@ -4962,23 +4927,23 @@
     </row>
     <row r="29" spans="2:74" ht="26.1" customHeight="1">
       <c r="B29" s="64" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C29" s="66"/>
       <c r="F29" s="34" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>0</v>
       </c>
       <c r="J29" s="34" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K29" s="34" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AB29" s="53"/>
       <c r="BA29" s="53"/>
@@ -5006,7 +4971,7 @@
       </c>
       <c r="AB30" s="53"/>
       <c r="AC30" s="78" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AD30" s="78" t="s">
         <v>0</v>
@@ -5048,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="79" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="V31" s="79" t="s">
         <v>0</v>
@@ -5060,48 +5025,48 @@
         <v>0</v>
       </c>
       <c r="Y31" s="64" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Z31" s="65"/>
       <c r="AA31" s="65"/>
       <c r="AB31" s="66"/>
       <c r="AC31" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD31" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE31" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF31" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG31" s="79" t="s">
         <v>132</v>
       </c>
-      <c r="AD31" s="79" t="s">
+      <c r="AH31" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="AE31" s="79" t="s">
+      <c r="AI31" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="AF31" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG31" s="79" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH31" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI31" s="79" t="s">
-        <v>138</v>
-      </c>
       <c r="AW31" s="64" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AX31" s="65"/>
       <c r="AY31" s="65"/>
       <c r="AZ31" s="65"/>
       <c r="BA31" s="66"/>
       <c r="BM31" s="64" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="BN31" s="65"/>
       <c r="BO31" s="65"/>
       <c r="BP31" s="65"/>
       <c r="BQ31" s="66"/>
       <c r="BR31" s="64" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="BS31" s="65"/>
       <c r="BT31" s="65"/>
@@ -5112,7 +5077,7 @@
       <c r="B32" s="67"/>
       <c r="C32" s="69"/>
       <c r="F32" s="34" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G32" s="34" t="s">
         <v>0</v>
@@ -5124,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="U32" s="80" t="s">
         <v>0</v>
@@ -5313,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O35" s="53"/>
       <c r="P35" s="53"/>
@@ -5373,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="AR35" s="53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AS35" s="53" t="s">
         <v>0</v>
@@ -5592,7 +5557,7 @@
       <c r="B38" s="57"/>
       <c r="C38" s="58"/>
       <c r="D38" s="40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E38" s="40"/>
       <c r="F38" s="40"/>
@@ -5609,7 +5574,7 @@
       <c r="Q38" s="58"/>
       <c r="R38" s="58"/>
       <c r="S38" s="54" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="T38" s="55"/>
       <c r="U38" s="55"/>
@@ -5621,7 +5586,7 @@
       <c r="AA38" s="122"/>
       <c r="AB38" s="123"/>
       <c r="AC38" s="82" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AD38" s="82"/>
       <c r="AE38" s="82"/>
@@ -5643,7 +5608,7 @@
       <c r="AU38" s="63"/>
       <c r="AV38" s="63"/>
       <c r="AW38" s="139" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AX38" s="140"/>
       <c r="AY38" s="140"/>
@@ -5663,7 +5628,7 @@
       <c r="BM38" s="134"/>
       <c r="BN38" s="135"/>
       <c r="BO38" s="54" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="BP38" s="55"/>
       <c r="BQ38" s="55"/>
@@ -5822,7 +5787,7 @@
     </row>
     <row r="41" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="D41" s="40" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E41" s="40"/>
       <c r="F41" s="40"/>
@@ -5855,7 +5820,7 @@
       <c r="AG41" s="128"/>
       <c r="AH41" s="129"/>
       <c r="AI41" s="82" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AJ41" s="82"/>
       <c r="AK41" s="82"/>
@@ -5871,7 +5836,7 @@
       <c r="AU41" s="63"/>
       <c r="AV41" s="63"/>
       <c r="AW41" s="139" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AX41" s="140"/>
       <c r="AY41" s="140"/>
@@ -5879,7 +5844,7 @@
       <c r="BA41" s="140"/>
       <c r="BB41" s="141"/>
       <c r="BC41" s="54" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="BD41" s="55" t="s">
         <v>0</v>
@@ -6264,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L46" s="53" t="s">
         <v>0</v>
@@ -6283,7 +6248,7 @@
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
       <c r="T46" s="53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="U46" s="53" t="s">
         <v>0</v>
@@ -6298,142 +6263,142 @@
         <v>0</v>
       </c>
       <c r="Y46" s="79" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="79" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="79" t="s">
+        <v>276</v>
+      </c>
+      <c r="AK46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR46" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="79" t="s">
+        <v>270</v>
+      </c>
+      <c r="AX46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="79" t="s">
+        <v>143</v>
+      </c>
+      <c r="BA46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="79" t="s">
+        <v>265</v>
+      </c>
+      <c r="BE46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="79" t="s">
+        <v>265</v>
+      </c>
+      <c r="BJ46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM46" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="Z46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="79" t="s">
+      <c r="BN46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR46" s="79" t="s">
         <v>145</v>
-      </c>
-      <c r="AE46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="AG46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="79" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR46" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="AS46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW46" s="79" t="s">
-        <v>275</v>
-      </c>
-      <c r="AX46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="79" t="s">
-        <v>147</v>
-      </c>
-      <c r="BA46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD46" s="79" t="s">
-        <v>270</v>
-      </c>
-      <c r="BE46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="79" t="s">
-        <v>270</v>
-      </c>
-      <c r="BJ46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM46" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="BN46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR46" s="79" t="s">
-        <v>149</v>
       </c>
       <c r="BS46" s="91" t="s">
         <v>0</v>
@@ -6606,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F48" s="46"/>
       <c r="G48" s="46"/>
@@ -6791,20 +6756,20 @@
         <v>0</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F50" s="48"/>
       <c r="H50" s="48" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I50" s="48"/>
       <c r="K50" s="48" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L50" s="48"/>
       <c r="O50" s="22"/>
       <c r="AH50" s="84" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AI50" s="84"/>
       <c r="AJ50" s="84"/>
@@ -6844,31 +6809,31 @@
         <v>0</v>
       </c>
       <c r="D51" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I51" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="J51" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="K51" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="M51" s="49" t="s">
         <v>156</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J51" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="K51" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="L51" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="M51" s="49" t="s">
-        <v>160</v>
       </c>
       <c r="O51" s="22"/>
       <c r="T51" s="31"/>
@@ -6935,41 +6900,41 @@
         <v>0</v>
       </c>
       <c r="T52" s="77" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="U52" s="77"/>
       <c r="W52" s="77" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="X52" s="77"/>
       <c r="AB52" s="78" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AC52" s="78"/>
       <c r="AD52" s="78"/>
       <c r="AK52" s="94" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AL52" s="94"/>
       <c r="AM52" s="94"/>
       <c r="AR52" s="77" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AS52" s="77"/>
       <c r="AU52" s="77" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AV52" s="77"/>
       <c r="AZ52" s="48" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="BA52" s="48"/>
       <c r="BH52" s="48" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="BI52" s="48"/>
       <c r="BK52" s="48" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="BL52" s="48"/>
       <c r="BR52" s="92" t="s">
@@ -7013,85 +6978,85 @@
         <v>0</v>
       </c>
       <c r="W53" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="X53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR53" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS53" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="X53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="34" t="s">
+      <c r="AU53" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="AC53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM53" s="34" t="s">
+      <c r="AV53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="AN53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR53" s="34" t="s">
+      <c r="BA53" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="AS53" s="34" t="s">
+      <c r="BC53" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="AU53" s="34" t="s">
+      <c r="BD53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH53" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="AV53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AX53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="34" t="s">
+      <c r="BI53" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="BK53" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="BL53" s="34" t="s">
         <v>174</v>
-      </c>
-      <c r="BA53" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="BC53" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="BD53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH53" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="BI53" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="BK53" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="BL53" s="34" t="s">
-        <v>178</v>
       </c>
       <c r="BN53" s="3" t="s">
         <v>0</v>
@@ -7120,19 +7085,19 @@
         <v>0</v>
       </c>
       <c r="E54" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="H54" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="I54" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K54" s="37" t="s">
         <v>163</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="K54" s="37" t="s">
-        <v>167</v>
       </c>
       <c r="L54" s="43" t="s">
         <v>0</v>
@@ -7212,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="BN54" s="34" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="BR54" s="79" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BS54" s="91" t="s">
         <v>0</v>
@@ -7350,74 +7315,74 @@
         <v>0</v>
       </c>
       <c r="T56" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="U56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="W56" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="X56" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="U56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="W56" s="34" t="s">
+      <c r="AM56" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="X56" s="34" t="s">
+      <c r="AN56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR56" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="AB56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="34" t="s">
+      <c r="AS56" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="AE56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="34" t="s">
+      <c r="AU56" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="AM56" s="34" t="s">
+      <c r="AV56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ56" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="AN56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="34" t="s">
+      <c r="BA56" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="AS56" s="34" t="s">
+      <c r="BC56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH56" s="34" t="s">
         <v>192</v>
-      </c>
-      <c r="AU56" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="AV56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ56" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="BA56" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="BC56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH56" s="34" t="s">
-        <v>196</v>
       </c>
       <c r="BI56" s="34"/>
       <c r="BK56" s="34" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="BL56" s="34" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="BN56" s="36" t="s">
         <v>0</v>
@@ -7443,22 +7408,22 @@
         <v>0</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F57" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="L57" s="37" t="s">
         <v>180</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="K57" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="L57" s="37" t="s">
-        <v>184</v>
       </c>
       <c r="O57" s="22"/>
       <c r="R57" s="2" t="s">
@@ -7535,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="BN57" s="34" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="BR57" s="92" t="s">
         <v>0</v>
@@ -7677,82 +7642,82 @@
         <v>0</v>
       </c>
       <c r="T59" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="U59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="W59" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="X59" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="U59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="W59" s="34" t="s">
+      <c r="AM59" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="X59" s="34" t="s">
+      <c r="AN59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="AB59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="34" t="s">
+      <c r="AU59" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="AE59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="34" t="s">
+      <c r="AV59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ59" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="AM59" s="34" t="s">
+      <c r="BA59" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="AN59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="34" t="s">
+      <c r="BC59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH59" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="AU59" s="34" t="s">
+      <c r="BI59" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="AV59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="34" t="s">
+      <c r="BK59" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="BA59" s="34" t="s">
+      <c r="BL59" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="BC59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH59" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="BI59" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="BK59" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="BL59" s="34" t="s">
-        <v>218</v>
-      </c>
       <c r="BN59" s="36" t="s">
         <v>0</v>
       </c>
       <c r="BR59" s="64" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="BS59" s="65"/>
       <c r="BT59" s="65"/>
@@ -7764,21 +7729,23 @@
         <v>0</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F60" s="43" t="s">
         <v>0</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="L60" s="37"/>
+        <v>200</v>
+      </c>
+      <c r="L60" s="37" t="s">
+        <v>303</v>
+      </c>
       <c r="O60" s="22"/>
       <c r="P60" s="10" t="s">
         <v>0</v>
@@ -7862,7 +7829,7 @@
         <v>0</v>
       </c>
       <c r="BN60" s="34" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="BR60" s="67"/>
       <c r="BS60" s="68"/>
@@ -7985,10 +7952,10 @@
         <v>0</v>
       </c>
       <c r="AB62" s="34" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AC62" s="34" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AE62" s="34" t="s">
         <v>0</v>
@@ -7997,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="BL62" s="47" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="BN62" s="36" t="s">
         <v>0</v>
@@ -8015,11 +7982,11 @@
       <c r="E63" s="41"/>
       <c r="F63" s="42"/>
       <c r="H63" s="41" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I63" s="42"/>
       <c r="K63" s="41" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L63" s="42"/>
       <c r="O63" s="22"/>
@@ -8054,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="BN63" s="34" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="BR63" s="67"/>
       <c r="BS63" s="68"/>
@@ -8079,76 +8046,74 @@
       <c r="Q64" s="10"/>
       <c r="R64" s="10"/>
       <c r="T64" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="U64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="W64" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="X64" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="AB64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="AM64" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="U64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="W64" s="34" t="s">
+      <c r="AN64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR64" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="X64" s="34" t="s">
+      <c r="AS64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU64" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="AB64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="34" t="s">
+      <c r="AV64" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="AM64" s="34" t="s">
+      <c r="AZ64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA64" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="AN64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR64" s="34" t="s">
+      <c r="BC64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD64" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="AS64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU64" s="34" t="s">
+      <c r="BH64" s="34" t="s">
         <v>233</v>
       </c>
-      <c r="AV64" s="34" t="s">
+      <c r="BI64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK64" s="34"/>
+      <c r="BL64" s="34" t="s">
         <v>234</v>
-      </c>
-      <c r="AZ64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA64" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="BC64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD64" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="BH64" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="BI64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK64" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="BL64" s="34" t="s">
-        <v>239</v>
       </c>
       <c r="BN64" s="35" t="s">
         <v>0</v>
@@ -8198,10 +8163,10 @@
         <v>0</v>
       </c>
       <c r="AB65" s="34" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AC65" s="34" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AE65" s="34" t="s">
         <v>0</v>
@@ -8251,9 +8216,7 @@
       <c r="BI65" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BK65" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK65" s="35"/>
       <c r="BL65" s="35" t="s">
         <v>0</v>
       </c>
@@ -8268,7 +8231,7 @@
     </row>
     <row r="66" spans="2:74" ht="26.1" customHeight="1">
       <c r="B66" s="79" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C66" s="79"/>
       <c r="D66" s="79"/>
@@ -8277,7 +8240,7 @@
       <c r="G66" s="79"/>
       <c r="H66" s="79"/>
       <c r="I66" s="85" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="J66" s="85"/>
       <c r="K66" s="85"/>
@@ -8354,9 +8317,7 @@
       <c r="BI66" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BK66" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK66" s="36"/>
       <c r="BL66" s="36" t="s">
         <v>0</v>
       </c>
@@ -8385,76 +8346,76 @@
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
       <c r="T67" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="U67" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="W67" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="X67" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM67" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="U67" s="34" t="s">
+      <c r="AN67" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="W67" s="34" t="s">
+      <c r="AR67" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="X67" s="34" t="s">
+      <c r="AS67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="AB67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK67" s="34" t="s">
+      <c r="AV67" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="AM67" s="34" t="s">
+      <c r="AZ67" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="BA67" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="AN67" s="34" t="s">
+      <c r="BC67" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="AR67" s="34" t="s">
+      <c r="BD67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK67" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="AS67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="34" t="s">
+      <c r="BL67" s="34" t="s">
         <v>250</v>
-      </c>
-      <c r="AV67" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="AZ67" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="BA67" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC67" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="BD67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK67" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="BL67" s="34" t="s">
-        <v>255</v>
       </c>
       <c r="BR67" s="67"/>
       <c r="BS67" s="68"/>
@@ -8493,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="88" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AC68" s="89" t="s">
         <v>0</v>
@@ -8673,13 +8634,13 @@
       <c r="Q70" s="10"/>
       <c r="R70" s="10"/>
       <c r="T70" s="41" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="U70" s="50" t="s">
         <v>0</v>
       </c>
       <c r="W70" s="41" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="X70" s="50" t="s">
         <v>0</v>
@@ -8693,13 +8654,13 @@
         <v>0</v>
       </c>
       <c r="AM70" s="41" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AN70" s="50" t="s">
         <v>0</v>
       </c>
       <c r="AU70" s="51" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AV70" s="52" t="s">
         <v>0</v>
@@ -8711,13 +8672,13 @@
         <v>0</v>
       </c>
       <c r="BH70" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BI70" s="42" t="s">
         <v>0</v>
       </c>
       <c r="BK70" s="73" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="BL70" s="74" t="s">
         <v>0</v>
@@ -8750,11 +8711,11 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="47" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BA71" s="47"/>
       <c r="BH71" s="47" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="BI71" s="47"/>
       <c r="BR71" s="67"/>
@@ -9537,7 +9498,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV12 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:BH58 P53:BH53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:BH57 P54:BH54 S66:BQ66 S68:BQ69 S64:BQ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D24:AI26 A21 D21:L21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:J29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BH55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A19:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV23 AW36 BE46:BH46 BJ46:CV46 A10:M12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:CV20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:CV26 BA24:BJ24 BL24:CV24 BJ53 BJ54 BJ55 BJ58:CV58 BJ56:CV57 L29:AA29 A18:M18 O18:AB18 D22:L23 N22:AI23 N21:AB21 O10:T12" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV9 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:BH58 P53:BH53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:BH57 P54:BH54 S66:BJ66 S68:BQ69 S64:BJ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D24:S26 A21 D21:L21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:J29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BH55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A19:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV23 AW36 BE46:BH46 BJ46:CV46 A10:M12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:CV20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:CV26 BA24:BJ24 BL24:CV24 BJ53 BJ54 BJ55 BJ58:CV58 BJ56:CV57 L29:AA29 A18:M18 O18:AB18 D22:L23 N22:W23 N21:W21 O10:T12 BA10:BS12 BU10:CV12 BL66:BQ66 BL64:BQ65 Y22:AI23 Y21:AB21 Y24:AI26 U24:W26" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/daerung.xlsx
+++ b/daerung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\수정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD023B8D-88C5-4600-9651-B58B3EA6C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D606502-7D30-4DEB-9A17-AD3694CE78CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="303">
   <si>
     <t/>
   </si>
@@ -373,9 +373,6 @@
   </si>
   <si>
     <t>김지영D</t>
-  </si>
-  <si>
-    <t>김성준</t>
   </si>
   <si>
     <t>빌링플랫폼개발팀</t>
@@ -2344,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="95" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AD2" s="95"/>
       <c r="AE2" s="95"/>
@@ -2353,7 +2350,7 @@
       <c r="AH2" s="95"/>
       <c r="AI2" s="95"/>
       <c r="AJ2" s="109" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AK2" s="110"/>
       <c r="AL2" s="110"/>
@@ -2443,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E3" s="46"/>
       <c r="F3" s="46"/>
@@ -2498,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="BC3" s="46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BD3" s="46"/>
       <c r="BE3" s="46"/>
@@ -2764,10 +2761,10 @@
         <v>7</v>
       </c>
       <c r="W7" s="34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="X7" s="34" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>0</v>
@@ -2806,7 +2803,7 @@
         <v>9</v>
       </c>
       <c r="BS7" s="78" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BT7" s="78"/>
       <c r="BU7" s="78"/>
@@ -3066,10 +3063,10 @@
       </c>
       <c r="U10" s="34"/>
       <c r="W10" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="X10" s="34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AA10" s="90" t="s">
         <v>24</v>
@@ -3131,7 +3128,9 @@
       <c r="BS10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BT10" s="35"/>
+      <c r="BT10" s="35" t="s">
+        <v>294</v>
+      </c>
       <c r="BU10" s="35" t="s">
         <v>32</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="X13" s="34" t="s">
         <v>0</v>
@@ -3797,13 +3796,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="78" t="s">
+        <v>116</v>
+      </c>
+      <c r="N17" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" s="78" t="s">
         <v>117</v>
-      </c>
-      <c r="N17" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="T17" s="78" t="s">
-        <v>118</v>
       </c>
       <c r="U17" s="78" t="s">
         <v>0</v>
@@ -3881,10 +3880,10 @@
         <v>68</v>
       </c>
       <c r="N18" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P18" s="34" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Q18" s="34" t="s">
         <v>0</v>
@@ -3946,9 +3945,7 @@
       <c r="BJ18" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="BK18" s="34" t="s">
-        <v>295</v>
-      </c>
+      <c r="BK18" s="34"/>
       <c r="BO18" s="34" t="s">
         <v>0</v>
       </c>
@@ -4056,9 +4053,7 @@
       <c r="BJ19" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BK19" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK19" s="35"/>
       <c r="BO19" s="35" t="s">
         <v>0</v>
       </c>
@@ -4166,9 +4161,7 @@
       <c r="BJ20" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="BK20" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK20" s="36"/>
       <c r="BO20" s="36" t="s">
         <v>0</v>
       </c>
@@ -4203,7 +4196,7 @@
         <v>85</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N21" s="34" t="s">
         <v>86</v>
@@ -4269,9 +4262,7 @@
       <c r="BJ21" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="BK21" s="34" t="s">
-        <v>296</v>
-      </c>
+      <c r="BK21" s="34"/>
       <c r="BO21" s="34" t="s">
         <v>0</v>
       </c>
@@ -4386,9 +4377,7 @@
       <c r="BJ22" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BK22" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK22" s="35"/>
       <c r="BO22" s="35" t="s">
         <v>0</v>
       </c>
@@ -4503,9 +4492,7 @@
       <c r="BJ23" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="BK23" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK23" s="36"/>
       <c r="BO23" s="36" t="s">
         <v>0</v>
       </c>
@@ -4536,9 +4523,7 @@
       <c r="I24" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="J24" s="34" t="s">
-        <v>104</v>
-      </c>
+      <c r="J24" s="34"/>
       <c r="M24" s="100" t="s">
         <v>0</v>
       </c>
@@ -4618,9 +4603,7 @@
       <c r="BJ24" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="BK24" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="BK24" s="34"/>
       <c r="BO24" s="34" t="s">
         <v>114</v>
       </c>
@@ -4631,10 +4614,10 @@
         <v>0</v>
       </c>
       <c r="BT24" s="34" t="s">
-        <v>116</v>
+        <v>295</v>
       </c>
       <c r="BU24" s="34" t="s">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="BV24" s="20" t="s">
         <v>0</v>
@@ -4651,9 +4634,7 @@
       <c r="I25" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="J25" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="J25" s="35"/>
       <c r="M25" s="101" t="s">
         <v>0</v>
       </c>
@@ -4733,9 +4714,7 @@
       <c r="BJ25" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="BK25" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK25" s="35"/>
       <c r="BO25" s="35" t="s">
         <v>0</v>
       </c>
@@ -4745,9 +4724,7 @@
       <c r="BS25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BT25" s="35" t="s">
-        <v>0</v>
-      </c>
+      <c r="BT25" s="35"/>
       <c r="BU25" s="35" t="s">
         <v>0</v>
       </c>
@@ -4769,9 +4746,7 @@
       <c r="I26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="J26" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="J26" s="36"/>
       <c r="K26" s="7" t="s">
         <v>0</v>
       </c>
@@ -4863,9 +4838,7 @@
       <c r="BJ26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="BK26" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="BK26" s="36"/>
       <c r="BM26" s="3" t="s">
         <v>0</v>
       </c>
@@ -4881,9 +4854,7 @@
       <c r="BS26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BT26" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="BT26" s="36"/>
       <c r="BU26" s="36" t="s">
         <v>0</v>
       </c>
@@ -4900,10 +4871,10 @@
       <c r="T27" s="47"/>
       <c r="U27" s="47"/>
       <c r="AB27" s="75" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BA27" s="75" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BV27" s="20" t="s">
         <v>0</v>
@@ -4914,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N28" s="78" t="s">
         <v>0</v>
@@ -4927,23 +4898,23 @@
     </row>
     <row r="29" spans="2:74" ht="26.1" customHeight="1">
       <c r="B29" s="64" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C29" s="66"/>
       <c r="F29" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="J29" s="34" t="s">
+      <c r="K29" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="M29" s="34" t="s">
         <v>121</v>
-      </c>
-      <c r="K29" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="M29" s="34" t="s">
-        <v>122</v>
       </c>
       <c r="AB29" s="53"/>
       <c r="BA29" s="53"/>
@@ -4971,7 +4942,7 @@
       </c>
       <c r="AB30" s="53"/>
       <c r="AC30" s="78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AD30" s="78" t="s">
         <v>0</v>
@@ -5013,60 +4984,60 @@
         <v>0</v>
       </c>
       <c r="U31" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="V31" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="W31" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="X31" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="64" t="s">
         <v>123</v>
-      </c>
-      <c r="V31" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="W31" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="X31" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="64" t="s">
-        <v>124</v>
       </c>
       <c r="Z31" s="65"/>
       <c r="AA31" s="65"/>
       <c r="AB31" s="66"/>
       <c r="AC31" s="79" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD31" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="AD31" s="79" t="s">
+      <c r="AE31" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="AE31" s="79" t="s">
+      <c r="AF31" s="79" t="s">
         <v>130</v>
       </c>
-      <c r="AF31" s="79" t="s">
+      <c r="AG31" s="79" t="s">
         <v>131</v>
       </c>
-      <c r="AG31" s="79" t="s">
+      <c r="AH31" s="79" t="s">
         <v>132</v>
       </c>
-      <c r="AH31" s="79" t="s">
+      <c r="AI31" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="AI31" s="79" t="s">
-        <v>134</v>
-      </c>
       <c r="AW31" s="64" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AX31" s="65"/>
       <c r="AY31" s="65"/>
       <c r="AZ31" s="65"/>
       <c r="BA31" s="66"/>
       <c r="BM31" s="64" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BN31" s="65"/>
       <c r="BO31" s="65"/>
       <c r="BP31" s="65"/>
       <c r="BQ31" s="66"/>
       <c r="BR31" s="64" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="BS31" s="65"/>
       <c r="BT31" s="65"/>
@@ -5077,19 +5048,19 @@
       <c r="B32" s="67"/>
       <c r="C32" s="69"/>
       <c r="F32" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34" t="s">
         <v>126</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="J32" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34" t="s">
-        <v>127</v>
       </c>
       <c r="U32" s="80" t="s">
         <v>0</v>
@@ -5278,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O35" s="53"/>
       <c r="P35" s="53"/>
@@ -5338,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="AR35" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AS35" s="53" t="s">
         <v>0</v>
@@ -5557,7 +5528,7 @@
       <c r="B38" s="57"/>
       <c r="C38" s="58"/>
       <c r="D38" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E38" s="40"/>
       <c r="F38" s="40"/>
@@ -5574,7 +5545,7 @@
       <c r="Q38" s="58"/>
       <c r="R38" s="58"/>
       <c r="S38" s="54" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T38" s="55"/>
       <c r="U38" s="55"/>
@@ -5586,7 +5557,7 @@
       <c r="AA38" s="122"/>
       <c r="AB38" s="123"/>
       <c r="AC38" s="82" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AD38" s="82"/>
       <c r="AE38" s="82"/>
@@ -5608,7 +5579,7 @@
       <c r="AU38" s="63"/>
       <c r="AV38" s="63"/>
       <c r="AW38" s="139" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AX38" s="140"/>
       <c r="AY38" s="140"/>
@@ -5628,7 +5599,7 @@
       <c r="BM38" s="134"/>
       <c r="BN38" s="135"/>
       <c r="BO38" s="54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BP38" s="55"/>
       <c r="BQ38" s="55"/>
@@ -5787,7 +5758,7 @@
     </row>
     <row r="41" spans="2:74" ht="26.1" customHeight="1" thickBot="1">
       <c r="D41" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E41" s="40"/>
       <c r="F41" s="40"/>
@@ -5820,7 +5791,7 @@
       <c r="AG41" s="128"/>
       <c r="AH41" s="129"/>
       <c r="AI41" s="82" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ41" s="82"/>
       <c r="AK41" s="82"/>
@@ -5836,7 +5807,7 @@
       <c r="AU41" s="63"/>
       <c r="AV41" s="63"/>
       <c r="AW41" s="139" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AX41" s="140"/>
       <c r="AY41" s="140"/>
@@ -5844,7 +5815,7 @@
       <c r="BA41" s="140"/>
       <c r="BB41" s="141"/>
       <c r="BC41" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BD41" s="55" t="s">
         <v>0</v>
@@ -6229,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L46" s="53" t="s">
         <v>0</v>
@@ -6248,7 +6219,7 @@
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
       <c r="T46" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U46" s="53" t="s">
         <v>0</v>
@@ -6263,142 +6234,142 @@
         <v>0</v>
       </c>
       <c r="Y46" s="79" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="Z46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="79" t="s">
+      <c r="AE46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="AE46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="79" t="s">
+      <c r="AG46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="AK46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR46" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="79" t="s">
+        <v>269</v>
+      </c>
+      <c r="AX46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="AG46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="79" t="s">
-        <v>276</v>
-      </c>
-      <c r="AK46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR46" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="AW46" s="79" t="s">
-        <v>270</v>
-      </c>
-      <c r="AX46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="79" t="s">
+      <c r="BA46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC46" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="79" t="s">
+        <v>264</v>
+      </c>
+      <c r="BE46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="79" t="s">
+        <v>264</v>
+      </c>
+      <c r="BJ46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM46" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="BA46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC46" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD46" s="79" t="s">
-        <v>265</v>
-      </c>
-      <c r="BE46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="79" t="s">
-        <v>265</v>
-      </c>
-      <c r="BJ46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM46" s="79" t="s">
+      <c r="BN46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ46" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR46" s="79" t="s">
         <v>144</v>
-      </c>
-      <c r="BN46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ46" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR46" s="79" t="s">
-        <v>145</v>
       </c>
       <c r="BS46" s="91" t="s">
         <v>0</v>
@@ -6571,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F48" s="46"/>
       <c r="G48" s="46"/>
@@ -6756,20 +6727,20 @@
         <v>0</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F50" s="48"/>
       <c r="H50" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I50" s="48"/>
       <c r="K50" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L50" s="48"/>
       <c r="O50" s="22"/>
       <c r="AH50" s="84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AI50" s="84"/>
       <c r="AJ50" s="84"/>
@@ -6809,31 +6780,31 @@
         <v>0</v>
       </c>
       <c r="D51" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="F51" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="H51" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="I51" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="I51" s="37" t="s">
+      <c r="J51" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="J51" s="38" t="s">
+      <c r="K51" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="K51" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="L51" s="37" t="s">
+      <c r="M51" s="49" t="s">
         <v>155</v>
-      </c>
-      <c r="M51" s="49" t="s">
-        <v>156</v>
       </c>
       <c r="O51" s="22"/>
       <c r="T51" s="31"/>
@@ -6900,41 +6871,41 @@
         <v>0</v>
       </c>
       <c r="T52" s="77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U52" s="77"/>
       <c r="W52" s="77" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X52" s="77"/>
       <c r="AB52" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AC52" s="78"/>
       <c r="AD52" s="78"/>
       <c r="AK52" s="94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AL52" s="94"/>
       <c r="AM52" s="94"/>
       <c r="AR52" s="77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AS52" s="77"/>
       <c r="AU52" s="77" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AV52" s="77"/>
       <c r="AZ52" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BA52" s="48"/>
       <c r="BH52" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BI52" s="48"/>
       <c r="BK52" s="48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BL52" s="48"/>
       <c r="BR52" s="92" t="s">
@@ -6978,85 +6949,85 @@
         <v>0</v>
       </c>
       <c r="W53" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="X53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="X53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="34" t="s">
+      <c r="AC53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="AC53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM53" s="34" t="s">
+      <c r="AN53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR53" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AN53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR53" s="34" t="s">
+      <c r="AS53" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="AS53" s="34" t="s">
+      <c r="AU53" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="AU53" s="34" t="s">
+      <c r="AV53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="AV53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AX53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="34" t="s">
+      <c r="BA53" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="BA53" s="34" t="s">
+      <c r="BC53" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="BC53" s="34" t="s">
+      <c r="BD53" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH53" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="BD53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH53" s="34" t="s">
+      <c r="BI53" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="BK53" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="BL53" s="34" t="s">
         <v>173</v>
-      </c>
-      <c r="BI53" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="BK53" s="34" t="s">
-        <v>282</v>
-      </c>
-      <c r="BL53" s="34" t="s">
-        <v>174</v>
       </c>
       <c r="BN53" s="3" t="s">
         <v>0</v>
@@ -7085,19 +7056,19 @@
         <v>0</v>
       </c>
       <c r="E54" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="F54" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="F54" s="37" t="s">
+      <c r="H54" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="H54" s="37" t="s">
+      <c r="I54" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="I54" s="37" t="s">
+      <c r="K54" s="37" t="s">
         <v>162</v>
-      </c>
-      <c r="K54" s="37" t="s">
-        <v>163</v>
       </c>
       <c r="L54" s="43" t="s">
         <v>0</v>
@@ -7177,10 +7148,10 @@
         <v>0</v>
       </c>
       <c r="BN54" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BR54" s="79" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BS54" s="91" t="s">
         <v>0</v>
@@ -7315,74 +7286,74 @@
         <v>0</v>
       </c>
       <c r="T56" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="U56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="W56" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="U56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="W56" s="34" t="s">
+      <c r="X56" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="X56" s="34" t="s">
+      <c r="AB56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="AB56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="34" t="s">
+      <c r="AE56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="AE56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="34" t="s">
+      <c r="AM56" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="AM56" s="34" t="s">
+      <c r="AN56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR56" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="AN56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="34" t="s">
+      <c r="AS56" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="AS56" s="34" t="s">
+      <c r="AU56" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="AU56" s="34" t="s">
+      <c r="AV56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ56" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="AV56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ56" s="34" t="s">
+      <c r="BA56" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="BA56" s="34" t="s">
+      <c r="BC56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD56" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH56" s="34" t="s">
         <v>191</v>
-      </c>
-      <c r="BC56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD56" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH56" s="34" t="s">
-        <v>192</v>
       </c>
       <c r="BI56" s="34"/>
       <c r="BK56" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="BL56" s="34" t="s">
         <v>194</v>
-      </c>
-      <c r="BL56" s="34" t="s">
-        <v>195</v>
       </c>
       <c r="BN56" s="36" t="s">
         <v>0</v>
@@ -7408,22 +7379,22 @@
         <v>0</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F57" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="H57" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="37" t="s">
+      <c r="I57" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="I57" s="37" t="s">
+      <c r="K57" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="L57" s="37" t="s">
         <v>179</v>
-      </c>
-      <c r="L57" s="37" t="s">
-        <v>180</v>
       </c>
       <c r="O57" s="22"/>
       <c r="R57" s="2" t="s">
@@ -7500,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="BN57" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BR57" s="92" t="s">
         <v>0</v>
@@ -7642,82 +7613,82 @@
         <v>0</v>
       </c>
       <c r="T59" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="U59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="W59" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="U59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="W59" s="34" t="s">
+      <c r="X59" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="X59" s="34" t="s">
+      <c r="AB59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="AB59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="34" t="s">
+      <c r="AE59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="AE59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="34" t="s">
+      <c r="AM59" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="AM59" s="34" t="s">
+      <c r="AN59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="AN59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="34" t="s">
+      <c r="AU59" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="AU59" s="34" t="s">
+      <c r="AV59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ59" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="AV59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="34" t="s">
+      <c r="BA59" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="BA59" s="34" t="s">
+      <c r="BC59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH59" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="BC59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH59" s="34" t="s">
+      <c r="BI59" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="BI59" s="34" t="s">
+      <c r="BK59" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="BK59" s="34" t="s">
+      <c r="BL59" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="BL59" s="34" t="s">
-        <v>214</v>
-      </c>
       <c r="BN59" s="36" t="s">
         <v>0</v>
       </c>
       <c r="BR59" s="64" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BS59" s="65"/>
       <c r="BT59" s="65"/>
@@ -7729,22 +7700,22 @@
         <v>0</v>
       </c>
       <c r="E60" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H60" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="F60" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="H60" s="37" t="s">
+      <c r="I60" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="I60" s="37" t="s">
+      <c r="K60" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="K60" s="37" t="s">
-        <v>200</v>
-      </c>
       <c r="L60" s="37" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O60" s="22"/>
       <c r="P60" s="10" t="s">
@@ -7829,7 +7800,7 @@
         <v>0</v>
       </c>
       <c r="BN60" s="34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BR60" s="67"/>
       <c r="BS60" s="68"/>
@@ -7952,11 +7923,11 @@
         <v>0</v>
       </c>
       <c r="AB62" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="AC62" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="AC62" s="34" t="s">
-        <v>221</v>
-      </c>
       <c r="AE62" s="34" t="s">
         <v>0</v>
       </c>
@@ -7964,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="BL62" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BN62" s="36" t="s">
         <v>0</v>
@@ -7982,11 +7953,11 @@
       <c r="E63" s="41"/>
       <c r="F63" s="42"/>
       <c r="H63" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I63" s="42"/>
       <c r="K63" s="41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L63" s="42"/>
       <c r="O63" s="22"/>
@@ -8021,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="BN63" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BR63" s="67"/>
       <c r="BS63" s="68"/>
@@ -8046,74 +8017,74 @@
       <c r="Q64" s="10"/>
       <c r="R64" s="10"/>
       <c r="T64" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="U64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="W64" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="U64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="W64" s="34" t="s">
+      <c r="X64" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="X64" s="34" t="s">
+      <c r="AB64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="AB64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF64" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="34" t="s">
+      <c r="AM64" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="AM64" s="34" t="s">
+      <c r="AN64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR64" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="AN64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR64" s="34" t="s">
+      <c r="AS64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU64" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="AS64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU64" s="34" t="s">
+      <c r="AV64" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="AV64" s="34" t="s">
+      <c r="AZ64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA64" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="AZ64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA64" s="34" t="s">
+      <c r="BC64" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD64" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="BC64" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD64" s="34" t="s">
+      <c r="BH64" s="34" t="s">
         <v>232</v>
-      </c>
-      <c r="BH64" s="34" t="s">
-        <v>233</v>
       </c>
       <c r="BI64" s="34" t="s">
         <v>0</v>
       </c>
       <c r="BK64" s="34"/>
       <c r="BL64" s="34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BN64" s="35" t="s">
         <v>0</v>
@@ -8163,10 +8134,10 @@
         <v>0</v>
       </c>
       <c r="AB65" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC65" s="34" t="s">
         <v>235</v>
-      </c>
-      <c r="AC65" s="34" t="s">
-        <v>236</v>
       </c>
       <c r="AE65" s="34" t="s">
         <v>0</v>
@@ -8231,7 +8202,7 @@
     </row>
     <row r="66" spans="2:74" ht="26.1" customHeight="1">
       <c r="B66" s="79" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C66" s="79"/>
       <c r="D66" s="79"/>
@@ -8240,7 +8211,7 @@
       <c r="G66" s="79"/>
       <c r="H66" s="79"/>
       <c r="I66" s="85" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J66" s="85"/>
       <c r="K66" s="85"/>
@@ -8346,76 +8317,76 @@
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
       <c r="T67" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="U67" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="U67" s="34" t="s">
+      <c r="W67" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="W67" s="34" t="s">
+      <c r="X67" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="X67" s="34" t="s">
+      <c r="AB67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="AB67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF67" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK67" s="34" t="s">
+      <c r="AM67" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="AM67" s="34" t="s">
+      <c r="AN67" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="AN67" s="34" t="s">
+      <c r="AR67" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="AR67" s="34" t="s">
+      <c r="AS67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="AS67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="34" t="s">
+      <c r="AV67" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="AV67" s="34" t="s">
+      <c r="AZ67" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="BA67" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="AZ67" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="BA67" s="34" t="s">
+      <c r="BC67" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="BC67" s="34" t="s">
+      <c r="BD67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK67" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="BD67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK67" s="34" t="s">
+      <c r="BL67" s="34" t="s">
         <v>249</v>
-      </c>
-      <c r="BL67" s="34" t="s">
-        <v>250</v>
       </c>
       <c r="BR67" s="67"/>
       <c r="BS67" s="68"/>
@@ -8454,7 +8425,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AC68" s="89" t="s">
         <v>0</v>
@@ -8634,13 +8605,13 @@
       <c r="Q70" s="10"/>
       <c r="R70" s="10"/>
       <c r="T70" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="U70" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="W70" s="41" t="s">
         <v>252</v>
-      </c>
-      <c r="U70" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="W70" s="41" t="s">
-        <v>253</v>
       </c>
       <c r="X70" s="50" t="s">
         <v>0</v>
@@ -8654,31 +8625,31 @@
         <v>0</v>
       </c>
       <c r="AM70" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="AN70" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="AN70" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="AU70" s="51" t="s">
+      <c r="AV70" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ70" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA70" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH70" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="AV70" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ70" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA70" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="BH70" s="41" t="s">
+      <c r="BI70" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK70" s="73" t="s">
         <v>257</v>
-      </c>
-      <c r="BI70" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK70" s="73" t="s">
-        <v>258</v>
       </c>
       <c r="BL70" s="74" t="s">
         <v>0</v>
@@ -8711,11 +8682,11 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BA71" s="47"/>
       <c r="BH71" s="47" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BI71" s="47"/>
       <c r="BR71" s="67"/>
@@ -9498,7 +9469,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV9 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:BH58 P53:BH53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:BH57 P54:BH54 S66:BJ66 S68:BQ69 S64:BJ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D24:S26 A21 D21:L21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:J29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BH55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A19:AB20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:CV23 AW36 BE46:BH46 BJ46:CV46 A10:M12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:CV20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:CV26 BA24:BJ24 BL24:CV24 BJ53 BJ54 BJ55 BJ58:CV58 BJ56:CV57 L29:AA29 A18:M18 O18:AB18 D22:L23 N22:W23 N21:W21 O10:T12 BA10:BS12 BU10:CV12 BL66:BQ66 BL64:BQ65 Y22:AI23 Y21:AB21 Y24:AI26 U24:W26" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV1 A6:AB6 A3:C3 X3:AB3 A4:C5 X4:AB4 BU3:CV3 BU5:CV5 A22:A26 A13:V13 BA13:CV13 A14:AB15 BA14:CV15 A52:B53 A50:B50 AW50:CV50 A51:B51 AW51:AY51 A36:A37 A35 S35:X35 A48:B48 A46:J46 P46:AI46 A74:CV76 A66 A67:A73 A65:N65 A59:B59 BW59:CV59 BW66:CV66 BW67:CV73 BW60:CV65 A55:B57 A54:B54 BS54:CV54 A32:A34 BI31:BJ34 BI35:BJ35 X5:AB5 BA5:BB5 A2:AB2 BA2:CV2 BA6:CV6 BA3:BB3 BA4:BB4 A16:AB16 BA16:CV17 BU4:CV4 BA8:CV9 BA7:BR7 BW7:CV7 AX46:BC46 A60:B60 P60:BQ61 P59:BQ59 A58:B58 P58:BH58 P53:BH53 P50:Z50 P51:S51 A49:B49 P49:CV49 P56:BH57 P54:BH54 S66:BJ66 S68:BQ69 S64:BJ65 S62 A63:B63 S73:BQ73 A28:AA28 AC28:AZ29 A31 AJ31:AV31 BB31:BD31 BB35:BD35 BB32:BD34 AJ30:AV30 BB30:BJ30 BW32:CV34 BW35:CV35 BW31:CV31 BW30:CV30 AJ35:AV35 AJ33:AV34 AJ32:AV32 BB28:CV29 A27:L27 AC27:AZ27 BB27:CV27 D24:I26 A21 D21:L21 D35:M35 D32:X34 A30 D30:AA30 D31:Y31 A29 D29:J29 A9:AB9 A7:B7 D7:V7 A8:B8 D8:AB8 A40:C41 A38 A62:B62 A61:B61 N61 N59 N60 N58 N63 N62 A64:D64 M64:N64 AK46:AV46 A39 A42:A45 BW38:CV38 BW36:CV37 BW39:CV39 BW42:CV45 BU40:CV41 P52:S52 V52 V51 Y52:AA52 Y51:AA51 U62:V62 X62:AK62 AD51:AG51 AE52:AJ52 S72:BQ72 S70:AA70 AD70:BQ70 AD50:AG50 AN52:AQ52 S63:AK63 AN63:AQ63 AN62:AQ62 AT52 AW62:BK62 AW52:AY52 AT63 AT62 AW63:BQ63 BJ51 BJ52 BM51:CV51 BM52:CV52 BM62:BQ62 BB52:BG52 BA51:BG51 BL53:CV53 P55:BH55 BL55:CV55 BL54:BQ54 S71:AZ71 BB71:BH71 BJ71:BQ71 A47:B47 M47:CV47 N52:N53 N50 N51 N48:CV48 N55:N57 N54 N49 A19:O20 A17:L17 V17:AB17 V27:AA27 O17:S17 O27:S27 AW44 AO36 BA22:BJ23 AW36 BE46:BH46 BJ46:CV46 A10:M12 V11:AB12 Y7:AB7 V10 Y10:AB10 X13:AB13 S67:AY67 BA67:BQ67 BA19:BJ20 BA18:BJ18 BL18:CV18 BA21:BJ21 BL21:CV21 BA25:BJ26 BA24:BJ24 BL24:BS24 BJ53 BJ54 BJ55 BJ58:CV58 BJ56:CV57 L29:AA29 A18:M18 O18 D22:L23 N22:W23 N21:W21 O10:T12 BA10:BS12 BU10:CV12 BL66:BQ66 BL64:BQ65 Y22:AI23 Y21:AB21 Y24:AI26 U24:W26 BU25:CV26 BV24:CV24 BL22:CV23 BL19:CV20 BL25:BS26 Q19:AB20 Q18:AB18 K24:S26" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>